--- a/BPH_Master.xlsx
+++ b/BPH_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y61"/>
+  <dimension ref="A1:Y64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -671,7 +671,7 @@
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
-          <t>IOCTA-2026; INTRINSEC-PROSPERO; Trustwave SpiderLabs; GreyNoise (Ivanti EPMM, Feb 2026)</t>
+          <t>IOCTA-2026; INTRINSEC-PROSPERO; TRUSTWAVE-PROSPERO; GREYNOISE-PROSPERO</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -737,12 +737,12 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>OFAC July 1 2025; UK NCA July 1 2025; OFAC expanded Nov 19 2025 (Hypercore; Datavice)</t>
+          <t>OFAC July 1 2025 (in coordination with UK NCA); UK designation Sept 19 2025; OFAC expanded Nov 19 2025 (Hypercore; Datavice)</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>CEO Penzev (arrested April 2025); GD Bozoyan; CTO Gast; 33% owner Knyazev</t>
+          <t>CEO + 33% owner Penzev (arrested April 2025); GD + 33% owner Bozoyan; CTO Gast; 33% owner Knyazev</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,7 +836,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>EU May 20 2025 (17th Russia package)</t>
+          <t>EU May 20 2025 (Hybrid Threats Regulation (EU) 2024/2642 - NOT the 17th Russia package; adopted same day but a separate legal basis)</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1038,12 +1038,12 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>OFAC/UK/AU trilateral Nov 19 2025</t>
+          <t>OFAC/UK/AU trilateral Nov 19 2025; EU July 13 2026 (Impl. Reg. (EU) 2026/1714 - Media Land + Volosovik + ML.Cloud); DOJ indictment unsealed July 14 2026 (N.D. Ohio)</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Yalishanda (Alexander Volosovyk)</t>
+          <t>Yalishanda (Alexander Volosovik; also transliterated Volosovyk); Kirill Zatolokin; Yulia Pankova; Kozlov (UK-designated)</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1069,13 +1069,13 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
-          <t>OFAC-MEDIALAND; INTEL471-MEDIALAND; Team Cymru; SPAMHAUS-BPH</t>
+          <t>OFAC-MEDIALAND; INTEL471-MEDIALAND; TEAMCYMRU-VIRTUALINE; SPAMHAUS-BPH; EU-CYBER-2026-1714; DOJ-MEDIALAND-INDICTMENT</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1240,7 +1240,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>OFAC May 2025</t>
+          <t>OFAC May 29 2025</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1277,7 +1277,7 @@
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
-          <t>OFAC-FUNNULL; SILENTPUSH-FUNNULL; FBI IC3</t>
+          <t>OFAC-FUNNULL; SILENTPUSH-FUNNULL; FBI-IC3-FUNNULL</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1366,18 +1366,18 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
-          <t>RF-STARK; GREYNOISE-STARK; CENSYS-BPH; EU-STARK</t>
+          <t>RF-STARK; GREYNOISE-STARK; CENSYS-BPH; EU-STARK; KREBS-FIOD-STARK; DARKREADING-ELLIO-STARK</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Dutch post-sanctions successor to Stark Industries/PQ.Hosting. AS209847 created June 24 2025. GreyNoise confirmed seamless migration from AS44477. Censys confirmed via RDP hostname fingerprint reuse (WIN-J9D866ESIJ2).</t>
+          <t>Dutch post-sanctions successor to Stark Industries/PQ.Hosting. AS209847 created June 24 2025. GreyNoise confirmed seamless migration from AS44477. Censys confirmed via RDP hostname fingerprint reuse (WIN-J9D866ESIJ2). FIOD raided the Dutch nodes May 18 2026 (800+ servers seized; directors Youssef Zinad and Andrey Nesterenko arrested), but ELLIO telemetry showed the reseller-distributed network back at near pre-raid scanning levels within a week - a partial seizure the successor structure was built to survive. Status kept as evading (network operational) rather than seized.</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1438,7 +1438,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>OFAC/UK Nov 19 2025</t>
+          <t>OFAC Nov 19 2025 (E.O. 13694); UK: not separately listed - captured via ownership/control as a Subsidiaries entry on the Aeza Group LLC row of the FCDO UK Sanctions List</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -1653,7 +1653,7 @@
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
-          <t>abuse.ch; HYAS-RISEPRO; QURIUM-DOPPELGANGER; RF-AUROLOGIC</t>
+          <t>ABUSECH-FEEDS; HYAS-RISEPRO; QURIUM-DOPPELGANGER; RF-AUROLOGIC</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -2108,7 +2108,7 @@
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
-          <t>HALCYON-CLOUDZY; Flare/SRA-TIGR (March 2026)</t>
+          <t>HALCYON-CLOUDZY; FLARE-CLOUDZY</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -2191,7 +2191,7 @@
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
-          <t>RF-TAE-2026; RF-AUROLOGIC; Krebs (reader comments, Sep 2025)</t>
+          <t>RF-TAE-2026; RF-AUROLOGIC; KREBS-BPH</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -2278,7 +2278,7 @@
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
-          <t>RF-AUROLOGIC; RIPE registry</t>
+          <t>RF-AUROLOGIC; RIPE-DB</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -2440,7 +2440,7 @@
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
-          <t>LowEndTalk; BreachForums</t>
+          <t>OSINT-FORUMS</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -2581,7 +2581,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>OFAC April 2022; EU 16th package Feb 2026; servers/domains seized March 2025; OFAC re-designation Aug 14 2025 expanded to Grinex Exved InDeFi Bank A7A5</t>
+          <t>OFAC April 5 2022; EU 16th package Feb 24 2025 (first EU crypto-exchange listing; 6 wallet addresses); servers/domains seized March 2025; OFAC re-designation Aug 14 2025 expanded to Grinex Exved InDeFi Bank A7A5</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2697,7 +2697,7 @@
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Scamalytics; SIGIL</t>
+          <t>OSINT-REVIEWS</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -2780,7 +2780,7 @@
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
-          <t>STISC; Moldovan govt reporting</t>
+          <t>STISC-ALEXHOST</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -3025,7 +3025,7 @@
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
-          <t>SPAMHAUS-BPH; WebHostingTalk</t>
+          <t>SPAMHAUS-BPH; OSINT-FORUMS</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -3108,7 +3108,7 @@
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Trustpilot</t>
+          <t>OSINT-REVIEWS</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -3170,7 +3170,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>EU May 20 2025 (via Stark/Neculiti designation)</t>
+          <t>EU May 20 2025 (via Stark/Neculiti designation under Hybrid Threats Regulation (EU) 2024/2642)</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3375,18 +3375,18 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Krebs; RF-INFRA-2025; GREYNOISE-STARK</t>
+          <t>KREBS-BPH; RF-INFRA-2025; GREYNOISE-STARK; KREBS-FIOD-STARK</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Operated by Andrey Nesterenko. Historically hosted StopGeorgia.ru (2008 Russia-Georgia cyberwar). Netherlands infrastructure pillar for Stark Industries and now WorkTitans/THE.Hosting. Youssef Zinad (WorkTitans founder) was part of MIRhosting legal team.</t>
+          <t>Operated by Andrey Nesterenko (arrested in the FIOD raid of May 18 2026). Historically hosted StopGeorgia.ru (2008 Russia-Georgia cyberwar). Netherlands infrastructure pillar for Stark Industries and now WorkTitans/THE.Hosting. Youssef Zinad (WorkTitans founder) was part of MIRhosting legal team. MIRhosting stated it "temporarily paused" services to WorkTitans after the raid.</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
@@ -3609,7 +3609,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>OFAC May 2025 (via FUNNULL designation)</t>
+          <t>OFAC May 29 2025 (via FUNNULL designation)</t>
         </is>
       </c>
       <c r="O35" t="inlineStr"/>
@@ -3832,7 +3832,7 @@
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
-          <t>SOPHOS-VMMANAGER; BleepingComputer; TrollEye Security</t>
+          <t>SOPHOS-VMMANAGER; BLEEPINGCOMPUTER-BPH; TROLLEYE-FIRSTSERVER</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -4367,7 +4367,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>OFAC May 2025 (via FUNNULL lineage)</t>
+          <t>OFAC May 29 2025 (via FUNNULL lineage)</t>
         </is>
       </c>
       <c r="O45" t="inlineStr"/>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Triad Nexus-affiliated per SIGIL labeling. Likely among Silent Push-identified clean CDN front brands feeding traffic into laundered FUNNULL ecosystem.</t>
+          <t>Triad Nexus-affiliated CDN front brand. Likely among Silent Push-identified clean CDN front brands feeding traffic into laundered FUNNULL ecosystem.</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>RF-TAE-2026; SPAMHAUS-BPH; BleepingComputer; Europol (Op Endgame, Nov 2025)</t>
+          <t>RF-TAE-2026; SPAMHAUS-BPH; BLEEPINGCOMPUTER-BPH; EUROPOL-ENDGAME-2025</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
@@ -4829,18 +4829,18 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
         <is>
-          <t>OFAC-GARANTEX; CHAINALYSIS-A7A5; CHAINALYSIS-OFAC; TRM-A7A5-2026</t>
+          <t>OFAC-GARANTEX; CHAINALYSIS-A7A5; CHAINALYSIS-OFAC; TRM-A7A5-2026; ELLIPTIC-GRINEX</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Direct successor / likely rebrand of OFAC-sanctioned Garantex after the March 2025 disruption. Forensically confirmed shared on-chain infrastructure and asset migration (user funds + newly minted A7A5 via Old Vector). Processed &gt;=$4.76B in 2025. OFAC designated Aug 14 2025 as Garantex's 'direct successor.'</t>
+          <t>Direct successor / likely rebrand of OFAC-sanctioned Garantex after the March 2025 disruption. Forensically confirmed shared on-chain infrastructure and asset migration (user funds + newly minted A7A5 via Old Vector). Processed &gt;=$4.76B in 2025. OFAC designated Aug 14 2025 as Garantex's 'direct successor.' Suspended operations April 16 2026 claiming a ~$13.7M cyberattack (Elliptic/Chainalysis skeptical - possible false-flag exit); functionally offline since. Designation stands; status kept sanctioned (no "suspended" state in the model); operationally offline.</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="V51" t="inlineStr"/>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Russian ruble-backed stablecoin facilitating $93.3B in 10 months. No-KYC Instant Swapper converted &gt;$2.2B of sanctioned A7A5 into mainstream USD-pegged stablecoins. EU banned A7A5 transactions in its 19th sanctions package (Oct 2025).</t>
+          <t>Russian ruble-backed stablecoin facilitating $93.3B in 10 months. No-KYC Instant Swapper converted &gt;$2.2B of sanctioned A7A5 into mainstream USD-pegged stablecoins. EU banned A7A5 transactions in its 19th sanctions package (Oct 23 2025). Did not depeg (built without a freeze function) but its economy ran through Grinex, so on-chain volume collapsed ~96% from peak after Grinex suspended April 16 2026.</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>T2-High Risk</t>
+          <t>T2-High Risk (Anonymization/Proxy Enabler)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="V61" t="inlineStr"/>
@@ -5811,6 +5811,287 @@
       <c r="Y61" t="inlineStr">
         <is>
           <t>Malicious residential-proxy / anonymity-infrastructure TAE built on covertly infected devices; LE-disrupted May 2026 (Asocks attribution is press-sourced).</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Datavice MCHJ</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>sanctioned</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>T1-Confirmed BPH</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Uzbekistan</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Uzbekistan (Tashkent)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Datavice MCHJ</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Aeza expansion entity</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Aeza Group LLC (linked to)</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Aeza Group LLC</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>OFAC Nov 19 2025 (E.O. 13694; CAATSA-RUSSIA; CYBER4; Linked To Aeza Group LLC); NOT UK-designated</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Sanctions-evasion vehicle; Corporate shell</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Shell company structure; Sanctioned; Aeza-linked; short corporate history</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>OFAC-MEDIALAND</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Uzbekistan-registered (Tashkent) Aeza expansion entity, established 2025-07-03 (Tax ID 312252645; Business Reg. 2868352). OFAC-designated Nov 19 2025 alongside Hypercore Ltd as part of the Aeza pressure campaign. Verified against the live FCDO UK Sanctions List (2026-07-17): NOT UK-designated, unlike Hypercore - Treasury designated Datavice OFAC-only. No ASN stated in the OFAC/Federal Register entry.</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>OFAC-sanctioned Aeza expansion/front entity registered in Uzbekistan; designated alongside Hypercore in the Nov 2025 Aeza action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>First VPN Service (1VPNS)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>sanctioned</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>T1-Confirmed BPH (Anonymization/Proxy Enabler)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Russia/Ukraine nexus (operator identity obscured)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>1VPNS; First VPN Service</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>OFAC July 13 2026 (E.O. 13694 as amended, in furtherance of E.O. 14390; coordinated with UK FCDO)</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Dmytro Rashevskyi (admin; aliases Maksim Sorin, Roman Chabanenko)</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Ransomware operators (unnamed in designation)</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Criminal VPN / anonymization enabler; No-log policy; Forum-advertised since 2014; Refuses LE cooperation</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>No KYC; Underground forum presence; Non-cooperative with LE; Sanctioned</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>OFAC-1VPNS</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>OFAC-designated July 13 2026 under E.O. 13694 (in furtherance of E.O. 14390), coordinated with UK FCDO, for enabling ransomware attacks on US targets. No-log criminal VPN advertised on cybercrime forums since 2014. Admin Dmytro Rashevskyi used false identities (Maksim Sorin, Roman Chabanenko) to procure infrastructure. Belarusian cryptor-seller Yegeniy Vladimirovich Silayev co-designated in the same action. European LE took down 1VPNS infrastructure ~May 2026 (referenced by FBI FLASH-20260521-001).</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>OFAC-sanctioned criminal no-log VPN / anonymization enabler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>NetNut (Alarum Technologies)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>seized</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>T2-High Risk (Anonymization/Proxy Enabler)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Israel (parent); global residential-proxy exit nodes</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Alarum Technologies Ltd (NASDAQ: ALAR)</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>NetNut; Popa botnet (exit-node source)</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Alarum Technologies Ltd</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>316 distinct threat-actor clusters (Google GTIG, June 2026)</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Popa (proxy botnet)</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Commercial residential-proxy platform with botnet-sourced exit nodes; Traffic obfuscation; Covert device enrollment via SDKs</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Residential-proxy exit nodes; Botnet-sourced infrastructure; LE-seized</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>GTIG-NETNUT; KREBS-NETNUT</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>FBI (with Google, Lumen, Shadowserver, IRS-CI) seized hundreds of NetNut domains July 2 2026 and disrupted the associated Popa botnet (2M+ hijacked devices - smart TVs, streaming boxes, Android). NetNut is operated by NASDAQ-listed Alarum Technologies (ALAR). Google GTIG observed 316 distinct threat-actor clusters using suspected NetNut exit nodes in a single week in June 2026; Google set Play Protect to disable apps carrying NetNut SDKs. Alarum stock fell ~67% within a week. Builds on Google's Jan 2026 IPIDEA disruption. Not sanctioned - a commercial proxy provider whose exit-node supply was botnet-sourced.</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>LE-seized commercial residential-proxy platform (Alarum/NASDAQ: ALAR) with botnet-sourced exit nodes.</t>
         </is>
       </c>
     </row>

--- a/BPH_Master.xlsx
+++ b/BPH_Master.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BPH_Master" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="BPH_Master" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y64"/>
+  <dimension ref="A1:Y65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -633,15 +633,11 @@
           <t>BEARHOST; SecureHost; Underground; Chang Way Technologies</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>St. Petersburg IXP</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>GootLoader; SocGholish; FIN7</t>
@@ -662,13 +658,11 @@
           <t>No KYC; Underground forum presence; Bulletproof self-identification; High malicious traffic ratio</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>IOCTA-2026; INTRINSEC-PROSPERO; TRUSTWAVE-PROSPERO; GREYNOISE-PROSPERO</t>
@@ -679,7 +673,6 @@
           <t>Coupled Russian AS pair assessed by Intrinsec + Trustwave SpiderLabs as single operator marketing on Russian-language forums as BEARHOST/SecureHost/UNDERGROUND. Feb 2026 GreyNoise: AS200593 dominant source of Ivanti EPMM mass exploitation (83% from one IP). Likely rebrand arm: Chang Way Technologies (HK). Block at CIDR level.</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -707,7 +700,6 @@
           <t>AS216246</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Russia</t>
@@ -728,13 +720,11 @@
           <t>Aeza Group LLC; Aeza Logistic LLC; Cloud Solutions LLC; Datavice</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>aurologic GmbH (AS30823)</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>OFAC July 1 2025 (in coordination with UK NCA); UK designation Sept 19 2025; OFAC expanded Nov 19 2025 (Hypercore; Datavice)</t>
@@ -765,13 +755,11 @@
           <t>High malicious traffic ratio; Sanctioned personnel; No KYC</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>IOCTA-2026; RF-TAE-2026; OFAC-AEZA; CHAINALYSIS-OFAC</t>
@@ -782,7 +770,6 @@
           <t>OFAC-designated July 1 2025 (coordinated with UK NCA). Hosts Meduza Lumma RedLine infopanels BianLian ransomware BlackSprut darknet drug marketplace RomCom RAT. TRON wallet TU4tDFRvcKhAZ1jdihojmBWZqvJhQCnJ4F designated. Nov 19 2025 OFAC expanded to Hypercore Ltd and Datavice. Upstream transit still flows through aurologic AS30823. AS211522 is registered to the Aeza front Hypercore Ltd (RIPE as-name HYPERCORELTD, created 2025-07-10), not to Aeza International directly.</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -805,8 +792,6 @@
           <t>AS44477 (transferred)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>United Kingdom (dissolved)</t>
@@ -832,8 +817,6 @@
           <t>WorkTitans B.V. / THE.Hosting (successor)</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>EU May 20 2025 (Hybrid Threats Regulation (EU) 2024/2642 - NOT the 17th Russia package; adopted same day but a separate legal basis)</t>
@@ -874,7 +857,6 @@
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>IOCTA-2026; RF-TAE-2026; RF-STARK; GREYNOISE-STARK; CENSYS-BPH; EU-STARK</t>
@@ -885,7 +867,6 @@
           <t>EU-sanctioned May 20 2025. UK-incorporated Feb 10 2022 — two weeks before Russia invaded Ukraine. White-label front for Moldova PQ Hosting and Netherlands MIRhosting. Preempted sanctions by transferring AS44477 to PQ Hosting Plus S.R.L. ~12 days ahead. Now formally dissolved.</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -913,7 +894,6 @@
           <t>AS213194; AS61336; AS213010</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Russia</t>
@@ -934,9 +914,6 @@
           <t>XHost; XHOST Internet Solutions LP</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>US/UK/AU trilateral Feb 11 2025</t>
@@ -967,13 +944,11 @@
           <t>Sanctioned personnel; High malicious traffic ratio; Underground forum presence</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>OFAC-ZSERVERS; CHAINALYSIS-BPH</t>
@@ -984,7 +959,6 @@
           <t>First Russia-based BPH sanctioned in 2025 wave. Chainalysis tied payments to LockBit BianLian Hunters International Mallox Dharma Phobos Globeimposter Cryptolocker REvil. Linked to 2022 Medibank breach. Post-sanction prefix-hopping to AS213194 AS61336 AS213010.</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1012,7 +986,6 @@
           <t>AS48721; AS211409; AS215311</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Russia</t>
@@ -1033,9 +1006,6 @@
           <t>Yalishanda; Alexander Volosovyk; ML.Cloud; Media Land Technology</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>OFAC/UK/AU trilateral Nov 19 2025; EU July 13 2026 (Impl. Reg. (EU) 2026/1714 - Media Land + Volosovik + ML.Cloud); DOJ indictment unsealed July 14 2026 (N.D. Ohio)</t>
@@ -1066,13 +1036,11 @@
           <t>High malicious traffic ratio; No KYC; Underground forum presence</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>OFAC-MEDIALAND; INTEL471-MEDIALAND; TEAMCYMRU-VIRTUALINE; SPAMHAUS-BPH; EU-CYBER-2026-1714; DOJ-MEDIALAND-INDICTMENT</t>
@@ -1083,7 +1051,6 @@
           <t>OFAC/UK/AU trilateral sanctions Nov 19 2025 (FBI-coordinated). Operated by Yalishanda — veteran Russian BPH operator. Three leaders + three sister companies sanctioned. Long-documented by Intel 471 Team Cymru Spamhaus.</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1136,15 +1103,11 @@
           <t>ELITETEAM-PEERING-AZ1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>Crex Fex Pex; AS Infolika; OOO RAIT TELECOM; DDoS-Guard; Filanco/Datahouse.ru</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Turla (Secret Blizzard)</t>
@@ -1175,7 +1138,6 @@
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>TRENDMICRO-INTERPOL</t>
@@ -1186,7 +1148,6 @@
           <t>Russia-operated BPH registered in Seychelles at Panama Papers-linked address. VirusTotal flags 100% of 185.215.113.0/24 as malicious. Block at perimeter.</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1204,13 +1165,11 @@
           <t>T1-Confirmed BPH</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>routes through AS152194 (CTG Server Limited)</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Philippines</t>
@@ -1236,8 +1195,6 @@
           <t>CTG Server Limited (backbone)</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>OFAC May 29 2025</t>
@@ -1268,13 +1225,11 @@
           <t>High malicious traffic ratio; Infrastructure laundering; Sanctioned personnel</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>OFAC-FUNNULL; SILENTPUSH-FUNNULL; FBI-IC3-FUNNULL</t>
@@ -1285,7 +1240,6 @@
           <t>OFAC-sanctioned May 2025 for $200M+ pig-butchering fraud and 200000+ unique hostnames. Post-sanction pivot to infrastructure laundering via compromised AWS/Cloudflare/Google/Microsoft accounts. Triad Nexus reportedly rebuilding into 2026 as Bole CDN / CDN1.ai.</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1308,8 +1262,6 @@
           <t>AS209847</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Netherlands</t>
@@ -1335,8 +1287,6 @@
           <t>Stark Industries Solutions (predecessor)</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Not directly designated; successor to EU-sanctioned Stark Industries/Neculiti (AS209847 created June 24 2025, after the May 20 2025 designation)</t>
@@ -1347,8 +1297,6 @@
           <t>Youssef Zinad (MIRhosting legal-team associate)</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>Sanctions-evasion vehicle; Rapid rebranding</t>
@@ -1369,7 +1317,6 @@
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>RF-STARK; GREYNOISE-STARK; CENSYS-BPH; EU-STARK; KREBS-FIOD-STARK; DARKREADING-ELLIO-STARK</t>
@@ -1380,7 +1327,6 @@
           <t>Dutch post-sanctions successor to Stark Industries/PQ.Hosting. AS209847 created June 24 2025. GreyNoise confirmed seamless migration from AS44477. Censys confirmed via RDP hostname fingerprint reuse (WIN-J9D866ESIJ2). FIOD raided the Dutch nodes May 18 2026 (800+ servers seized; directors Youssef Zinad and Andrey Nesterenko arrested), but ELLIO telemetry showed the reseller-distributed network back at near pre-raid scanning levels within a week - a partial seizure the successor structure was built to survive. Status kept as evading (network operational) rather than seized.</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1408,7 +1354,6 @@
           <t>AS211522</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -1434,16 +1379,11 @@
           <t>Aeza Group LLC (parent)</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>OFAC Nov 19 2025 (E.O. 13694); UK: not separately listed - captured via ownership/control as a Subsidiaries entry on the Aeza Group LLC row of the FCDO UK Sanctions List</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>Sanctions-evasion vehicle; Corporate shell</t>
@@ -1454,13 +1394,11 @@
           <t>Shell company structure; Sanctioned personnel (via Aeza)</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>OFAC-AEZA; OFAC-MEDIALAND</t>
@@ -1471,7 +1409,6 @@
           <t>UK-registered Aeza Group front. Second iteration of Aeza UK-shell playbook. Any transactions trigger OFAC secondary-sanctions exposure. AS211522 created 2025-07-10 (RIPE HYPERCORELTD); Companies House No. 16558658, incorporated 2025-07-03, 120 Fleet Street, London EC4A 2BE. Migrated 2,100+ IPs from Aeza AS210644 to AS211522 starting 2025-07-20. OFAC/OFSI designated Hypercore Nov 19 2025 as an Aeza front.</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1494,8 +1431,6 @@
           <t>AS214351</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>United Kingdom (shell)</t>
@@ -1516,7 +1451,6 @@
           <t>Defhost; defhost.co; FEMOIT</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>aurologic GmbH (AS30823)</t>
@@ -1527,13 +1461,11 @@
           <t>aurologic GmbH</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>Artur Mikhailovich Vovk (DOB 1988-09-12 Rohatyn UA)</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
           <t>SVCStealer; CoinMiner; DonutLoader; Rhadamanthys; Stealc; RemcosRAT; QuasarRAT; RedLine; Lumma; OrcusRAT; PrivateLoader; SmokeLoader; Amadey; CastleLoader; Evilginx/EvilGoPhish; DanaBot; Meduza Stealer</t>
@@ -1559,7 +1491,6 @@
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>RF-TAE-2026; RF-AUROLOGIC</t>
@@ -1570,7 +1501,6 @@
           <t>UK shell running defhost.co BPH brand. 2 /24 prefixes via aurologic GmbH AS30823. Shodan: 1142 servers in Germany. Hosts C2/loader infrastructure for 15+ malware families. Payment via Heleket.com; clustered with qckl.net/qckl.host.</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1593,8 +1523,6 @@
           <t>AS216309</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Germany</t>
@@ -1615,7 +1543,6 @@
           <t>EVILEMPIRE</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>aurologic GmbH (AS30823)</t>
@@ -1626,14 +1553,11 @@
           <t>aurologic GmbH</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Doppelganger disinformation</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>abuse.ch ASN-DROP listed; Doppelganger infrastructure</t>
@@ -1644,13 +1568,11 @@
           <t>ASN-DROP inclusion; High malicious traffic ratio; Conflicting geolocation</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>ABUSECH-FEEDS; HYAS-RISEPRO; QURIUM-DOPPELGANGER; RF-AUROLOGIC</t>
@@ -1661,7 +1583,6 @@
           <t>abuse.ch ASN-DROP list flags 'do not route or peer — under cybercriminal control.' HYAS April 2024 flagged for unusually high malware activity. Qurium tied to Doppelganger disinformation. AS-level block recommended.</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1684,8 +1605,6 @@
           <t>AS214943</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Russia</t>
@@ -1706,7 +1625,6 @@
           <t>Virtualine Technologies; RAILNET</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>aurologic GmbH (AS30823)</t>
@@ -1717,8 +1635,6 @@
           <t>aurologic GmbH</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>UAC-0050; UAC-0006</t>
@@ -1739,7 +1655,6 @@
           <t>Underground forum presence; High malicious traffic ratio; No route diversification</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
           <t>2026-06-29</t>
@@ -1760,7 +1675,6 @@
           <t>Operated by Virtualine Technologies. Advertised on Russian-language underground forums for phishing/spam enablement. GBHackers tied to UAC-0050 and UAC-0006 infrastructure shifts against Ukrainian banking and energy. RF Threat Density chart shows Virtualine as #1 highest risk TAE in 2025. | Merged record (was a duplicate AS214943 row): Virtualine Technologies is the operator behind Railnet LLC; per RF TAE case study it shifted IPv4 resources to metaspinner net GmbH in April 2025 and became a primary distribution hub for Latrodectus and AsyncRAT.</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1783,7 +1697,6 @@
           <t>AS213702</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>141.98.6.0/24</t>
@@ -1804,17 +1717,11 @@
           <t>QWINS LTD</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
           <t>Kristina Konstantinova (nominee director Nov 2024-April 2025)</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
         <is>
           <t>Makoob; Guloader; AgentTesla; Lumma; Amadey; RedLine</t>
@@ -1840,7 +1747,6 @@
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>INTEL-INSIGHTS-QWINS</t>
@@ -1851,7 +1757,6 @@
           <t>Incorporated Nov 11 2024 UK. Cheap VPS via Telegram bot (~$2/mo). Nominee director pattern (6-month tenure). Vasilis Orlof tied AS213702 to multiple malware families via 141.98.6.0/24.</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1874,14 +1779,11 @@
           <t>AS215540</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>United Kingdom (LLP shell)</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Global Connectivity Solutions LLP</t>
@@ -1892,17 +1794,11 @@
           <t>GCSAS</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Black Basta; Cactus ransomware</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>UK LLP shell; Routing conduit for Stark Industries</t>
@@ -1913,13 +1809,11 @@
           <t>Shell company structure; No route diversification; Ransomware C2</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>GBHACKERS-BPH</t>
@@ -1930,7 +1824,6 @@
           <t>UK LLP (OC450701 ~2024) operating AS215540. ~176 prefixes / ~41K IPs. Routing conduit for Black Basta and Cactus ransomware C2 via Stark Industries AS44477. Fits Russia-linked UK-LLP BPH pattern.</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1953,7 +1846,6 @@
           <t>AS215789</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>147.45.44.0/24 (CH); 82.115.223.0/24 (NL)</t>
@@ -1969,13 +1861,11 @@
           <t>Netherlands; Switzerland</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>KARINAR; ORG-KR98-RIPE</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>aurologic GmbH (AS30823)</t>
@@ -1986,9 +1876,6 @@
           <t>aurologic GmbH</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
           <t>RisePro stealer</t>
@@ -2014,7 +1901,6 @@
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>HYAS-RISEPRO; RF-AUROLOGIC</t>
@@ -2025,7 +1911,6 @@
           <t>RIPE-registered Jan 3 2024 to individual at Vysoke 53200 Dnipropetrovska UA. Upstream: aurologic AS30823. HYAS flagged for RisePro stealer C2. 2223 domains across 72 IPs. Classic aurologic-downstream single-maintainer shell.</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2048,8 +1933,6 @@
           <t>AS14956</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>United States (Wyoming shell)</t>
@@ -2070,10 +1953,6 @@
           <t>abrNOC</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>Hannan Nozari</t>
@@ -2099,13 +1978,11 @@
           <t>No KYC; Anonymous crypto RDP VPS; Shell company structure; High malicious traffic ratio (40-60%)</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>HALCYON-CLOUDZY; FLARE-CLOUDZY</t>
@@ -2116,7 +1993,6 @@
           <t>Wyoming-incorporated C2P exposed by Halcyon Aug 2023 as operational front for Iranian firm abrNOC (Tehran). 40-60% of infrastructure supports malicious activity. Used by multiple nation-state APTs.</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2139,8 +2015,6 @@
           <t>AS209800</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>Germany</t>
@@ -2156,8 +2030,6 @@
           <t>metaspinner net GmbH</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>aurologic GmbH (AS30823)</t>
@@ -2168,10 +2040,6 @@
           <t>aurologic GmbH</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
           <t>Prefix migration recipient from Virtualine</t>
@@ -2182,13 +2050,11 @@
           <t>No route diversification; Malicious traffic migration indicator</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>RF-TAE-2026; RF-AUROLOGIC; KREBS-BPH</t>
@@ -2199,7 +2065,6 @@
           <t>Insikt-named aurologic downstream. Co-resident on AS30823 transit cluster. Krebs comments noted malicious traffic migration from Virtualine AS214943 to AS209800.</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2222,14 +2087,11 @@
           <t>AS214940</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>United States (Kentucky shell)</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>KPROHOST LLC</t>
@@ -2240,7 +2102,6 @@
           <t>KPRONET</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>aurologic GmbH (AS30823)</t>
@@ -2251,10 +2112,6 @@
           <t>aurologic GmbH</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>Shell company; Gmail abuse contact; aurologic downstream</t>
@@ -2275,7 +2132,6 @@
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
           <t>RF-AUROLOGIC; RIPE-DB</t>
@@ -2286,7 +2142,6 @@
           <t>RIPE-registered 2024-05-10 by KPROHOST LLC (Frankfort KY). 2 /24 IPv4 + 1 /48 IPv6. Abuse contact kprohost.abuse@gmail.com. Upstream relationship with aurologic cluster.</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2304,9 +2159,6 @@
           <t>T3-Suspected</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>Russia</t>
@@ -2317,9 +2169,6 @@
           <t>Europe shell</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>aurologic GmbH (AS30823)</t>
@@ -2330,7 +2179,6 @@
           <t>aurologic GmbH</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
           <t>Daniil Yevchenko</t>
@@ -2341,7 +2189,6 @@
           <t>Doppelganger disinformation</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>aurologic downstream; Russia-linked</t>
@@ -2352,13 +2199,11 @@
           <t>No route diversification; Russia-linked</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>QURIUM-DOPPELGANGER; RF-AUROLOGIC</t>
@@ -2369,7 +2214,6 @@
           <t>Named by Qurium + Insikt as aurologic-downstream Russia-linked infrastructure enabler tied to Doppelganger disinformation network.</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2392,8 +2236,6 @@
           <t>AS208046</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>Netherlands</t>
@@ -2404,23 +2246,16 @@
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>hostslick.com</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>ColocationX (upstream)</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
           <t>Forum advertising on underground platforms; Tiered abuse tolerance</t>
@@ -2431,13 +2266,11 @@
           <t>Underground forum presence; DMCA-ignored marketing</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>OSINT-FORUMS</t>
@@ -2448,7 +2281,6 @@
           <t>Netherlands offshore host advertising on LowEndTalk cracked.io BlackHatWorld BreachForums. Self-advertises DMCA Ignored. Operator transparent that abuse tolerance tracks pricing tier.</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2471,8 +2303,6 @@
           <t>AS30823</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>Germany</t>
@@ -2493,17 +2323,11 @@
           <t>combahton GmbH (predecessor); fastpipe.io</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>CEO Hofmann</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>Central upstream hub; LIR manipulation</t>
@@ -2524,7 +2348,6 @@
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
           <t>RF-AUROLOGIC; RF-TAE-2026</t>
@@ -2535,7 +2358,6 @@
           <t>Central upstream hub for Europe's high-risk hosting ecosystem. Formed Oct 2023 from combahton GmbH's fastpipe.io. 1-5 Tbps at Tornado Datacenter GmbH Langen. Remains primary upstream for Aeza despite sanctions. Downstream cluster: Femo IT Railnet/Virtualine SWISSNETWORK02 metaspinner Tnsecurity WAIcore Altawk Karina Rashkovska KPROHOST. Top-10 globally by malicious activity concentration.</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2553,9 +2375,6 @@
           <t>T1-Confirmed BPH (Financial Enabler)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>Russia</t>
@@ -2576,9 +2395,6 @@
           <t>Grinex; Exved; InDeFi Bank; A7A5; MKAN Coin</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>OFAC April 5 2022; EU 16th package Feb 24 2025 (first EU crypto-exchange listing; 6 wallet addresses); servers/domains seized March 2025; OFAC re-designation Aug 14 2025 expanded to Grinex Exved InDeFi Bank A7A5</t>
@@ -2589,8 +2405,6 @@
           <t>Mira Serda ($5M State Dept reward)</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
           <t>Sanctions evasion; Successor spawning</t>
@@ -2611,7 +2425,6 @@
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>OFAC-GARANTEX; CHAINALYSIS-OFAC; CHAINALYSIS-BPH</t>
@@ -2622,7 +2435,6 @@
           <t>Foundational payment rail for BPH ecosystem. Zservers Aeza Media Land received proceeds via Garantex wallets. Post-takedown successors: ABCeX Rapira Exmo Aifory Pro Bitpapa MKAN Coin.</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2645,8 +2457,6 @@
           <t>AS53667</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>Canada</t>
@@ -2662,18 +2472,11 @@
           <t>Frantech Solutions</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>Francisco Dias</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
           <t>Permissive hosting; Tor-friendly</t>
@@ -2694,7 +2497,6 @@
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
           <t>OSINT-REVIEWS</t>
@@ -2705,7 +2507,6 @@
           <t>Canadian low-cost VPS provider. Operates data centers in Las Vegas and Luxembourg. Permits Tor exit relays. AUP formally prohibits malicious content but abuse response is slow. Scamalytics 40/100 fraud score.</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2728,7 +2529,6 @@
           <t>AS200019</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>176.123.0.0/16; 37.221.64.0/19</t>
@@ -2749,18 +2549,11 @@
           <t>S.R.L. AlexHost</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>Voxility (DDoS mitigation)</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
           <t>DMCA-ignored marketing; Offshore jurisdiction; Crypto payment</t>
@@ -2771,13 +2564,11 @@
           <t>No KYC optional; DMCA-ignored; Crypto payment; Slow abuse response</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
           <t>STISC-ALEXHOST</t>
@@ -2788,7 +2579,6 @@
           <t>Moldovan offshore hoster in former Soviet bomb shelter. Markets DMCA-ignored hosting. Named in STISC reporting after 1330-email phishing wave spoofing Moldovan government. Expanded footprint to NL SE BG CH DE FR UK RO.</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2811,8 +2601,6 @@
           <t>AS51852</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>Switzerland</t>
@@ -2833,13 +2621,6 @@
           <t>Private Layer; privatealps.net</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
           <t>DMCA-ignored; Monero-friendly; Tor-permissive; Swiss jurisdiction</t>
@@ -2860,7 +2641,6 @@
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>RF-TAE-2026</t>
@@ -2871,7 +2651,6 @@
           <t>Swiss-jurisdiction offshore brand with ties to Private Layer AG. Markets fully DMCA ignored no-logs anonymous registration Monero-friendly. Swiss non-EU jurisdiction provides compliance cushion.</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2894,8 +2673,6 @@
           <t>AS200651</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>Seychelles</t>
@@ -2911,14 +2688,6 @@
           <t>Floki Network Services Ltd</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
           <t>Free-speech BPH; Multi-jurisdiction</t>
@@ -2929,13 +2698,11 @@
           <t>Messaging-only possible; DMCA-ignored; Offshore registration</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
           <t>TRENDMICRO-INTERPOL</t>
@@ -2946,7 +2713,6 @@
           <t>Commercialized free-speech BPH brand with multi-jurisdiction presence. Trend Micro/Interpol 2023-named (13% of Africa offshore BPH sourcing). Explicit uncensored hosting marketing.</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2974,7 +2740,6 @@
           <t>multiple regional ASNs</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>Malaysia</t>
@@ -2995,13 +2760,6 @@
           <t>Shinjiru Technology</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>DMCA-ignored; Multi-jurisdiction; Crypto payment; Advises Cloudflare fronting</t>
@@ -3022,7 +2780,6 @@
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>SPAMHAUS-BPH; OSINT-FORUMS</t>
@@ -3033,7 +2790,6 @@
           <t>20+ year veteran Malaysian offshore host. 8 jurisdictions. Markets DMCA-ignored hosting. Spamhaus flagged unnamed Malaysia-based ISP matching Shinjiru profile. Non-response to phishing/malware abuse complaints.</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3056,8 +2812,6 @@
           <t>AS49042</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>Netherlands</t>
@@ -3078,17 +2832,11 @@
           <t>Phanes Cloud; Flaunt7 (predecessor); SpectraIP</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
           <t>Sijmen Klaas Bakker</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
           <t>Rebranded from Flaunt7</t>
@@ -3099,13 +2847,11 @@
           <t>Slow abuse response; Rebranded from flagged entity</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>OSINT-REVIEWS</t>
@@ -3116,7 +2862,6 @@
           <t>Dutch hoster at Keteldiep 15 Urk. Rebranded from Flaunt7. Trustpilot reviews document unresponsive abuse handling for phishing complaints.</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3139,8 +2884,6 @@
           <t>AS44477 (post-transfer)</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>Moldova</t>
@@ -3166,8 +2909,6 @@
           <t>Stark Industries Solutions (predecessor)</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>EU May 20 2025 (via Stark/Neculiti designation under Hybrid Threats Regulation (EU) 2024/2642)</t>
@@ -3178,8 +2919,6 @@
           <t>Ivan Neculiti; Iurie Neculiti</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
           <t>Sanctions-evasion vehicle</t>
@@ -3190,13 +2929,11 @@
           <t>Sanctioned personnel; Rapid rebranding</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
           <t>RF-TAE-2026; EU-STARK</t>
@@ -3207,7 +2944,6 @@
           <t>Moldova-registered Stark Industries successor entity. Holds AS44477 after pre-sanctions transfer. Same beneficial ownership (Neculiti brothers — EU-sanctioned).</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3230,8 +2966,6 @@
           <t>AS33993</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>Russia</t>
@@ -3262,15 +2996,11 @@
           <t>StormWall (DDoS fronting)</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
           <t>Savushkin Mikhail Yuryevich</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
           <t>Sanctions-resilient vehicle; Prefix migration recipient</t>
@@ -3291,7 +3021,6 @@
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
           <t>RF-STARK</t>
@@ -3302,7 +3031,6 @@
           <t>Russia-based ISP RIPE-registered March 13 2025. Identified as sanctions-resilient vehicle for Stark Industries Russian prefix migration beginning April 10 2025. AS33993 announced 21 prefixes.</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3325,8 +3053,6 @@
           <t>AS52000</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>Netherlands</t>
@@ -3347,17 +3073,11 @@
           <t>Innovation IT Solutions Corp; Nesterenko</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
           <t>Andrey Nesterenko</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
           <t>Netherlands infrastructure pillar for Stark/WorkTitans chain</t>
@@ -3378,7 +3098,6 @@
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
           <t>KREBS-BPH; RF-INFRA-2025; GREYNOISE-STARK; KREBS-FIOD-STARK</t>
@@ -3389,7 +3108,6 @@
           <t>Operated by Andrey Nesterenko (arrested in the FIOD raid of May 18 2026). Historically hosted StopGeorgia.ru (2008 Russia-Georgia cyberwar). Netherlands infrastructure pillar for Stark Industries and now WorkTitans/THE.Hosting. Youssef Zinad (WorkTitans founder) was part of MIRhosting legal team. MIRhosting stated it "temporarily paused" services to WorkTitans after the raid.</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3412,8 +3130,6 @@
           <t>AS34888; AS42624</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>Switzerland</t>
@@ -3434,7 +3150,6 @@
           <t>SWISSNETWORK02; Simple Carrier LLC (predecessor)</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>aurologic GmbH (AS30823)</t>
@@ -3445,10 +3160,6 @@
           <t>aurologic GmbH</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
           <t>Zero route diversification; aurologic-locked</t>
@@ -3459,13 +3170,11 @@
           <t>No route diversification (11 prefixes all through AS30823); Shell entity</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
           <t>RF-AUROLOGIC</t>
@@ -3476,7 +3185,6 @@
           <t>Aurologic downstream with zero route diversification. 11 active prefixes all through AS30823. ASNs transferred from Simple Carrier LLC.</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3499,8 +3207,6 @@
           <t>AS44050</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>Russia</t>
@@ -3521,13 +3227,6 @@
           <t>PIN; Pinspb</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
           <t>Long-running Russian BPH</t>
@@ -3538,13 +3237,11 @@
           <t>High malicious traffic ratio; Non-cooperative with LE</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
           <t>TRENDMICRO-INTERPOL</t>
@@ -3555,7 +3252,6 @@
           <t>Long-running Russian BPH. Trend Micro + Interpol 2023 ranked PIN as 19% of malicious offshore BPH sourcing — behind ELITETEAM (48%) ahead of FlokiNET (13%).</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3578,8 +3274,6 @@
           <t>AS152194</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>Hong Kong</t>
@@ -3605,14 +3299,11 @@
           <t>FUNNULL Technology Inc. (parent)</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>OFAC May 29 2025 (via FUNNULL designation)</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Triad Nexus</t>
@@ -3633,13 +3324,11 @@
           <t>Infrastructure laundering; Geofencing; Sanctioned (via FUNNULL); On Spamhaus ASN droplist</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
         <is>
           <t>SILENTPUSH-FUNNULL; OFAC-FUNNULL; INFOBLOX-DCLOUD</t>
@@ -3682,7 +3371,6 @@
           <t>AS210281</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>United Kingdom (registered)</t>
@@ -3703,7 +3391,6 @@
           <t>WAIcore Hosting LTD</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>aurologic GmbH (AS30823); RoyaleHosting BV; iFog GmbH; Netshield LTD</t>
@@ -3714,14 +3401,11 @@
           <t>aurologic GmbH</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Doppelganger disinformation</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
           <t>aurologic downstream; Doppelganger infrastructure</t>
@@ -3742,7 +3426,6 @@
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>RF-AUROLOGIC; QURIUM-DOPPELGANGER</t>
@@ -3753,7 +3436,6 @@
           <t>AS213887 registered Nov 8 2024 via RIPE. 68 IPv4 and 11 IPv6 prefixes. Named by RF Insikt and Qurium as aurologic-downstream within Doppelganger disinformation infrastructure. Multiple upstreams but aurologic primary.</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3781,7 +3463,6 @@
           <t>AS50113; AS205090</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>United Kingdom</t>
@@ -3797,12 +3478,6 @@
           <t>First Server Limited</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>LockBit; Conti; BlackCat/ALPHV; Qilin</t>
@@ -3823,13 +3498,11 @@
           <t>High malicious traffic ratio; Shell company structure; Ransomware infrastructure</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
           <t>SOPHOS-VMMANAGER; BLEEPINGCOMPUTER-BPH; TROLLEYE-FIRSTSERVER</t>
@@ -3840,7 +3513,6 @@
           <t>Named by Sophos Feb 2026 alongside Stark Industries for VMmanager Windows-template ransomware VM supply operation. Multiple ASNs: AS204997 AS50113 AS205090. ISPsystem VMmanager default Windows templates reuse hostnames enabling stealthy payload delivery for WantToCry and other ransomware families.</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3863,27 +3535,16 @@
           <t>AS215240</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Silent Connection Ltd</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
           <t>Dissolved-but-live pattern</t>
@@ -3894,7 +3555,6 @@
           <t>Dissolved-but-live; Network persists after corporate dissolution</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
           <t>2026-05-16</t>
@@ -3915,7 +3575,6 @@
           <t>Compulsorily dissolved at UK Companies House January 2025. AS215240 network remains live and continues to facilitate cybercrime despite corporate dissolution. Appears at position 9 in RF 2025 Threat Density chart.</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3938,14 +3597,11 @@
           <t>AS215208</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Dolphon 1337 Ltd</t>
@@ -3956,13 +3612,6 @@
           <t>Dolphin 1337 Limited</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
           <t>Dissolved-but-live; Possible ELITETEAM connection (1337 naming)</t>
@@ -3983,7 +3632,6 @@
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
           <t>EXCEDO-ASN</t>
@@ -3994,7 +3642,6 @@
           <t>Companion dissolved-but-live entity to Silent Connection Ltd. AS215208 registered March 28 2024 via RIPE. 1337 naming convention suggests possible ELITETEAM/1337TEAM orbital relationship. Compulsorily dissolved Jan 2025 but ASN persists.</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4012,9 +3659,6 @@
           <t>T5-Watch List</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>Hong Kong</t>
@@ -4025,23 +3669,16 @@
           <t>China (Alibaba-routed)</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>cdnclouds.net</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>Alibaba Cloud</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
           <t>Low-footprint CDN brand</t>
@@ -4062,14 +3699,11 @@
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr">
         <is>
           <t>Low-footprint provider on Hong Kong Alibaba infrastructure. Limited public CTI reporting. Watch-list as CDN brand that could front Asian BPH.</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4087,9 +3721,6 @@
           <t>T5-Watch List</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>Russia</t>
@@ -4100,15 +3731,6 @@
           <t>Russia</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
           <t>Small Russian-operator BPH profile</t>
@@ -4119,20 +3741,16 @@
           <t>Insufficient data; Russian operator pattern</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr">
         <is>
           <t>Naming pattern fits small Russian-operator BPH profile. Active baseline pending ASN enumeration.</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4150,9 +3768,6 @@
           <t>T5-Watch List</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>United States (shell)</t>
@@ -4163,15 +3778,6 @@
           <t>Eastern Europe (likely)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
           <t>US shell pattern</t>
@@ -4182,20 +3788,16 @@
           <t>Insufficient data; Shell company pattern</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr">
         <is>
           <t>LLC suffix without country qualifier suggests US or offshore-US shell. No sanctions or public CTI designation.</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4213,9 +3815,6 @@
           <t>T5-Watch List</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -4226,19 +3825,11 @@
           <t>Unknown (likely Asia/CIS)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>SOW-A</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -4249,20 +3840,16 @@
           <t>Insufficient data</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr">
         <is>
           <t>SOW-A qualifier unusual. Limited public OSINT. Enrichment needed.</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4280,9 +3867,6 @@
           <t>T5-Watch List</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -4293,15 +3877,6 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr">
         <is>
           <t>Unknown small operator</t>
@@ -4312,20 +3887,16 @@
           <t>Insufficient data</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr">
         <is>
           <t>Minimal public profile. Short-form naming matches small-operator pattern.</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4343,16 +3914,11 @@
           <t>T3-Suspected</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>Asia (Philippines/China likely)</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>Triad Nexus-affiliated brand</t>
@@ -4363,20 +3929,16 @@
           <t>FUNNULL Technology Inc. (affiliated)</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>OFAC May 29 2025 (via FUNNULL lineage)</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Triad Nexus</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr">
         <is>
           <t>Triad Nexus CDN front brand</t>
@@ -4387,13 +3949,11 @@
           <t>Infrastructure laundering; Triad Nexus connection</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
           <t>SILENTPUSH-FUNNULL</t>
@@ -4404,7 +3964,6 @@
           <t>Triad Nexus-affiliated CDN front brand. Likely among Silent Push-identified clean CDN front brands feeding traffic into laundered FUNNULL ecosystem.</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4432,7 +3991,6 @@
           <t>AS57724</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>Russia</t>
@@ -4448,14 +4006,6 @@
           <t>DDoS-Guard LTD</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr">
         <is>
           <t>Dual-use DDoS mitigation + hosting</t>
@@ -4466,20 +4016,16 @@
           <t>Dual-use; Historical controversial customers; Russian ecosystem</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr">
         <is>
           <t>Dual-use Russian DDoS mitigation + hosting. Historical Parler/8chan host. ELITETEAM AS51381 peer. Not classified BPH but persistent presence in Russian cybercrime ecosystem.</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4502,8 +4048,6 @@
           <t>AS14315</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>United States</t>
@@ -4519,13 +4063,6 @@
           <t>1GSERVERS LLC</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
           <t>Lumma</t>
@@ -4541,13 +4078,11 @@
           <t>Single source; Limited indicators</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
         <is>
           <t>INTEL-INSIGHTS-QWINS</t>
@@ -4558,7 +4093,6 @@
           <t>Small US-registered operator appearing alongside Proton66 Railnet Femo IT in Lumma malware hunt.</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4586,7 +4120,6 @@
           <t>AS211252</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>Netherlands</t>
@@ -4607,19 +4140,16 @@
           <t>Delis LLC; CrazyRDP; crazyrdp.com</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>Serverion (colocation)</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>Seized Nov 12 2025 (Operation Endgame; Dutch police)</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>80+ LE investigations; ransomware; CSAM distribution</t>
@@ -4640,7 +4170,6 @@
           <t>No KYC; No logs; Underground forum presence; High malicious traffic ratio</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr">
         <is>
           <t>2026-05-16</t>
@@ -4661,7 +4190,6 @@
           <t>Major BPH seized Nov 12 2025 by Dutch police as part of Operation Endgame. ~250 physical servers seized in The Hague and Zoetermeer. Operated as Limenet LLC (AS394711) and previously as Delis LLC (AS211252). Implicated in 80+ LE investigations spanning ransomware CSAM and malware distribution. No-KYC no-logs policy. Infrastructure now completely offline.</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4684,8 +4212,6 @@
           <t>AS138915</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>Hong Kong</t>
@@ -4706,17 +4232,11 @@
           <t>Keepo Cloud HK</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>Cogent; Arelion; NTT; Level3; PCCW Global</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
           <t>Large IP allocation; BitTorrent/Tor/VPN activity observed</t>
@@ -4752,7 +4272,6 @@
           <t>Hong Kong ISP with 182272 IPv4 addresses across 50+ netblocks and 48429 hosted domains. Appeared at #4 in RF 2025 Threat Density chart. APNIC-registered March 2019. Global router presence in SG VN SA PH US HK. Tagged with BitTorrent Tor exit node and VPN activity. Large infrastructure footprint warrants monitoring.</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4770,9 +4289,6 @@
           <t>T1-Confirmed BPH (Financial Enabler)</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>Russia / Kyrgyz Republic</t>
@@ -4798,8 +4314,6 @@
           <t>Garantex (predecessor)</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>OFAC Aug 14 2025 (successor to Garantex); UK OFSI Aug 20 2025</t>
@@ -4810,8 +4324,6 @@
           <t>Mira Serda ($5M State Dept reward)</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr">
         <is>
           <t>Sanctions-evasion vehicle; On-chain asset migration from Garantex</t>
@@ -4832,7 +4344,6 @@
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
         <is>
           <t>OFAC-GARANTEX; CHAINALYSIS-A7A5; CHAINALYSIS-OFAC; TRM-A7A5-2026; ELLIPTIC-GRINEX</t>
@@ -4865,9 +4376,6 @@
           <t>T1-Confirmed BPH (Financial Enabler)</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>Russia / Kyrgyz Republic</t>
@@ -4893,16 +4401,11 @@
           <t>Garantex/Grinex ecosystem</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>OFAC Aug 14 2025 (Old Vector); EU 19th package Oct 2025 (A7A5 transactions banned)</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr">
         <is>
           <t>Ruble-backed stablecoin laundering; No-KYC stablecoin swapping</t>
@@ -4923,7 +4426,6 @@
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>OFAC-GARANTEX; CHAINALYSIS-A7A5; TRM-A7A5-2026</t>
@@ -4956,9 +4458,6 @@
           <t>T2-High Risk (Financial Enabler)</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>Iran</t>
@@ -4974,18 +4473,11 @@
           <t>Nobitex</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>OFAC June 2 2026 (E.O. 13902 + counterterrorism E.O. 13224)</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
         <is>
           <t>Terror-finance facilitation; Sanctions evasion</t>
@@ -4996,13 +4488,11 @@
           <t>Sanctioned; Iran's largest crypto exchange</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
         <is>
           <t>OFAC-IRAN-FURY; CHAINALYSIS-OFAC</t>
@@ -5035,9 +4525,6 @@
           <t>T3-Suspected (Financial Enabler)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>Iran</t>
@@ -5053,18 +4540,11 @@
           <t>Wallex</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>OFAC June 2 2026 (E.O. 13902)</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr">
         <is>
           <t>Iranian crypto on-ramp; Sanctions evasion</t>
@@ -5075,13 +4555,11 @@
           <t>Sanctioned under 'Economic Fury'</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
           <t>OFAC-IRAN-FURY</t>
@@ -5114,9 +4592,6 @@
           <t>T3-Suspected (Financial Enabler)</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>Iran</t>
@@ -5132,18 +4607,11 @@
           <t>Bitpin</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>OFAC June 2 2026 (E.O. 13902)</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr">
         <is>
           <t>Iranian crypto on-ramp; Sanctions evasion</t>
@@ -5154,13 +4622,11 @@
           <t>Sanctioned under 'Economic Fury'</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
           <t>OFAC-IRAN-FURY</t>
@@ -5193,9 +4659,6 @@
           <t>T3-Suspected (Financial Enabler)</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>Iran</t>
@@ -5211,18 +4674,11 @@
           <t>Ramzinex</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>OFAC June 2 2026 (E.O. 13902)</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr">
         <is>
           <t>Iranian crypto on-ramp; Sanctions evasion</t>
@@ -5233,13 +4689,11 @@
           <t>Sanctioned under 'Economic Fury'</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr">
         <is>
           <t>OFAC-IRAN-FURY</t>
@@ -5307,14 +4761,11 @@
           <t>BtHoster; BTCloud; btcloud.ro</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
           <t>UAB Host Baltic (AS209605); Tube-Hosting (AS49581, aurologic)</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
           <t>Nominee dirs: Murray Charles / Jonathan Reynolds / Brooks William Thomas; provisioned via Khatibi (UAE, wcd maintainer) + Mashayekhi (Iran LIR)</t>
@@ -5350,7 +4801,6 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
         <is>
           <t>INTRINSEC-BTHOSTER; SECURITYONLINE-BTHOSTER; RIPE-AAWG-BTHOSTER</t>
@@ -5388,8 +4838,6 @@
           <t>AS51396</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>Germany</t>
@@ -5405,18 +4853,11 @@
           <t>Pfcloud UG (haftungsbeschraenkt)</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>aurologic-linked ecosystem</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr">
         <is>
           <t>Bulletproof-adjacent; Sustained scanning/proxy abuse</t>
@@ -5437,7 +4878,6 @@
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr">
         <is>
           <t>RUDIS-BPH-WATCH; RF-AUROLOGIC</t>
@@ -5470,9 +4910,6 @@
           <t>T2-High Risk (Financial Enabler)</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>China (Telegram-based)</t>
@@ -5493,11 +4930,6 @@
           <t>大白担保; @DBTM301</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Chinese-language scam-compound ecosystem</t>
@@ -5528,7 +4960,6 @@
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr">
         <is>
           <t>RF-GUARANTEE-2026</t>
@@ -5561,9 +4992,6 @@
           <t>T2-High Risk (Financial Enabler)</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>Cambodia / Telegram-based</t>
@@ -5589,12 +5017,6 @@
           <t>Huione (30% stake, Dec 2024)</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr">
         <is>
           <t>Guarantee/escrow marketplace; Money-laundering facilitation; Wound down post-arrest</t>
@@ -5605,13 +5027,11 @@
           <t>3rd-largest illicit marketplace; Admin-wallet collapse after Chen Zhi arrest</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr">
         <is>
           <t>ELLIPTIC-TUDOU; RF-GUARANTEE-2026; OFAC-HUIONE-PRINCE</t>
@@ -5644,9 +5064,6 @@
           <t>T2-High Risk (Financial Enabler)</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>Cambodia</t>
@@ -5672,16 +5089,11 @@
           <t>Huione Group</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>FinCEN proposed Section 311 amendment June 23 2026 (successor-entity rule)</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr">
         <is>
           <t>Successor facilitator; Inherited Huione Pay branches/customers/branding</t>
@@ -5702,7 +5114,6 @@
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr">
         <is>
           <t>OFAC-HUIONE-PRINCE</t>
@@ -5740,7 +5151,6 @@
           <t>AS48266</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>205.198.91.136; 205.198.91.155; 194.147.16.244</t>
@@ -5756,17 +5166,11 @@
           <t>Netherlands (servers); global botnet</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>asocks.com; LVCHA VPN-linked</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>PROXYLIB (2024)</t>
@@ -5797,7 +5201,6 @@
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr">
         <is>
           <t>NCSC-NL-ASOCKS; SILENTPUSH-CHINESEVPN</t>
@@ -5830,9 +5233,6 @@
           <t>T1-Confirmed BPH</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>Uzbekistan</t>
@@ -5858,7 +5258,6 @@
           <t>Aeza Group LLC (linked to)</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
           <t>Aeza Group LLC</t>
@@ -5869,9 +5268,6 @@
           <t>OFAC Nov 19 2025 (E.O. 13694; CAATSA-RUSSIA; CYBER4; Linked To Aeza Group LLC); NOT UK-designated</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr">
         <is>
           <t>Sanctions-evasion vehicle; Corporate shell</t>
@@ -5892,7 +5288,6 @@
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr">
         <is>
           <t>OFAC-MEDIALAND</t>
@@ -5925,9 +5320,6 @@
           <t>T1-Confirmed BPH (Anonymization/Proxy Enabler)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -5938,15 +5330,11 @@
           <t>Russia/Ukraine nexus (operator identity obscured)</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>1VPNS; First VPN Service</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
           <t>OFAC July 13 2026 (E.O. 13694 as amended, in furtherance of E.O. 14390; coordinated with UK FCDO)</t>
@@ -5962,7 +5350,6 @@
           <t>Ransomware operators (unnamed in designation)</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr">
         <is>
           <t>Criminal VPN / anonymization enabler; No-log policy; Forum-advertised since 2014; Refuses LE cooperation</t>
@@ -5983,7 +5370,6 @@
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr">
         <is>
           <t>OFAC-1VPNS</t>
@@ -6016,9 +5402,6 @@
           <t>T2-High Risk (Anonymization/Proxy Enabler)</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>Israel</t>
@@ -6044,10 +5427,6 @@
           <t>Alarum Technologies Ltd</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>316 distinct threat-actor clusters (Google GTIG, June 2026)</t>
@@ -6078,7 +5457,6 @@
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr">
         <is>
           <t>GTIG-NETNUT; KREBS-NETNUT</t>
@@ -6092,6 +5470,98 @@
       <c r="Y64" t="inlineStr">
         <is>
           <t>LE-seized commercial residential-proxy platform (Alarum/NASDAQ: ALAR) with botnet-sourced exit nodes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SHANGXING TECH LIMITED</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>suspected</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>T2-High Risk</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AS400619</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>103.112.97.0/24</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Hong Kong/US</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>SHANGXING TECH LIMITED</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Fastmos Co Limited; AROSSCLOUD INC.; Zun Cloud Limited</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>China-nexus</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Gshell C2; Vshell-adjacent; mass web-exploitation (Java memshell / CVE PoC)</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Multi-org HK reseller ASN; recurring China-nexus C2 + exploitation staging; SOCKS relays</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Gshell default cert on tenants; mass-exploitation open directories; multiple org names on one ASN</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>CV-GSHELL-2026-07; CV-OPENDIR-2026-09</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>AS400619 is a Hong Kong reseller ASN announced under multiple org names (Fastmos Co Limited, AROSSCLOUD INC., Zun Cloud Limited, PEG TECH INC, AS Data HK). Hosts the July 2026 unreported Gshell C2 cluster (SHANGXING pair 103.112.97.163/.199) and a Sept 2026 mass web-exploitation workspace (Fastmos :8889 - gen_targets/CVE-PoC/Java-memshell RCE-verify/k8s scan, 283KB target list) plus a second exploit box (AROSSCLOUD :9999). First-party CrimsonVector open-directory hunt.</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>HK reseller ASN, recurring China-nexus C2 and mass-exploitation host (SHANGXING/Fastmos/Arosscloud).</t>
         </is>
       </c>
     </row>

--- a/BPH_Master.xlsx
+++ b/BPH_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y65"/>
+  <dimension ref="A1:Y72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>45.135.232.0/24; 45.140.17.0/24</t>
+          <t>91.202.233.0/24; 91.215.85.0/24; 193.24.123.0/24 (AS200593); 37.77.150.0/24; 176.120.22.0/24; 193.143.1.0/24 (AS198953) - announced 2026-09-25, all on Spamhaus DROP. Historical Proton66 blocks now originated by unrelated ASNs (do not attribute): 45.135.232.0/24 (AS62300); 45.140.17.0/24 (AS58061)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -630,22 +630,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>BEARHOST; SecureHost; Underground; Chang Way Technologies</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>St. Petersburg IXP</t>
+          <t>BEARHOST; SecureHost; UNDERGROUND</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>GootLoader; SocGholish; FIN7</t>
+          <t>GootLoader; SocGholish; Mora_001 (SuperBlack); ShinyHunters (CVE-2026-35273 exploitation, per Hunt.io); Blind Eagle / APT-C-36; The Gentlemen RaaS affiliate</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>GootLoader; SocGholish; SpyNote; FakeBat; XWorm; StrelaStealer; WeaXor/Mallox; SuperBlack (Mora_001)</t>
+          <t>GootLoader; SocGholish; SpyNote; FakeBat; XWorm; StrelaStealer; WeaXor/Mallox; SuperBlack; Coper/Octo</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -655,22 +650,22 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>No KYC; Underground forum presence; Bulletproof self-identification; High malicious traffic ratio</t>
+          <t>Spamhaus ASN-DROP (AS200593 pro-spero.ru; AS198953 proton66.ru); all announced /24s on Spamhaus DROP; Underground forum presence; Bulletproof self-identification; High malicious traffic ratio</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>IOCTA-2026; INTRINSEC-PROSPERO; TRUSTWAVE-PROSPERO; GREYNOISE-PROSPERO</t>
+          <t>IOCTA-2026; INTRINSEC-PROSPERO; TRUSTWAVE-PROSPERO; GREYNOISE-PROSPERO; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09; HUNTIO-EE-2026; HUNTIO-GENTLEMEN-2026; LEVELBLUE-BLINDEAGLE-2026</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Coupled Russian AS pair assessed by Intrinsec + Trustwave SpiderLabs as single operator marketing on Russian-language forums as BEARHOST/SecureHost/UNDERGROUND. Feb 2026 GreyNoise: AS200593 dominant source of Ivanti EPMM mass exploitation (83% from one IP). Likely rebrand arm: Chang Way Technologies (HK). Block at CIDR level.</t>
+          <t>Coupled Russian AS pair assessed by Intrinsec (high confidence) and Trustwave SpiderLabs as one operator marketed on Russian-language forums as BEARHOST/SecureHost/UNDERGROUND. Feb 2026 GreyNoise: 346 of 417 Ivanti EPMM exploitation sessions (83%) came from one AS200593 address, 193.24.123.42. 2026 activity: Hunt.io linked Proton66 to exploitation of Oracle PeopleSoft CVE-2026-35273 attributed to ShinyHunters (July) and found a The Gentlemen RaaS affiliate toolkit in an open directory at 176.120.22.127 (reported June); LevelBlue SpiderLabs reports Blind Eagle delivery infrastructure on Proton66 since June 2025. Chang Way Technologies (HK) is likely related (SpiderLabs saw IP shifts and a re-themed panel) and is tracked as its own row, not as an alias. Corrections 2026-09-25: the former known_prefixes 45.135.232.0/24 and 45.140.17.0/24 were historical Proton66 blocks now held by unrelated networks; FIN7 and the 'St. Petersburg IXP' upstream were removed (no supporting source). Block at CIDR level.</t>
         </is>
       </c>
     </row>
@@ -697,27 +692,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AS216246</t>
+          <t>AS216246; AS203273 (NetCrafters OU [EE]; Spamhaus ASN-DROP under aeza.net)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>United Kingdom (Companies House 15109642; UK front of Russia-registered Aeza Group LLC)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Russia (St. Petersburg)</t>
+          <t>Russia (St. Petersburg); EU-hosted infrastructure</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Aeza International Ltd</t>
+          <t>Aeza International Ltd (UK front, inc. 2023-09-01); Aeza Group LLC (Russia) holds AS210644/AS216246</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Aeza Group LLC; Aeza Logistic LLC; Cloud Solutions LLC; Datavice</t>
+          <t>Aeza; Aeza Group</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Aeza Group LLC (Russia; primary OFAC designee)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -727,22 +727,22 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>OFAC July 1 2025 (in coordination with UK NCA); UK designation Sept 19 2025; OFAC expanded Nov 19 2025 (Hypercore; Datavice)</t>
+          <t>OFAC July 1 2025 (sb0185): Aeza Group LLC (primary) + Aeza International Ltd, Aeza Logistic LLC, Cloud Solutions LLC and four executives, coordinated with UK NCA; UK Nov 19 2025: Aeza Group LLC designated under the Russia regime (Aeza International Ltd not separately listed); OFAC Nov 19 2025 follow-on: Hypercore Ltd, Smart Digital Ideas DOO (RS), Datavice MCHJ (UZ), Maksim Makarov, Ilya Zakirov</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>CEO + 33% owner Penzev (arrested April 2025); GD + 33% owner Bozoyan; CTO Gast; 33% owner Knyazev</t>
+          <t>CEO + 33% owner Arsenii Penzev; GD + 33% owner Yurii Bozoyan (both detained by Russian authorities in early April 2025 over BlackSprut hosting); technical director Vladimir Gast; 33% owner Igor Knyazev; Maksim Makarov (new executive, OFAC Nov 2025)</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>BianLian ransomware</t>
+          <t>BianLian ransomware; Void Rabisu (RomCom); Dark Caracal (GoCaracal C2, 2026); Doppelganger influence operation</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Meduza; Lumma; RedLine; BianLian; BlackSprut; RomCom RAT</t>
+          <t>Meduza; Lumma; RedLine; BianLian; RomCom RAT; GoCaracal; Go-based macOS crypto-drainer (2026); BlackSprut darknet market (hosted)</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -752,22 +752,22 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>High malicious traffic ratio; Sanctioned personnel; No KYC</t>
+          <t>Spamhaus ASN-DROP (AS210644; AS216246; AS203273 under aeza.net); Sanctioned entity and personnel; High malicious traffic ratio; No KYC</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>IOCTA-2026; RF-TAE-2026; OFAC-AEZA; CHAINALYSIS-OFAC</t>
+          <t>IOCTA-2026; RF-TAE-2026; OFAC-AEZA; CHAINALYSIS-OFAC; UK-COMPANIES-HOUSE; SPAMHAUS-ASNDROP-2026; ARCTICWOLF-DARKCARACAL-2026; HUNTRESS-MACOS-AEZA-2026; FCDO-UK-SANCTIONS-LIST</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>OFAC-designated July 1 2025 (coordinated with UK NCA). Hosts Meduza Lumma RedLine infopanels BianLian ransomware BlackSprut darknet drug marketplace RomCom RAT. TRON wallet TU4tDFRvcKhAZ1jdihojmBWZqvJhQCnJ4F designated. Nov 19 2025 OFAC expanded to Hypercore Ltd and Datavice. Upstream transit still flows through aurologic AS30823. AS211522 is registered to the Aeza front Hypercore Ltd (RIPE as-name HYPERCORELTD, created 2025-07-10), not to Aeza International directly.</t>
+          <t>OFAC designated Aeza Group LLC and its UK front Aeza International Ltd on 2025-07-01 (coordinated with the UK NCA) for hosting Meduza and Lumma infostealer operators, BianLian and the BlackSprut market. The TRON address TU4tDFRvcKhAZ1jdihojmBWZqvJhQCnJ4F sits on the Aeza Group LLC SDN entry. Owners Penzev and Bozoyan and two staff were detained by Russian authorities in early April 2025 (a Russian drug-market case, not a Western action). Evasion: 2,100+ IPs moved to the UK front Hypercore (AS211522) from 2025-07-20; Serbian (Smart Digital Ideas DOO) and Uzbek (Datavice MCHJ) vehicles followed - all OFAC-designated 2025-11-19. Sanctions have not ended operational use: AS210644 still announces 176 IPv4 prefixes; Arctic Wolf (Aug 2026) found 23 of 24 Dark Caracal GoCaracal C2s on Aeza networks and Huntress (Aug 2026) traced a ClickFix macOS crypto-drainer's staging and C2 to Aeza. Spamhaus now also lists AS203273 (NetCrafters OU, EE) under aeza.net. Roughly half of Aeza's prefixes transited aurologic AS30823 as of Nov 2025.</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sanctioned</t>
+          <t>dissolved</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -789,12 +789,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AS44477 (transferred)</t>
+          <t>AS44477 (historical; transferred to PQ Hosting Plus 2025-05-16; now deregistered)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>United Kingdom (dissolved)</t>
+          <t>United Kingdom (Companies House 13906017; dissolved 2025-09-16)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -809,32 +809,32 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>PQ Hosting; PQ Hosting Plus S.R.L.; MIRhosting ties</t>
+          <t>stark-industries.solutions; PQ.Hosting white label</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>WorkTitans B.V. / THE.Hosting (successor)</t>
+          <t>PQ.Hosting (Neculiti) - RF describes Stark as its white-label pass-through; successors WorkTitans/THE.Hosting and UFO Hosting</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>EU May 20 2025 (Hybrid Threats Regulation (EU) 2024/2642 - NOT the 17th Russia package; adopted same day but a separate legal basis)</t>
+          <t>EU May 20 2025: Council Implementing Regulation (EU) 2025/965 under the hybrid-threats regime Reg. (EU) 2024/2642 (not the 17th Russia package) - Stark Industries Solutions Ltd; Iurie Neculiti; Ivan Neculiti</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Ivan Neculiti; Iurie Neculiti</t>
+          <t>Iurie Neculiti (CEO); Ivan Neculiti (owner of Stark Industries and PQ Hosting)</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>NoName057(16); FIN7/GrayAlpha; Sandworm</t>
+          <t>NoName057(16); FIN7/GrayAlpha</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>DDoSia; Doppelganger</t>
+          <t>Cobalt Strike; QuasarRAT; AsyncRAT; DarkGate; PlugX; GootLoader; RedLine; ShadowPad; SpyNote; Raccoon; Hook; Havoc; Mythic</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -854,17 +854,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>IOCTA-2026; RF-TAE-2026; RF-STARK; GREYNOISE-STARK; CENSYS-BPH; EU-STARK</t>
+          <t>IOCTA-2026; RF-TAE-2026; RF-STARK; GREYNOISE-STARK; CENSYS-BPH; EU-STARK; UK-COMPANIES-HOUSE; SPAMHAUS-ASNDROP-2026</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>EU-sanctioned May 20 2025. UK-incorporated Feb 10 2022 — two weeks before Russia invaded Ukraine. White-label front for Moldova PQ Hosting and Netherlands MIRhosting. Preempted sanctions by transferring AS44477 to PQ Hosting Plus S.R.L. ~12 days ahead. Now formally dissolved.</t>
+          <t>EU-listed 2025-05-20 (Impl. Reg. 2025/965). UK-incorporated 2022-02-10, two weeks before Russia's full-scale invasion of Ukraine; dissolved 2025-09-16. RF describes Stark as a white-label front for Moldova's PQ.Hosting, with MIRhosting (NL) as a key infrastructure partner. AS44477 moved to PQ Hosting Plus S.R.L. on 2025-05-16 - four days before designation (the often-quoted '12 days' is the lead time from the 2025-05-08 RFE/RL leak); the THE.Hosting rebrand followed on 2025-05-29. GreyNoise saw near-complete abandonment of AS44477 by Nov 2025; it has since left the routing table and the registry. The network continues as WorkTitans/THE.Hosting (AS209847, AS213999) and UFO Hosting (AS33993), all listed by Spamhaus ASN-DROP under stark-industries.solutions. RF attributes the chain's RIPE maintainer to Dmitrii Miasnikov. Doppelganger (an influence operation, not malware) and Sandworm were removed from the malware/actor fields for lack of a Stark-specific source.</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AS216071 (historical)</t>
+          <t>AS197414 (historical; XHOST-INTERNET-SOLUTIONS; deregistered)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AS213194; AS61336; AS213010</t>
+          <t>AS213194 (successor hop); AS61336 (successor hop); AS213010 (successor hop)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -906,22 +906,22 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Zservers</t>
+          <t>Zservers (Russia, Barnaul); XHOST Internet Solutions LP (UK front, UK-designated)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>XHost; XHOST Internet Solutions LP</t>
+          <t>XHost; zservers.ru; isxhost.uk</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>US/UK/AU trilateral Feb 11 2025</t>
+          <t>Feb 11 2025 trilateral, differing by authority - OFAC: Zservers, Alexander Mishin, Aleksandr Bolshakov (3 BTC addresses on Zservers, 1 on Mishin); UK: ZSERVERS, XHOST Internet Solutions LP and six individuals; Australia (Feb 12 2025 AEDT): Zservers and five individuals</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Admins Mishin; Bolshakov</t>
+          <t>Aleksandr Bolshakov; Alexander Mishin (admins; designated by US/UK/AU); Ilya Sidorov; Dmitry Bolshakov; Igor Odintsov (UK and AU); Vladimir Ananev (UK)</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -941,22 +941,22 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Sanctioned personnel; High malicious traffic ratio; Underground forum presence</t>
+          <t>Sanctioned entity and personnel; LE seizure (127 servers, NL, Feb 2025); High malicious traffic ratio; Underground forum presence</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>OFAC-ZSERVERS; CHAINALYSIS-BPH</t>
+          <t>OFAC-ZSERVERS; CHAINALYSIS-BPH; FCDO-UK-SANCTIONS-LIST; AU-DFAT-ZSERVERS; THERECORD-ZSERVERS-SEIZURE; INTRINSEC-UAC-2025; MALTRAIL-WORST-ASNS</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>First Russia-based BPH sanctioned in 2025 wave. Chainalysis tied payments to LockBit BianLian Hunters International Mallox Dharma Phobos Globeimposter Cryptolocker REvil. Linked to 2022 Medibank breach. Post-sanction prefix-hopping to AS213194 AS61336 AS213010.</t>
+          <t>Designated 2025-02-11 by the US, UK and Australia (per-authority lists in sanctions_designations). UK and Australian texts tie Zservers infrastructure to the 2022 Medibank data leak; Chainalysis traced payments from LockBit, BianLian, Hunters International and others. On 2025-02-12 Dutch police took 127 Zservers/XHOST servers offline in Amsterdam. The Zservers/XHOST ASN was AS197414 (historical prefixes 185.170.144.0/24 and 87.251.64.0/24, now held by unrelated networks); Spamhaus listed it under zservers.ru until at least Dec 2025 and it is now deregistered. Intrinsec assessed with high confidence that Zservers prefixes moved to AS213194, AS61336 and AS213010 (small footprints still announced; none on ASN-DROP). CORRECTION 2026-09-25: AS216071, previously listed here as historical, is VDSina / SERVERS TECH FZCO (UAE), an active ~156k-address network with no public link to Zservers - removed from this row; do not block it as Zservers infrastructure.</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AS48721; AS211409; AS215311</t>
+          <t>AS215376 (ML Cloud Ltd); AS211805 (registered to Media Land LLC; no routes)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>45.141.85.0/24; 91.220.163.0/24 (AS206728); 176.98.187.0/24 (AS215376) - all on Spamhaus DROP</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1003,17 +1008,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Yalishanda; Alexander Volosovyk; ML.Cloud; Media Land Technology</t>
+          <t>Yalishanda (operator handle); sshvps.net; ML.Cloud (sister company); Media Land Technology (subsidiary); Data Center Kirishi (subsidiary)</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>OFAC/UK/AU trilateral Nov 19 2025; EU July 13 2026 (Impl. Reg. (EU) 2026/1714 - Media Land + Volosovik + ML.Cloud); DOJ indictment unsealed July 14 2026 (N.D. Ohio)</t>
+          <t>OFAC Nov 19 2025 (sb0319): Media Land LLC, ML.Cloud LLC, Media Land Technology, Data Center Kirishi + Volosovik, Zatolokin, Pankova; UK Nov 19 2025 (Cyber regime): Media Land LLC, ML.Cloud LLC, Volosovik, Zatolokin, Pankova, Andrei Kozlov; Australia Nov 20 2025: Media Land LLC, ML.Cloud LLC, Volosovik, Zatolokin; EU July 13 2026 (Impl. Reg. (EU) 2026/1714): Media Land LLC, ML.Cloud, Volosovik; New Zealand Aug 8 2026: Volosovik; DOJ N.D. Ohio indictment (returned Dec 5 2024, unsealed July 14 2026)</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Yalishanda (Alexander Volosovik; also transliterated Volosovyk); Kirill Zatolokin; Yulia Pankova; Kozlov (UK-designated)</t>
+          <t>Aleksandr Volosovik ('Yalishanda'; general director; also transliterated Volosovyk); Kirill Zatolokin; Yulia Pankova; Andrei Kozlov (UK-designated only)</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1033,22 +1038,22 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>High malicious traffic ratio; No KYC; Underground forum presence</t>
+          <t>Spamhaus ASN-DROP (AS206728; AS215376 under sshvps.net); High malicious traffic ratio; No KYC; Underground forum presence</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>OFAC-MEDIALAND; INTEL471-MEDIALAND; TEAMCYMRU-VIRTUALINE; SPAMHAUS-BPH; EU-CYBER-2026-1714; DOJ-MEDIALAND-INDICTMENT</t>
+          <t>OFAC-MEDIALAND; INTEL471-MEDIALAND; TEAMCYMRU-VIRTUALINE; SPAMHAUS-BPH; EU-CYBER-2026-1714; DOJ-MEDIALAND-INDICTMENT; SPAMHAUS-ASNDROP-2026; AU-DFAT-MEDIALAND; INTEL471-BPH-2026; NZ-MFAT-RUSSIA-2026-08</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>OFAC/UK/AU trilateral sanctions Nov 19 2025 (FBI-coordinated). Operated by Yalishanda — veteran Russian BPH operator. Three leaders + three sister companies sanctioned. Long-documented by Intel 471 Team Cymru Spamhaus.</t>
+          <t>Designated 2025-11-19 by the US, UK and Australia with differing lists (see sanctions_designations); the EU followed on 2026-07-13 and New Zealand designated Volosovik on 2026-08-08. The N.D. Ohio indictment unsealed 2026-07-14 (Operation Riptide) charges Volosovik, Zatolokin, Pankova, Medialand LLC and ML.Cloud LLC over attacks causing more than $62M in victim losses. Treasury described Media Land as a launch pad for LockBit, BlackSuit and Play ransomware. The OFAC SDN entry for Volosovik carries BTC address 18dLDAWi8LmrHbEq3QzDJb9SLxCf4uimXB. Intel 471 (Aug 2026): roughly 80% of ~2,240 yalishanda customer domains stayed online into June 2026, with demand shifting to mainstream clouds and to new services (OtusCloud, reming, fluxy). Corrections 2026-09-25: AS48721 (Flyservers), AS211409 (FoxiBytes) and AS215311 (Regxa) were removed - no source links them to Media Land; AS215376 (ML Cloud Ltd, 176.98.187.0/24) and the dormant AS211805 were added.</t>
         </is>
       </c>
     </row>
@@ -1070,17 +1075,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AS51381</t>
+          <t>AS51381 (registered; no routes)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AS39770; AS60424; AS56873</t>
+          <t>AS39770 (historical; deregistered); AS60424 (historical; deregistered); AS56873 (registered; no routes)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>185.215.113.0/24</t>
+          <t>185.215.113.0/24 (historical; unrouted as of 2026-09-25)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1105,17 +1110,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Crex Fex Pex; AS Infolika; OOO RAIT TELECOM; DDoS-Guard; Filanco/Datahouse.ru</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Turla (Secret Blizzard)</t>
+          <t>Historical (2020-22): Crex Fex Pex (AS3555); Infolika (AS203804); RAIT TELECOM (AS213254); DDoS-Guard (AS49612)</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Amadey; RedLine; Stealc; BabbleLoader</t>
+          <t>Amadey; RedLine; Stealc</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1125,27 +1125,27 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>High malicious traffic ratio (100% of /24 flagged); No KYC; Offshore registration</t>
+          <t>Spamhaus ASN-DROP (AS51381; AS56873 under eliteteam.to); Offshore registration; Network dark (no prefixes announced, 2026-09-25)</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2020-11-13</t>
+          <t>2020-11</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>TRENDMICRO-INTERPOL</t>
+          <t>TRENDMICRO-INTERPOL; TEAMCYMRU-ELITETEAM-2022; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Russia-operated BPH registered in Seychelles at Panama Papers-linked address. VirusTotal flags 100% of 185.215.113.0/24 as malicious. Block at perimeter.</t>
+          <t>Russia-operated BPH registered in the Seychelles at an address that appears in the Panama Papers/Offshore Leaks (Team Cymru). Team Cymru (2022) listed four 1337TEAM ASNs operating mainly from AS51381 and recommended blocking 185.215.113.0/24, a long-running Amadey/RedLine C2 block. Current state (2026-09-25): AS51381 and AS56873 are still registered to 1337TEAM LIMITED and remain on Spamhaus ASN-DROP but announce nothing; AS39770 and AS60424 are gone from the registry; 185.215.113.0/24 is unrouted. Status kept 'active' because no dissolution, sanction or seizure is documented - treat the network as dormant and watch for re-announcement. Corrections 2026-09-25: upstreams are historical and Filanco (AS3175, Datahouse.ru) was a downstream, not an upstream; the Turla link was removed (Microsoft's Secret Blizzard/Amadey reporting does not name ELITETEAM); the unsourced 'VirusTotal 100%' claim and BabbleLoader were removed.</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>routes through AS152194 (CTG Server Limited)</t>
+          <t>AS152194 (hosting ASN used; CTG Server Limited - not FUNNULL-owned)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1187,22 +1187,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>FUNNULL CDN; Liu Lizhi</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>CTG Server Limited (backbone)</t>
+          <t>FUNNULL CDN; Fang Neng CDN; funnull.io; Bole CDN / CDN1.ai (pre-sanction front brands)</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>OFAC May 29 2025</t>
+          <t>OFAC May 29 2025 (sb0149): Funnull Technology Inc. and administrator Liu Lizhi</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Liu Lizhi</t>
+          <t>Liu Lizhi ('Steve'; administrator; Chinese national)</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1227,17 +1222,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>OFAC-FUNNULL; SILENTPUSH-FUNNULL; FBI-IC3-FUNNULL</t>
+          <t>OFAC-FUNNULL; SILENTPUSH-FUNNULL; FBI-IC3-FUNNULL; SILENTPUSH-TRIADNEXUS-2026</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>OFAC-sanctioned May 2025 for $200M+ pig-butchering fraud and 200000+ unique hostnames. Post-sanction pivot to infrastructure laundering via compromised AWS/Cloudflare/Google/Microsoft accounts. Triad Nexus reportedly rebuilding into 2026 as Bole CDN / CDN1.ai.</t>
+          <t>OFAC-designated 2025-05-29 (with Liu Lizhi) for infrastructure behind cryptocurrency investment scams causing more than $200M in US victim-reported losses; the FBI FLASH the same day counted 548 FUNNULL CNAMEs linked to 332,000+ domains since Jan 2025. Taguig (Philippines) company run by a Chinese national. CTG Server Limited (AS152194) was one of several ASNs hosting FUNNULL points of presence in Silent Push's 2024 mapping; it is not FUNNULL's parent and was not designated. Silent Push (Apr 2026): Triad Nexus kept operating through 'clean' front brands (Bole CDN, CDN1.ai and others) that were launched before the May 2025 sanctions, plus accounts at major clouds and US-IP geofencing.</t>
         </is>
       </c>
     </row>
@@ -1262,6 +1257,11 @@
           <t>AS209847</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AS213999 (THE-CLIENTS; registered, no routes)</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Netherlands</t>
@@ -1279,12 +1279,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>THE.Hosting; Misfits Media; WT Hosting; Fezzy BV</t>
+          <t>THE.Hosting; Misfits Media; WT Hosting</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Stark Industries Solutions (predecessor)</t>
+          <t>Fezzy B.V. (sole shareholder); Stark Industries Solutions (predecessor network)</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>MIRhosting B.V. (AS52000) - Krebs: sole connectivity</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1294,7 +1299,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Youssef Zinad (MIRhosting legal-team associate)</t>
+          <t>Youssef Zinad (owner; arrested 2026-05-18, name press-reported)</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>NoName057(16); MuddyWater (MOIS) and two other Iranian groups (Check Point 2026)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1304,27 +1314,27 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Shell company structure; Sanctioned personnel (via Neculiti); Rapid rebranding</t>
+          <t>Spamhaus ASN-DROP (AS209847; AS213999 under stark-industries.solutions); Shell company structure; Sanctioned personnel (via Neculiti); Rapid rebranding</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>RF-STARK; GREYNOISE-STARK; CENSYS-BPH; EU-STARK; KREBS-FIOD-STARK; DARKREADING-ELLIO-STARK</t>
+          <t>RF-STARK; GREYNOISE-STARK; CENSYS-BPH; EU-STARK; KREBS-FIOD-STARK; DARKREADING-ELLIO-STARK; SPAMHAUS-ASNDROP-2026; CHECKPOINT-WORKTITANS-IRAN-2026</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Dutch post-sanctions successor to Stark Industries/PQ.Hosting. AS209847 created June 24 2025. GreyNoise confirmed seamless migration from AS44477. Censys confirmed via RDP hostname fingerprint reuse (WIN-J9D866ESIJ2). FIOD raided the Dutch nodes May 18 2026 (800+ servers seized; directors Youssef Zinad and Andrey Nesterenko arrested), but ELLIO telemetry showed the reseller-distributed network back at near pre-raid scanning levels within a week - a partial seizure the successor structure was built to survive. Status kept as evading (network operational) rather than seized.</t>
+          <t>Dutch post-sanctions successor to Stark Industries/PQ.Hosting. WorkTitans B.V. was formed in 2019 as a recruitment firm; its Stark-successor role starts with RIPE org ORG-THE3-RIPE (created 2025-05-28) and prefix transfers from 2025-05-29; AS209847 was created 2025-06-24 and AS213999 (THE-CLIENTS) also belongs to WorkTitans. AS209847 announced 21 prefixes in Aug 2025 and 11 today. GreyNoise confirmed the migration from AS44477 (Aug-Nov 2025); Censys matched RDP hostname reuse (WIN-J9D866ESIJ2). FIOD raided the Dutch nodes on 2026-05-18: 800+ servers seized at data centres in Dronten and Schiphol-Rijk; WorkTitans owner Youssef Zinad and MIRhosting founder Andrey Nesterenko arrested (names press-reported). ELLIO saw scanning back near pre-raid levels more than a week later, but later reports conflict (one telemetry source reports a 94% drop in the indexed fleet; a Russian-language hosting knowledge base says the THE.Hosting site announced it had stopped operating) - status kept 'evading' pending clarity. Check Point (June 2026): three Iranian groups including MuddyWater used WorkTitans infrastructure for core operations.</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1356,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AS215552</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AS211522</t>
+          <t>AS211522 (dark since ~2026-02)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1361,7 +1366,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UK registered office only; infrastructure was Aeza's (EU/RU)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1376,12 +1381,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Aeza Group LLC (parent)</t>
+          <t>Aeza Group LLC (front company)</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>OFAC Nov 19 2025 (E.O. 13694); UK: not separately listed - captured via ownership/control as a Subsidiaries entry on the Aeza Group LLC row of the FCDO UK Sanctions List</t>
+          <t>OFAC Nov 19 2025 (E.O. 13694, as an Aeza Group front); not listed in the UK notices of the same date</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1396,17 +1401,17 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>OFAC-AEZA; OFAC-MEDIALAND</t>
+          <t>OFAC-AEZA; OFAC-MEDIALAND; UK-COMPANIES-HOUSE; SILENTPUSH-AEZA-2025; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>UK-registered Aeza Group front. Second iteration of Aeza UK-shell playbook. Any transactions trigger OFAC secondary-sanctions exposure. AS211522 created 2025-07-10 (RIPE HYPERCORELTD); Companies House No. 16558658, incorporated 2025-07-03, 120 Fleet Street, London EC4A 2BE. Migrated 2,100+ IPs from Aeza AS210644 to AS211522 starting 2025-07-20. OFAC/OFSI designated Hypercore Nov 19 2025 as an Aeza front.</t>
+          <t>UK-registered Aeza Group front (Companies House 16558658; 120 Fleet Street, London); the second iteration of Aeza's UK-shell playbook. AS211522 (RIPE as-name HYPERCORELTD) was allocated ~2025-07-10 and received 2,100+ IPs from Aeza's AS210644 starting 2025-07-20 (Silent Push). OFAC designated Hypercore on 2025-11-19; it is an OFAC-only designation (the earlier 'OFAC/OFSI' wording was wrong). Spamhaus listed AS211522 under aeza.net in Dec 2025; it has since been delisted and the ASN has announced nothing since ~2026-02. Former Hypercore prefixes now originate from First Server Limited ASNs (45.142.122.0/24 via AS205090; 185.174.136.0/24 via AS200740) - a lead, not proof of common control. Incorporation date 2025-07-03 is unverified (possibly conflated with Datavice). CORRECTION 2026-09-25: AS215552, previously the primary ASN, belongs to an unrelated Romanian individual and was removed.</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1428,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T2-High Risk</t>
+          <t>T1-Confirmed BPH</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1431,6 +1436,11 @@
           <t>AS214351</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>62.60.226.0/24; 192.162.199.0/24; 196.251.107.0/24; 196.251.122.0/24 (announced 2026-09-25; all on Spamhaus DROP)</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>United Kingdom (shell)</t>
@@ -1463,7 +1473,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Artur Mikhailovich Vovk (DOB 1988-09-12 Rohatyn UA)</t>
+          <t>Artur Vovk (director, per RF)</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1478,7 +1488,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>High malicious traffic ratio; No route diversification; Shell company structure</t>
+          <t>Spamhaus ASN-DROP (AS214351); Self-advertised abuse-resilient hosting; High malicious traffic ratio; No route diversification; Shell company structure</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1488,17 +1498,22 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>RF 2025 top-10 (#8, as Defhost)</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>RF-TAE-2026; RF-AUROLOGIC</t>
+          <t>RF-TAE-2026; RF-AUROLOGIC; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>UK shell running defhost.co BPH brand. 2 /24 prefixes via aurologic GmbH AS30823. Shodan: 1142 servers in Germany. Hosts C2/loader infrastructure for 15+ malware families. Payment via Heleket.com; clustered with qckl.net/qckl.host.</t>
+          <t>UK shell (incorporated 2024-08-08; AS214351 allocated seven days later) that RF Insikt assesses with high confidence to be under the control of the Defhost BPH brand, which advertises 'fast abusive VPS/VDS' resilient against Western law enforcement. Payment via Heleket.com, shared across the cluster. Hosts C2 and loader infrastructure for 15+ malware families. RF ranks Defhost #8 in its 2025 Threat Density top 10 and AS214351 is on Spamhaus ASN-DROP (domain as214351.com). Tier raised T2 -&gt; T1 on 2026-09-25 (taxonomy T1: self-advertised bulletproof with corroborating infrastructure evidence; RF top-decile density). Announced space grew from 2 /24s (62.60.226.0/24, 176.46.152.0/24 at RF publication) to 4 /24s now; 176.46.152.0/24 has moved to an unrelated Iranian network. The unsourced date and place of birth previously given for the director were removed.</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1525,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>flagged</t>
+          <t>dissolved</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1520,17 +1535,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AS216309</t>
+          <t>AS216309 (historical; reassigned to InvisionTech Group S.r.l. [IT] - do not block)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Russia (conflicting)</t>
+          <t>Germany-hosted (Tornado DC, Langen) behind aurologic; operator Russia-linked</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1540,7 +1555,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>EVILEMPIRE</t>
+          <t>EVILEMPIRE; Lethost</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1555,32 +1570,37 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Doppelganger disinformation</t>
+          <t>Doppelganger influence operation</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>abuse.ch ASN-DROP listed; Doppelganger infrastructure</t>
+          <t>Doppelganger infrastructure; aurologic downstream</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>ASN-DROP inclusion; High malicious traffic ratio; Conflicting geolocation</t>
+          <t>Historical Spamhaus ASN-DROP listing (Feb 2024 snapshot); High malicious traffic ratio; ASN since reassigned</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>ABUSECH-FEEDS; HYAS-RISEPRO; QURIUM-DOPPELGANGER; RF-AUROLOGIC</t>
+          <t>ABUSECH-FEEDS; HYAS-RISEPRO; QURIUM-DOPPELGANGER; RF-AUROLOGIC; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>abuse.ch ASN-DROP list flags 'do not route or peer — under cybercriminal control.' HYAS April 2024 flagged for unusually high malware activity. Qurium tied to Doppelganger disinformation. AS-level block recommended.</t>
+          <t>UK-registered (RIPE org TNSECURITY LTD, GB) network that announced 185.172.128.0/24 via AS216309 (as-name EVILEMPIRE-AS) behind aurologic; Qurium tied hundreds of Doppelganger domains to 185.172.128.161 between Oct 2023 and Jul 2024. AS216309 was on Spamhaus ASN-DROP in the Feb 2024 snapshot, but not in Dec 2025 or now. The ASN has since been re-issued to InvisionTech Group S.r.l. (IT) and the Doppelganger IP now sits in an unrelated Russian network, so the entity is no longer identifiable as a live network - status set to 'dissolved' (network defunct) on 2026-09-25. Do not block AS216309. Corrections: registration is UK, not Germany (Germany is where servers sat); ASN-DROP is a Spamhaus list, not abuse.ch.</t>
         </is>
       </c>
     </row>
@@ -1597,22 +1617,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T2-High Risk</t>
+          <t>T1-Confirmed BPH</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AS214943</t>
+          <t>AS214943 (registered to Railnet LLC; dark since ~2026-02)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AS202412 (OMEGATECH / Omegatech LTD [SC]; live Virtualine network, Spamhaus ASN-DROP under virtualine.org)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>United States (Kentucky LLC)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Russia-linked operator; EU-hosted infrastructure</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1622,12 +1647,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Virtualine Technologies; RAILNET</t>
+          <t>Virtualine Technologies; RAILNET; OMEGATECH; DripHosting/DiorHost; RetryHost</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>aurologic GmbH (AS30823)</t>
+          <t>aurologic GmbH (AS30823) (~95% of prefixes, Aug 2025); Pfcloud UG (AS51396) (one /24)</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1652,27 +1677,27 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Underground forum presence; High malicious traffic ratio; No route diversification</t>
+          <t>Spamhaus ASN-DROP (AS202412 under virtualine.org; AS214943 and AS214940 listed under virtualine.org in Dec 2025); Underground forum advertising; High malicious traffic ratio</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>~20% (highest in RF chart)</t>
+          <t>RF 2025 top-10 (#1, as Virtualine)</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>RF-TAE-2026; GBHACKERS-BPH; TEAMCYMRU-VIRTUALINE; SPAMHAUS-BPH; RF-AUROLOGIC</t>
+          <t>RF-TAE-2026; GBHACKERS-BPH; TEAMCYMRU-VIRTUALINE; SPAMHAUS-BPH; RF-AUROLOGIC; SPAMHAUS-ASNDROP-2026; INTRINSEC-OMEGATECH-2026; INTRINSEC-UAC-2025; REGISTRY-SNAPSHOT-2026-09; INTRINSEC-FDN3-2025</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Operated by Virtualine Technologies. Advertised on Russian-language underground forums for phishing/spam enablement. GBHackers tied to UAC-0050 and UAC-0006 infrastructure shifts against Ukrainian banking and energy. RF Threat Density chart shows Virtualine as #1 highest risk TAE in 2025. | Merged record (was a duplicate AS214943 row): Virtualine Technologies is the operator behind Railnet LLC; per RF TAE case study it shifted IPv4 resources to metaspinner net GmbH in April 2025 and became a primary distribution hub for Latrodectus and AsyncRAT.</t>
+          <t>Virtualine Technologies is the operator behind Railnet LLC (AS214943, Kentucky LLC), KPROHOST (AS214940), the 'metaspinner' AS209800 front, likely Karina Rashkovska (AS215789) and now OMEGATECH (AS202412) - at least five number-resource identities. Advertised on Russian-language forums for phishing/spam enablement ('DMCA &amp; Abuse Ignored'). RF ranked Virtualine #1 by Threat Density for 2025; Intrinsec documented UAC-0050/UAC-0006 activity on its infrastructure and, in May 2026, assessed OMEGATECH as 'yet another network created by Virtualine' (642k+ honeypot hits in March 2026). In April 2025 it shifted IPv4 resources to the 'metaspinner' AS209800; those ranges now sit on AS202412. AS214943 has announced nothing since ~2026-02 and was dropped from ASN-DROP; OMEGATECH is the live network (15 /24s, 13 on Spamhaus DROP). Tier raised T2 -&gt; T1 on 2026-09-25 (taxonomy T1: RF top-decile density; forum BPH advertising with infrastructure evidence; 3+ independent vendors). | Merged record (was a duplicate AS214943 row).</t>
         </is>
       </c>
     </row>
@@ -1697,9 +1722,14 @@
           <t>AS213702</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AS218731 (Spamhaus ASN-DROP under qwins.co; 35 IPv4 prefixes); AS214422 (NET67X; Spamhaus ASN-DROP under qwins.co; no routes)</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>141.98.6.0/24</t>
+          <t>141.98.6.0/24; 93.123.39.0/24</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1734,7 +1764,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Shell company structure; No KYC (Telegram bot ~$2/mo); High malicious traffic ratio</t>
+          <t>Spamhaus ASN-DROP (AS213702; AS218731; AS214422 under qwins.co); Shell company structure; No KYC (Telegram bot ~$2/mo); High malicious traffic ratio</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -1744,17 +1774,17 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>INTEL-INSIGHTS-QWINS</t>
+          <t>INTEL-INSIGHTS-QWINS; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Incorporated Nov 11 2024 UK. Cheap VPS via Telegram bot (~$2/mo). Nominee director pattern (6-month tenure). Vasilis Orlof tied AS213702 to multiple malware families via 141.98.6.0/24.</t>
+          <t>UK shell (reported incorporated 2024-11-11) selling cheap VPS via a Telegram bot (~$2/mo), with a six-month nominee director. Vasilis Orlof tied AS213702 to multiple malware families via 141.98.6.0/24. Spamhaus ASN-DROP now lists three ASNs under qwins.co: AS213702, AS218731 (newly listed; registered to an individual in Latvia; announces 35 IPv4 prefixes) and AS214422 (NET67X; no routes). Third parties give UK company no. 16072422 and link QWINS to the Aeza UK-shell network (single source, unverified).</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1796,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>suspected</t>
+          <t>flagged</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1796,7 +1826,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Black Basta; Cactus ransomware</t>
+          <t>Gamaredon (C2 hosting, 2023); SilkParasite (SpiceRAT C2, 2026 - IP-to-ASN mapping); UAC-linked activity (Intrinsec)</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Gamaredon tooling; SpiceRAT</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1809,19 +1844,24 @@
           <t>Shell company structure; No route diversification; Ransomware C2</t>
         </is>
       </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>GBHACKERS-BPH</t>
+          <t>GBHACKERS-BPH; ESET-GAMAREDON-IOC; INTRINSEC-UAC-2025; HUNTIO-SILKPARASITE-2026; REGISTRY-SNAPSHOT-2026-09; INTRINSEC-FDN3-2025</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>UK LLP (OC450701 ~2024) operating AS215540. ~176 prefixes / ~41K IPs. Routing conduit for Black Basta and Cactus ransomware C2 via Stark Industries AS44477. Fits Russia-linked UK-LLP BPH pattern.</t>
+          <t>UK LLP operating AS215540: 181 IPv4 prefixes / 62,720 addresses plus 24 IPv6 prefixes (2026-09-25; the earlier '~176 / ~41K' is outdated). ESET lists Gamaredon infrastructure on GCSAS addresses first seen Aug-Sep 2023. Intrinsec named GCSAS in its March 2025 UAC-infrastructure report and in Aug 2025 among shell-fronted networks announcing prefixes moved out of the FDN3 cluster. A SpiceRAT C2 active in March 2026 (Hunt.io, SilkParasite campaign; 171.22.16.187) maps to AS215540 by our own IP-to-ASN lookup. Status raised suspected -&gt; flagged (two independent B-grade sources). Unverified and retained with caution: LLP number OC450701; Black Basta/Cactus C2 routing via Stark AS44477. Not on Spamhaus ASN-DROP.</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1873,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>flagged</t>
+          <t>dissolved</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1843,12 +1883,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AS215789</t>
+          <t>AS215789 (historical; reassigned to BLIK / Polski Standard Platnosci SA [PL] - do not block)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>147.45.44.0/24 (CH); 82.115.223.0/24 (NL)</t>
+          <t>Historical: 147.45.44.0/24 (now AS202799 SYSECT); 147.45.47.0/24; 82.115.223.0/24 (now AS214927 PSB Hosting, on Spamhaus ASN-DROP)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1873,7 +1913,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>aurologic GmbH</t>
+          <t>aurologic GmbH; assessed part of the Virtualine cluster</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1883,32 +1923,32 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Single-maintainer shell; No route diversification</t>
+          <t>Single-maintainer shell; Virtualine sub-network (UAC-0050 spam)</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>No route diversification; Shell entity; High malicious traffic ratio</t>
+          <t>ASN since reassigned; historical RisePro C2 hosting</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2024-01-03</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>HYAS-RISEPRO; RF-AUROLOGIC</t>
+          <t>HYAS-RISEPRO; RF-AUROLOGIC; REGISTRY-SNAPSHOT-2026-09; INTRINSEC-UAC-2025</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>RIPE-registered Jan 3 2024 to individual at Vysoke 53200 Dnipropetrovska UA. Upstream: aurologic AS30823. HYAS flagged for RisePro stealer C2. 2223 domains across 72 IPs. Classic aurologic-downstream single-maintainer shell.</t>
+          <t>Individual-registered RIPE network (2024) behind aurologic that HYAS (Apr 2024) flagged for RisePro stealer C2 (147.45.47.93); Intrinsec (via a third party) ties AS215789 to Virtualine's UAC-0050 spam. AS215789 has since been returned and re-issued to BLIK / Polski Standard Platnosci SA (PL), which announces nothing from it - do not block AS215789. Its former prefixes now originate from SYSECT D.O.O. (AS202799, ME) and PSB Hosting Ltd (AS214927, on Spamhaus ASN-DROP under psb.hosting) - successor-watch leads, not attribution. Status set to 'dissolved' (registration defunct) on 2026-09-25. Unverified: the exact 2024-01-03 date and the '2223 domains across 72 IPs' figure.</t>
         </is>
       </c>
     </row>
@@ -1933,9 +1973,14 @@
           <t>AS14956</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AS200038 (Cloudzy A I Information Technology L.L.C [AE]; registered, no routes)</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>United States (Wyoming shell)</t>
+          <t>United States (incorporated; Wyoming unverified)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1955,17 +2000,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Hannan Nozari</t>
+          <t>Hassan Nozari</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>APT10; APT33/34; Kimsuky/BlueNoroff; APT29/Turla; Candiru spyware; Ghost Clown; Space Kook</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>EvilProxy AiTM</t>
+          <t>APT10; Sidewinder; APT33; APT34; Kimsuky; Konni; Lazarus; Transparent Tribe; APT29; Turla; OceanLotus; Evil Corp; FIN12; Ghost Clown (Black Basta); Space Kook (Royal); Candiru</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1975,34 +2015,34 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>No KYC; Anonymous crypto RDP VPS; Shell company structure; High malicious traffic ratio (40-60%)</t>
+          <t>No KYC; Anonymous crypto RDP VPS; Shell company structure; Halcyon: potentially 40-60% of activity malicious; Historical Spamhaus ASN-DROP listing (Dec 2025; delisted by Sep 2026)</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>HALCYON-CLOUDZY; FLARE-CLOUDZY</t>
+          <t>HALCYON-CLOUDZY; FLARE-CLOUDZY; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Wyoming-incorporated C2P exposed by Halcyon Aug 2023 as operational front for Iranian firm abrNOC (Tehran). 40-60% of infrastructure supports malicious activity. Used by multiple nation-state APTs.</t>
+          <t>US-incorporated command-and-control provider that Halcyon (Aug 2023) exposed as an operational front for the Iranian firm abrNOC (Tehran), estimating that potentially 40-60% of its overall activity could be malicious. Used by a long list of state and criminal actors (see associated_threat_actors; BlueNoroff is not in Halcyon's list). AS14956 (RouterHosting) still announces 66 IPv4 prefixes; it was on Spamhaus ASN-DROP (cloudzy.com) in Dec 2025 and has since been delisted. A UAE registration, AS200038, has no routes. Corrections 2026-09-25: operator name is Hassan (not Hannan) Nozari; the unsourced EvilProxy link was removed.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>metaspinner net GmbH</t>
+          <t>metaspinner-named AS209800 (Virtualine front)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>suspected</t>
+          <t>dissolved</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2012,22 +2052,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AS209800</t>
+          <t>AS209800 (historical; reassigned to ZEMA GbR [DE] - do not block)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Germany (registration used the name of a legitimate company)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Germany-hosted behind aurologic</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>metaspinner net GmbH</t>
+          <t>None verified - RF says Virtualine-affiliated actors controlled AS209800 and impersonated the legitimate Hamburg firm metaspinner net GmbH, which is not the operator</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>metaspinner; LANEDONET (Oct 2025 prefix re-description)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2042,27 +2087,32 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Prefix migration recipient from Virtualine</t>
+          <t>Prefix migration recipient from Virtualine; Name impersonation of a legitimate company</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>No route diversification; Malicious traffic migration indicator</t>
+          <t>Impersonated corporate identity; No route diversification; ASN since reassigned</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>RF-TAE-2026; RF-AUROLOGIC; KREBS-BPH</t>
+          <t>RF-TAE-2026; RF-AUROLOGIC; KREBS-BPH; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Insikt-named aurologic downstream. Co-resident on AS30823 transit cluster. Krebs comments noted malicious traffic migration from Virtualine AS214943 to AS209800.</t>
+          <t>AS209800 was created 2025-04-25 and announced solely via aurologic; RF Insikt says it was controlled by Virtualine-affiliated actors who impersonated the long-standing legitimate Hamburg company metaspinner net GmbH (RENAMED 2026-09-25 so the row no longer names that company as the operator). Its prefixes (91.92.240.0/22, 158.94.208.0/22, 178.16.52.0/22) received Virtualine traffic from April 2025 and now originate from OMEGATECH AS202412 (see the Railnet/Virtualine row). The ASN has been re-issued to an unrelated German GbR (ZEMA) - do not block AS209800. Status set to 'dissolved' (network defunct).</t>
         </is>
       </c>
     </row>
@@ -2074,17 +2124,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>suspected</t>
+          <t>flagged</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>T3-Suspected</t>
+          <t>T2-High Risk</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AS214940</t>
+          <t>AS214940 (dark since ~2026-08)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2099,27 +2149,27 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>KPRONET</t>
+          <t>KPRONET; Virtualine network (Intrinsec; Spamhaus Dec 2025)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>aurologic GmbH (AS30823)</t>
+          <t>Pfcloud UG (AS51396) and AS215436 (peers); IPv6 via AS43641</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>aurologic GmbH</t>
+          <t>Virtualine cluster</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Shell company; Gmail abuse contact; aurologic downstream</t>
+          <t>Shell company; Gmail abuse contact; Virtualine sub-network</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>Shell company structure; No route diversification; Gmail abuse contact</t>
+          <t>Shell company structure; Gmail abuse contact; Historical Spamhaus ASN-DROP listing under virtualine.org (Dec 2025)</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -2129,17 +2179,17 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>RF-AUROLOGIC; RIPE-DB</t>
+          <t>RF-AUROLOGIC; RIPE-DB; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09; INTRINSEC-FDN3-2025</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>RIPE-registered 2024-05-10 by KPROHOST LLC (Frankfort KY). 2 /24 IPv4 + 1 /48 IPv6. Abuse contact kprohost.abuse@gmail.com. Upstream relationship with aurologic cluster.</t>
+          <t>RIPE-registered 2024-05-10 by KPROHOST LLC (Frankfort, KY; Kentucky reg. 1360766); abuse contact kprohost.abuse@gmail.com. Intrinsec attributes AS214940 to Virtualine, and Spamhaus listed it under virtualine.org in Dec 2025 (since delisted). Its two historical /24s (195.211.191.0/24, 45.144.212.0/24) now originate from HBING (AS208949) and Pfcloud (AS51396). The ASN has announced nothing since ~2026-08-12. Tier raised T3 -&gt; T2 on 2026-09-25 (shell structure; part of a T1 operator; blocklisting). Correction: its upstreams were Pfcloud and AS215436, not aurologic.</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2201,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>suspected</t>
+          <t>flagged</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>T3-Suspected</t>
+          <t>T2-High Risk</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AS209946 (ALINDA LLC [UA]; Spamhaus ASN-DROP under altawk.com)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AS203727 (historical; reassigned to byon GmbH [DE] - do not block); AS215826 (Partner Hosting LTD [GB]; listed under altawk.com in Dec 2025, delisted)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2166,7 +2226,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Europe shell</t>
+          <t>Geolocated Finland/Sweden; servers at Tornado DC (Langen) behind aurologic</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2196,22 +2256,22 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>No route diversification; Russia-linked</t>
+          <t>Spamhaus ASN-DROP (AS209946 under altawk.com); Russia-linked; aurologic downstream</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>QURIUM-DOPPELGANGER; RF-AUROLOGIC</t>
+          <t>QURIUM-DOPPELGANGER; RF-AUROLOGIC; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Named by Qurium + Insikt as aurologic-downstream Russia-linked infrastructure enabler tied to Doppelganger disinformation network.</t>
+          <t>Named by Qurium as Russia-linked infrastructure behind aurologic serving the Doppelganger disinformation network, historically on AS203727 (now re-issued to byon GmbH - do not block). Spamhaus now lists AS209946 (ALINDA LLC, UA) under altawk.com; it announces 4 prefixes, all on Spamhaus DROP. An earlier Altawk-domain ASN, AS215826, was listed in Dec 2025 and later removed. Tier raised T3 -&gt; T2 on 2026-09-25 (ASN-DROP inclusion plus Qurium).</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2283,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>suspected</t>
+          <t>flagged</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2233,27 +2293,32 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>AS208046</t>
+          <t>AS197170 (TECHTIES-AS, TechTies Inc. [SC]; Spamhaus ASN-DROP under hostslick.de)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AS208046 (historical; ColocationX Ltd; reassigned to a French individual - do not block)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>Seychelles (AS197170 holder); Netherlands (historical operations)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>hostslick.com</t>
+          <t>hostslick.com; hostslick.de</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>ColocationX (upstream)</t>
+          <t>Historical: WorldStream (AS49981), ColocationX was the AS holder</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2263,22 +2328,22 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Underground forum presence; DMCA-ignored marketing</t>
+          <t>Spamhaus ASN-DROP (AS197170 under hostslick.de); Underground forum presence; DMCA-ignored marketing</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>OSINT-FORUMS</t>
+          <t>OSINT-FORUMS; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Netherlands offshore host advertising on LowEndTalk cracked.io BlackHatWorld BreachForums. Self-advertises DMCA Ignored. Operator transparent that abuse tolerance tracks pricing tier.</t>
+          <t>Offshore host advertising on LowEndTalk, cracked.io, BlackHatWorld and BreachForums, self-described 'DMCA Ignored', with abuse tolerance tied to pricing tier (marketing evidence, grade E). Spamhaus now lists AS197170 (TechTies Inc., SC) under hostslick.de; it announces 13 IPv4 /24s, all on Spamhaus DROP. The earlier AS208046 was ColocationX Ltd's network (a HostSlick VPS sat there in Nov 2023) and has been re-issued - do not block it. Held at T3 (status flagged): ASN-DROP inclusion would normally escalate to T2, but only one independent B/C source supports it.</t>
         </is>
       </c>
     </row>
@@ -2303,6 +2368,11 @@
           <t>AS30823</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AS43043 (AUROLOGIC-CLOUD)</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>Germany</t>
@@ -2320,12 +2390,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>combahton GmbH (predecessor); fastpipe.io</t>
+          <t>fastpipe.io; combahton GmbH (predecessor network)</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>CEO Hofmann</t>
+          <t>CEO Joseph Maximilian Hofmann (also CEO of Tornado Datacenter GmbH)</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2335,27 +2405,27 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>High malicious traffic ratio (top-10 globally); Upstream for multiple T1-T2 entities</t>
+          <t>Upstream for multiple T1-T2 entities (RF: ~70% of prominent high-risk TAEs); Not on Spamhaus ASN-DROP</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>RF-AUROLOGIC; RF-TAE-2026</t>
+          <t>RF-AUROLOGIC; RF-TAE-2026; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Central upstream hub for Europe's high-risk hosting ecosystem. Formed Oct 2023 from combahton GmbH's fastpipe.io. 1-5 Tbps at Tornado Datacenter GmbH Langen. Remains primary upstream for Aeza despite sanctions. Downstream cluster: Femo IT Railnet/Virtualine SWISSNETWORK02 metaspinner Tnsecurity WAIcore Altawk Karina Rashkovska KPROHOST. Top-10 globally by malicious activity concentration.</t>
+          <t>Central upstream for Europe's high-risk hosting ecosystem. RF: formed in 2023 following the transition of combahton GmbH's fastpipe (combahton announced the transition in Nov 2023); multi-terabit backbone at Tornado Datacenter, Langen. RF's 2025 review says it transits about 70% of the most prominent high-risk TAE networks, and ~50% of Aeza's announced prefixes ran via aurologic (Nov 2025). Downstreams named by RF: Femo IT/Defhost, Global-Data (SWISSNETWORK02), the metaspinner-named front, Railnet/Virtualine and Aeza; Qurium adds Tnsecurity, WAIcore and Altawk. Corrections 2026-09-25: the 'top-10 globally' ranking belongs to SWISSNETWORK02, not aurologic; the '1-5 Tbps' figure is unsourced; KPROHOST is not an aurologic downstream. Several named downstreams have since gone dark or had their ASNs re-issued.</t>
         </is>
       </c>
     </row>
@@ -2382,57 +2452,57 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Russia / Estonia shell / Moscow-City</t>
+          <t>Russia (Moscow / St. Petersburg); originally Estonia-registered (licence revoked Feb 2022)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Garantex</t>
+          <t>Garantex Europe OU</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Grinex; Exved; InDeFi Bank; A7A5; MKAN Coin</t>
+          <t>Garantex; garantex.org / .io</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>OFAC April 5 2022; EU 16th package Feb 24 2025 (first EU crypto-exchange listing; 6 wallet addresses); servers/domains seized March 2025; OFAC re-designation Aug 14 2025 expanded to Grinex Exved InDeFi Bank A7A5</t>
+          <t>OFAC April 5 2022 (with Hydra Market); EU 16th package Feb 24 2025 (first EU crypto-exchange listing; 6 wallet addresses); domains seized March 6 2025 (USSS with NL/DE/EE/FI) and E.D. Va. indictment of Besciokov and Mira Serda unsealed March 7 2025; OFAC Aug 14 2025 re-designation of Garantex Europe OU alongside successor Grinex, executives and six related companies</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Mira Serda ($5M State Dept reward)</t>
+          <t>Aleksandr Mira Serda (co-founder/CCO; State Dept reward up to $5M); Sergey Mendeleev (co-founder); Pavel Karavatsky (co-founder); Aleksej Besciokov (technical administrator; indicted; arrested in India ~2025-03-11)</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Sanctions evasion; Successor spawning</t>
+          <t>Sanctions evasion; Successor spawning (Grinex)</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Sanctioned personnel; Evading via successor entities</t>
+          <t>Sanctioned entity and personnel; Evading via successor entity</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>OFAC-GARANTEX; CHAINALYSIS-OFAC; CHAINALYSIS-BPH</t>
+          <t>OFAC-GARANTEX; CHAINALYSIS-OFAC; CHAINALYSIS-BPH; DOJ-GARANTEX-2025</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Foundational payment rail for BPH ecosystem. Zservers Aeza Media Land received proceeds via Garantex wallets. Post-takedown successors: ABCeX Rapira Exmo Aifory Pro Bitpapa MKAN Coin.</t>
+          <t>Cryptocurrency exchange founded 2019 (not a mixer; the 'EUR 1.3B since 2016' figure belongs to Cryptomixer). DOJ: processed at least $96B since 2019. Foundational payment rail for the BPH/ransomware ecosystem - Zservers, Aeza and Media Land proceeds moved through Garantex wallets. The US Secret Service seized garantex.org/.io/.academy around 2025-03-06 and DOJ unsealed charges; Grinex (Kyrgyzstan, registered Dec 2024) became the successor. The Aug 2025 OFAC action also designated Exved and InDeFi Bank (Mendeleev-linked payment firms) and the A7 network (A7 LLC, A71 LLC, A7 Agent LLC, Old Vector LLC) - related entities, not aliases. In May 2026 the UK designated Exmo, Rapira, Bitpapa and ABCeX (Nueva Cryptologia), so earlier 'active successor' labels for those venues are outdated; MKAN Coin is unverified.</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2529,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Canada (company); United States (ARIN registry country for AS53667)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2494,17 +2564,17 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>OSINT-REVIEWS</t>
+          <t>OSINT-REVIEWS; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Canadian low-cost VPS provider. Operates data centers in Las Vegas and Luxembourg. Permits Tor exit relays. AUP formally prohibits malicious content but abuse response is slow. Scamalytics 40/100 fraud score.</t>
+          <t>Low-cost VPS provider (AS53667, PONYNET) with data centres in Las Vegas and Luxembourg. Permits Tor exit relays. AUP formally prohibits malicious content but abuse response is slow. Scamalytics 40/100 fraud score. AS53667 appears in maltrail's worst-ASN list; it is not on Spamhaus ASN-DROP. Founding year and fraud score are unverified.</t>
         </is>
       </c>
     </row>
@@ -2529,9 +2599,14 @@
           <t>AS200019</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AS207636 (ALEXHOST-SRL)</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>176.123.0.0/16; 37.221.64.0/19</t>
+          <t>176.123.0.0/21; 176.123.8.0/22; 37.221.65.0/24; 37.221.67.0/24 (78 prefixes / 44,800 addresses in total, 2026-09-25)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2554,6 +2629,11 @@
           <t>Voxility (DDoS mitigation)</t>
         </is>
       </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Dark Caracal (Bandook C2, 2026); Cl0p (Cleo campaign callback infrastructure, Dec 2024)</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr">
         <is>
           <t>DMCA-ignored marketing; Offshore jurisdiction; Crypto payment</t>
@@ -2566,17 +2646,17 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>STISC-ALEXHOST</t>
+          <t>STISC-ALEXHOST; ARCTICWOLF-DARKCARACAL-2026; HUNTRESS-CLEO-2024; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Moldovan offshore hoster in former Soviet bomb shelter. Markets DMCA-ignored hosting. Named in STISC reporting after 1330-email phishing wave spoofing Moldovan government. Expanded footprint to NL SE BG CH DE FR UK RO.</t>
+          <t>Moldovan offshore hoster marketing DMCA-ignored hosting (Silent Push: ~10,000 active IPs and 400+ malicious domains in an 8-day sample). Named in STISC reporting after a 1,330-email phishing wave spoofing the Moldovan government. Arctic Wolf (Aug 2026): Dark Caracal's Bandook C2s were hosted on AlexHost, 'a provider previously associated with Dark Caracal'. Cl0p's Cleo campaign (Dec 2024) used AlexHost addresses (176.123.5.126 per Huntress). Do not conflate with the Russian 'Alex Host LLC' that Intrinsec ties to the FDN3 cluster. Correction 2026-09-25: the former known_prefixes (176.123.0.0/16; 37.221.64.0/19) overstated AlexHost's space - most of those ranges belong to other networks. Unverified: the 'former Soviet bomb shelter' claim.</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2673,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T4-Gray Zone</t>
+          <t>T3-Suspected</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2601,19 +2681,24 @@
           <t>AS51852</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AS52288 (PRIVATE-LAYER; registered, no routes)</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Panama (Private Layer INC is the registry holder of AS51852 and AS52288)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Switzerland (marketed); unverified</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Private Layer AG</t>
+          <t>Private Layer INC</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2638,17 +2723,22 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>RF 2025 top-10 (#6, as PrivateAlps)</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>RF-TAE-2026</t>
+          <t>RF-TAE-2026; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Swiss-jurisdiction offshore brand with ties to Private Layer AG. Markets fully DMCA ignored no-logs anonymous registration Monero-friendly. Swiss non-EU jurisdiction provides compliance cushion.</t>
+          <t>Swiss-marketed offshore brand (privatealps.net) of Private Layer INC (Panama registry holder of AS51852/AS52288), marketing DMCA-ignored, no-logs, anonymous, Monero-friendly hosting. RF ranks PrivateAlps #6 in its 2025 Threat Density top 10, and RF's aurologic report ties Global-Data System IT (SWISSNETWORK02) to PrivateAlps. Tier raised T4 -&gt; T3 on 2026-09-25: a top-10 density ranking is inconsistent with T4's 'not predominantly malicious'; T2/T1 would need further independent evidence (not on Spamhaus ASN-DROP). Correction: registry entity is Private Layer INC (Panama), not Private Layer AG (Switzerland).</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2765,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Iceland (FlokiNET ehf, registry holder of AS200651)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2685,7 +2775,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Floki Network Services Ltd</t>
+          <t>FlokiNET ehf</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2700,17 +2790,17 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>TRENDMICRO-INTERPOL</t>
+          <t>TRENDMICRO-INTERPOL; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Commercialized free-speech BPH brand with multi-jurisdiction presence. Trend Micro/Interpol 2023-named (13% of Africa offshore BPH sourcing). Explicit uncensored hosting marketing.</t>
+          <t>Commercialized free-speech hosting brand with a multi-jurisdiction presence (Romania, Finland, Iceland); explicit uncensored-hosting marketing. Trend Micro/Interpol 2023 reportedly attributed 13% of Africa-related offshore BPH sourcing to FlokiNET (figure unverified). Correction 2026-09-25: the registry holder is FlokiNET ehf (Iceland); the earlier Seychelles / 'Floki Network Services Ltd' details are unverified.</t>
         </is>
       </c>
     </row>
@@ -2752,7 +2842,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Shinjiru MSC Sdn Bhd</t>
+          <t>Shinjiru Technology Sdn Bhd</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2777,17 +2867,17 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>SPAMHAUS-BPH; OSINT-FORUMS</t>
+          <t>SPAMHAUS-BPH; OSINT-FORUMS; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>20+ year veteran Malaysian offshore host. 8 jurisdictions. Markets DMCA-ignored hosting. Spamhaus flagged unnamed Malaysia-based ISP matching Shinjiru profile. Non-response to phishing/malware abuse complaints.</t>
+          <t>Veteran Malaysian offshore host (APNIC holder Shinjiru Technology Sdn Bhd; AS45839 announces 16 IPv4 prefixes, 5 overlapping Spamhaus DROP). Markets DMCA-ignored hosting across several jurisdictions; Silent Push reports a 12-day abuse response and a 10-day grace period. Spamhaus flagged an unnamed Malaysia-based ISP matching Shinjiru's profile. Unverified: founding year (~2003) and the eight-jurisdiction count.</t>
         </is>
       </c>
     </row>
@@ -2809,7 +2899,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AS49042</t>
+          <t>AS49042 (historical; deregistered)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2829,7 +2919,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Phanes Cloud; Flaunt7 (predecessor); SpectraIP</t>
+          <t>Phanes Cloud; Flaunt7 (predecessor)</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>SpectraIP (AS62068/AS218878; single peering partner per Silent Push)</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2849,17 +2944,17 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>OSINT-REVIEWS</t>
+          <t>OSINT-REVIEWS; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Dutch hoster at Keteldiep 15 Urk. Rebranded from Flaunt7. Trustpilot reviews document unresponsive abuse handling for phishing complaints.</t>
+          <t>Dutch hoster (reported address Keteldiep 15, Urk) rebranded from Flaunt7. AS49042 was historically 'Phanes Networks B.V.' and is now absent from the registry and routing data. Silent Push reports 'bulletproof' in Phanes' marketing and a 4-day abuse response; Trustpilot reviews document unresponsive handling of phishing complaints. SpectraIP is its peering partner, not an alias. SKB Enterprise B.V. held a separate ASN (AS64425) and its relationship to Phanes is unverified.</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2966,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>sanctioned</t>
+          <t>evading</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2881,7 +2976,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AS44477 (post-transfer)</t>
+          <t>AS44477 (historical; received 2025-05-16; withdrawn from routing ~2026-04 and deregistered)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2901,22 +2996,22 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>PQ Hosting successor; Neculiti brothers</t>
+          <t>PQ.Hosting successor entity; WEISS HOSTING GROUP S.R.L. (Neculiti-linked LIR)</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Stark Industries Solutions (predecessor)</t>
+          <t>PQ.Hosting (Neculiti) - RF: PQ.Hosting was Stark's parent</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>EU May 20 2025 (via Stark/Neculiti designation under Hybrid Threats Regulation (EU) 2024/2642)</t>
+          <t>Not designated: PQ Hosting Plus S.R.L. is absent from Annex I of Reg. (EU) 2024/2642 (only the 'PQ Hosting' brand/pq.hosting appears inside Stark's entry); exposure arises indirectly via ownership/control by EU-listed Ivan Neculiti</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Ivan Neculiti; Iurie Neculiti</t>
+          <t>Ivan Neculiti; Iurie Neculiti (EU-listed); RIPE maintainer attributed by RF to Dmitrii Miasnikov</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2929,19 +3024,24 @@
           <t>Sanctioned personnel; Rapid rebranding</t>
         </is>
       </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>RF-TAE-2026; EU-STARK</t>
+          <t>RF-TAE-2026; EU-STARK; RF-STARK</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Moldova-registered Stark Industries successor entity. Holds AS44477 after pre-sanctions transfer. Same beneficial ownership (Neculiti brothers — EU-sanctioned).</t>
+          <t>Moldova-registered LIR (ORG-PHPS1-RIPE, Chisinau, created 2025-05-13) that received AS44477 from Stark Industries on 2025-05-16, four days before the EU listing. RF: 'although PQ.Hosting was referenced within the sanctions multiple times... the company itself was not sanctioned' - status corrected sanctioned -&gt; evading on 2026-09-25 (T1 retained: sanctioned beneficial owners; sanctions-evasion vehicle). ELLIO reports AS44477 has not been visible in the global routing table since about 2026-04-16; the ASN is now deregistered and was never on Spamhaus ASN-DROP. Successor capacity sits with WorkTitans/THE.Hosting and UFO Hosting.</t>
         </is>
       </c>
     </row>
@@ -2983,7 +3083,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>YuFO Hosting; ufo.hosting</t>
+          <t>YuFO Hosting; ufo.hosting; GEO.Hosting (linked brand, D-grade)</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2991,11 +3091,6 @@
           <t>Stark Industries Solutions (prefix recipient)</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>StormWall (DDoS fronting)</t>
-        </is>
-      </c>
       <c r="O31" t="inlineStr">
         <is>
           <t>Savushkin Mikhail Yuryevich</t>
@@ -3008,7 +3103,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Shell company structure; Rapid infrastructure migration</t>
+          <t>Spamhaus ASN-DROP (AS33993 under stark-industries.solutions); Shell company structure; Rapid infrastructure migration</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -3018,17 +3113,17 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>RF-STARK</t>
+          <t>RF-STARK; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Russia-based ISP RIPE-registered March 13 2025. Identified as sanctions-resilient vehicle for Stark Industries Russian prefix migration beginning April 10 2025. AS33993 announced 21 prefixes.</t>
+          <t>Russian ISP (company registered 2025-02-18; INN 5043089443; Chekhov district, Moscow region) whose RIPE org was created 2025-03-13. RF identified it as the sanctions-resilient vehicle for Stark Industries' Russian prefixes, with most transfers on 2025-04-13. AS33993 announced 21 prefixes as of 2025-05-16 and 27 today; Spamhaus lists it under stark-industries.solutions. Russian-language sources report THE.Hosting, UFO.Hosting and GEO.Hosting customers losing VPSs around the May 2026 raid (D-grade). Correction 2026-09-25: StormWall s.r.o. provided DDoS-protection fronting for Stark/PQ domains; it is not a BGP upstream.</t>
         </is>
       </c>
     </row>
@@ -3053,6 +3148,11 @@
           <t>AS52000</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AS206932 (MIRHOSTING-NL)</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>Netherlands</t>
@@ -3070,7 +3170,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Innovation IT Solutions Corp; Nesterenko</t>
+          <t>mirhosting.com; Innovation IT Solutions Corp (related company)</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3090,22 +3190,22 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>~2008</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>KREBS-BPH; RF-INFRA-2025; GREYNOISE-STARK; KREBS-FIOD-STARK</t>
+          <t>KREBS-BPH; RF-INFRA-2025; GREYNOISE-STARK; KREBS-FIOD-STARK; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Operated by Andrey Nesterenko (arrested in the FIOD raid of May 18 2026). Historically hosted StopGeorgia.ru (2008 Russia-Georgia cyberwar). Netherlands infrastructure pillar for Stark Industries and now WorkTitans/THE.Hosting. Youssef Zinad (WorkTitans founder) was part of MIRhosting legal team. MIRhosting stated it "temporarily paused" services to WorkTitans after the raid.</t>
+          <t>Founded in 2004 by Andrey Nesterenko, who was arrested in the FIOD raid of 2026-05-18 (name press-reported). Krebs: WorkTitans reached the internet solely through MIRhosting, and AS52000 is the first peer in AS209847's aut-num. The 2008 StopGeorgia.ru hosting is attributed (Jeffrey Carr) to the related Innovation IT Solutions Corp; Nesterenko said he could not verify it. De Volkskrant data showed WorkTitans and MIRhosting as the most-used networks in pro-Russian attacks on Danish bodies (Nov 2025). AS52000 has shrunk to two IPv4 /24s (185.15.209.0/24, 185.15.210.0/24). T1 candidate if the FIOD seizure is confirmed to have covered MIRhosting-operated infrastructure. Unverified: the 'temporarily paused services to WorkTitans' quote.</t>
         </is>
       </c>
     </row>
@@ -3127,17 +3227,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AS34888; AS42624</t>
+          <t>AS34888 (registered; no routes); AS42624 (registered; no routes)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Switzerland (claimed; unverified); aurologic-transited</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3147,7 +3247,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>SWISSNETWORK02; Simple Carrier LLC (predecessor)</t>
+          <t>SWISSNETWORK01; SWISSNETWORK02; Simple Carrier LLC (predecessor); simplecarrier.net</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3160,6 +3260,11 @@
           <t>aurologic GmbH</t>
         </is>
       </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Cobalt Strike; Sliver; QuasarRAT; Remcos; DCRat; Latrodectus; Amadey; Rhadamanthys; RedLine; Meduza</t>
+        </is>
+      </c>
       <c r="R33" t="inlineStr">
         <is>
           <t>Zero route diversification; aurologic-locked</t>
@@ -3167,22 +3272,27 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>No route diversification (11 prefixes all through AS30823); Shell entity</t>
+          <t>Historical Spamhaus ASN-DROP listing (simplecarrier.net, Dec 2025; delisted); RF top-10 malicious-activity density (Sept 2025); No route diversification; Network now unrouted</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>RF-AUROLOGIC</t>
+          <t>RF-AUROLOGIC; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aurologic downstream with zero route diversification. 11 active prefixes all through AS30823. ASNs transferred from Simple Carrier LLC.</t>
+          <t>Seychelles-registered holder of AS34888 and AS42624, transferred from Simple Carrier LLC (July 2024). RF (Sept-Nov 2025): 11 IPv4 prefixes (2,816 addresses) all via aurologic AS30823, top ten for malicious-activity density in Sept 2025, linked to PrivateAlps. Both ASNs were on Spamhaus ASN-DROP (simplecarrier.net) in Dec 2025 and have since been delisted; neither announces anything now (e.g. 185.196.8.0/22 and 185.208.156.0/22 are unrouted). Do not confuse with the unrelated Iranian swissnetwork.io ASNs (AS199467, AS209373). Correction 2026-09-25: registration is Seychelles, not Switzerland.</t>
         </is>
       </c>
     </row>
@@ -3207,6 +3317,11 @@
           <t>AS44050</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AS34665 (PINDC-AS; Petersburg Internet Network Ltd)</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>Russia</t>
@@ -3227,6 +3342,11 @@
           <t>PIN; Pinspb</t>
         </is>
       </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Cl0p (torrent seeding server, 2023); TACTICALOCTOPUS (C2)</t>
+        </is>
+      </c>
       <c r="R34" t="inlineStr">
         <is>
           <t>Long-running Russian BPH</t>
@@ -3234,22 +3354,22 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>High malicious traffic ratio; Non-cooperative with LE</t>
+          <t>Long-running Russian hosting with repeated malicious tenancy; Not on Spamhaus ASN-DROP</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>TRENDMICRO-INTERPOL</t>
+          <t>TRENDMICRO-INTERPOL; UNIT42-CL0P-TORRENTS; SECURONIX-TACTICALOCTOPUS; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Long-running Russian BPH. Trend Micro + Interpol 2023 ranked PIN as 19% of malicious offshore BPH sourcing — behind ELITETEAM (48%) ahead of FlokiNET (13%).</t>
+          <t>Long-running St. Petersburg hoster (AS44050 announces 13 IPv4 prefixes; sister AS34665 PINDC-AS announces 69). Unit 42 (Sept 2023): a Cl0p torrent-seeding server, 95.215.0.76, was hosted by PIN DC on AS34665 (that block is now originated by AS44050). Securonix: TACTICALOCTOPUS C2 addresses 5.8.8.100 and 109.206.240.67 were registered to Petersburg Internet Network Ltd. Its T2 tier rests heavily on the Trend Micro/Interpol 2023 figure (PIN 19% of malicious offshore BPH sourcing, behind ELITETEAM 48% and ahead of FlokiNET 13%), which could not be re-verified; without it the vendor evidence supports T3. Not on Spamhaus ASN-DROP.</t>
         </is>
       </c>
     </row>
@@ -3291,17 +3411,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>FUNNULL backbone</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>FUNNULL Technology Inc. (parent)</t>
+          <t>CTGSERVERLIMITED-AS-AP; ctgserver.com</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>OFAC May 29 2025 (via FUNNULL designation)</t>
+          <t>Not designated (OFAC's May 29 2025 action named only Funnull Technology Inc. and Liu Lizhi); hosting ASN used by the designated FUNNULL</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3311,7 +3426,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Pig-butchering infrastructure; brand impersonation</t>
+          <t>Pig-butchering infrastructure; brand impersonation; Cobalt Strike C2 (2026)</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3321,22 +3436,22 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Infrastructure laundering; Geofencing; Sanctioned (via FUNNULL); On Spamhaus ASN droplist</t>
+          <t>Spamhaus ASN-DROP (AS152194 under ctgserver.com); Infrastructure laundering; Geofencing; Hosts FUNNULL points of presence</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>SILENTPUSH-FUNNULL; OFAC-FUNNULL; INFOBLOX-DCLOUD</t>
+          <t>SILENTPUSH-FUNNULL; OFAC-FUNNULL; INFOBLOX-DCLOUD; SPAMHAUS-ASNDROP-2026; GREYNOISE-REACT2SHELL-2026; C2INTELFEEDS</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Persistent backbone ASN for FUNNULL/Triad Nexus. $200M+ pig-butchering losses. FUNNULL parent sanctioned. 175+ rotating CNAMEs and infrastructure laundering via compromised cloud accounts. Infoblox (June 2026): hosts 19 of the top 20 BPH-hosted DCloud Uni-App scam SLDs (236,000+ total since mid-2022); on the Spamhaus ASN droplist.</t>
+          <t>Hong Kong-registered ASN (119 IPv4 prefixes, 192,768 addresses) that hosted FUNNULL CDN points of presence in Silent Push's Oct 2024 mapping (Silent Push labels it 'China Telecom Global'); a hosting relationship, not ownership - CTG is not FUNNULL's parent and was not designated. Infoblox (June 2026): about 6% of visible DCloud Uni-App investment-scam domains use BPH providers such as CTG Server Limited; the campaign spans 236,493 distinct scam SLDs since mid-2022. Spamhaus ASN-DROP lists AS152194 (ctgserver.com; not in the Feb 2024 snapshot). Current activity: Cobalt Strike C2s on CTG addresses (Aug-Sep 2026, C2IntelFeeds) and AS152194 among GreyNoise's React2Shell exploitation sources. Kept T1 (multiple independent vendors plus Spamhaus). Corrections 2026-09-25: the OFAC 'via FUNNULL designation' entry was removed; '175+ rotating CNAMEs' conflicts with the FBI's 548 FUNNULL CNAMEs; the '19 of the top 20' figure is unverified.</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -3368,7 +3483,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AS210281</t>
+          <t>AS210281 (historical; reassigned to EcoConnect LLC [RU] - do not block); AS219262 (WAICORE-RUSSIA; registered, no routes)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3413,27 +3528,27 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>No route diversification; Russia-linked</t>
+          <t>Historical Spamhaus ASN-DROP listings (AS202973, AS206425, AS210281 under waicore.com, Feb 2024); Serial ASN rotation; Russia-linked</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>RF-AUROLOGIC; QURIUM-DOPPELGANGER</t>
+          <t>RF-AUROLOGIC; QURIUM-DOPPELGANGER; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>AS213887 registered Nov 8 2024 via RIPE. 68 IPv4 and 11 IPv6 prefixes. Named by RF Insikt and Qurium as aurologic-downstream within Doppelganger disinformation infrastructure. Multiple upstreams but aurologic primary.</t>
+          <t>UK-registered operator (AS213887 announces 29 IPv4 and 7 IPv6 prefixes; the earlier '68 IPv4 / 11 IPv6' is outdated). WAIcore activity predates the AS213887 registration: Spamhaus ASN-DROP listed three earlier WAIcore ASNs (AS202973, AS206425, AS210281; domain waicore.com) by Feb 2024; all three have since been re-issued to unrelated networks (do not block them). A new registration, AS219262 'WAICORE-RUSSIA', is held by a Russian individual and has no routes yet. Qurium names WAIcore within Doppelganger infrastructure behind aurologic; the RF naming is unverified. Not on the current ASN-DROP.</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3575,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AS50113; AS205090</t>
+          <t>AS50113; AS205090; AS200740; AS204339; AS204154; AS35196; AS214602</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3480,12 +3595,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>LockBit; Conti; BlackCat/ALPHV; Qilin</t>
+          <t>Ransomware operators leasing ISPsystem VMmanager templates (LockBit; Qilin; Conti; BlackCat/ALPHV; WantToCry)</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>LockBit; Conti; BlackCat; Qilin; TrickBot; Ursnif; RedLine; NetSupport; WantToCry</t>
+          <t>LockBit; Conti; BlackCat; Qilin; Ursnif; RedLine; NetSupport; PureRAT; Lampion; Lumma; WantToCry</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3495,22 +3610,22 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>High malicious traffic ratio; Shell company structure; Ransomware infrastructure</t>
+          <t>Shared VMmanager template hostnames; GreyNoise React2Shell exploitation sources (AS200740, AS205090); Not on Spamhaus ASN-DROP</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>SOPHOS-VMMANAGER; BLEEPINGCOMPUTER-BPH; TROLLEYE-FIRSTSERVER</t>
+          <t>SOPHOS-VMMANAGER; BLEEPINGCOMPUTER-BPH; TROLLEYE-FIRSTSERVER; GREYNOISE-REACT2SHELL-2026; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Named by Sophos Feb 2026 alongside Stark Industries for VMmanager Windows-template ransomware VM supply operation. Multiple ASNs: AS204997 AS50113 AS205090. ISPsystem VMmanager default Windows templates reuse hostnames enabling stealthy payload delivery for WantToCry and other ransomware families.</t>
+          <t>UK-registered network with at least eight ASNs registered to FIRST SERVER LIMITED (AS204997, AS50113, AS205090, AS200740, AS204339, AS204154, AS35196, AS214602; plus a Spanish affiliate on AS199685). Linked to the Sophos (Feb 2026) research on ISPsystem VMmanager default Windows templates, whose reused hostnames appear across LockBit, Qilin, Conti, BlackCat, Ursnif, NetSupport, PureRAT, Lampion, Lumma and RedLine infrastructure - associations of the template ecosystem, not specifically of First Server; the Sophos naming of First Server could not be re-verified. Former Hypercore prefixes now originate from AS205090 and AS200740 (lead only). Do not confuse AS204997's handle FIRSTBYTE-AS with the unrelated Iranian AS210703 'FIRSTBYTE-AS' on ASN-DROP. TrickBot was removed (not in the Sophos summary).</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3647,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AS215240</t>
+          <t>AS215240 (historical; re-registered to Microdex UG [DE]; no routes - do not block)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3545,6 +3660,11 @@
           <t>Silent Connection Ltd</t>
         </is>
       </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>XWorm; AsyncRAT (Blue Stylthon WsgiDAV servers, Nov-Dec 2024)</t>
+        </is>
+      </c>
       <c r="R38" t="inlineStr">
         <is>
           <t>Dissolved-but-live pattern</t>
@@ -3552,27 +3672,27 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Dissolved-but-live; Network persists after corporate dissolution</t>
+          <t>RF 2025 top-10 density (#9); ASN since re-registered; network dark</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>~1-2% (RF chart)</t>
+          <t>RF 2025 top-10 (#9)</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>EXCEDO-ASN; RF-TAE-2026</t>
+          <t>EXCEDO-ASN; RF-TAE-2026; ORANGE-CD-BLUESTYLTHON; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Compulsorily dissolved at UK Companies House January 2025. AS215240 network remains live and continues to facilitate cybercrime despite corporate dissolution. Appears at position 9 in RF 2025 Threat Density chart.</t>
+          <t>UK company reported compulsorily dissolved at Companies House in January 2025 (not re-verified). RF ranked Silent Connection #9 in its 2025 Threat Density top 10; Orange Cyberdefense placed Blue Stylthon WsgiDAV servers delivering XWorm/AsyncRAT (Nov-Dec 2024) in AS215240. As of 2026-09-25 the ASN is registered to Microdex UG (DE) under a new handle and announces nothing, so the earlier 'network remains live' note is outdated. Another German UG holds a second ASN under the same MICRODEX-AS handle - a possible re-homing by the same operator (unproven).</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3709,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>T3-Suspected</t>
+          <t>T5-Watch List</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>AS215208</t>
+          <t>AS215208 (historical; reassigned to PT Citra Celebas Multimedia [ID] - do not block)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3614,12 +3734,12 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Dissolved-but-live; Possible ELITETEAM connection (1337 naming)</t>
+          <t>Dissolved shell; ASN recycled</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Dissolved-but-live; 1337 naming convention</t>
+          <t>ASN recycled to an unrelated live network; single-source evidence</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -3629,17 +3749,17 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>EXCEDO-ASN</t>
+          <t>EXCEDO-ASN; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Companion dissolved-but-live entity to Silent Connection Ltd. AS215208 registered March 28 2024 via RIPE. 1337 naming convention suggests possible ELITETEAM/1337TEAM orbital relationship. Compulsorily dissolved Jan 2025 but ASN persists.</t>
+          <t>UK shell reported compulsorily dissolved in Jan 2025 (not re-verified); AS215208 (reported registered 2024-03-28) is now held by PT Citra Celebas Multimedia (Indonesia) and announces three live prefixes - this is ASN recycling, not a dissolved shell still operating, so the ASN must not be blocked. The only source is Excedo. RF's 2025 top-10 #10 is 'DolphinHost Limited' (AS214717/AS207184, dolphinhost.net), a different entity; the repo previously conflated the two. The '1337' naming link to ELITETEAM is speculative. Tier lowered T3 -&gt; T5 on 2026-09-25 (historically associated; currently quiescent; single source).</t>
         </is>
       </c>
     </row>
@@ -3696,12 +3816,12 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Low-footprint provider on Hong Kong Alibaba infrastructure. Limited public CTI reporting. Watch-list as CDN brand that could front Asian BPH.</t>
+          <t>Low-footprint brand claimed to sit on Hong Kong Alibaba infrastructure. The 2026-09-25 audit found no ASN, registry record, Spamhaus ASN-DROP listing or CTI report for CDNCloud or cdnclouds.net, and it is absent from the Silent Push 2025 red-flag table that appears to be the source of the other T5 rows. It does not meet the T5 minimum ('credible source with structural indicators'); retained only pending a source and a candidate for removal at the next review.</t>
         </is>
       </c>
     </row>
@@ -3713,42 +3833,57 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>suspected</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>T5-Watch List</t>
+          <t>T3-Suspected</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AS213194 (NECHAEVDS-AS; 193.37.69.0/24)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>193.37.69.0/24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
+          <t>Russia (individual registrant)</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
           <t>Russia</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Russia</t>
-        </is>
-      </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Small Russian-operator BPH profile</t>
+          <t>Zservers successor hop network</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Insufficient data; Russian operator pattern</t>
+          <t>Association with sanctioned entity (Zservers prefix recipient); 100% DGA domains and TutaMail abuse contact (Silent Push, relayed)</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>INTRINSEC-UAC-2025; MALTRAIL-WORST-ASNS; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Naming pattern fits small Russian-operator BPH profile. Active baseline pending ASN enumeration.</t>
+          <t>AS213194, registered to a Russian individual (the AS-name derives from the registrant's surname), announces only 193.37.69.0/24. It is the same ASN the Zservers row lists as a post-sanction hop: Intrinsec (March 2025) assessed with high confidence that Zservers prefixes moved to AS213194, AS61336 and AS213010. A relayed Silent Push 2025 table flags it for 100% DGA domains and a TutaMail abuse contact. Tier raised T5 -&gt; T3 on 2026-09-25; merging into the Zservers row is an alternative. Not on Spamhaus ASN-DROP.</t>
         </is>
       </c>
     </row>
@@ -3760,94 +3895,144 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>flagged</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>T5-Watch List</t>
+          <t>T3-Suspected</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AS62864 (NILAS; ARIN)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AS23865; AS34985; AS149286 (APNIC; registered, no routes)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>United States (shell)</t>
+          <t>United States (registry); Japan per Spamhaus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Eastern Europe (likely)</t>
+          <t>Mixed APNIC/ARIN/AFRINIC space (no evidence of Eastern Europe)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>net innovation llc</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>netinnovation.net</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>US shell pattern</t>
+          <t>Multi-registry ASN set; DGA hosting</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Insufficient data; Shell company pattern</t>
+          <t>Spamhaus ASN-DROP (all four ASNs under netinnovation.net); Gmail abuse contact; DGA domains; 18-day abuse response (Silent Push, relayed)</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>LLC suffix without country qualifier suggests US or offshore-US shell. No sanctions or public CTI designation.</t>
+          <t>Four ASNs registered to 'net innovation llc' - AS62864 (ARIN; 14 prefixes including DROP-listed 164.155.0.0/16 and 168.80.0.0/15 space), AS34985 (7), AS23865 (5) and AS149286 (none) - all on Spamhaus ASN-DROP under netinnovation.net (cc JP). A relayed Silent Push 2025 table flags AS34985 for a Gmail abuse contact, DGA usage and an 18-day abuse response. The earlier 'no public CTI designation' note was wrong. Raised T5 -&gt; T3 (status flagged) on 2026-09-25; the ASN-DROP escalation rule implies T2 once a second independent B/C source is read directly.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Tiger Net (SOW-A)</t>
+          <t>Tiger Network Limited (Tiger Net)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>flagged</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>T5-Watch List</t>
+          <t>T3-Suspected</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AS48589 (TIGER)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AS211121 (INDIA)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>43.255.16.0/22; 103.239.0.0/22; 112.143.0.0/20; 112.143.30.0/23; 124.68.32.0/19 (AS48589)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>United Kingdom (registry)</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Unknown (likely Asia/CIS)</t>
+          <t>Asian address space; operator reportedly Ukraine-linked (Silent Push, relayed)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Tiger Network Limited</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>SOW-A</t>
+          <t>Tiger Net; imtigernet</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Asian address space under a UK registrant</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>Insufficient data</t>
+          <t>Spamhaus ASN-DROP (AS48589; AS211121 under imtigernet); Gmail abuse contact; DGA domains (Silent Push, relayed)</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>SOW-A qualifier unusual. Limited public OSINT. Enrichment needed.</t>
+          <t>Renamed from 'Tiger Net (SOW-A)' on 2026-09-25. Tiger Network Limited (GB) holds AS48589 (5 prefixes, 14,848 addresses of Asian space) and AS211121 (4 prefixes); both are on Spamhaus ASN-DROP (imtigernet) and their prefixes overlap Spamhaus DROP. A relayed Silent Push 2025 table lists 'AS48589 SOW-A-AS (Tiger Net) - Ukraine, Gmail, DGA'. No current 'SOW-A' handle exists; the only registry match, AS43613 'SOWA' (LLC BIGNET UKRAINE), is a separate ASN-DROP entry, so the relay may have merged two records. Raised T5 -&gt; T3 (status flagged); T2 pending a second independent B/C source.</t>
         </is>
       </c>
     </row>
@@ -3867,34 +4052,54 @@
           <t>T5-Watch List</t>
         </is>
       </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AS49217 (registered; no routes)</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>United States (Wyoming LLC per Silent Push; registry cc US)</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Turkey per Spamhaus</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>HOSTYPE LLC</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>hostype.com</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Unknown small operator</t>
+          <t>Wyoming shell; dormant</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>Insufficient data</t>
+          <t>Historical Spamhaus ASN-DROP listing (Feb 2024 and Dec 2025 snapshots; delisted); Gmail abuse contact; DGA domains; 30-day abuse response (Silent Push, relayed)</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Minimal public profile. Short-form naming matches small-operator pattern.</t>
+          <t>AS49217 is registered to HOSTYPE LLC (registry cc US; Spamhaus cc TR; a relayed Silent Push 2025 table calls it a Wyoming shell with a Gmail abuse contact, DGA usage and a 30-day abuse response). It was on Spamhaus ASN-DROP in the Feb 2024 and Dec 2025 snapshots, has since been delisted, and announces nothing. Fits T5's 'historically associated with abuse, currently quiescent'; watch for re-announcement.</t>
         </is>
       </c>
     </row>
@@ -3914,9 +4119,24 @@
           <t>T3-Suspected</t>
         </is>
       </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AS140224 (historical; registry now 'Nebula Global LLC' [US]; no routes)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AS149040 (STARCLOUD GLOBAL PTE. LTD.; no routes)</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Asia (Philippines/China likely)</t>
+          <t>Singapore (PTE. LTD.); US (Colorado) registrant address per Silent Push</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>StarCloud Global Pte. Ltd.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3924,19 +4144,14 @@
           <t>Triad Nexus-affiliated brand</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>FUNNULL Technology Inc. (affiliated)</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>OFAC May 29 2025 (via FUNNULL lineage)</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Triad Nexus</t>
+          <t>Triad Nexus; Silver Fox</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Triad Nexus scam infrastructure; Silver Fox phishing domains; Cobalt Strike C2</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -3946,22 +4161,22 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Infrastructure laundering; Triad Nexus connection</t>
+          <t>Phishing-ASN ranking (#13); Triad Nexus infrastructure (Silent Push, relayed); ESET Silver Fox hosting</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>SILENTPUSH-FUNNULL</t>
+          <t>SILENTPUSH-FUNNULL; ESET-SILVERFOX-IOC; C2INTELFEEDS; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Triad Nexus-affiliated CDN front brand. Likely among Silent Push-identified clean CDN front brands feeding traffic into laundered FUNNULL ecosystem.</t>
+          <t>Singapore-registered hosting brand. A relayed Silent Push 2025 table lists AS140224 'STARCLOUD GLOBAL SG' as Triad Nexus infrastructure with a residential Colorado address and a 4-day abuse response; a phishing-ASN ranking put AS140224 at #13 (237,056 routed IPv4; 3,032 phishing attacks). ESET lists Silver Fox domains on 149.104.24.24 with hosting provider 'STARCLOUD GLOBAL PTE. LTD.' (first seen 2026-03-10), and a Cobalt Strike C2 on 154.38.114.115 was recorded under the same provider (Sept 2026); both IPs are now routed by other HK ASNs. AS140224 now shows as 'Nebula Global LLC' (US) and AS149040 announces nothing. CORRECTION 2026-09-25: StarCloud is NOT an OFAC designee - the earlier 'OFAC May 29 2025 (via FUNNULL lineage)' entry was removed (OFAC named only Funnull Technology Inc. and Liu Lizhi).</t>
         </is>
       </c>
     </row>
@@ -3983,12 +4198,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>AS49612</t>
+          <t>AS57724 (DDOS-GUARD)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AS57724</t>
+          <t>AS49612 (COGNITIVE-CLOUD-NET handle; 1 prefix)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4018,12 +4233,17 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Dual-use Russian DDoS mitigation + hosting. Historical Parler/8chan host. ELITETEAM AS51381 peer. Not classified BPH but persistent presence in Russian cybercrime ecosystem.</t>
+          <t>Dual-use Russian DDoS mitigation and hosting provider. Main network is AS57724 (21 IPv4 prefixes); AS49612 now announces a single /24 under the handle COGNITIVE-CLOUD-NET; a further 'DDoS-Guard Corp' ASN (AS262254) is dark. Historically an upstream of ELITETEAM (as of Sept 2022, per Team Cymru). Not on Spamhaus ASN-DROP. Unverified in this audit: the Parler/8chan hosting history. Not classified BPH, but persistently present in the Russian cybercrime ecosystem.</t>
         </is>
       </c>
     </row>
@@ -4080,17 +4300,17 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>INTEL-INSIGHTS-QWINS</t>
+          <t>INTEL-INSIGHTS-QWINS; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Small US-registered operator appearing alongside Proton66 Railnet Femo IT in Lumma malware hunt.</t>
+          <t>Small US-registered operator (AS14315; 51 IPv4 prefixes; ipverse role 'midsize transit') appearing alongside Proton66, Railnet and Femo IT in a Lumma malware hunt (single source; the blog could not be re-read). Not on Spamhaus ASN-DROP.</t>
         </is>
       </c>
     </row>
@@ -4112,24 +4332,24 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>AS394711</t>
+          <t>AS394711 (historical; Limenet; reassigned to KorGrid LLC [US] - do not block)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AS211252</t>
+          <t>AS211252 (historical; Delis LLC; reassigned to Marushin K.K. [JP] - do not block)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
+          <t>United States (registry country of both ASNs); servers in the Netherlands</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>Limenet LLC</t>
@@ -4142,12 +4362,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Serverion (colocation)</t>
+          <t>Serverion / Des Capital B.V. (colocation; community-sourced, weak)</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Seized Nov 12 2025 (Operation Endgame; Dutch police)</t>
+          <t>Dutch police seizure Nov 12 2025 (announced Nov 14 2025; ~250 physical servers in The Hague and Zoetermeer) - police did not name the service and said the case is not connected to Operation Endgame</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -4172,7 +4392,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4182,12 +4402,12 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>RF-TAE-2026; SPAMHAUS-BPH; BLEEPINGCOMPUTER-BPH; EUROPOL-ENDGAME-2025</t>
+          <t>RF-TAE-2026; SPAMHAUS-BPH; BLEEPINGCOMPUTER-BPH; REGISTRY-SNAPSHOT-2026-09; POLITIE-CRAZYRDP-2025</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Major BPH seized Nov 12 2025 by Dutch police as part of Operation Endgame. ~250 physical servers seized in The Hague and Zoetermeer. Operated as Limenet LLC (AS394711) and previously as Delis LLC (AS211252). Implicated in 80+ LE investigations spanning ransomware CSAM and malware distribution. No-KYC no-logs policy. Infrastructure now completely offline.</t>
+          <t>Major no-KYC RDP/VPS host (RF 2025 Threat Density #2). On 2025-11-12 Dutch police seized about 250 physical servers in data centres in The Hague and Zoetermeer (thousands of virtual servers taken offline) of a bulletproof hoster active since 2022 and seen in 80+ investigations (ransomware, botnets, phishing, CSAM). Police did not name it; sources told BleepingComputer it was CrazyRDP, which went offline. Dutch police told BleepingComputer the case is NOT connected to Operation Endgame (the earlier Endgame label was wrong). The Limenet (AS394711) and Delis (AS211252) ASNs rest on community sources and Spamhaus ASN-DROP listings of Feb 2024 (limenet.io; delis.one); both ASNs have since been re-issued to unrelated companies - do not block them.</t>
         </is>
       </c>
     </row>
@@ -4199,12 +4419,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>flagged</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>T3-Suspected</t>
+          <t>T2-High Risk</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4212,6 +4432,11 @@
           <t>AS138915</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AS58854 (Kaopu Cloud [CN]); AS154177 (LIGHT NODE LIMITED [HK]; Spamhaus-attributed via kaopuyun.com)</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>Hong Kong</t>
@@ -4237,6 +4462,16 @@
           <t>Cogent; Arelion; NTT; Level3; PCCW Global</t>
         </is>
       </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>RedHotel (C2, 2022-23); ToolShell/SharePoint exploitation (2025); FortiGate SSO abuse (Dec 2025); Bulbature/GobRAT operators</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>RedHotel tooling; GobRAT; Cobalt Strike</t>
+        </is>
+      </c>
       <c r="R49" t="inlineStr">
         <is>
           <t>Large IP allocation; BitTorrent/Tor/VPN activity observed</t>
@@ -4244,7 +4479,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>High malicious traffic ratio; Large IP space relative to business size</t>
+          <t>Spamhaus ASN-DROP (AS138915; AS58854; AS154177 under kaopuyun.com); C2 for 3+ families/actors; GreyNoise React2Shell exploitation source</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -4254,7 +4489,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -4264,12 +4499,12 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>RF-TAE-2026</t>
+          <t>RF-TAE-2026; SPAMHAUS-ASNDROP-2026; RF-REDHOTEL-2023; ESET-TOOLSHELL-2025; SEKOIA-BULBATURE; GREYNOISE-REACT2SHELL-2026; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Hong Kong ISP with 182272 IPv4 addresses across 50+ netblocks and 48429 hosted domains. Appeared at #4 in RF 2025 Threat Density chart. APNIC-registered March 2019. Global router presence in SG VN SA PH US HK. Tagged with BitTorrent Tor exit node and VPN activity. Large infrastructure footprint warrants monitoring.</t>
+          <t>Hong Kong ISP (APNIC-registered 2019) announcing 113,664 IPv4 addresses in 168 prefixes on AS138915 (Sept 2026; the earlier '182,272 / 50+ netblocks' is outdated). RF ranks Kaopu #4 in its 2025 Threat Density top 10. Spamhaus ASN-DROP lists three kaopuyun.com ASNs: AS138915, AS58854 and AS154177 (LIGHT NODE LIMITED, 129 IPv4 prefixes); a fourth (AS140666, ANY DIGITAL PTE. LTD.) was listed earlier and removed. Independent vendor evidence: RF Insikt (RedHotel heavily favouring Kaopu for C2, 2022-23); ESET (ToolShell SharePoint exploitation from Kaopu IPs, July 2025); Arctic Wolf (malicious FortiGate SSO logins, Dec 2025); Sekoia (Bulbature/GobRAT staging servers all on AS138915); GreyNoise React2Shell sources. Tier raised T3 -&gt; T2 (status flagged) on 2026-09-25 per the ASN-DROP escalation rule; T1 candidate on the RF top-10 ranking.</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4541,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Exved; Garantex successor</t>
+          <t>Garantex successor; TokenSpot (likely front, per TRM)</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4316,12 +4551,12 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>OFAC Aug 14 2025 (successor to Garantex); UK OFSI Aug 20 2025</t>
+          <t>OFAC Aug 14 2025 (as Garantex's direct successor); UK Aug 20 2025 (Grinex LLC, Russia regime); EU 19th package Oct 23 2025 (A7A5-ecosystem trading platform)</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Mira Serda ($5M State Dept reward)</t>
+          <t>Aleksandr Mira Serda (Garantex co-founder; State Dept reward up to $5M)</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4336,12 +4571,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -4351,7 +4586,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Direct successor / likely rebrand of OFAC-sanctioned Garantex after the March 2025 disruption. Forensically confirmed shared on-chain infrastructure and asset migration (user funds + newly minted A7A5 via Old Vector). Processed &gt;=$4.76B in 2025. OFAC designated Aug 14 2025 as Garantex's 'direct successor.' Suspended operations April 16 2026 claiming a ~$13.7M cyberattack (Elliptic/Chainalysis skeptical - possible false-flag exit); functionally offline since. Designation stands; status kept sanctioned (no "suspended" state in the model); operationally offline.</t>
+          <t>Kyrgyzstan-incorporated successor to Garantex: registered December 2024 (TRM) and promoted on Telegram days after the March 2025 Garantex takedown; forensically tied to Garantex by shared on-chain infrastructure and asset migration (user funds plus A7A5 minted via Old Vector). OFAC designated it on 2025-08-14 as Garantex's 'direct successor'. On 2026-04-15 about 12:00 UTC roughly $13-15M was drained (Grinex claimed &gt;1bn rubles and blamed foreign 'special services'; Elliptic measured ~$15M USDT); Grinex then suspended operations, and Chainalysis raised the possibility of a false-flag exit. TokenSpot, a Kyrgyz exchange TRM considers a likely Grinex front, was hit the same day; Rapira had &gt;$72M in direct transactions with Grinex (Elliptic). Exved is a separately designated company, not an alias. Unverified: '&gt;=$4.76B processed in 2025'. Designation stands; operationally offline.</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -4393,17 +4628,17 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>A7A5 stablecoin; A7 LLC; Instant Swapper</t>
+          <t>A7A5 stablecoin; Instant Swapper</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Garantex/Grinex ecosystem</t>
+          <t>A7 network (A7 LLC, A71 LLC, A7 Agent LLC - owned by Ilan Shor and Promsvyazbank); Garantex/Grinex ecosystem</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>OFAC Aug 14 2025 (Old Vector); EU 19th package Oct 2025 (A7A5 transactions banned)</t>
+          <t>UK May 2025 (A7) and Aug 20 2025 (Old Vector LLC); EU July 2025 (A7) and 19th package Oct 23 2025 (full A7A5 transaction ban from Nov 25 2025); OFAC Aug 14 2025 (Old Vector LLC, A7 LLC, A71 LLC, A7 Agent LLC)</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4418,12 +4653,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -4433,7 +4668,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Russian ruble-backed stablecoin facilitating $93.3B in 10 months. No-KYC Instant Swapper converted &gt;$2.2B of sanctioned A7A5 into mainstream USD-pegged stablecoins. EU banned A7A5 transactions in its 19th sanctions package (Oct 23 2025). Did not depeg (built without a freeze function) but its economy ran through Grinex, so on-chain volume collapsed ~96% from peak after Grinex suspended April 16 2026.</t>
+          <t>Russian ruble-backed stablecoin issued by Kyrgyzstan's Old Vector; A7 LLC is the token's creator. Chainalysis (2026 Crypto Crime Report): $93.3B moved 'in less than a year'; Elliptic: more than $100B in under a year (the $93.1B and $72B figures elsewhere are earlier snapshots). Garantex moved funds into A7A5 from as early as January 2025 (TRM). The no-KYC Instant Swapper reportedly converted &gt;$2.2B of A7A5 into mainstream USD stablecoins (unverified). The EU banned A7A5 transactions from 2025-11-25. Its economy ran through Grinex, so on-chain volume reportedly collapsed after Grinex suspended in April 2026 (the '~96%' figure is unverified). A7 LLC, A71 LLC and A7 Agent LLC are separately designated related entities, not aliases.</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -4475,7 +4710,12 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>OFAC June 2 2026 (E.O. 13902 + counterterrorism E.O. 13224)</t>
+          <t>OFAC June 2 2026 (sb0519, 'Economic Fury'): E.O. 13224 (material support to the IRGC) and E.O. 13902; four executives designated under E.O. 13224</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Amir Hossein Rad (chairman/co-founder); Seyed Ali Khoee (CEO); two Kharrazi-family co-founders (name renderings vary across sources)</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4490,7 +4730,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -4500,7 +4740,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Iran's largest digital-asset exchange. OFAC-designated June 2 2026 under 'Economic Fury' -- uniquely also under counterterrorism E.O. 13224.</t>
+          <t>Iran's largest digital-asset exchange. OFAC-designated 2026-06-02 under 'Economic Fury' - uniquely also under counterterrorism E.O. 13224 - together with four executives. The four designated Iranian exchanges handled about $7.7B, roughly 78% of Iran's attributed 2025 crypto volume. Follow-on actions: OFAC added Central Bank of Iran wallets (2026-07-16) and designated the exchanges Shelbit and Aban Tether (2026-08-07), the latter for transactions with Nobitex, Wallex, Bitpin and Ramzinex.</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -4733,7 +4973,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AS213388; AS214295 (dark); AS215476 (dead); AS198465 (predecessor, recycled to CN)</t>
+          <t>AS213388 (IIC RAIL LIMITED [GB]; downstream); AS214295 (dark); AS215476 (dead); AS198465 (predecessor, recycled to CN)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4788,7 +5028,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>On Spamhaus ASN-DROP (AS213790 + AS213388); self-advertised bulletproof (@bthosterltd); masscan ~1300 kpps; shell/nominee structure; shared wcd RIPE maintainer</t>
+          <t>On Spamhaus ASN-DROP (AS213790 under btcloud.ro; AS213388 under iic-rail); upstreams AS209605, AS49581 and AS204428 are themselves on ASN-DROP; self-advertised bulletproof (@bthosterltd); masscan ~1300 kpps; shell/nominee structure; shared wcd RIPE maintainer</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -4798,17 +5038,17 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>INTRINSEC-BTHOSTER; SECURITYONLINE-BTHOSTER; RIPE-AAWG-BTHOSTER</t>
+          <t>INTRINSEC-BTHOSTER; SECURITYONLINE-BTHOSTER; RIPE-AAWG-BTHOSTER; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Confirmed multi-vector (2026-06): BtHoster = "BTCloud" operator running recycled UK '[Word] Network LTD' shells -- BtHoster LTD (AS198465, dead 2024-03) -&gt; Skynet Network Ltd (AS214295) + Inside Network LTD (AS215476) (struck off 2025) -&gt; Limited Network LTD (AS213790, ACTIVE) + downstream AS213388. Live identity tied by: the 45.142.193.0/24 inetnum is owned by Limited Network LTD (migrated Skynet-&gt;AS213388 on 2026-06-23, owner unchanged); abuse@btcloud.ro brand on its ARIN blocks; direct AS213790&lt;-&gt;AS214295 peering; shared 'wcd' RIPE maintainer (Khatibi/UAE). Sells pre-configured masscan servers (~1300 kpps) to Initial Access Brokers; transfers prefixes between shells to erase reputation; reuses Iranian-origin prefixes to fake Iran attribution. Both live ASNs on Spamhaus ASN-DROP. Transit via UAB Host Baltic (AS209605) + Tube-Hosting (AS49581, aurologic) with a Bulgarian backstop (SS-NET AS204428 / 4Vendeta). Full attribution dossier in internal investigation.</t>
+          <t>Confirmed multi-vector (2026-06): BtHoster = 'BTCloud' operator running recycled UK '[Word] Network LTD' shells -- BtHoster LTD (AS198465, dead 2024-03) -&gt; Skynet Network Ltd (AS214295) + Inside Network LTD (AS215476) (struck off 2025) -&gt; Limited Network LTD (AS213790, ACTIVE) + downstream AS213388. Live identity tied by: the 45.142.193.0/24 inetnum is owned by Limited Network LTD (migrated Skynet-&gt;AS213388 on 2026-06-23, owner unchanged); abuse@btcloud.ro brand on its ARIN blocks; direct AS213790&lt;-&gt;AS214295 peering; shared 'wcd' RIPE maintainer (Khatibi/UAE). Sells pre-configured masscan servers (~1300 kpps) to Initial Access Brokers; transfers prefixes between shells to erase reputation; reuses Iranian-origin prefixes to fake Iran attribution. Spamhaus ASN-DROP lists AS213790 with domain btcloud.ro (a direct BTCloud tie) and, since 2026, AS213388 (registry holder 'IIC RAIL LIMITED'); the old shells AS214295/AS215476 were delisted after Dec 2025. A sibling-looking AS214018 'IIC-AS' (INTERNET INTELLIGENCE COMPANY LTD) is also on ASN-DROP (lead only). Transit via UAB Host Baltic (AS209605) + Tube-Hosting (AS49581) with a Bulgarian backstop (SS-NET AS204428 / 4Vendeta) - all three transit ASNs are themselves on ASN-DROP. Securonix DanaBot IOC 45.129.14.157 resolved to 157.hosted-by.bthoster.com. Full attribution dossier in internal investigation.</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
@@ -4825,12 +5065,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>flagged</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>T3-Suspected</t>
+          <t>T2-High Risk</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4838,6 +5078,11 @@
           <t>AS51396</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AS215310 (USERCLOUD; Pfcloud UG); AS400328 (Intelligence Hosting LLC [NL/ARIN]; Spamhaus-attributed via pfcloud.io)</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
           <t>Germany</t>
@@ -4858,6 +5103,11 @@
           <t>aurologic-linked ecosystem</t>
         </is>
       </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Hikvision CVE-2021-36260 exploitation source; AsyncRAT C2 (2025); FortiGate 60F exploit-kit staging (2026)</t>
+        </is>
+      </c>
       <c r="R57" t="inlineStr">
         <is>
           <t>Bulletproof-adjacent; Sustained scanning/proxy abuse</t>
@@ -4865,27 +5115,27 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>Censys BULLETPROOF label; Honeypot scanning telemetry; aurologic-ecosystem adjacency</t>
+          <t>Spamhaus ASN-DROP (AS51396 since at least Feb 2024; AS215310 and AS400328 under pfcloud.io); GreyNoise exploitation sources; aurologic-ecosystem adjacency (Railnet transit)</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>RUDIS-BPH-WATCH; RF-AUROLOGIC</t>
+          <t>RUDIS-BPH-WATCH; RF-AUROLOGIC; SPAMHAUS-ASNDROP-2026; GREYNOISE-WEEKLY-2026-08; GREYNOISE-REACT2SHELL-2026; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Real RIPE-registered German micro-provider (AS51396). Recorded Future lists it in the aurologic-linked malicious-infrastructure ecosystem (Railnet routes a /24 through it); ai.rud.is honeypot telemetry (June 2026) flagged it as the week's most active scanner. CAVEAT: dedicated 'bulletproof' signal leans on one honeypot tracker; RF provides the independent anchor.</t>
+          <t>German micro-provider (AS51396: 26 IPv4 and 24 IPv6 prefixes). Spamhaus ASN-DROP has listed AS51396 since at least Feb 2024 (with a since-recycled AS202685 'as-pfcloud'); it now also lists AS215310 (USERCLOUD) and AS400328 (Intelligence Hosting LLC) under pfcloud.io. RF lists Pfcloud as an upstream of the Virtualine/Railnet 'hosting island' alongside aurologic. GreyNoise (Aug 2026): 204.76.203.43 on AS51396 generated 393,777 sessions and most of the period's 121,068 Hikvision CVE-2021-36260 exploitation attempts; Pfcloud IPs also appear among React2Shell sources. A community note (Sept 2026, D-grade) describes a Pfcloud open directory staging FortiGate 60F exploit modules on an IP previously listed as AsyncRAT C2. Tier raised T3 -&gt; T2 (status flagged) on 2026-09-25 per the ASN-DROP escalation rule; the earlier single-honeypot caveat is outdated.</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
@@ -4957,17 +5207,17 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>RF-GUARANTEE-2026</t>
+          <t>RF-GUARANTEE-2026; OFAC-XINBI-2026</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Recorded Future/Insikt (Feb 2026): major Chinese-language guarantee (danbao) marketplace resembling defunct Huione; emerged ~Dec 2024 and rose as a leading successor after the May 2025 Huione/Xinbi Telegram bans (30+ successors emerged). Largest group ~19,225 members. Brokers laundering, compromised accounts, SIM/PII, MaaS, deepfakes, KYC-bypass; sweeping ops vs South Korea/Japan. NOTE: pre-dated the bans (~Dec 2024); rose as successor rather than 'emerged after.'</t>
+          <t>Recorded Future/Insikt: major Chinese-language guarantee (danbao) Telegram marketplace resembling the defunct Huione Guarantee, with thousands of thematic channels (overseas phishing, laundering, 'sweeping' goods in Japan and South Korea) and a search bot. The RF report appears to date from about April 2026 (the relaying digest is dated 2026-04-23), not February. Reported emergence ~Dec 2024 and ~19,225 members in its largest group are unverified. Flare counts more than 30 marketplaces that emerged after Huione Guarantee ceased operations in May 2025; Xinbi (disrupted by the US on 2026-09-09) is the largest of the successors.</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
@@ -4984,7 +5234,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>dissolved</t>
+          <t>flagged</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5014,12 +5264,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Huione (30% stake, Dec 2024)</t>
+          <t>Huione / Haowang Guarantee (announced a stake in Dec 2024; 30% figure unverified)</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Guarantee/escrow marketplace; Money-laundering facilitation; Wound down post-arrest</t>
+          <t>Guarantee/escrow marketplace; Money-laundering facilitation; Public fraud-market activity ceased Jan 2026</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -5029,17 +5279,17 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>ELLIPTIC-TUDOU; RF-GUARANTEE-2026; OFAC-HUIONE-PRINCE</t>
+          <t>ELLIPTIC-TUDOU; RF-GUARANTEE-2026; OFAC-HUIONE-PRINCE; OFAC-PRINCE-2025</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Huione's designated successor (Huione took 30% stake Dec 2024). Processed &gt;$12B -- 3rd-largest illicit marketplace ever. Wound down (returned merchant deposits) after the Jan 6 2026 arrest of Prince Group chairman Chen Zhi; Elliptic shows admin-wallet activity collapsing thereafter.</t>
+          <t>Huione's designated successor: in December 2024 Haowang (ex-Huione) Guarantee announced it was buying a stake in Tudou (FinCEN; the 30% figure is unverified). Processed &gt;$12B - the third-largest illicit marketplace ever (Elliptic). In January 2026, after Prince Group chairman Chen Zhi was arrested in Cambodia and extradited to China (reported 2026-01-07), Tudou effectively ceased transactions through its public Telegram groups and admin-wallet activity collapsed; gambling operations continue and Elliptic says it remains to be seen whether this is a full shutdown or a pivot. Status corrected dissolved -&gt; flagged on 2026-09-25 (no legal dissolution documented).</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -5091,7 +5341,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>FinCEN proposed Section 311 amendment June 23 2026 (successor-entity rule)</t>
+          <t>FinCEN proposed rule (Federal Register 2026-12794, published June 25 2026) adding H-Pay and any successor to the Huione Group Section 311 special measure - a proposal, not a final rule</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5111,17 +5361,17 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>OFAC-HUIONE-PRINCE</t>
+          <t>OFAC-HUIONE-PRINCE; FINCEN-HPAY-2026</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>FinCEN (June 23 2026) proposed amending its Oct 2025 Huione Section 311 Final Rule to add Cambodia-based H-Pay Service PLC and 'any successor entity,' naming H-Pay the successor facilitator that inherited Huione Pay's branches, customer base, branding, and operational footprint.</t>
+          <t>FinCEN (announced 2026-06-23 with the DOJ Huione cloud-account seizure and Prince Group designations) proposed amending its Oct 2025 Huione Group Section 311 final rule to cover Cambodia-based H-Pay Service PLC (reg. no. 00074959) and 'any successor entity', to stop Huione circumventing the cut-off. The comment period was extended in July 2026 after a portal outage; the rule is not yet final. FinCEN notes the National Bank of Cambodia revoked H-Pay's payment licence on 2026-04-10.</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
@@ -5146,19 +5396,14 @@
           <t>T2-High Risk (Anonymization/Proxy Enabler)</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>AS48266</t>
-        </is>
-      </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>205.198.91.136; 205.198.91.155; 194.147.16.244</t>
+          <t>IOC IPs (not Asocks-owned ranges): 205.198.91.136; 205.198.91.155 (Cogent AS174); 194.147.16.244 (Catixs AS48266)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Unknown (UK-hosted infra)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5173,7 +5418,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>PROXYLIB (2024)</t>
+          <t>PROXYLIB SDK apps (HUMAN, 2024)</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -5198,17 +5443,17 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>NCSC-NL-ASOCKS; SILENTPUSH-CHINESEVPN</t>
+          <t>NCSC-NL-ASOCKS; SILENTPUSH-CHINESEVPN; HUMAN-PROXYLIB-2024</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Residential-proxy network (asocks[.]com, 7M+ marketed IPs). Dutch Politie + NCSC-NL dismantled a 17M-device residential-proxy botnet (~200 servers seized) ~May 28 2026; PRESS (not police) attributes it to Asocks -- flag the name-linkage caveat. Silent Push tied IP 205.198.91[.]136 to asocks[.]com via the Mandarin-language LVCHA VPN (lvcha[.]in); related ASN AS48266 (catixs[.]com). No operators named. Storefront remained live post-seizure.</t>
+          <t>Residential-proxy network (asocks.com; proxies sold at $5-15/month). On 2026-05-28 Dutch police and NCSC-NL announced the takedown of a botnet of at least 17 million infected devices whose backend ran on more than 200 servers in the Netherlands; police seized a subset of those servers from a hosting provider, which then took the botnet offline. Authorities did not name the service - NL Times reported it was Asocks (name-linkage caveat). HUMAN Satori (Mar 2024) believed PROXYLIB apps were monetized through Asocks. Silent Push tied the Mandarin-language LVCHA VPN (lvcha.in) to residential-proxy IOCs; the specific Asocks-IP tie is not in the available summary. Corrections 2026-09-25: AS48266 is Catixs Ltd, an ordinary hosting provider, not an Asocks ASN (removed as primary_asn); 205.198.91.x is Cogent space; the '~163 countries' figure belongs to SocksEscort. Storefront reportedly remained live after the seizure.</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -5285,7 +5530,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -5295,7 +5540,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Uzbekistan-registered (Tashkent) Aeza expansion entity, established 2025-07-03 (Tax ID 312252645; Business Reg. 2868352). OFAC-designated Nov 19 2025 alongside Hypercore Ltd as part of the Aeza pressure campaign. Verified against the live FCDO UK Sanctions List (2026-07-17): NOT UK-designated, unlike Hypercore - Treasury designated Datavice OFAC-only. No ASN stated in the OFAC/Federal Register entry.</t>
+          <t>Uzbekistan-registered (Tashkent) Aeza expansion entity. OFAC SDN record: established 2025-07-03; Tax ID 312252645; Business Registration 2868352; address 3 Irrigator Massive, Hamid Olimjon MFY, Tashkent; programs CYBER4 and CAATSA-RUSSIA; 'Linked To: AEZA GROUP LLC'. Designated 2025-11-19 alongside Hypercore Ltd, Smart Digital Ideas DOO, Maksim Makarov and Ilya Zakirov; absent from the UK's 19 Nov 2025 notices (OFAC-only). No ASN is stated in the designation; the registry lists a dark AS206336 as 'DATAVICE MCHJ', but per-ASN metadata still shows a previous holder, so treat it as an unverified lead.</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
@@ -5327,7 +5572,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Russia/Ukraine nexus (operator identity obscured)</t>
+          <t>Ukrainian administrator; infrastructure in ~27 countries</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5337,7 +5582,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>OFAC July 13 2026 (E.O. 13694 as amended, in furtherance of E.O. 14390; coordinated with UK FCDO)</t>
+          <t>OFAC July 13 2026 (E.O. 13694 as amended, in furtherance of E.O. 14390; coordinated with UK FCDO, which did not co-designate)</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5367,17 +5612,17 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>OFAC-1VPNS</t>
+          <t>OFAC-1VPNS; EUROPOL-SAFFRON-2026</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>OFAC-designated July 13 2026 under E.O. 13694 (in furtherance of E.O. 14390), coordinated with UK FCDO, for enabling ransomware attacks on US targets. No-log criminal VPN advertised on cybercrime forums since 2014. Admin Dmytro Rashevskyi used false identities (Maksim Sorin, Roman Chabanenko) to procure infrastructure. Belarusian cryptor-seller Yegeniy Vladimirovich Silayev co-designated in the same action. European LE took down 1VPNS infrastructure ~May 2026 (referenced by FBI FLASH-20260521-001).</t>
+          <t>OFAC-designated 2026-07-13 (sb0559) under E.O. 13694 as amended, in furtherance of E.O. 14390, for enabling ransomware attacks on US targets; the UK did not co-designate it. No-log criminal VPN advertised on cybercrime forums since 2014; ~32 exit nodes in ~27 countries used by at least 25 ransomware groups (FBI FLASH-20260521-001). Administrator Dmytro Rashevskyi (45, Ukrainian) used false identities (Maksim Sorin, Roman Chabanenko) to buy infrastructure. Belarusian cryptor seller Yegeniy Silayev was co-designated. The service was dismantled in Operation Saffron (19-20 May 2026, France- and Netherlands-led with Europol and Eurojust): 33 servers taken down, 1vpns domains seized and a suspected administrator arrested. SDN entries carry 5 addresses for the service and 8 for Rashevskyi.</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -5449,22 +5694,22 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>GTIG-NETNUT; KREBS-NETNUT</t>
+          <t>GTIG-NETNUT; KREBS-NETNUT; QURIUM-POPA-2026; KREBS-POPA-2026</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>FBI (with Google, Lumen, Shadowserver, IRS-CI) seized hundreds of NetNut domains July 2 2026 and disrupted the associated Popa botnet (2M+ hijacked devices - smart TVs, streaming boxes, Android). NetNut is operated by NASDAQ-listed Alarum Technologies (ALAR). Google GTIG observed 316 distinct threat-actor clusters using suspected NetNut exit nodes in a single week in June 2026; Google set Play Protect to disable apps carrying NetNut SDKs. Alarum stock fell ~67% within a week. Builds on Google's Jan 2026 IPIDEA disruption. Not sanctioned - a commercial proxy provider whose exit-node supply was botnet-sourced.</t>
+          <t>On 2026-07-02 the FBI seized hundreds of NetNut-linked domains (the seizure notice thanks Google, Lumen and Shadowserver) and Google disrupted the associated Popa botnet (at least 2 million hijacked smart TVs, streaming boxes and Android devices): Google disabled accounts used for C2 and set Play Protect to disable apps carrying NetNut SDKs. GTIG observed 316 distinct threat clusters using suspected NetNut exit nodes in a single week of June 2026. Popa was first flagged by QiAnXin XLab in March 2025 as an Android component of the Vo1d botnet and was tied to NetNut in June 2026 by Krebs, Qurium, Nokia Deepfield and Synthient. NetNut is operated by NASDAQ-listed Alarum Technologies (ALAR), which disputes the allegations and paused traffic on the affected network; its shares fell 23.6% after hours. Builds on Google's Jan 2026 IPIDEA disruption. Not sanctioned. Corrections 2026-09-25: IRS-CI involvement and a '~67% stock fall' were not supported by any source and were removed.</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
@@ -5491,7 +5736,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>AS400619</t>
+          <t>AS400619 (origin ASN; registry holder AROSSCLOUD INC. [US])</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AS136452 (SHANGXING TECH LIMITED; no routes); AS151468 (SHANGXING TECH LIMITED; no routes)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5501,7 +5751,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Hong Kong (SHANGXING TECH LIMITED); United States (AROSSCLOUD INC., AS400619 registrant)</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5511,12 +5761,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>SHANGXING TECH LIMITED</t>
+          <t>SHANGXING TECH LIMITED (named in first-party finding; holds AS136452/AS151468); AROSSCLOUD INC. (AS400619 registrant)</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Fastmos Co Limited; AROSSCLOUD INC.; Zun Cloud Limited</t>
+          <t>Fastmos Co Limited (AS138644; shares 191.124.0.0/16 with AS400619); AROSSCLOUD INC.; Zun Cloud Limited (AS140212)</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -5536,7 +5786,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>Gshell default cert on tenants; mass-exploitation open directories; multiple org names on one ASN</t>
+          <t>Gshell default cert on tenants; mass-exploitation open directories; multiple org names on one ASN; GreyNoise React2Shell exploitation source; Cobalt Strike C2s (C2IntelFeeds); Not on Spamhaus ASN-DROP</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
@@ -5546,22 +5796,631 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>CV-GSHELL-2026-07; CV-OPENDIR-2026-09</t>
+          <t>CV-GSHELL-2026-07; CV-OPENDIR-2026-09; GREYNOISE-REACT2SHELL-2026; C2INTELFEEDS; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>AS400619 is a Hong Kong reseller ASN announced under multiple org names (Fastmos Co Limited, AROSSCLOUD INC., Zun Cloud Limited, PEG TECH INC, AS Data HK). Hosts the July 2026 unreported Gshell C2 cluster (SHANGXING pair 103.112.97.163/.199) and a Sept 2026 mass web-exploitation workspace (Fastmos :8889 - gen_targets/CVE-PoC/Java-memshell RCE-verify/k8s scan, 283KB target list) plus a second exploit box (AROSSCLOUD :9999). First-party CrimsonVector open-directory hunt.</t>
+          <t>AS400619 is registered to AROSSCLOUD INC. (US) and originates 70 IPv4 prefixes (191,744 addresses), including 103.112.96.0/22 which covers the tracked 103.112.97.0/24; SHANGXING TECH LIMITED itself holds AS136452 and AS151468 (HK; neither announced), so the row name most likely reflects the inetnum holder while AROSSCLOUD owns the origin ASN (APNIC inetnum not yet confirmed). AS400619 and Fastmos (AS138644) tile 191.124.0.0/16 exactly between them - strong registry evidence of a shared reseller relationship. Hosts the July 2026 unreported Gshell C2 cluster (103.112.97.163/.199) and a Sept 2026 mass web-exploitation workspace (Fastmos :8889 - gen_targets/CVE-PoC/Java-memshell RCE-verify/k8s scan, 283KB target list) plus a second exploit box (AROSSCLOUD :9999) - first-party CrimsonVector open-directory hunts. Public corroboration: GreyNoise lists AS400619 among React2Shell exploitation sources (Jan 2026); C2IntelFeeds recorded Cobalt Strike C2s on AROSSCLOUD addresses (Aug-Sep 2026); community RAT feeds list several 103.112.97.x hosts. PEG TECH INC and 'AS Data HK' links are unverified.</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
           <t>HK reseller ASN, recurring China-nexus C2 and mass-exploitation host (SHANGXING/Fastmos/Arosscloud).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>HostZealot (HZ Hosting Ltd)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>T4-Gray Zone</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>AS59711 (HZ-EU-AS)</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AS202015 (HZ-US-AS); AS61046 (HZ-UK-AS); AS201525 (HZ-CA-AS)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Cl0p-used blocks: 79.141.160.0/22; 185.33.84.0/22; 193.42.38.0/24 (AS202015); 185.104.194.0/24; 185.117.88.0/22; 77.83.196.0/23; 185.80.52.0/22; 5.149.248.0/23 (AS59711); 185.81.112.0/23; 5.149.250.0/23 (AS61046); 79.141.166.0/23 (AS201525). Full footprint: 187 IPv4 prefixes / 79,360 addresses plus 2a01:8640::/32 (2026-09-25)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Bulgaria (Plovdiv HQ); servers marketed in ~20 locations (NL, DE, FR, PL, EE, SE, UK, US, CA, HK and others)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>HZ HOSTING LTD. / ХЗ ХОСТИНГ ЕООД (EIK 203391232; VAT BG203391232)</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>HostZealot; hostzealot.com; HZ-EU / HZ-UK / HZ-CA / HZ-US AS names; ORG-FNL9-RIPE</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Cl0p / TA505 / FIN11 (Lace Tempest); SideWinder APT; Akira and Fog ransomware affiliates; TrickBot/Conti operators (2020)</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Cl0p MFT mass-exploitation infrastructure (Accellion FTA; GoAnywhere; MOVEit; Cleo); DEWMODE webshell C2; DanaBot C2; SideWinder C2</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Recurrent multi-actor abuse of commercial VPS; Country-coded multi-ASN split under one LIR; VPN/proxy and Tor-relay hosting; Crypto payment accepted</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Repeated vendor attribution of tenant infrastructure (CISA, Mandiant, Black Lotus Labs, Huntress, Kaspersky, Arctic Wolf, Team Cymru); Not on Spamhaus DROP or ASN-DROP; KYC and AUP present (counter-indicator); Vendor IOC geolocation (NL/US/CA/EE) differs from registry country (BG)</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>2020-07</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>TEAMCYMRU-CL0P-2026; CISA-AA23-158A; CISA-AR21-055A; MANDIANT-ACCELLION-2021; BLACKLOTUS-ACCELLION; HUNTRESS-CLEO-2024; KASPERSKY-SIDEWINDER-2024; BLACKBERRY-SIDEWINDER-2024; ARCTICWOLF-FOG-AKIRA-2024; BLACKLOTUS-DANABOT; CONTI-LEAKS-2020; WOODWARD-CLOP-SANKEY; BG-COMMREG-HZ; REGISTRY-SNAPSHOT-2026-09</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Plovdiv-based commercial VPS/dedicated/colocation host (HZ HOSTING LTD., an EOOD incorporated January 2015; its RIPE LIR org ORG-FNL9-RIPE dates from 2012) announcing 187 IPv4 prefixes through four country-coded ASNs registered in Bulgaria. The Swedish AS209668 'HZ-HOSTING AB' is unrelated. Cl0p's most-reused provider: HZ ranges appear in 4 of the 10 Cl0p mass-exploitation campaigns (Accellion FTA 2020-21, GoAnywhere 2023, MOVEit 2023, Cleo 2024), matching Team Cymru's 'most frequently observed provider ... four of nine' (Aug 2026); Eli Woodward's campaign dataset shows HZ in 5 of 8 campaigns, adding PTC Windchill (June 2026), which is not reproducible from the published Windchill IOCs. 21 distinct HZ addresses appear in A/B-grade IOC lists (CISA AA23-158A: 10 GoAnywhere and 9 MOVEit; CISA MAR AR21-055A and Black Lotus Labs: 2 Accellion; Huntress: 1 Cleo). Reuse is block-level: only 79.141.160.78 recurs exactly (GoAnywhere and MOVEit), while 79.141.160.0/22 spans Accellion -&gt; GoAnywhere -&gt; MOVEit (~23-27 months) and 5.149.248.0/23 spans MOVEit -&gt; Cleo (~18 months). Other tenants: SideWinder (Kaspersky 2024: 'preference for HZ Hosting'), Akira/Fog SSL-VPN logins (Arctic Wolf 2024), a DanaBot C2 (Black Lotus Labs), a TrickBot/Conti server (2020 leaked chats), and APT28-attributed addresses in 79.141.161.x (maltrail). Counter-indicators: passport KYC demanded of a Conti operator (2020 chats); a 3-strike AUP; no Spamhaus DROP/ASN-DROP listing; reputation density comparable to mainstream hosts (many hits are Tor relays or VPN/proxy exits). The evidence shows repeated use by sophisticated tenants, not deliberate enablement - hence T4, not T3. Escalate on documented ignored abuse reports, forum BPH advertising, an above-baseline RF density score, or a substantiated ownership link to flagged personnel (Bulgarian registry aggregators disagree on the owner - verify in the Commercial Register). Use the Cl0p-used blocks for watchlisting and risk scoring rather than blanket blocking. See analysis/CL0P_HOSTZEALOT_REUSE.md.</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>Bulgarian commercial hosting brand (HZ Hosting Ltd; four country-coded ASNs) repeatedly chosen by Cl0p and other advanced actors; gray-zone rather than bulletproof on current evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Chang Way Technologies Co. Limited</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>flagged</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>T2-High Risk</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AS57523 (CHANGWAY-AS; no routes)</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AS59425 (HORIZONMSK-AS; no routes); AS207566 (LD007-AS; no routes); AS201738 (UFO TECHNOLOGIES LIMITED [GB]; Spamhaus-attributed via changway.hk); AS211663 (GALEON LLC [RU]; Spamhaus-attributed via changway.hk)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>45.93.20.0/24; 62.204.41.0/24; 91.240.118.0/24; 109.238.86.0/24; 185.11.61.0/24; 185.81.68.0/24; 193.178.158.0/24 (AS201738); 37.72.140.0/24 (AS211663) - all on Spamhaus DROP (2026-09)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Hong Kong (Chang Way); shell ASN holders in the UK and Russia</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Russia-linked (Proton66/PROSPERO cluster)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Chang Way Technologies Co. Limited</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>changway.hk; CHANGWAY/HOSTWAY panel theme (my.31337.hk)</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Proton66/PROSPERO tenants (IP shifts observed by SpiderLabs)</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Rotating HK/UK/RU shell ASNs; Prefix hopping; Proton66-linked</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Spamhaus ASN-DROP (five ASNs under changway.hk); announced prefixes on Spamhaus DROP; high ASN churn (4 delisted and 2 added within ~9 months)</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>SPAMHAUS-ASNDROP-2026; INTRINSEC-PROSPERO; TRUSTWAVE-PROSPERO; REGISTRY-SNAPSHOT-2026-09</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Hong Kong provider that Intrinsec (Nov 2024) calls a 'likely related' network of PROSPERO/Proton66; Trustwave SpiderLabs observed IP shifts from Proton66 to Chang Way ASNs and the my.31337.hk panel re-themed 'CHANGWAY/HOSTWAY'. Split out of the PROSPERO row (where it was listed as an alias) on 2026-09-25. Spamhaus ASN-DROP lists five ASNs under changway.hk: Chang Way's own AS57523, AS59425 and AS207566 (none announcing) plus the newly added AS201738 (UFO TECHNOLOGIES LIMITED, GB; 7 /24s, all on Spamhaus DROP) and AS211663 (GALEON LLC, RU; 1 /24). Four other changway.hk ASNs listed in Dec 2025 (AS57678, AS208312, AS209309, AS213355) have since been delisted - a rotating-shell pattern. The name similarity between 'UFO Technologies Limited' and Stark's UFO Hosting is not an established link. T2 on ASN-DROP inclusion plus Intrinsec and SpiderLabs reporting.</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>Hong Kong-anchored ring of rotating shell ASNs linked to the Proton66/PROSPERO bulletproof cluster; five ASNs on Spamhaus ASN-DROP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>UAB Host Baltic (serveroffer.lt)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>flagged</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>T2-High Risk (Upstream Enabler)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AS209605 (HOSTBALTIC)</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AS211872 (ALPHA-NETWORKS; no routes); AS135388 (RPL-HK, RMP Protection Limited [HK]; Spamhaus-attributed via serveroffer.lt)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>141.98.8.0/22; 185.36.81.0/24 (AS209605); 93.152.223.0/24; 94.26.0.0/24 (AS135388)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Lithuania; Hong Kong (sibling ASN)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>UAB Host Baltic</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>serveroffer.lt; HOSTBALTIC</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>BtHoster/BTCloud (transit customer); Initial Access Brokers (via BtHoster masscan servers)</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Upstream transit for BPH AS-leasing operators; HK sibling ASN</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Spamhaus ASN-DROP (AS209605; AS135388 under serveroffer.lt); 5 of 6 announced prefixes overlap Spamhaus DROP; Upstream of T1 BtHoster</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>INTRINSEC-BTHOSTER; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Lithuanian hoster named by Intrinsec (June 2025) as a transit provider of the BtHoster/BTCloud AS-leasing operation (see the BtHoster row). Spamhaus ASN-DROP lists AS209605 (serveroffer.lt; 6 announced prefixes including 141.98.8.0/22 and 185.36.81.0/24, 5 of them overlapping Spamhaus DROP) and a newly listed Hong Kong sibling, AS135388 'RPL-HK' (RMP Protection Limited; 93.152.223.0/24 and 94.26.0.0/24). A second Host Baltic registration, AS211872 'ALPHA-NETWORKS', has no routes. Added 2026-09-25 as an upstream enabler (ASN-DROP inclusion plus upstream of a T1 entity, two independent sources).</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>Lithuanian hoster and BtHoster transit provider; two serveroffer.lt ASNs on Spamhaus ASN-DROP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>VPSVAULT.HOST LTD</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>flagged</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>T2-High Risk</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AS215925</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>45.194.92.0/24 (on Spamhaus DROP); 45.198.224.0/24; 45.205.1.0/24</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>VPSVAULT.HOST LTD</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>vpsvault.host</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Mass proxy-scanning sweep (96 hosts; 10.1M connection attempts, Aug 2026)</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Persistent mass-scanning source</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Spamhaus ASN-DROP (AS215925 under vpsvault.host); GreyNoise weekly-brief notable ASN since 2025-12-15</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>SPAMHAUS-ASNDROP-2026; GREYNOISE-WEEKLY-2026-08; REGISTRY-SNAPSHOT-2026-09</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>UK-registered VPS provider whose AS215925 has been on Spamhaus ASN-DROP since at least Dec 2025. GreyNoise has carried it in its weekly brief since 2025-12-15; in the period to 2026-08-30 it produced 10,135,029 connection attempts in a 96-host proxy-scanning sweep. GreyNoise advises against an ASN-level block (shared tenancy). Announces 45.194.92.0/24 (on Spamhaus DROP), 45.198.224.0/24 and 45.205.1.0/24. Added 2026-09-25 at T2 under the taxonomy's ASN-DROP escalation rule (Spamhaus plus GreyNoise meet the two-source T2 evidence floor); no malware/C2 attribution yet.</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>UK VPS provider on Spamhaus ASN-DROP and a persistent GreyNoise-tracked mass-scanning source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Feo Prest SRL</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>flagged</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>T2-High Risk</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AS208137</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>62.60.131.0/24; 213.177.179.0/24; 213.209.159.0/24 (on Spamhaus DROP)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Feo Prest SRL</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>feoprest.info</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>ENV/secret-file crawling; CVE-2025-48927 exploitation attempts</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Persistent high-volume scanning and exploitation source</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Spamhaus ASN-DROP (AS208137 under feoprest.info); GreyNoise weekly-brief notable IPs since 2026-06-22</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>SPAMHAUS-ASNDROP-2026; GREYNOISE-WEEKLY-2026-08; REGISTRY-SNAPSHOT-2026-09</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Romanian provider on Spamhaus ASN-DROP (feoprest.info). GreyNoise (weekly brief to 2026-08-30): 40 active hosts; 213.209.159.175, carried since the 2026-06-22 brief, produced 1.8M sessions and 23% of CVE-2025-48927 exploitation attempts; 213.209.159.154 and .175 were top-volume ENV crawlers. Announces 62.60.131.0/24, 213.177.179.0/24 and 213.209.159.0/24 (the last on Spamhaus DROP). Added 2026-09-25 at T2 under the taxonomy's ASN-DROP escalation rule (Spamhaus plus GreyNoise meet the two-source T2 evidence floor); no malware/C2 attribution yet.</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>Romanian provider on Spamhaus ASN-DROP hosting persistent high-volume scanning and exploitation sources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>QTFY (QScan / QTRouter)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>seized</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>T1-Confirmed BPH (Anonymization/Proxy Enabler)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>China (Nanjing); global proxy/ORB nodes</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Nanjing Xinjiuwei Network Technology Co. (employer of the QTFY operators)</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>QTFY; QScan; QTRouter; qtproxy.xyz; Fast Labyrinth / QTProxy (Lumen tracking names)</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>DOJ/FBI court-authorised seizure of QScan and QTRouter domains, Aug 26 2026</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>PRC state-sponsored actors (MSS and PLA customers)</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>QScan (IoT scanner and infector); QTRouter (obfuscation network)</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>State-enablement 'infrastructure quartermaster'; ORB network mixing compromised IoT, commercial proxy subscriptions and leased VPS</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>LE seizure; Commercial proxy-service nodes and leased VPS chained through Clash</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>DOJ-QTFY-2026; LUMEN-QTFY-2026</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>On 2026-08-26 DOJ and the FBI seized, under court authorisation, the domains hard-coded into QScan (an IoT scanner and infector) and QTRouter (an obfuscation network) run by the 'QTFY' technical-quartermaster group, whose staff work for Nanjing Xinjiuwei Network Technology Co. and whose customers include the MSS and PLA. QTRouter chained compromised IoT devices, bulk-bought Chinese commercial proxy subscriptions and leased VPSs through Clash, with admin servers at qtproxy.xyz; reported victims include NASA, the Federal Reserve, DOE, DOJ, HHS, NIH and the US Senate. Lumen Black Lotus Labs, which tracked the network as 'Fast Labyrinth'/'QTProxy', collaborated. A state-enablement proxy TAE showing commercial proxy supply feeding espionage ORB networks. No ASN of its own has been published.</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>PRC 'infrastructure quartermaster' proxy/ORB platform serving state hackers; domains seized by DOJ/FBI in Aug 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>IPIDEA residential-proxy network</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>exposed</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>T2-High Risk (Anonymization/Proxy Enabler)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Global residential exit nodes</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>360 Proxy; 922 Proxy; ABC Proxy; Cherry Proxy; IP2World; Luna Proxy; PIA S5 Proxy; PY Proxy; SDKs: Castar, Earn, Hex, Packet SDK</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>550+ threat groups in one week (GTIG), reportedly including APT28, Sandworm and Volt Typhoon</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>BADBOX 2.0 (facilitated)</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Residential-proxy network built from SDK-enrolled and compromised devices; Multi-brand resale</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Private-sector disruption (Google GTIG, Jan 2026); SDK-based covert device enrollment</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>GTIG-IPIDEA-2026</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>On 2026-01-29 Google's Threat Intelligence Group announced legal action against IPIDEA's command domains, with Cloudflare, Spur and Lumen Black Lotus Labs, shrinking its device pool by millions; Play Protect now removes apps carrying IPIDEA SDKs. GTIG saw more than 550 threat groups using the network in a single week (Google's John Hultquist named APT28, Sandworm and Volt Typhoon among them); IPIDEA advertised 6.1M IPs updated daily. It is resold under at least eight brands and enrolled devices through the Castar, Earn, Hex and Packet SDKs; it also facilitated BADBOX 2.0. Part of the residential-proxy enforcement lineage 911 S5 -&gt; Moonlander (5socks/Anyproxy) -&gt; SocksEscort -&gt; IPIDEA -&gt; Asocks -&gt; NetNut -&gt; QTRouter. Operator identity and jurisdiction are unverified; not sanctioned. Status 'exposed' because the disruption was a private-sector legal action rather than a law-enforcement seizure.</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>Multi-brand residential-proxy network used by 550+ threat groups; disrupted by Google in Jan 2026.</t>
         </is>
       </c>
     </row>

--- a/BPH_Master.xlsx
+++ b/BPH_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y72"/>
+  <dimension ref="A1:Y71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>dormant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Russia-operated BPH registered in the Seychelles at an address that appears in the Panama Papers/Offshore Leaks (Team Cymru). Team Cymru (2022) listed four 1337TEAM ASNs operating mainly from AS51381 and recommended blocking 185.215.113.0/24, a long-running Amadey/RedLine C2 block. Current state (2026-09-25): AS51381 and AS56873 are still registered to 1337TEAM LIMITED and remain on Spamhaus ASN-DROP but announce nothing; AS39770 and AS60424 are gone from the registry; 185.215.113.0/24 is unrouted. Status kept 'active' because no dissolution, sanction or seizure is documented - treat the network as dormant and watch for re-announcement. Corrections 2026-09-25: upstreams are historical and Filanco (AS3175, Datahouse.ru) was a downstream, not an upstream; the Turla link was removed (Microsoft's Secret Blizzard/Amadey reporting does not name ELITETEAM); the unsourced 'VirusTotal 100%' claim and BabbleLoader were removed.</t>
+          <t>Russia-operated BPH registered in the Seychelles at an address that appears in the Panama Papers/Offshore Leaks (Team Cymru). Team Cymru (2022) listed four 1337TEAM ASNs operating mainly from AS51381 and recommended blocking 185.215.113.0/24, a long-running Amadey/RedLine C2 block. Current state (2026-09-25): AS51381 and AS56873 are still registered to 1337TEAM LIMITED and remain on Spamhaus ASN-DROP but announce nothing; AS39770 and AS60424 are gone from the registry; 185.215.113.0/24 is unrouted. Status set to 'dormant' on 2026-09-25: both live ASNs remain registered to 1337TEAM LIMITED but announce nothing, and no dissolution, sanction or seizure is documented, so the T1 tier stands; watch AS51381/AS56873 for re-announcement or transfer. Corrections 2026-09-25: upstreams are historical and Filanco (AS3175, Datahouse.ru) was a downstream, not an upstream; the Turla link was removed (Microsoft's Secret Blizzard/Amadey reporting does not name ELITETEAM); the unsourced 'VirusTotal 100%' claim and BabbleLoader were removed.</t>
         </is>
       </c>
     </row>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T3-Suspected</t>
+          <t>T1-Confirmed BPH</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Switzerland (marketed); unverified</t>
+          <t>Switzerland (marketed; rud.is places PLI-AS hosts in Zurich/Rumlang data centres)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>No KYC; DMCA-ignored; Crypto payment (Monero); Permits Tor/Kali</t>
+          <t>No KYC; DMCA-ignored; Crypto payment (Monero); Permits Tor/Kali; Self-advertised 'Abuse &amp; DMCA ignore' hosting (BlackHatWorld); Honeypot-observed brute-force and scanning from PLI-AS (rud.is)</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>RF-TAE-2026; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>RF-TAE-2026; RF-AUROLOGIC; RUDIS-BPH-WATCH; BOLSTER-BPH; BHW-PRIVATEALPS; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Swiss-marketed offshore brand (privatealps.net) of Private Layer INC (Panama registry holder of AS51852/AS52288), marketing DMCA-ignored, no-logs, anonymous, Monero-friendly hosting. RF ranks PrivateAlps #6 in its 2025 Threat Density top 10, and RF's aurologic report ties Global-Data System IT (SWISSNETWORK02) to PrivateAlps. Tier raised T4 -&gt; T3 on 2026-09-25: a top-10 density ranking is inconsistent with T4's 'not predominantly malicious'; T2/T1 would need further independent evidence (not on Spamhaus ASN-DROP). Correction: registry entity is Private Layer INC (Panama), not Private Layer AG (Switzerland).</t>
+          <t>Swiss-marketed offshore brand (privatealps.net) of Private Layer INC (Panama registry holder of AS51852/AS52288), marketing DMCA-ignored, no-logs, anonymous, Monero-friendly hosting. RF ranks PrivateAlps #6 in its 2025 Threat Density top 10, and RF's aurologic report ties Global-Data System IT (SWISSNETWORK02) to PrivateAlps. Independent corroboration: the rud.is weekly Bulletproof Hosting Watch tracks PLI-AS among 26 curated BPH ASNs and names it one of the most aggressive (e.g. week of 2026-06-08: RDP brute-force, DCE/RPC enumeration, WordPress login scanning); a Bolster AI phishing study names Private Alps among high-profile BPH providers popular on underground forums for VPS/RDP/VPN hosting; and PrivateAlps advertised 'Abuse &amp; DMCA ignore' offshore servers on BlackHatWorld. Tier raised T4 -&gt; T1 on 2026-09-25 (taxonomy T1: RF top-decile Threat Density - #6 in RF's 2025 top 10, above Femo IT/Defhost at #8; minimum evidence met by RF, rud.is and Bolster). Not on Spamhaus ASN-DROP, and the rud.is and Bolster texts were read via search excerpts only - re-check both at the next review. Correction: registry entity is Private Layer INC (Panama), not Private Layer AG (Switzerland).</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>T2-High Risk</t>
+          <t>T1-Confirmed BPH</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Non-cooperative with LE historically; Key infrastructure node</t>
+          <t>Non-cooperative with LE historically; Key infrastructure node; Founder arrested in FIOD action (2026-05-18)</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>KREBS-BPH; RF-INFRA-2025; GREYNOISE-STARK; KREBS-FIOD-STARK; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>KREBS-BPH; RF-INFRA-2025; RF-STARK; GREYNOISE-STARK; KREBS-FIOD-STARK; DCD-FIOD-2026; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Founded in 2004 by Andrey Nesterenko, who was arrested in the FIOD raid of 2026-05-18 (name press-reported). Krebs: WorkTitans reached the internet solely through MIRhosting, and AS52000 is the first peer in AS209847's aut-num. The 2008 StopGeorgia.ru hosting is attributed (Jeffrey Carr) to the related Innovation IT Solutions Corp; Nesterenko said he could not verify it. De Volkskrant data showed WorkTitans and MIRhosting as the most-used networks in pro-Russian attacks on Danish bodies (Nov 2025). AS52000 has shrunk to two IPv4 /24s (185.15.209.0/24, 185.15.210.0/24). T1 candidate if the FIOD seizure is confirmed to have covered MIRhosting-operated infrastructure. Unverified: the 'temporarily paused services to WorkTitans' quote.</t>
+          <t>Founded in 2004 by Andrey Nesterenko, who was arrested in the FIOD raid of 2026-05-18 (name press-reported). Krebs: WorkTitans reached the internet solely through MIRhosting, and AS52000 is the first peer in AS209847's aut-num. The 2008 StopGeorgia.ru hosting is attributed (Jeffrey Carr) to the related Innovation IT Solutions Corp; Nesterenko said he could not verify it. De Volkskrant data showed WorkTitans and MIRhosting as the most-used networks in pro-Russian attacks on Danish bodies (Nov 2025). AS52000 has shrunk to two IPv4 /24s (185.15.209.0/24, 185.15.210.0/24). Tier raised T2 -&gt; T1 on 2026-09-25 (taxonomy T1: subject of a law-enforcement action targeting hosting infrastructure - its founder was arrested in the FIOD action against the WorkTitans network, which reached the internet solely through MIRhosting; reported by Krebs and DatacenterDynamics). Whether MIRhosting-operated servers were among the 800+ seized is unconfirmed. Unverified: the 'temporarily paused services to WorkTitans' quote.</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>flagged</t>
+          <t>dormant</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Seychelles-registered holder of AS34888 and AS42624, transferred from Simple Carrier LLC (July 2024). RF (Sept-Nov 2025): 11 IPv4 prefixes (2,816 addresses) all via aurologic AS30823, top ten for malicious-activity density in Sept 2025, linked to PrivateAlps. Both ASNs were on Spamhaus ASN-DROP (simplecarrier.net) in Dec 2025 and have since been delisted; neither announces anything now (e.g. 185.196.8.0/22 and 185.208.156.0/22 are unrouted). Do not confuse with the unrelated Iranian swissnetwork.io ASNs (AS199467, AS209373). Correction 2026-09-25: registration is Seychelles, not Switzerland.</t>
+          <t>Seychelles-registered holder of AS34888 and AS42624, transferred from Simple Carrier LLC (July 2024). RF (Sept-Nov 2025): 11 IPv4 prefixes (2,816 addresses) all via aurologic AS30823, top ten for malicious-activity density in Sept 2025, linked to PrivateAlps. Both ASNs were on Spamhaus ASN-DROP (simplecarrier.net) in Dec 2025 and have since been delisted; neither announces anything now (e.g. 185.196.8.0/22 and 185.208.156.0/22 are unrouted). Do not confuse with the unrelated Iranian swissnetwork.io ASNs (AS199467, AS209373). Correction 2026-09-25: registration is Seychelles, not Switzerland. Status flagged -&gt; dormant on 2026-09-25: both ASNs remain registered to Global-Data but announce nothing, and the newest reporting (RF, Sept-Nov 2025) is more than six months old. The T2 tier stands; watch for re-announcement, particularly behind aurologic.</t>
         </is>
       </c>
     </row>
@@ -3766,52 +3766,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CDNCloud</t>
+          <t>NECHAEVDS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>suspected</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>T5-Watch List</t>
+          <t>T3-Suspected</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AS213194 (NECHAEVDS-AS; 193.37.69.0/24)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>193.37.69.0/24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Russia (individual registrant)</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>China (Alibaba-routed)</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>cdnclouds.net</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Alibaba Cloud</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Low-footprint CDN brand</t>
+          <t>Zservers successor hop network</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>Insufficient data</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>2015-01</t>
+          <t>Association with sanctioned entity (Zservers prefix recipient); 100% DGA domains and TutaMail abuse contact (Silent Push, relayed)</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -3819,21 +3814,26 @@
           <t>2026-09-25</t>
         </is>
       </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>INTRINSEC-UAC-2025; MALTRAIL-WORST-ASNS; REGISTRY-SNAPSHOT-2026-09</t>
+        </is>
+      </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Low-footprint brand claimed to sit on Hong Kong Alibaba infrastructure. The 2026-09-25 audit found no ASN, registry record, Spamhaus ASN-DROP listing or CTI report for CDNCloud or cdnclouds.net, and it is absent from the Silent Push 2025 red-flag table that appears to be the source of the other T5 rows. It does not meet the T5 minimum ('credible source with structural indicators'); retained only pending a source and a candidate for removal at the next review.</t>
+          <t>AS213194, registered to a Russian individual (the AS-name derives from the registrant's surname), announces only 193.37.69.0/24. It is the same ASN the Zservers row lists as a post-sanction hop: Intrinsec (March 2025) assessed with high confidence that Zservers prefixes moved to AS213194, AS61336 and AS213010. A relayed Silent Push 2025 table flags it for 100% DGA domains and a TutaMail abuse contact. Tier raised T5 -&gt; T3 on 2026-09-25; merging into the Zservers row is an alternative. Not on Spamhaus ASN-DROP.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NECHAEVDS</t>
+          <t>NETINNOVATIONLLC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>suspected</t>
+          <t>flagged</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3843,32 +3843,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AS213194 (NECHAEVDS-AS; 193.37.69.0/24)</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>193.37.69.0/24</t>
+          <t>AS62864 (NILAS; ARIN)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AS23865; AS34985; AS149286 (APNIC; registered, no routes)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Russia (individual registrant)</t>
+          <t>United States (registry); Japan per Spamhaus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Mixed APNIC/ARIN/AFRINIC space (no evidence of Eastern Europe)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>net innovation llc</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>netinnovation.net</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Zservers successor hop network</t>
+          <t>Multi-registry ASN set; DGA hosting</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Association with sanctioned entity (Zservers prefix recipient); 100% DGA domains and TutaMail abuse contact (Silent Push, relayed)</t>
+          <t>Spamhaus ASN-DROP (all four ASNs under netinnovation.net); Gmail abuse contact; DGA domains; 18-day abuse response (Silent Push, relayed)</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -3878,19 +3888,19 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>INTRINSEC-UAC-2025; MALTRAIL-WORST-ASNS; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>AS213194, registered to a Russian individual (the AS-name derives from the registrant's surname), announces only 193.37.69.0/24. It is the same ASN the Zservers row lists as a post-sanction hop: Intrinsec (March 2025) assessed with high confidence that Zservers prefixes moved to AS213194, AS61336 and AS213010. A relayed Silent Push 2025 table flags it for 100% DGA domains and a TutaMail abuse contact. Tier raised T5 -&gt; T3 on 2026-09-25; merging into the Zservers row is an alternative. Not on Spamhaus ASN-DROP.</t>
+          <t>Four ASNs registered to 'net innovation llc' - AS62864 (ARIN; 14 prefixes including DROP-listed 164.155.0.0/16 and 168.80.0.0/15 space), AS34985 (7), AS23865 (5) and AS149286 (none) - all on Spamhaus ASN-DROP under netinnovation.net (cc JP). A relayed Silent Push 2025 table flags AS34985 for a Gmail abuse contact, DGA usage and an 18-day abuse response. The earlier 'no public CTI designation' note was wrong. Raised T5 -&gt; T3 (status flagged) on 2026-09-25; the ASN-DROP escalation rule implies T2 once a second independent B/C source is read directly.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NETINNOVATIONLLC</t>
+          <t>Tiger Network Limited (Tiger Net)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3905,42 +3915,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>AS62864 (NILAS; ARIN)</t>
+          <t>AS48589 (TIGER)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AS23865; AS34985; AS149286 (APNIC; registered, no routes)</t>
+          <t>AS211121 (INDIA)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>43.255.16.0/22; 103.239.0.0/22; 112.143.0.0/20; 112.143.30.0/23; 124.68.32.0/19 (AS48589)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>United States (registry); Japan per Spamhaus</t>
+          <t>United Kingdom (registry)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Mixed APNIC/ARIN/AFRINIC space (no evidence of Eastern Europe)</t>
+          <t>Asian address space; operator reportedly Ukraine-linked (Silent Push, relayed)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>net innovation llc</t>
+          <t>Tiger Network Limited</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>netinnovation.net</t>
+          <t>Tiger Net; imtigernet</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Multi-registry ASN set; DGA hosting</t>
+          <t>Asian address space under a UK registrant</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Spamhaus ASN-DROP (all four ASNs under netinnovation.net); Gmail abuse contact; DGA domains; 18-day abuse response (Silent Push, relayed)</t>
+          <t>Spamhaus ASN-DROP (AS48589; AS211121 under imtigernet); Gmail abuse contact; DGA domains (Silent Push, relayed)</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -3955,69 +3970,59 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Four ASNs registered to 'net innovation llc' - AS62864 (ARIN; 14 prefixes including DROP-listed 164.155.0.0/16 and 168.80.0.0/15 space), AS34985 (7), AS23865 (5) and AS149286 (none) - all on Spamhaus ASN-DROP under netinnovation.net (cc JP). A relayed Silent Push 2025 table flags AS34985 for a Gmail abuse contact, DGA usage and an 18-day abuse response. The earlier 'no public CTI designation' note was wrong. Raised T5 -&gt; T3 (status flagged) on 2026-09-25; the ASN-DROP escalation rule implies T2 once a second independent B/C source is read directly.</t>
+          <t>Renamed from 'Tiger Net (SOW-A)' on 2026-09-25. Tiger Network Limited (GB) holds AS48589 (5 prefixes, 14,848 addresses of Asian space) and AS211121 (4 prefixes); both are on Spamhaus ASN-DROP (imtigernet) and their prefixes overlap Spamhaus DROP. A relayed Silent Push 2025 table lists 'AS48589 SOW-A-AS (Tiger Net) - Ukraine, Gmail, DGA'. No current 'SOW-A' handle exists; the only registry match, AS43613 'SOWA' (LLC BIGNET UKRAINE), is a separate ASN-DROP entry, so the relay may have merged two records. Raised T5 -&gt; T3 (status flagged); T2 pending a second independent B/C source.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Tiger Network Limited (Tiger Net)</t>
+          <t>HOSTYPE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>flagged</t>
+          <t>dormant</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>T3-Suspected</t>
+          <t>T5-Watch List</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>AS48589 (TIGER)</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>AS211121 (INDIA)</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>43.255.16.0/22; 103.239.0.0/22; 112.143.0.0/20; 112.143.30.0/23; 124.68.32.0/19 (AS48589)</t>
+          <t>AS49217 (registered; no routes)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>United Kingdom (registry)</t>
+          <t>United States (Wyoming LLC per Silent Push; registry cc US)</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Asian address space; operator reportedly Ukraine-linked (Silent Push, relayed)</t>
+          <t>Turkey per Spamhaus</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Tiger Network Limited</t>
+          <t>HOSTYPE LLC</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Tiger Net; imtigernet</t>
+          <t>hostype.com</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Asian address space under a UK registrant</t>
+          <t>Wyoming shell; dormant</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>Spamhaus ASN-DROP (AS48589; AS211121 under imtigernet); Gmail abuse contact; DGA domains (Silent Push, relayed)</t>
+          <t>Historical Spamhaus ASN-DROP listing (Feb 2024 and Dec 2025 snapshots; delisted); Gmail abuse contact; DGA domains; 30-day abuse response (Silent Push, relayed)</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -4032,59 +4037,69 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Renamed from 'Tiger Net (SOW-A)' on 2026-09-25. Tiger Network Limited (GB) holds AS48589 (5 prefixes, 14,848 addresses of Asian space) and AS211121 (4 prefixes); both are on Spamhaus ASN-DROP (imtigernet) and their prefixes overlap Spamhaus DROP. A relayed Silent Push 2025 table lists 'AS48589 SOW-A-AS (Tiger Net) - Ukraine, Gmail, DGA'. No current 'SOW-A' handle exists; the only registry match, AS43613 'SOWA' (LLC BIGNET UKRAINE), is a separate ASN-DROP entry, so the relay may have merged two records. Raised T5 -&gt; T3 (status flagged); T2 pending a second independent B/C source.</t>
+          <t>AS49217 is registered to HOSTYPE LLC (registry cc US; Spamhaus cc TR; a relayed Silent Push 2025 table calls it a Wyoming shell with a Gmail abuse contact, DGA usage and a 30-day abuse response). It was on Spamhaus ASN-DROP in the Feb 2024 and Dec 2025 snapshots, has since been delisted, and announces nothing. Fits T5's 'historically associated with abuse, currently quiescent'; status set to 'dormant' on 2026-09-25 - watch for re-announcement or transfer.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HOSTYPE</t>
+          <t>StarCloud Global (Triad Nexus)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>flagged</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>T5-Watch List</t>
+          <t>T3-Suspected</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AS49217 (registered; no routes)</t>
+          <t>AS140224 (historical; registry now 'Nebula Global LLC' [US]; no routes)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AS149040 (STARCLOUD GLOBAL PTE. LTD.; no routes)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>United States (Wyoming LLC per Silent Push; registry cc US)</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Turkey per Spamhaus</t>
+          <t>Singapore (PTE. LTD.); US (Colorado) registrant address per Silent Push</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>HOSTYPE LLC</t>
+          <t>StarCloud Global Pte. Ltd.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>hostype.com</t>
+          <t>Triad Nexus-affiliated brand</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Triad Nexus; Silver Fox</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Triad Nexus scam infrastructure; Silver Fox phishing domains; Cobalt Strike C2</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Wyoming shell; dormant</t>
+          <t>Triad Nexus CDN front brand</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>Historical Spamhaus ASN-DROP listing (Feb 2024 and Dec 2025 snapshots; delisted); Gmail abuse contact; DGA domains; 30-day abuse response (Silent Push, relayed)</t>
+          <t>Phishing-ASN ranking (#13); Triad Nexus infrastructure (Silent Push, relayed); ESET Silver Fox hosting</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -4094,74 +4109,64 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>SILENTPUSH-FUNNULL; ESET-SILVERFOX-IOC; C2INTELFEEDS; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>AS49217 is registered to HOSTYPE LLC (registry cc US; Spamhaus cc TR; a relayed Silent Push 2025 table calls it a Wyoming shell with a Gmail abuse contact, DGA usage and a 30-day abuse response). It was on Spamhaus ASN-DROP in the Feb 2024 and Dec 2025 snapshots, has since been delisted, and announces nothing. Fits T5's 'historically associated with abuse, currently quiescent'; watch for re-announcement.</t>
+          <t>Singapore-registered hosting brand. A relayed Silent Push 2025 table lists AS140224 'STARCLOUD GLOBAL SG' as Triad Nexus infrastructure with a residential Colorado address and a 4-day abuse response; a phishing-ASN ranking put AS140224 at #13 (237,056 routed IPv4; 3,032 phishing attacks). ESET lists Silver Fox domains on 149.104.24.24 with hosting provider 'STARCLOUD GLOBAL PTE. LTD.' (first seen 2026-03-10), and a Cobalt Strike C2 on 154.38.114.115 was recorded under the same provider (Sept 2026); both IPs are now routed by other HK ASNs. AS140224 now shows as 'Nebula Global LLC' (US) and AS149040 announces nothing. CORRECTION 2026-09-25: StarCloud is NOT an OFAC designee - the earlier 'OFAC May 29 2025 (via FUNNULL lineage)' entry was removed (OFAC named only Funnull Technology Inc. and Liu Lizhi).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>StarCloud Global (Triad Nexus)</t>
+          <t>DDoS-Guard</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>flagged</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>T3-Suspected</t>
+          <t>T5-Watch List</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>AS140224 (historical; registry now 'Nebula Global LLC' [US]; no routes)</t>
+          <t>AS57724 (DDOS-GUARD)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AS149040 (STARCLOUD GLOBAL PTE. LTD.; no routes)</t>
+          <t>AS49612 (COGNITIVE-CLOUD-NET handle; 1 prefix)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Singapore (PTE. LTD.); US (Colorado) registrant address per Silent Push</t>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Russia</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>StarCloud Global Pte. Ltd.</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Triad Nexus-affiliated brand</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Triad Nexus; Silver Fox</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>Triad Nexus scam infrastructure; Silver Fox phishing domains; Cobalt Strike C2</t>
+          <t>DDoS-Guard LTD</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Triad Nexus CDN front brand</t>
+          <t>Dual-use DDoS mitigation + hosting</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Phishing-ASN ranking (#13); Triad Nexus infrastructure (Silent Push, relayed); ESET Silver Fox hosting</t>
+          <t>Dual-use; Historical controversial customers; Russian ecosystem</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -4171,19 +4176,19 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>SILENTPUSH-FUNNULL; ESET-SILVERFOX-IOC; C2INTELFEEDS; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Singapore-registered hosting brand. A relayed Silent Push 2025 table lists AS140224 'STARCLOUD GLOBAL SG' as Triad Nexus infrastructure with a residential Colorado address and a 4-day abuse response; a phishing-ASN ranking put AS140224 at #13 (237,056 routed IPv4; 3,032 phishing attacks). ESET lists Silver Fox domains on 149.104.24.24 with hosting provider 'STARCLOUD GLOBAL PTE. LTD.' (first seen 2026-03-10), and a Cobalt Strike C2 on 154.38.114.115 was recorded under the same provider (Sept 2026); both IPs are now routed by other HK ASNs. AS140224 now shows as 'Nebula Global LLC' (US) and AS149040 announces nothing. CORRECTION 2026-09-25: StarCloud is NOT an OFAC designee - the earlier 'OFAC May 29 2025 (via FUNNULL lineage)' entry was removed (OFAC named only Funnull Technology Inc. and Liu Lizhi).</t>
+          <t>Dual-use Russian DDoS mitigation and hosting provider. Main network is AS57724 (21 IPv4 prefixes); AS49612 now announces a single /24 under the handle COGNITIVE-CLOUD-NET; a further 'DDoS-Guard Corp' ASN (AS262254) is dark. Historically an upstream of ELITETEAM (as of Sept 2022, per Team Cymru). Not on Spamhaus ASN-DROP. Unverified in this audit: the Parler/8chan hosting history. Not classified BPH, but persistently present in the Russian cybercrime ecosystem.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DDoS-Guard</t>
+          <t>1GSERVERS LLC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4198,37 +4203,37 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>AS57724 (DDOS-GUARD)</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>AS49612 (COGNITIVE-CLOUD-NET handle; 1 prefix)</t>
+          <t>AS14315</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>DDoS-Guard LTD</t>
+          <t>1GSERVERS LLC</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Lumma</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Dual-use DDoS mitigation + hosting</t>
+          <t>Small US operator appearing alongside BPH entities</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Dual-use; Historical controversial customers; Russian ecosystem</t>
+          <t>Single source; Limited indicators</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -4238,64 +4243,89 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>REGISTRY-SNAPSHOT-2026-09</t>
+          <t>INTEL-INSIGHTS-QWINS; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Dual-use Russian DDoS mitigation and hosting provider. Main network is AS57724 (21 IPv4 prefixes); AS49612 now announces a single /24 under the handle COGNITIVE-CLOUD-NET; a further 'DDoS-Guard Corp' ASN (AS262254) is dark. Historically an upstream of ELITETEAM (as of Sept 2022, per Team Cymru). Not on Spamhaus ASN-DROP. Unverified in this audit: the Parler/8chan hosting history. Not classified BPH, but persistently present in the Russian cybercrime ecosystem.</t>
+          <t>Small US-registered operator (AS14315; 51 IPv4 prefixes; ipverse role 'midsize transit') appearing alongside Proton66, Railnet and Femo IT in a Lumma malware hunt (single source; the blog could not be re-read). Not on Spamhaus ASN-DROP.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1GSERVERS LLC</t>
+          <t>CrazyRDP</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>T5-Watch List</t>
+          <t>T1-Confirmed BPH</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>AS14315</t>
+          <t>AS394711 (historical; Limenet; reassigned to KorGrid LLC [US] - do not block)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AS211252 (historical; Delis LLC; reassigned to Marushin K.K. [JP] - do not block)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United States (registry country of both ASNs); servers in the Netherlands</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1GSERVERS LLC</t>
+          <t>Limenet LLC</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Delis LLC; CrazyRDP; crazyrdp.com</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Serverion / Des Capital B.V. (colocation; community-sourced, weak)</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Dutch police seizure Nov 12 2025 (announced Nov 14 2025; ~250 physical servers in The Hague and Zoetermeer) - police did not name the service and said the case is not connected to Operation Endgame</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>80+ LE investigations; ransomware; CSAM distribution</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>Lumma</t>
+          <t>Rhadamanthys; VenomRAT; Elysium botnet</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Small US operator appearing alongside BPH entities</t>
+          <t>No-KYC no-logs; RDP/VPS services; Telegram operations</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Single source; Limited indicators</t>
+          <t>No KYC; No logs; Underground forum presence; High malicious traffic ratio</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -4303,26 +4333,31 @@
           <t>2026-09-25</t>
         </is>
       </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>~17-18% (RF chart #2)</t>
+        </is>
+      </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>INTEL-INSIGHTS-QWINS; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>RF-TAE-2026; SPAMHAUS-BPH; BLEEPINGCOMPUTER-BPH; REGISTRY-SNAPSHOT-2026-09; POLITIE-CRAZYRDP-2025</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Small US-registered operator (AS14315; 51 IPv4 prefixes; ipverse role 'midsize transit') appearing alongside Proton66, Railnet and Femo IT in a Lumma malware hunt (single source; the blog could not be re-read). Not on Spamhaus ASN-DROP.</t>
+          <t>Major no-KYC RDP/VPS host (RF 2025 Threat Density #2). On 2025-11-12 Dutch police seized about 250 physical servers in data centres in The Hague and Zoetermeer (thousands of virtual servers taken offline) of a bulletproof hoster active since 2022 and seen in 80+ investigations (ransomware, botnets, phishing, CSAM). Police did not name it; sources told BleepingComputer it was CrazyRDP, which went offline. Dutch police told BleepingComputer the case is NOT connected to Operation Endgame (the earlier Endgame label was wrong). The Limenet (AS394711) and Delis (AS211252) ASNs rest on community sources and Spamhaus ASN-DROP listings of Feb 2024 (limenet.io; delis.one); both ASNs have since been re-issued to unrelated companies - do not block them.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CrazyRDP</t>
+          <t>Kaopu Cloud HK Limited</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>flagged</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4332,62 +4367,62 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>AS394711 (historical; Limenet; reassigned to KorGrid LLC [US] - do not block)</t>
+          <t>AS138915</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AS211252 (historical; Delis LLC; reassigned to Marushin K.K. [JP] - do not block)</t>
+          <t>AS58854 (Kaopu Cloud [CN]); AS154177 (LIGHT NODE LIMITED [HK]; Spamhaus-attributed via kaopuyun.com)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>United States (registry country of both ASNs); servers in the Netherlands</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Hong Kong/Global</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Limenet LLC</t>
+          <t>Kaopu Cloud HK Limited</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Delis LLC; CrazyRDP; crazyrdp.com</t>
+          <t>Keepo Cloud HK</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Serverion / Des Capital B.V. (colocation; community-sourced, weak)</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Dutch police seizure Nov 12 2025 (announced Nov 14 2025; ~250 physical servers in The Hague and Zoetermeer) - police did not name the service and said the case is not connected to Operation Endgame</t>
+          <t>Cogent; Arelion; NTT; Level3; PCCW Global</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>80+ LE investigations; ransomware; CSAM distribution</t>
+          <t>RedHotel (C2, 2022-23); ToolShell/SharePoint exploitation (2025); FortiGate SSO abuse (Dec 2025); Bulbature/GobRAT operators</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>Rhadamanthys; VenomRAT; Elysium botnet</t>
+          <t>RedHotel tooling; GobRAT; Cobalt Strike</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>No-KYC no-logs; RDP/VPS services; Telegram operations</t>
+          <t>Large IP allocation; BitTorrent/Tor/VPN activity observed</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>No KYC; No logs; Underground forum presence; High malicious traffic ratio</t>
+          <t>Spamhaus ASN-DROP (AS138915; AS58854; AS154177 under kaopuyun.com); C2 for 3+ families/actors; GreyNoise React2Shell exploitation source</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>2019-03-19</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -4397,94 +4432,84 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>~17-18% (RF chart #2)</t>
+          <t>~8-10% (RF chart #4)</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>RF-TAE-2026; SPAMHAUS-BPH; BLEEPINGCOMPUTER-BPH; REGISTRY-SNAPSHOT-2026-09; POLITIE-CRAZYRDP-2025</t>
+          <t>RF-TAE-2026; SPAMHAUS-ASNDROP-2026; RF-REDHOTEL-2023; ESET-TOOLSHELL-2025; SEKOIA-BULBATURE; GREYNOISE-REACT2SHELL-2026; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Major no-KYC RDP/VPS host (RF 2025 Threat Density #2). On 2025-11-12 Dutch police seized about 250 physical servers in data centres in The Hague and Zoetermeer (thousands of virtual servers taken offline) of a bulletproof hoster active since 2022 and seen in 80+ investigations (ransomware, botnets, phishing, CSAM). Police did not name it; sources told BleepingComputer it was CrazyRDP, which went offline. Dutch police told BleepingComputer the case is NOT connected to Operation Endgame (the earlier Endgame label was wrong). The Limenet (AS394711) and Delis (AS211252) ASNs rest on community sources and Spamhaus ASN-DROP listings of Feb 2024 (limenet.io; delis.one); both ASNs have since been re-issued to unrelated companies - do not block them.</t>
+          <t>Hong Kong ISP (APNIC-registered 2019) announcing 113,664 IPv4 addresses in 168 prefixes on AS138915 (Sept 2026; the earlier '182,272 / 50+ netblocks' is outdated). RF ranks Kaopu #4 in its 2025 Threat Density top 10. Spamhaus ASN-DROP lists three kaopuyun.com ASNs: AS138915, AS58854 and AS154177 (LIGHT NODE LIMITED, 129 IPv4 prefixes); a fourth (AS140666, ANY DIGITAL PTE. LTD.) was listed earlier and removed. Independent vendor evidence: RF Insikt (RedHotel heavily favouring Kaopu for C2, 2022-23); ESET (ToolShell SharePoint exploitation from Kaopu IPs, July 2025); Arctic Wolf (malicious FortiGate SSO logins, Dec 2025); Sekoia (Bulbature/GobRAT staging servers all on AS138915); GreyNoise React2Shell sources. Tier raised T3 -&gt; T1 (status flagged) on 2026-09-25 (taxonomy T1: RF top-decile Threat Density - #4 in RF's 2025 top 10, the basis also used for Femo IT/Defhost at #8; minimum evidence met by RF, Spamhaus, ESET, Sekoia and GreyNoise).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kaopu Cloud HK Limited</t>
+          <t>Grinex</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>flagged</t>
+          <t>sanctioned</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>T2-High Risk</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>AS138915</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>AS58854 (Kaopu Cloud [CN]); AS154177 (LIGHT NODE LIMITED [HK]; Spamhaus-attributed via kaopuyun.com)</t>
+          <t>T1-Confirmed BPH (Financial Enabler)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Russia / Kyrgyz Republic</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Hong Kong/Global</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Kaopu Cloud HK Limited</t>
+          <t>Grinex</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Keepo Cloud HK</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Cogent; Arelion; NTT; Level3; PCCW Global</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>RedHotel (C2, 2022-23); ToolShell/SharePoint exploitation (2025); FortiGate SSO abuse (Dec 2025); Bulbature/GobRAT operators</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>RedHotel tooling; GobRAT; Cobalt Strike</t>
+          <t>Garantex successor; TokenSpot (likely front, per TRM)</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Garantex (predecessor)</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>OFAC Aug 14 2025 (as Garantex's direct successor); UK Aug 20 2025 (Grinex LLC, Russia regime); EU 19th package Oct 23 2025 (A7A5-ecosystem trading platform)</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Aleksandr Mira Serda (Garantex co-founder; State Dept reward up to $5M)</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Large IP allocation; BitTorrent/Tor/VPN activity observed</t>
+          <t>Sanctions-evasion vehicle; On-chain asset migration from Garantex</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Spamhaus ASN-DROP (AS138915; AS58854; AS154177 under kaopuyun.com); C2 for 3+ families/actors; GreyNoise React2Shell exploitation source</t>
+          <t>Sanctioned personnel; Shared on-chain infrastructure with Garantex</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>2019-03-19</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -4492,26 +4517,26 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>~8-10% (RF chart #4)</t>
-        </is>
-      </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>RF-TAE-2026; SPAMHAUS-ASNDROP-2026; RF-REDHOTEL-2023; ESET-TOOLSHELL-2025; SEKOIA-BULBATURE; GREYNOISE-REACT2SHELL-2026; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>OFAC-GARANTEX; CHAINALYSIS-A7A5; CHAINALYSIS-OFAC; TRM-A7A5-2026; ELLIPTIC-GRINEX</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Hong Kong ISP (APNIC-registered 2019) announcing 113,664 IPv4 addresses in 168 prefixes on AS138915 (Sept 2026; the earlier '182,272 / 50+ netblocks' is outdated). RF ranks Kaopu #4 in its 2025 Threat Density top 10. Spamhaus ASN-DROP lists three kaopuyun.com ASNs: AS138915, AS58854 and AS154177 (LIGHT NODE LIMITED, 129 IPv4 prefixes); a fourth (AS140666, ANY DIGITAL PTE. LTD.) was listed earlier and removed. Independent vendor evidence: RF Insikt (RedHotel heavily favouring Kaopu for C2, 2022-23); ESET (ToolShell SharePoint exploitation from Kaopu IPs, July 2025); Arctic Wolf (malicious FortiGate SSO logins, Dec 2025); Sekoia (Bulbature/GobRAT staging servers all on AS138915); GreyNoise React2Shell sources. Tier raised T3 -&gt; T2 (status flagged) on 2026-09-25 per the ASN-DROP escalation rule; T1 candidate on the RF top-10 ranking.</t>
+          <t>Kyrgyzstan-incorporated successor to Garantex: registered December 2024 (TRM) and promoted on Telegram days after the March 2025 Garantex takedown; forensically tied to Garantex by shared on-chain infrastructure and asset migration (user funds plus A7A5 minted via Old Vector). OFAC designated it on 2025-08-14 as Garantex's 'direct successor'. On 2026-04-15 about 12:00 UTC roughly $13-15M was drained (Grinex claimed &gt;1bn rubles and blamed foreign 'special services'; Elliptic measured ~$15M USDT); Grinex then suspended operations, and Chainalysis raised the possibility of a false-flag exit. TokenSpot, a Kyrgyz exchange TRM considers a likely Grinex front, was hit the same day; Rapira had &gt;$72M in direct transactions with Grinex (Elliptic). Exved is a separately designated company, not an alias. Unverified: '&gt;=$4.76B processed in 2025'. Designation stands; operationally offline.</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>Russian no-KYC cryptocurrency exchange; primary Garantex successor laundering rail for the BPH/ransomware ecosystem.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Grinex</t>
+          <t>A7A5 / Old Vector</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4531,47 +4556,42 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Russia / Kyrgyzstan</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Grinex</t>
+          <t>Old Vector LLC (issuer)</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Garantex successor; TokenSpot (likely front, per TRM)</t>
+          <t>A7A5 stablecoin; Instant Swapper</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Garantex (predecessor)</t>
+          <t>A7 network (A7 LLC, A71 LLC, A7 Agent LLC - owned by Ilan Shor and Promsvyazbank); Garantex/Grinex ecosystem</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>OFAC Aug 14 2025 (as Garantex's direct successor); UK Aug 20 2025 (Grinex LLC, Russia regime); EU 19th package Oct 23 2025 (A7A5-ecosystem trading platform)</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>Aleksandr Mira Serda (Garantex co-founder; State Dept reward up to $5M)</t>
+          <t>UK May 2025 (A7) and Aug 20 2025 (Old Vector LLC); EU July 2025 (A7) and 19th package Oct 23 2025 (full A7A5 transaction ban from Nov 25 2025); OFAC Aug 14 2025 (Old Vector LLC, A7 LLC, A71 LLC, A7 Agent LLC)</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Sanctions-evasion vehicle; On-chain asset migration from Garantex</t>
+          <t>Ruble-backed stablecoin laundering; No-KYC stablecoin swapping</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Sanctioned personnel; Shared on-chain infrastructure with Garantex</t>
+          <t>Sanctioned; Ruble-pegged sanctions-evasion stablecoin</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -4581,24 +4601,24 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>OFAC-GARANTEX; CHAINALYSIS-A7A5; CHAINALYSIS-OFAC; TRM-A7A5-2026; ELLIPTIC-GRINEX</t>
+          <t>OFAC-GARANTEX; CHAINALYSIS-A7A5; TRM-A7A5-2026</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Kyrgyzstan-incorporated successor to Garantex: registered December 2024 (TRM) and promoted on Telegram days after the March 2025 Garantex takedown; forensically tied to Garantex by shared on-chain infrastructure and asset migration (user funds plus A7A5 minted via Old Vector). OFAC designated it on 2025-08-14 as Garantex's 'direct successor'. On 2026-04-15 about 12:00 UTC roughly $13-15M was drained (Grinex claimed &gt;1bn rubles and blamed foreign 'special services'; Elliptic measured ~$15M USDT); Grinex then suspended operations, and Chainalysis raised the possibility of a false-flag exit. TokenSpot, a Kyrgyz exchange TRM considers a likely Grinex front, was hit the same day; Rapira had &gt;$72M in direct transactions with Grinex (Elliptic). Exved is a separately designated company, not an alias. Unverified: '&gt;=$4.76B processed in 2025'. Designation stands; operationally offline.</t>
+          <t>Russian ruble-backed stablecoin issued by Kyrgyzstan's Old Vector; A7 LLC is the token's creator. Chainalysis (2026 Crypto Crime Report): $93.3B moved 'in less than a year'; Elliptic: more than $100B in under a year (the $93.1B and $72B figures elsewhere are earlier snapshots). Garantex moved funds into A7A5 from as early as January 2025 (TRM). The no-KYC Instant Swapper reportedly converted &gt;$2.2B of A7A5 into mainstream USD stablecoins (unverified). The EU banned A7A5 transactions from 2025-11-25. Its economy ran through Grinex, so on-chain volume reportedly collapsed after Grinex suspended in April 2026 (the '~96%' figure is unverified). A7 LLC, A71 LLC and A7 Agent LLC are separately designated related entities, not aliases.</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>Russian no-KYC cryptocurrency exchange; primary Garantex successor laundering rail for the BPH/ransomware ecosystem.</t>
+          <t>Sanctions-evasion stablecoin and swap rail bridging sanctioned Russian crypto into mainstream stablecoins.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A7A5 / Old Vector</t>
+          <t>Nobitex</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4608,52 +4628,42 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>T1-Confirmed BPH (Financial Enabler)</t>
+          <t>T2-High Risk (Financial Enabler)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Russia / Kyrgyz Republic</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Russia / Kyrgyzstan</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Old Vector LLC (issuer)</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>A7A5 stablecoin; Instant Swapper</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>A7 network (A7 LLC, A71 LLC, A7 Agent LLC - owned by Ilan Shor and Promsvyazbank); Garantex/Grinex ecosystem</t>
+          <t>Nobitex</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>UK May 2025 (A7) and Aug 20 2025 (Old Vector LLC); EU July 2025 (A7) and 19th package Oct 23 2025 (full A7A5 transaction ban from Nov 25 2025); OFAC Aug 14 2025 (Old Vector LLC, A7 LLC, A71 LLC, A7 Agent LLC)</t>
+          <t>OFAC June 2 2026 (sb0519, 'Economic Fury'): E.O. 13224 (material support to the IRGC) and E.O. 13902; four executives designated under E.O. 13224</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Amir Hossein Rad (chairman/co-founder); Seyed Ali Khoee (CEO); two Kharrazi-family co-founders (name renderings vary across sources)</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Ruble-backed stablecoin laundering; No-KYC stablecoin swapping</t>
+          <t>Terror-finance facilitation; Sanctions evasion</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>Sanctioned; Ruble-pegged sanctions-evasion stablecoin</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>2025-01</t>
+          <t>Sanctioned; Iran's largest crypto exchange</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -4663,24 +4673,24 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>OFAC-GARANTEX; CHAINALYSIS-A7A5; TRM-A7A5-2026</t>
+          <t>OFAC-IRAN-FURY; CHAINALYSIS-OFAC</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Russian ruble-backed stablecoin issued by Kyrgyzstan's Old Vector; A7 LLC is the token's creator. Chainalysis (2026 Crypto Crime Report): $93.3B moved 'in less than a year'; Elliptic: more than $100B in under a year (the $93.1B and $72B figures elsewhere are earlier snapshots). Garantex moved funds into A7A5 from as early as January 2025 (TRM). The no-KYC Instant Swapper reportedly converted &gt;$2.2B of A7A5 into mainstream USD stablecoins (unverified). The EU banned A7A5 transactions from 2025-11-25. Its economy ran through Grinex, so on-chain volume reportedly collapsed after Grinex suspended in April 2026 (the '~96%' figure is unverified). A7 LLC, A71 LLC and A7 Agent LLC are separately designated related entities, not aliases.</t>
+          <t>Iran's largest digital-asset exchange. OFAC-designated 2026-06-02 under 'Economic Fury' - uniquely also under counterterrorism E.O. 13224 - together with four executives. The four designated Iranian exchanges handled about $7.7B, roughly 78% of Iran's attributed 2025 crypto volume. Follow-on actions: OFAC added Central Bank of Iran wallets (2026-07-16) and designated the exchanges Shelbit and Aban Tether (2026-08-07), the latter for transactions with Nobitex, Wallex, Bitpin and Ramzinex.</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>Sanctions-evasion stablecoin and swap rail bridging sanctioned Russian crypto into mainstream stablecoins.</t>
+          <t>Iranian cryptocurrency exchange sanctioned for terror finance and sanctions evasion.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Nobitex</t>
+          <t>Wallex</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4690,7 +4700,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>T2-High Risk (Financial Enabler)</t>
+          <t>T3-Suspected (Financial Enabler)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4705,54 +4715,49 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Nobitex</t>
+          <t>Wallex</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>OFAC June 2 2026 (sb0519, 'Economic Fury'): E.O. 13224 (material support to the IRGC) and E.O. 13902; four executives designated under E.O. 13224</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>Amir Hossein Rad (chairman/co-founder); Seyed Ali Khoee (CEO); two Kharrazi-family co-founders (name renderings vary across sources)</t>
+          <t>OFAC June 2 2026 (E.O. 13902)</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Terror-finance facilitation; Sanctions evasion</t>
+          <t>Iranian crypto on-ramp; Sanctions evasion</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>Sanctioned; Iran's largest crypto exchange</t>
+          <t>Sanctioned under 'Economic Fury'</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>OFAC-IRAN-FURY; CHAINALYSIS-OFAC</t>
+          <t>OFAC-IRAN-FURY</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Iran's largest digital-asset exchange. OFAC-designated 2026-06-02 under 'Economic Fury' - uniquely also under counterterrorism E.O. 13224 - together with four executives. The four designated Iranian exchanges handled about $7.7B, roughly 78% of Iran's attributed 2025 crypto volume. Follow-on actions: OFAC added Central Bank of Iran wallets (2026-07-16) and designated the exchanges Shelbit and Aban Tether (2026-08-07), the latter for transactions with Nobitex, Wallex, Bitpin and Ramzinex.</t>
+          <t>Iranian crypto exchange designated June 2 2026 under 'Economic Fury' (E.O. 13902, Iran financial sector).</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>Iranian cryptocurrency exchange sanctioned for terror finance and sanctions evasion.</t>
+          <t>Iranian cryptocurrency exchange sanctioned June 2026.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Wallex</t>
+          <t>Bitpin</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4777,7 +4782,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Wallex</t>
+          <t>Bitpin</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4819,7 +4824,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bitpin</t>
+          <t>Ramzinex</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4844,7 +4849,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Bitpin</t>
+          <t>Ramzinex</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4886,154 +4891,174 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ramzinex</t>
+          <t>BtHoster</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>sanctioned</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>T3-Suspected (Financial Enabler)</t>
+          <t>T1-Confirmed BPH</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AS213790</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AS213388 (IIC RAIL LIMITED [GB]; downstream); AS214295 (dark); AS215476 (dead); AS198465 (predecessor, recycled to CN)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>45.142.193.0/24; 77.90.185.0/24; 172.94.9.0/24; 192.253.248.0/24; 206.123.156.0/24; 185.93.89.0/24; 45.129.14.0/24</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>United Kingdom (shells)</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Lithuania / Bulgaria (transit)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Ramzinex</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>OFAC June 2 2026 (E.O. 13902)</t>
+          <t>Limited Network LTD; Skynet Network Ltd; Inside Network LTD; BtHoster LTD (predecessor)</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>BtHoster; BTCloud; btcloud.ro</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>UAB Host Baltic (AS209605); Tube-Hosting (AS49581, aurologic)</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Nominee dirs: Murray Charles / Jonathan Reynolds / Brooks William Thomas; provisioned via Khatibi (UAE, wcd maintainer) + Mashayekhi (Iran LIR)</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Initial Access Brokers</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Mirai; RisePro; Cobalt Strike; Remcos; Moobot; HookBot</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Iranian crypto on-ramp; Sanctions evasion</t>
+          <t>AS-leasing; Shell rebranding (BtHoster LTD-&gt;Skynet/Inside-&gt;Limited Network); Prefix transfer w/ inetnum retained across ASN rotation; masscan-server provisioning; Iranian-prefix false-flag</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>Sanctioned under 'Economic Fury'</t>
+          <t>On Spamhaus ASN-DROP (AS213790 under btcloud.ro; AS213388 under iic-rail); upstreams AS209605, AS49581 and AS204428 are themselves on ASN-DROP; self-advertised bulletproof (@bthosterltd); masscan ~1300 kpps; shell/nominee structure; shared wcd RIPE maintainer</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>2023</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>OFAC-IRAN-FURY</t>
+          <t>INTRINSEC-BTHOSTER; SECURITYONLINE-BTHOSTER; RIPE-AAWG-BTHOSTER; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Iranian crypto exchange designated June 2 2026 under 'Economic Fury' (E.O. 13902, Iran financial sector).</t>
+          <t>Confirmed multi-vector (2026-06): BtHoster = 'BTCloud' operator running recycled UK '[Word] Network LTD' shells -- BtHoster LTD (AS198465, dead 2024-03) -&gt; Skynet Network Ltd (AS214295) + Inside Network LTD (AS215476) (struck off 2025) -&gt; Limited Network LTD (AS213790, ACTIVE) + downstream AS213388. Live identity tied by: the 45.142.193.0/24 inetnum is owned by Limited Network LTD (migrated Skynet-&gt;AS213388 on 2026-06-23, owner unchanged); abuse@btcloud.ro brand on its ARIN blocks; direct AS213790&lt;-&gt;AS214295 peering; shared 'wcd' RIPE maintainer (Khatibi/UAE). Sells pre-configured masscan servers (~1300 kpps) to Initial Access Brokers; transfers prefixes between shells to erase reputation; reuses Iranian-origin prefixes to fake Iran attribution. Spamhaus ASN-DROP lists AS213790 with domain btcloud.ro (a direct BTCloud tie) and, since 2026, AS213388 (registry holder 'IIC RAIL LIMITED'); the old shells AS214295/AS215476 were delisted after Dec 2025. A sibling-looking AS214018 'IIC-AS' (INTERNET INTELLIGENCE COMPANY LTD) is also on ASN-DROP (lead only). Transit via UAB Host Baltic (AS209605) + Tube-Hosting (AS49581) with a Bulgarian backstop (SS-NET AS204428 / 4Vendeta) - all three transit ASNs are themselves on ASN-DROP. Securonix DanaBot IOC 45.129.14.157 resolved to 157.hosted-by.bthoster.com. Full attribution dossier in internal investigation.</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>Iranian cryptocurrency exchange sanctioned June 2026.</t>
+          <t>Confirmed bulletproof / AS-leasing operator ('BTCloud') running rotating UK nominee shells; live as Limited Network LTD (AS213790)/AS213388; masscan-as-a-service to IABs.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BtHoster</t>
+          <t>Pfcloud UG</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>flagged</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>T1-Confirmed BPH</t>
+          <t>T2-High Risk</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>AS213790</t>
+          <t>AS51396</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AS213388 (IIC RAIL LIMITED [GB]; downstream); AS214295 (dark); AS215476 (dead); AS198465 (predecessor, recycled to CN)</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>45.142.193.0/24; 77.90.185.0/24; 172.94.9.0/24; 192.253.248.0/24; 206.123.156.0/24; 185.93.89.0/24; 45.129.14.0/24</t>
+          <t>AS215310 (USERCLOUD; Pfcloud UG); AS400328 (Intelligence Hosting LLC [NL/ARIN]; Spamhaus-attributed via pfcloud.io)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>United Kingdom (shells)</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Lithuania / Bulgaria (transit)</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Limited Network LTD; Skynet Network Ltd; Inside Network LTD; BtHoster LTD (predecessor)</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>BtHoster; BTCloud; btcloud.ro</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>UAB Host Baltic (AS209605); Tube-Hosting (AS49581, aurologic)</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>Nominee dirs: Murray Charles / Jonathan Reynolds / Brooks William Thomas; provisioned via Khatibi (UAE, wcd maintainer) + Mashayekhi (Iran LIR)</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Initial Access Brokers</t>
+          <t>Pfcloud UG (haftungsbeschraenkt)</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>aurologic-linked ecosystem</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>Mirai; RisePro; Cobalt Strike; Remcos; Moobot; HookBot</t>
+          <t>Hikvision CVE-2021-36260 exploitation source; AsyncRAT C2 (2025); FortiGate 60F exploit-kit staging (2026)</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>AS-leasing; Shell rebranding (BtHoster LTD-&gt;Skynet/Inside-&gt;Limited Network); Prefix transfer w/ inetnum retained across ASN rotation; masscan-server provisioning; Iranian-prefix false-flag</t>
+          <t>Bulletproof-adjacent; Sustained scanning/proxy abuse</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>On Spamhaus ASN-DROP (AS213790 under btcloud.ro; AS213388 under iic-rail); upstreams AS209605, AS49581 and AS204428 are themselves on ASN-DROP; self-advertised bulletproof (@bthosterltd); masscan ~1300 kpps; shell/nominee structure; shared wcd RIPE maintainer</t>
+          <t>Spamhaus ASN-DROP (AS51396 since at least Feb 2024; AS215310 and AS400328 under pfcloud.io); GreyNoise exploitation sources; aurologic-ecosystem adjacency (Railnet transit)</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -5043,84 +5068,79 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>INTRINSEC-BTHOSTER; SECURITYONLINE-BTHOSTER; RIPE-AAWG-BTHOSTER; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>RUDIS-BPH-WATCH; RF-AUROLOGIC; SPAMHAUS-ASNDROP-2026; GREYNOISE-WEEKLY-2026-08; GREYNOISE-REACT2SHELL-2026; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Confirmed multi-vector (2026-06): BtHoster = 'BTCloud' operator running recycled UK '[Word] Network LTD' shells -- BtHoster LTD (AS198465, dead 2024-03) -&gt; Skynet Network Ltd (AS214295) + Inside Network LTD (AS215476) (struck off 2025) -&gt; Limited Network LTD (AS213790, ACTIVE) + downstream AS213388. Live identity tied by: the 45.142.193.0/24 inetnum is owned by Limited Network LTD (migrated Skynet-&gt;AS213388 on 2026-06-23, owner unchanged); abuse@btcloud.ro brand on its ARIN blocks; direct AS213790&lt;-&gt;AS214295 peering; shared 'wcd' RIPE maintainer (Khatibi/UAE). Sells pre-configured masscan servers (~1300 kpps) to Initial Access Brokers; transfers prefixes between shells to erase reputation; reuses Iranian-origin prefixes to fake Iran attribution. Spamhaus ASN-DROP lists AS213790 with domain btcloud.ro (a direct BTCloud tie) and, since 2026, AS213388 (registry holder 'IIC RAIL LIMITED'); the old shells AS214295/AS215476 were delisted after Dec 2025. A sibling-looking AS214018 'IIC-AS' (INTERNET INTELLIGENCE COMPANY LTD) is also on ASN-DROP (lead only). Transit via UAB Host Baltic (AS209605) + Tube-Hosting (AS49581) with a Bulgarian backstop (SS-NET AS204428 / 4Vendeta) - all three transit ASNs are themselves on ASN-DROP. Securonix DanaBot IOC 45.129.14.157 resolved to 157.hosted-by.bthoster.com. Full attribution dossier in internal investigation.</t>
+          <t>German micro-provider (AS51396: 26 IPv4 and 24 IPv6 prefixes). Spamhaus ASN-DROP has listed AS51396 since at least Feb 2024 (with a since-recycled AS202685 'as-pfcloud'); it now also lists AS215310 (USERCLOUD) and AS400328 (Intelligence Hosting LLC) under pfcloud.io. RF lists Pfcloud as an upstream of the Virtualine/Railnet 'hosting island' alongside aurologic. GreyNoise (Aug 2026): 204.76.203.43 on AS51396 generated 393,777 sessions and most of the period's 121,068 Hikvision CVE-2021-36260 exploitation attempts; Pfcloud IPs also appear among React2Shell sources. A community note (Sept 2026, D-grade) describes a Pfcloud open directory staging FortiGate 60F exploit modules on an IP previously listed as AsyncRAT C2. Tier raised T3 -&gt; T2 (status flagged) on 2026-09-25 per the ASN-DROP escalation rule; the earlier single-honeypot caveat is outdated.</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>Confirmed bulletproof / AS-leasing operator ('BTCloud') running rotating UK nominee shells; live as Limited Network LTD (AS213790)/AS213388; masscan-as-a-service to IABs.</t>
+          <t>German micro-provider, bulletproof-adjacent; corroborated abuse signal with single-honeypot caveat.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Pfcloud UG</t>
+          <t>Dabai Guarantee</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>flagged</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>T2-High Risk</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>AS51396</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AS215310 (USERCLOUD; Pfcloud UG); AS400328 (Intelligence Hosting LLC [NL/ARIN]; Spamhaus-attributed via pfcloud.io)</t>
+          <t>T2-High Risk (Financial Enabler)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>China (Telegram-based)</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Southeast Asia / China</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Pfcloud UG (haftungsbeschraenkt)</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>aurologic-linked ecosystem</t>
+          <t>Dabai Guarantee</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>大白担保; @DBTM301</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Chinese-language scam-compound ecosystem</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>Hikvision CVE-2021-36260 exploitation source; AsyncRAT C2 (2025); FortiGate 60F exploit-kit staging (2026)</t>
+          <t>MaaS; deepfake tooling; KYC-bypass services</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>Bulletproof-adjacent; Sustained scanning/proxy abuse</t>
+          <t>Guarantee/escrow marketplace; Money-laundering facilitation</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>Spamhaus ASN-DROP (AS51396 since at least Feb 2024; AS215310 and AS400328 under pfcloud.io); GreyNoise exploitation sources; aurologic-ecosystem adjacency (Railnet transit)</t>
+          <t>Telegram guarantee marketplace; Huione-successor pattern</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -5130,29 +5150,29 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>RUDIS-BPH-WATCH; RF-AUROLOGIC; SPAMHAUS-ASNDROP-2026; GREYNOISE-WEEKLY-2026-08; GREYNOISE-REACT2SHELL-2026; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>RF-GUARANTEE-2026; OFAC-XINBI-2026</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>German micro-provider (AS51396: 26 IPv4 and 24 IPv6 prefixes). Spamhaus ASN-DROP has listed AS51396 since at least Feb 2024 (with a since-recycled AS202685 'as-pfcloud'); it now also lists AS215310 (USERCLOUD) and AS400328 (Intelligence Hosting LLC) under pfcloud.io. RF lists Pfcloud as an upstream of the Virtualine/Railnet 'hosting island' alongside aurologic. GreyNoise (Aug 2026): 204.76.203.43 on AS51396 generated 393,777 sessions and most of the period's 121,068 Hikvision CVE-2021-36260 exploitation attempts; Pfcloud IPs also appear among React2Shell sources. A community note (Sept 2026, D-grade) describes a Pfcloud open directory staging FortiGate 60F exploit modules on an IP previously listed as AsyncRAT C2. Tier raised T3 -&gt; T2 (status flagged) on 2026-09-25 per the ASN-DROP escalation rule; the earlier single-honeypot caveat is outdated.</t>
+          <t>Recorded Future/Insikt: major Chinese-language guarantee (danbao) Telegram marketplace resembling the defunct Huione Guarantee, with thousands of thematic channels (overseas phishing, laundering, 'sweeping' goods in Japan and South Korea) and a search bot. The RF report appears to date from about April 2026 (the relaying digest is dated 2026-04-23), not February. Reported emergence ~Dec 2024 and ~19,225 members in its largest group are unverified. Flare counts more than 30 marketplaces that emerged after Huione Guarantee ceased operations in May 2025; Xinbi (disrupted by the US on 2026-09-09) is the largest of the successors.</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>German micro-provider, bulletproof-adjacent; corroborated abuse signal with single-honeypot caveat.</t>
+          <t>Chinese-language Telegram guarantee/escrow marketplace and laundering facilitator; Huione successor.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Dabai Guarantee</t>
+          <t>Tudou Guarantee</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>flagged</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5162,47 +5182,37 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>China (Telegram-based)</t>
+          <t>Cambodia / Telegram-based</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Southeast Asia / China</t>
+          <t>Southeast Asia</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Dabai Guarantee</t>
+          <t>Tudou Guarantee</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>大白担保; @DBTM301</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Chinese-language scam-compound ecosystem</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>MaaS; deepfake tooling; KYC-bypass services</t>
+          <t>Potato; 土豆担保</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Huione / Haowang Guarantee (announced a stake in Dec 2024; 30% figure unverified)</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Guarantee/escrow marketplace; Money-laundering facilitation</t>
+          <t>Guarantee/escrow marketplace; Money-laundering facilitation; Public fraud-market activity ceased Jan 2026</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>Telegram guarantee marketplace; Huione-successor pattern</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>2024-12</t>
+          <t>3rd-largest illicit marketplace; Admin-wallet collapse after Chen Zhi arrest</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -5212,24 +5222,24 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>RF-GUARANTEE-2026; OFAC-XINBI-2026</t>
+          <t>ELLIPTIC-TUDOU; RF-GUARANTEE-2026; OFAC-HUIONE-PRINCE; OFAC-PRINCE-2025</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Recorded Future/Insikt: major Chinese-language guarantee (danbao) Telegram marketplace resembling the defunct Huione Guarantee, with thousands of thematic channels (overseas phishing, laundering, 'sweeping' goods in Japan and South Korea) and a search bot. The RF report appears to date from about April 2026 (the relaying digest is dated 2026-04-23), not February. Reported emergence ~Dec 2024 and ~19,225 members in its largest group are unverified. Flare counts more than 30 marketplaces that emerged after Huione Guarantee ceased operations in May 2025; Xinbi (disrupted by the US on 2026-09-09) is the largest of the successors.</t>
+          <t>Huione's designated successor: in December 2024 Haowang (ex-Huione) Guarantee announced it was buying a stake in Tudou (FinCEN; the 30% figure is unverified). Processed &gt;$12B - the third-largest illicit marketplace ever (Elliptic). In January 2026, after Prince Group chairman Chen Zhi was arrested in Cambodia and extradited to China (reported 2026-01-07), Tudou effectively ceased transactions through its public Telegram groups and admin-wallet activity collapsed; gambling operations continue and Elliptic says it remains to be seen whether this is a full shutdown or a pivot. Status corrected dissolved -&gt; flagged on 2026-09-25 (no legal dissolution documented).</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>Chinese-language Telegram guarantee/escrow marketplace and laundering facilitator; Huione successor.</t>
+          <t>Telegram guarantee marketplace for the SEA scam economy; Huione successor, wound down Jan 2026.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Tudou Guarantee</t>
+          <t>H-Pay Service PLC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5244,37 +5254,47 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cambodia / Telegram-based</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Southeast Asia</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Tudou Guarantee</t>
+          <t>H-Pay Service PLC</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Potato; 土豆担保</t>
+          <t>Huione Pay successor</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Huione / Haowang Guarantee (announced a stake in Dec 2024; 30% figure unverified)</t>
+          <t>Huione Group</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>FinCEN proposed rule (Federal Register 2026-12794, published June 25 2026) adding H-Pay and any successor to the Huione Group Section 311 special measure - a proposal, not a final rule</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Guarantee/escrow marketplace; Money-laundering facilitation; Public fraud-market activity ceased Jan 2026</t>
+          <t>Successor facilitator; Inherited Huione Pay branches/customers/branding</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>3rd-largest illicit marketplace; Admin-wallet collapse after Chen Zhi arrest</t>
+          <t>Named FinCEN successor facilitator; Huione-ecosystem continuity</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>2026</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -5284,79 +5304,79 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>ELLIPTIC-TUDOU; RF-GUARANTEE-2026; OFAC-HUIONE-PRINCE; OFAC-PRINCE-2025</t>
+          <t>OFAC-HUIONE-PRINCE; FINCEN-HPAY-2026</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Huione's designated successor: in December 2024 Haowang (ex-Huione) Guarantee announced it was buying a stake in Tudou (FinCEN; the 30% figure is unverified). Processed &gt;$12B - the third-largest illicit marketplace ever (Elliptic). In January 2026, after Prince Group chairman Chen Zhi was arrested in Cambodia and extradited to China (reported 2026-01-07), Tudou effectively ceased transactions through its public Telegram groups and admin-wallet activity collapsed; gambling operations continue and Elliptic says it remains to be seen whether this is a full shutdown or a pivot. Status corrected dissolved -&gt; flagged on 2026-09-25 (no legal dissolution documented).</t>
+          <t>FinCEN (announced 2026-06-23 with the DOJ Huione cloud-account seizure and Prince Group designations) proposed amending its Oct 2025 Huione Group Section 311 final rule to cover Cambodia-based H-Pay Service PLC (reg. no. 00074959) and 'any successor entity', to stop Huione circumventing the cut-off. The comment period was extended in July 2026 after a portal outage; the rule is not yet final. FinCEN notes the National Bank of Cambodia revoked H-Pay's payment licence on 2026-04-10.</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>Telegram guarantee marketplace for the SEA scam economy; Huione successor, wound down Jan 2026.</t>
+          <t>Cambodian successor facilitator to the shut-down Huione Pay laundering operation.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>H-Pay Service PLC</t>
+          <t>Asocks</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>flagged</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>T2-High Risk (Financial Enabler)</t>
+          <t>T2-High Risk (Anonymization/Proxy Enabler)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>IOC IPs (not Asocks-owned ranges): 205.198.91.136; 205.198.91.155 (Cogent AS174); 194.147.16.244 (Catixs AS48266)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Cambodia</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>H-Pay Service PLC</t>
+          <t>Netherlands (servers); global botnet</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Huione Pay successor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Huione Group</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>FinCEN proposed rule (Federal Register 2026-12794, published June 25 2026) adding H-Pay and any successor to the Huione Group Section 311 special measure - a proposal, not a final rule</t>
+          <t>asocks.com; LVCHA VPN-linked</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>PROXYLIB SDK apps (HUMAN, 2024)</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Residential-proxy botnet (17M+ devices); malicious SDK enrollment</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Successor facilitator; Inherited Huione Pay branches/customers/branding</t>
+          <t>Residential-proxy / traffic-obfuscation enabler; Covert device enrollment</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>Named FinCEN successor facilitator; Huione-ecosystem continuity</t>
+          <t>LE-disrupted (NCSC-NL May 2026); Clearnet storefront persists; Silent Push IOC cluster</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -5366,79 +5386,84 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>OFAC-HUIONE-PRINCE; FINCEN-HPAY-2026</t>
+          <t>NCSC-NL-ASOCKS; SILENTPUSH-CHINESEVPN; HUMAN-PROXYLIB-2024</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>FinCEN (announced 2026-06-23 with the DOJ Huione cloud-account seizure and Prince Group designations) proposed amending its Oct 2025 Huione Group Section 311 final rule to cover Cambodia-based H-Pay Service PLC (reg. no. 00074959) and 'any successor entity', to stop Huione circumventing the cut-off. The comment period was extended in July 2026 after a portal outage; the rule is not yet final. FinCEN notes the National Bank of Cambodia revoked H-Pay's payment licence on 2026-04-10.</t>
+          <t>Residential-proxy network (asocks.com; proxies sold at $5-15/month). On 2026-05-28 Dutch police and NCSC-NL announced the takedown of a botnet of at least 17 million infected devices whose backend ran on more than 200 servers in the Netherlands; police seized a subset of those servers from a hosting provider, which then took the botnet offline. Authorities did not name the service - NL Times reported it was Asocks (name-linkage caveat). HUMAN Satori (Mar 2024) believed PROXYLIB apps were monetized through Asocks. Silent Push tied the Mandarin-language LVCHA VPN (lvcha.in) to residential-proxy IOCs; the specific Asocks-IP tie is not in the available summary. Corrections 2026-09-25: AS48266 is Catixs Ltd, an ordinary hosting provider, not an Asocks ASN (removed as primary_asn); 205.198.91.x is Cogent space; the '~163 countries' figure belongs to SocksEscort. Storefront reportedly remained live after the seizure.</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>Cambodian successor facilitator to the shut-down Huione Pay laundering operation.</t>
+          <t>Malicious residential-proxy / anonymity-infrastructure TAE built on covertly infected devices; LE-disrupted May 2026 (Asocks attribution is press-sourced).</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Asocks</t>
+          <t>Datavice MCHJ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>sanctioned</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>T2-High Risk (Anonymization/Proxy Enabler)</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>IOC IPs (not Asocks-owned ranges): 205.198.91.136; 205.198.91.155 (Cogent AS174); 194.147.16.244 (Catixs AS48266)</t>
+          <t>T1-Confirmed BPH</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Netherlands (servers); global botnet</t>
+          <t>Uzbekistan (Tashkent)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Datavice MCHJ</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>asocks.com; LVCHA VPN-linked</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>PROXYLIB SDK apps (HUMAN, 2024)</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>Residential-proxy botnet (17M+ devices); malicious SDK enrollment</t>
+          <t>Aeza expansion entity</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Aeza Group LLC (linked to)</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Aeza Group LLC</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>OFAC Nov 19 2025 (E.O. 13694; CAATSA-RUSSIA; CYBER4; Linked To Aeza Group LLC); NOT UK-designated</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>Residential-proxy / traffic-obfuscation enabler; Covert device enrollment</t>
+          <t>Sanctions-evasion vehicle; Corporate shell</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>LE-disrupted (NCSC-NL May 2026); Clearnet storefront persists; Silent Push IOC cluster</t>
+          <t>Shell company structure; Sanctioned; Aeza-linked; short corporate history</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -5448,24 +5473,24 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>NCSC-NL-ASOCKS; SILENTPUSH-CHINESEVPN; HUMAN-PROXYLIB-2024</t>
+          <t>OFAC-MEDIALAND</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Residential-proxy network (asocks.com; proxies sold at $5-15/month). On 2026-05-28 Dutch police and NCSC-NL announced the takedown of a botnet of at least 17 million infected devices whose backend ran on more than 200 servers in the Netherlands; police seized a subset of those servers from a hosting provider, which then took the botnet offline. Authorities did not name the service - NL Times reported it was Asocks (name-linkage caveat). HUMAN Satori (Mar 2024) believed PROXYLIB apps were monetized through Asocks. Silent Push tied the Mandarin-language LVCHA VPN (lvcha.in) to residential-proxy IOCs; the specific Asocks-IP tie is not in the available summary. Corrections 2026-09-25: AS48266 is Catixs Ltd, an ordinary hosting provider, not an Asocks ASN (removed as primary_asn); 205.198.91.x is Cogent space; the '~163 countries' figure belongs to SocksEscort. Storefront reportedly remained live after the seizure.</t>
+          <t>Uzbekistan-registered (Tashkent) Aeza expansion entity. OFAC SDN record: established 2025-07-03; Tax ID 312252645; Business Registration 2868352; address 3 Irrigator Massive, Hamid Olimjon MFY, Tashkent; programs CYBER4 and CAATSA-RUSSIA; 'Linked To: AEZA GROUP LLC'. Designated 2025-11-19 alongside Hypercore Ltd, Smart Digital Ideas DOO, Maksim Makarov and Ilya Zakirov; absent from the UK's 19 Nov 2025 notices (OFAC-only). No ASN is stated in the designation; the registry lists a dark AS206336 as 'DATAVICE MCHJ', but per-ASN metadata still shows a previous holder, so treat it as an unverified lead.</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>Malicious residential-proxy / anonymity-infrastructure TAE built on covertly infected devices; LE-disrupted May 2026 (Asocks attribution is press-sourced).</t>
+          <t>OFAC-sanctioned Aeza expansion/front entity registered in Uzbekistan; designated alongside Hypercore in the Nov 2025 Aeza action.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Datavice MCHJ</t>
+          <t>First VPN Service (1VPNS)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5475,57 +5500,52 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>T1-Confirmed BPH</t>
+          <t>T1-Confirmed BPH (Anonymization/Proxy Enabler)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Uzbekistan (Tashkent)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Datavice MCHJ</t>
+          <t>Ukrainian administrator; infrastructure in ~27 countries</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Aeza expansion entity</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Aeza Group LLC (linked to)</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>Aeza Group LLC</t>
+          <t>1VPNS; First VPN Service</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>OFAC Nov 19 2025 (E.O. 13694; CAATSA-RUSSIA; CYBER4; Linked To Aeza Group LLC); NOT UK-designated</t>
+          <t>OFAC July 13 2026 (E.O. 13694 as amended, in furtherance of E.O. 14390; coordinated with UK FCDO, which did not co-designate)</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Dmytro Rashevskyi (admin; aliases Maksim Sorin, Roman Chabanenko)</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Ransomware operators (unnamed in designation)</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>Sanctions-evasion vehicle; Corporate shell</t>
+          <t>Criminal VPN / anonymization enabler; No-log policy; Forum-advertised since 2014; Refuses LE cooperation</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>Shell company structure; Sanctioned; Aeza-linked; short corporate history</t>
+          <t>No KYC; Underground forum presence; Non-cooperative with LE; Sanctioned</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -5535,79 +5555,84 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>OFAC-MEDIALAND</t>
+          <t>OFAC-1VPNS; EUROPOL-SAFFRON-2026</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Uzbekistan-registered (Tashkent) Aeza expansion entity. OFAC SDN record: established 2025-07-03; Tax ID 312252645; Business Registration 2868352; address 3 Irrigator Massive, Hamid Olimjon MFY, Tashkent; programs CYBER4 and CAATSA-RUSSIA; 'Linked To: AEZA GROUP LLC'. Designated 2025-11-19 alongside Hypercore Ltd, Smart Digital Ideas DOO, Maksim Makarov and Ilya Zakirov; absent from the UK's 19 Nov 2025 notices (OFAC-only). No ASN is stated in the designation; the registry lists a dark AS206336 as 'DATAVICE MCHJ', but per-ASN metadata still shows a previous holder, so treat it as an unverified lead.</t>
+          <t>OFAC-designated 2026-07-13 (sb0559) under E.O. 13694 as amended, in furtherance of E.O. 14390, for enabling ransomware attacks on US targets; the UK did not co-designate it. No-log criminal VPN advertised on cybercrime forums since 2014; ~32 exit nodes in ~27 countries used by at least 25 ransomware groups (FBI FLASH-20260521-001). Administrator Dmytro Rashevskyi (45, Ukrainian) used false identities (Maksim Sorin, Roman Chabanenko) to buy infrastructure. Belarusian cryptor seller Yegeniy Silayev was co-designated. The service was dismantled in Operation Saffron (19-20 May 2026, France- and Netherlands-led with Europol and Eurojust): 33 servers taken down, 1vpns domains seized and a suspected administrator arrested. SDN entries carry 5 addresses for the service and 8 for Rashevskyi.</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>OFAC-sanctioned Aeza expansion/front entity registered in Uzbekistan; designated alongside Hypercore in the Nov 2025 Aeza action.</t>
+          <t>OFAC-sanctioned criminal no-log VPN / anonymization enabler.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>First VPN Service (1VPNS)</t>
+          <t>NetNut (Alarum Technologies)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>sanctioned</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>T1-Confirmed BPH (Anonymization/Proxy Enabler)</t>
+          <t>T2-High Risk (Anonymization/Proxy Enabler)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Ukrainian administrator; infrastructure in ~27 countries</t>
+          <t>Israel (parent); global residential-proxy exit nodes</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Alarum Technologies Ltd (NASDAQ: ALAR)</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>1VPNS; First VPN Service</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>OFAC July 13 2026 (E.O. 13694 as amended, in furtherance of E.O. 14390; coordinated with UK FCDO, which did not co-designate)</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>Dmytro Rashevskyi (admin; aliases Maksim Sorin, Roman Chabanenko)</t>
+          <t>NetNut; Popa botnet (exit-node source)</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Alarum Technologies Ltd</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Ransomware operators (unnamed in designation)</t>
+          <t>316 distinct threat-actor clusters (Google GTIG, June 2026)</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Popa (proxy botnet)</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>Criminal VPN / anonymization enabler; No-log policy; Forum-advertised since 2014; Refuses LE cooperation</t>
+          <t>Commercial residential-proxy platform with botnet-sourced exit nodes; Traffic obfuscation; Covert device enrollment via SDKs</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>No KYC; Underground forum presence; Non-cooperative with LE; Sanctioned</t>
+          <t>Residential-proxy exit nodes; Botnet-sourced infrastructure; LE-seized</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -5617,84 +5642,94 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>OFAC-1VPNS; EUROPOL-SAFFRON-2026</t>
+          <t>GTIG-NETNUT; KREBS-NETNUT; QURIUM-POPA-2026; KREBS-POPA-2026</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>OFAC-designated 2026-07-13 (sb0559) under E.O. 13694 as amended, in furtherance of E.O. 14390, for enabling ransomware attacks on US targets; the UK did not co-designate it. No-log criminal VPN advertised on cybercrime forums since 2014; ~32 exit nodes in ~27 countries used by at least 25 ransomware groups (FBI FLASH-20260521-001). Administrator Dmytro Rashevskyi (45, Ukrainian) used false identities (Maksim Sorin, Roman Chabanenko) to buy infrastructure. Belarusian cryptor seller Yegeniy Silayev was co-designated. The service was dismantled in Operation Saffron (19-20 May 2026, France- and Netherlands-led with Europol and Eurojust): 33 servers taken down, 1vpns domains seized and a suspected administrator arrested. SDN entries carry 5 addresses for the service and 8 for Rashevskyi.</t>
+          <t>On 2026-07-02 the FBI seized hundreds of NetNut-linked domains (the seizure notice thanks Google, Lumen and Shadowserver) and Google disrupted the associated Popa botnet (at least 2 million hijacked smart TVs, streaming boxes and Android devices): Google disabled accounts used for C2 and set Play Protect to disable apps carrying NetNut SDKs. GTIG observed 316 distinct threat clusters using suspected NetNut exit nodes in a single week of June 2026. Popa was first flagged by QiAnXin XLab in March 2025 as an Android component of the Vo1d botnet and was tied to NetNut in June 2026 by Krebs, Qurium, Nokia Deepfield and Synthient. NetNut is operated by NASDAQ-listed Alarum Technologies (ALAR), which disputes the allegations and paused traffic on the affected network; its shares fell 23.6% after hours. Builds on Google's Jan 2026 IPIDEA disruption. Not sanctioned. Corrections 2026-09-25: IRS-CI involvement and a '~67% stock fall' were not supported by any source and were removed.</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>OFAC-sanctioned criminal no-log VPN / anonymization enabler.</t>
+          <t>LE-seized commercial residential-proxy platform (Alarum/NASDAQ: ALAR) with botnet-sourced exit nodes.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>NetNut (Alarum Technologies)</t>
+          <t>SHANGXING TECH LIMITED</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>suspected</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>T2-High Risk (Anonymization/Proxy Enabler)</t>
+          <t>T2-High Risk</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AS400619 (origin ASN; registry holder AROSSCLOUD INC. [US])</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AS136452 (SHANGXING TECH LIMITED; no routes); AS151468 (SHANGXING TECH LIMITED; no routes)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>103.112.97.0/24</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Hong Kong (SHANGXING TECH LIMITED); United States (AROSSCLOUD INC., AS400619 registrant)</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Israel (parent); global residential-proxy exit nodes</t>
+          <t>Hong Kong/US</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Alarum Technologies Ltd (NASDAQ: ALAR)</t>
+          <t>SHANGXING TECH LIMITED (named in first-party finding; holds AS136452/AS151468); AROSSCLOUD INC. (AS400619 registrant)</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>NetNut; Popa botnet (exit-node source)</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Alarum Technologies Ltd</t>
+          <t>Fastmos Co Limited (AS138644; shares 191.124.0.0/16 with AS400619); AROSSCLOUD INC.; Zun Cloud Limited (AS140212)</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>316 distinct threat-actor clusters (Google GTIG, June 2026)</t>
+          <t>China-nexus</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>Popa (proxy botnet)</t>
+          <t>Gshell C2; Vshell-adjacent; mass web-exploitation (Java memshell / CVE PoC)</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>Commercial residential-proxy platform with botnet-sourced exit nodes; Traffic obfuscation; Covert device enrollment via SDKs</t>
+          <t>Multi-org HK reseller ASN; recurring China-nexus C2 + exploitation staging; SOCKS relays</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>Residential-proxy exit nodes; Botnet-sourced infrastructure; LE-seized</t>
+          <t>Gshell default cert on tenants; mass-exploitation open directories; multiple org names on one ASN; GreyNoise React2Shell exploitation source; Cobalt Strike C2s (C2IntelFeeds); Not on Spamhaus ASN-DROP</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -5704,94 +5739,94 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>GTIG-NETNUT; KREBS-NETNUT; QURIUM-POPA-2026; KREBS-POPA-2026</t>
+          <t>CV-GSHELL-2026-07; CV-OPENDIR-2026-09; GREYNOISE-REACT2SHELL-2026; C2INTELFEEDS; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>On 2026-07-02 the FBI seized hundreds of NetNut-linked domains (the seizure notice thanks Google, Lumen and Shadowserver) and Google disrupted the associated Popa botnet (at least 2 million hijacked smart TVs, streaming boxes and Android devices): Google disabled accounts used for C2 and set Play Protect to disable apps carrying NetNut SDKs. GTIG observed 316 distinct threat clusters using suspected NetNut exit nodes in a single week of June 2026. Popa was first flagged by QiAnXin XLab in March 2025 as an Android component of the Vo1d botnet and was tied to NetNut in June 2026 by Krebs, Qurium, Nokia Deepfield and Synthient. NetNut is operated by NASDAQ-listed Alarum Technologies (ALAR), which disputes the allegations and paused traffic on the affected network; its shares fell 23.6% after hours. Builds on Google's Jan 2026 IPIDEA disruption. Not sanctioned. Corrections 2026-09-25: IRS-CI involvement and a '~67% stock fall' were not supported by any source and were removed.</t>
+          <t>AS400619 is registered to AROSSCLOUD INC. (US) and originates 70 IPv4 prefixes (191,744 addresses), including 103.112.96.0/22 which covers the tracked 103.112.97.0/24; SHANGXING TECH LIMITED itself holds AS136452 and AS151468 (HK; neither announced), so the row name most likely reflects the inetnum holder while AROSSCLOUD owns the origin ASN (APNIC inetnum not yet confirmed). AS400619 and Fastmos (AS138644) tile 191.124.0.0/16 exactly between them - strong registry evidence of a shared reseller relationship. Hosts the July 2026 unreported Gshell C2 cluster (103.112.97.163/.199) and a Sept 2026 mass web-exploitation workspace (Fastmos :8889 - gen_targets/CVE-PoC/Java-memshell RCE-verify/k8s scan, 283KB target list) plus a second exploit box (AROSSCLOUD :9999) - first-party CrimsonVector open-directory hunts. Public corroboration: GreyNoise lists AS400619 among React2Shell exploitation sources (Jan 2026); C2IntelFeeds recorded Cobalt Strike C2s on AROSSCLOUD addresses (Aug-Sep 2026); community RAT feeds list several 103.112.97.x hosts. PEG TECH INC and 'AS Data HK' links are unverified.</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>LE-seized commercial residential-proxy platform (Alarum/NASDAQ: ALAR) with botnet-sourced exit nodes.</t>
+          <t>HK reseller ASN, recurring China-nexus C2 and mass-exploitation host (SHANGXING/Fastmos/Arosscloud).</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SHANGXING TECH LIMITED</t>
+          <t>HostZealot (HZ Hosting Ltd)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>suspected</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>T2-High Risk</t>
+          <t>T4-Gray Zone</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>AS400619 (origin ASN; registry holder AROSSCLOUD INC. [US])</t>
+          <t>AS59711 (HZ-EU-AS)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AS136452 (SHANGXING TECH LIMITED; no routes); AS151468 (SHANGXING TECH LIMITED; no routes)</t>
+          <t>AS202015 (HZ-US-AS); AS61046 (HZ-UK-AS); AS201525 (HZ-CA-AS)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>103.112.97.0/24</t>
+          <t>Cl0p-used blocks: 79.141.160.0/22; 185.33.84.0/22; 193.42.38.0/24 (AS202015); 185.104.194.0/24; 185.117.88.0/22; 77.83.196.0/23; 185.80.52.0/22; 5.149.248.0/23 (AS59711); 185.81.112.0/23; 5.149.250.0/23 (AS61046); 79.141.166.0/23 (AS201525). Full footprint: 187 IPv4 prefixes / 79,360 addresses plus 2a01:8640::/32 (2026-09-25)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hong Kong (SHANGXING TECH LIMITED); United States (AROSSCLOUD INC., AS400619 registrant)</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Hong Kong/US</t>
+          <t>Bulgaria (Plovdiv HQ); servers marketed in ~20 locations (NL, DE, FR, PL, EE, SE, UK, US, CA, HK and others)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>SHANGXING TECH LIMITED (named in first-party finding; holds AS136452/AS151468); AROSSCLOUD INC. (AS400619 registrant)</t>
+          <t>HZ HOSTING LTD. / ХЗ ХОСТИНГ ЕООД (EIK 203391232; VAT BG203391232)</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Fastmos Co Limited (AS138644; shares 191.124.0.0/16 with AS400619); AROSSCLOUD INC.; Zun Cloud Limited (AS140212)</t>
+          <t>HostZealot; hostzealot.com; HZ-EU / HZ-UK / HZ-CA / HZ-US AS names; ORG-FNL9-RIPE</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>China-nexus</t>
+          <t>Cl0p / TA505 / FIN11 (Lace Tempest); SideWinder APT; Akira and Fog ransomware affiliates; TrickBot/Conti operators (2020)</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>Gshell C2; Vshell-adjacent; mass web-exploitation (Java memshell / CVE PoC)</t>
+          <t>Cl0p MFT mass-exploitation infrastructure (Accellion FTA; GoAnywhere; MOVEit; Cleo); DEWMODE webshell C2; DanaBot C2; SideWinder C2</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>Multi-org HK reseller ASN; recurring China-nexus C2 + exploitation staging; SOCKS relays</t>
+          <t>Recurrent multi-actor abuse of commercial VPS; Country-coded multi-ASN split under one LIR; VPN/proxy and Tor-relay hosting; Crypto payment accepted</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>Gshell default cert on tenants; mass-exploitation open directories; multiple org names on one ASN; GreyNoise React2Shell exploitation source; Cobalt Strike C2s (C2IntelFeeds); Not on Spamhaus ASN-DROP</t>
+          <t>Repeated vendor attribution of tenant infrastructure (CISA, Mandiant, Black Lotus Labs, Huntress, Kaspersky, Arctic Wolf, Team Cymru); Not on Spamhaus DROP or ASN-DROP; KYC and AUP present (counter-indicator); Vendor IOC geolocation (NL/US/CA/EE) differs from registry country (BG)</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2020-07</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -5801,94 +5836,89 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>CV-GSHELL-2026-07; CV-OPENDIR-2026-09; GREYNOISE-REACT2SHELL-2026; C2INTELFEEDS; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>TEAMCYMRU-CL0P-2026; CISA-AA23-158A; CISA-AR21-055A; MANDIANT-ACCELLION-2021; BLACKLOTUS-ACCELLION; HUNTRESS-CLEO-2024; KASPERSKY-SIDEWINDER-2024; BLACKBERRY-SIDEWINDER-2024; ARCTICWOLF-FOG-AKIRA-2024; BLACKLOTUS-DANABOT; CONTI-LEAKS-2020; WOODWARD-CLOP-SANKEY; BG-COMMREG-HZ; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>AS400619 is registered to AROSSCLOUD INC. (US) and originates 70 IPv4 prefixes (191,744 addresses), including 103.112.96.0/22 which covers the tracked 103.112.97.0/24; SHANGXING TECH LIMITED itself holds AS136452 and AS151468 (HK; neither announced), so the row name most likely reflects the inetnum holder while AROSSCLOUD owns the origin ASN (APNIC inetnum not yet confirmed). AS400619 and Fastmos (AS138644) tile 191.124.0.0/16 exactly between them - strong registry evidence of a shared reseller relationship. Hosts the July 2026 unreported Gshell C2 cluster (103.112.97.163/.199) and a Sept 2026 mass web-exploitation workspace (Fastmos :8889 - gen_targets/CVE-PoC/Java-memshell RCE-verify/k8s scan, 283KB target list) plus a second exploit box (AROSSCLOUD :9999) - first-party CrimsonVector open-directory hunts. Public corroboration: GreyNoise lists AS400619 among React2Shell exploitation sources (Jan 2026); C2IntelFeeds recorded Cobalt Strike C2s on AROSSCLOUD addresses (Aug-Sep 2026); community RAT feeds list several 103.112.97.x hosts. PEG TECH INC and 'AS Data HK' links are unverified.</t>
+          <t>Plovdiv-based commercial VPS/dedicated/colocation host (HZ HOSTING LTD., an EOOD incorporated January 2015; its RIPE LIR org ORG-FNL9-RIPE dates from 2012) announcing 187 IPv4 prefixes through four country-coded ASNs registered in Bulgaria. The Swedish AS209668 'HZ-HOSTING AB' is unrelated. Cl0p's most-reused provider: HZ ranges appear in 4 of the 10 Cl0p mass-exploitation campaigns (Accellion FTA 2020-21, GoAnywhere 2023, MOVEit 2023, Cleo 2024), matching Team Cymru's 'most frequently observed provider ... four of nine' (Aug 2026); Eli Woodward's campaign dataset shows HZ in 5 of 8 campaigns, adding PTC Windchill (June 2026), which is not reproducible from the published Windchill IOCs. 21 distinct HZ addresses appear in A/B-grade IOC lists (CISA AA23-158A: 10 GoAnywhere and 9 MOVEit; CISA MAR AR21-055A and Black Lotus Labs: 2 Accellion; Huntress: 1 Cleo). Reuse is block-level: only 79.141.160.78 recurs exactly (GoAnywhere and MOVEit), while 79.141.160.0/22 spans Accellion -&gt; GoAnywhere -&gt; MOVEit (~23-27 months) and 5.149.248.0/23 spans MOVEit -&gt; Cleo (~18 months). Other tenants: SideWinder (Kaspersky 2024: 'preference for HZ Hosting'), Akira/Fog SSL-VPN logins (Arctic Wolf 2024), a DanaBot C2 (Black Lotus Labs), a TrickBot/Conti server (2020 leaked chats), and APT28-attributed addresses in 79.141.161.x (maltrail). Counter-indicators: passport KYC demanded of a Conti operator (2020 chats); a 3-strike AUP; no Spamhaus DROP/ASN-DROP listing; reputation density comparable to mainstream hosts (many hits are Tor relays or VPN/proxy exits). The evidence shows repeated use by sophisticated tenants, not deliberate enablement - hence T4, not T3. Escalate on documented ignored abuse reports, forum BPH advertising, an above-baseline RF density score, or a substantiated ownership link to flagged personnel (Bulgarian registry aggregators disagree on the owner - verify in the Commercial Register). Use the Cl0p-used blocks for watchlisting and risk scoring rather than blanket blocking. See analysis/CL0P_HOSTZEALOT_REUSE.md.</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>HK reseller ASN, recurring China-nexus C2 and mass-exploitation host (SHANGXING/Fastmos/Arosscloud).</t>
+          <t>Bulgarian commercial hosting brand (HZ Hosting Ltd; four country-coded ASNs) repeatedly chosen by Cl0p and other advanced actors; gray-zone rather than bulletproof on current evidence.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HostZealot (HZ Hosting Ltd)</t>
+          <t>Chang Way Technologies Co. Limited</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>flagged</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>T4-Gray Zone</t>
+          <t>T2-High Risk</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>AS59711 (HZ-EU-AS)</t>
+          <t>AS57523 (CHANGWAY-AS; no routes)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AS202015 (HZ-US-AS); AS61046 (HZ-UK-AS); AS201525 (HZ-CA-AS)</t>
+          <t>AS59425 (HORIZONMSK-AS; no routes); AS207566 (LD007-AS; no routes); AS201738 (UFO TECHNOLOGIES LIMITED [GB]; Spamhaus-attributed via changway.hk); AS211663 (GALEON LLC [RU]; Spamhaus-attributed via changway.hk)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Cl0p-used blocks: 79.141.160.0/22; 185.33.84.0/22; 193.42.38.0/24 (AS202015); 185.104.194.0/24; 185.117.88.0/22; 77.83.196.0/23; 185.80.52.0/22; 5.149.248.0/23 (AS59711); 185.81.112.0/23; 5.149.250.0/23 (AS61046); 79.141.166.0/23 (AS201525). Full footprint: 187 IPv4 prefixes / 79,360 addresses plus 2a01:8640::/32 (2026-09-25)</t>
+          <t>45.93.20.0/24; 62.204.41.0/24; 91.240.118.0/24; 109.238.86.0/24; 185.11.61.0/24; 185.81.68.0/24; 193.178.158.0/24 (AS201738); 37.72.140.0/24 (AS211663) - all on Spamhaus DROP (2026-09)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Hong Kong (Chang Way); shell ASN holders in the UK and Russia</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Bulgaria (Plovdiv HQ); servers marketed in ~20 locations (NL, DE, FR, PL, EE, SE, UK, US, CA, HK and others)</t>
+          <t>Russia-linked (Proton66/PROSPERO cluster)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>HZ HOSTING LTD. / ХЗ ХОСТИНГ ЕООД (EIK 203391232; VAT BG203391232)</t>
+          <t>Chang Way Technologies Co. Limited</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>HostZealot; hostzealot.com; HZ-EU / HZ-UK / HZ-CA / HZ-US AS names; ORG-FNL9-RIPE</t>
+          <t>changway.hk; CHANGWAY/HOSTWAY panel theme (my.31337.hk)</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Cl0p / TA505 / FIN11 (Lace Tempest); SideWinder APT; Akira and Fog ransomware affiliates; TrickBot/Conti operators (2020)</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>Cl0p MFT mass-exploitation infrastructure (Accellion FTA; GoAnywhere; MOVEit; Cleo); DEWMODE webshell C2; DanaBot C2; SideWinder C2</t>
+          <t>Proton66/PROSPERO tenants (IP shifts observed by SpiderLabs)</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>Recurrent multi-actor abuse of commercial VPS; Country-coded multi-ASN split under one LIR; VPN/proxy and Tor-relay hosting; Crypto payment accepted</t>
+          <t>Rotating HK/UK/RU shell ASNs; Prefix hopping; Proton66-linked</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>Repeated vendor attribution of tenant infrastructure (CISA, Mandiant, Black Lotus Labs, Huntress, Kaspersky, Arctic Wolf, Team Cymru); Not on Spamhaus DROP or ASN-DROP; KYC and AUP present (counter-indicator); Vendor IOC geolocation (NL/US/CA/EE) differs from registry country (BG)</t>
+          <t>Spamhaus ASN-DROP (five ASNs under changway.hk); announced prefixes on Spamhaus DROP; high ASN churn (4 delisted and 2 added within ~9 months)</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>2020-07</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -5898,24 +5928,24 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>TEAMCYMRU-CL0P-2026; CISA-AA23-158A; CISA-AR21-055A; MANDIANT-ACCELLION-2021; BLACKLOTUS-ACCELLION; HUNTRESS-CLEO-2024; KASPERSKY-SIDEWINDER-2024; BLACKBERRY-SIDEWINDER-2024; ARCTICWOLF-FOG-AKIRA-2024; BLACKLOTUS-DANABOT; CONTI-LEAKS-2020; WOODWARD-CLOP-SANKEY; BG-COMMREG-HZ; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>SPAMHAUS-ASNDROP-2026; INTRINSEC-PROSPERO; TRUSTWAVE-PROSPERO; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Plovdiv-based commercial VPS/dedicated/colocation host (HZ HOSTING LTD., an EOOD incorporated January 2015; its RIPE LIR org ORG-FNL9-RIPE dates from 2012) announcing 187 IPv4 prefixes through four country-coded ASNs registered in Bulgaria. The Swedish AS209668 'HZ-HOSTING AB' is unrelated. Cl0p's most-reused provider: HZ ranges appear in 4 of the 10 Cl0p mass-exploitation campaigns (Accellion FTA 2020-21, GoAnywhere 2023, MOVEit 2023, Cleo 2024), matching Team Cymru's 'most frequently observed provider ... four of nine' (Aug 2026); Eli Woodward's campaign dataset shows HZ in 5 of 8 campaigns, adding PTC Windchill (June 2026), which is not reproducible from the published Windchill IOCs. 21 distinct HZ addresses appear in A/B-grade IOC lists (CISA AA23-158A: 10 GoAnywhere and 9 MOVEit; CISA MAR AR21-055A and Black Lotus Labs: 2 Accellion; Huntress: 1 Cleo). Reuse is block-level: only 79.141.160.78 recurs exactly (GoAnywhere and MOVEit), while 79.141.160.0/22 spans Accellion -&gt; GoAnywhere -&gt; MOVEit (~23-27 months) and 5.149.248.0/23 spans MOVEit -&gt; Cleo (~18 months). Other tenants: SideWinder (Kaspersky 2024: 'preference for HZ Hosting'), Akira/Fog SSL-VPN logins (Arctic Wolf 2024), a DanaBot C2 (Black Lotus Labs), a TrickBot/Conti server (2020 leaked chats), and APT28-attributed addresses in 79.141.161.x (maltrail). Counter-indicators: passport KYC demanded of a Conti operator (2020 chats); a 3-strike AUP; no Spamhaus DROP/ASN-DROP listing; reputation density comparable to mainstream hosts (many hits are Tor relays or VPN/proxy exits). The evidence shows repeated use by sophisticated tenants, not deliberate enablement - hence T4, not T3. Escalate on documented ignored abuse reports, forum BPH advertising, an above-baseline RF density score, or a substantiated ownership link to flagged personnel (Bulgarian registry aggregators disagree on the owner - verify in the Commercial Register). Use the Cl0p-used blocks for watchlisting and risk scoring rather than blanket blocking. See analysis/CL0P_HOSTZEALOT_REUSE.md.</t>
+          <t>Hong Kong provider that Intrinsec (Nov 2024) calls a 'likely related' network of PROSPERO/Proton66; Trustwave SpiderLabs observed IP shifts from Proton66 to Chang Way ASNs and the my.31337.hk panel re-themed 'CHANGWAY/HOSTWAY'. Split out of the PROSPERO row (where it was listed as an alias) on 2026-09-25. Spamhaus ASN-DROP lists five ASNs under changway.hk: Chang Way's own AS57523, AS59425 and AS207566 (none announcing) plus the newly added AS201738 (UFO TECHNOLOGIES LIMITED, GB; 7 /24s, all on Spamhaus DROP) and AS211663 (GALEON LLC, RU; 1 /24). Four other changway.hk ASNs listed in Dec 2025 (AS57678, AS208312, AS209309, AS213355) have since been delisted - a rotating-shell pattern. The name similarity between 'UFO Technologies Limited' and Stark's UFO Hosting is not an established link. T2 on ASN-DROP inclusion plus Intrinsec and SpiderLabs reporting.</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>Bulgarian commercial hosting brand (HZ Hosting Ltd; four country-coded ASNs) repeatedly chosen by Cl0p and other advanced actors; gray-zone rather than bulletproof on current evidence.</t>
+          <t>Hong Kong-anchored ring of rotating shell ASNs linked to the Proton66/PROSPERO bulletproof cluster; five ASNs on Spamhaus ASN-DROP.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Chang Way Technologies Co. Limited</t>
+          <t>UAB Host Baltic (serveroffer.lt)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5925,62 +5955,62 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>T2-High Risk</t>
+          <t>T2-High Risk (Upstream Enabler)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>AS57523 (CHANGWAY-AS; no routes)</t>
+          <t>AS209605 (HOSTBALTIC)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AS59425 (HORIZONMSK-AS; no routes); AS207566 (LD007-AS; no routes); AS201738 (UFO TECHNOLOGIES LIMITED [GB]; Spamhaus-attributed via changway.hk); AS211663 (GALEON LLC [RU]; Spamhaus-attributed via changway.hk)</t>
+          <t>AS211872 (ALPHA-NETWORKS; no routes); AS135388 (RPL-HK, RMP Protection Limited [HK]; Spamhaus-attributed via serveroffer.lt)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>45.93.20.0/24; 62.204.41.0/24; 91.240.118.0/24; 109.238.86.0/24; 185.11.61.0/24; 185.81.68.0/24; 193.178.158.0/24 (AS201738); 37.72.140.0/24 (AS211663) - all on Spamhaus DROP (2026-09)</t>
+          <t>141.98.8.0/22; 185.36.81.0/24 (AS209605); 93.152.223.0/24; 94.26.0.0/24 (AS135388)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hong Kong (Chang Way); shell ASN holders in the UK and Russia</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Russia-linked (Proton66/PROSPERO cluster)</t>
+          <t>Lithuania; Hong Kong (sibling ASN)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Chang Way Technologies Co. Limited</t>
+          <t>UAB Host Baltic</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>changway.hk; CHANGWAY/HOSTWAY panel theme (my.31337.hk)</t>
+          <t>serveroffer.lt; HOSTBALTIC</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Proton66/PROSPERO tenants (IP shifts observed by SpiderLabs)</t>
+          <t>BtHoster/BTCloud (transit customer); Initial Access Brokers (via BtHoster masscan servers)</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>Rotating HK/UK/RU shell ASNs; Prefix hopping; Proton66-linked</t>
+          <t>Upstream transit for BPH AS-leasing operators; HK sibling ASN</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>Spamhaus ASN-DROP (five ASNs under changway.hk); announced prefixes on Spamhaus DROP; high ASN churn (4 delisted and 2 added within ~9 months)</t>
+          <t>Spamhaus ASN-DROP (AS209605; AS135388 under serveroffer.lt); 5 of 6 announced prefixes overlap Spamhaus DROP; Upstream of T1 BtHoster</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -5990,24 +6020,24 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>SPAMHAUS-ASNDROP-2026; INTRINSEC-PROSPERO; TRUSTWAVE-PROSPERO; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>INTRINSEC-BTHOSTER; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Hong Kong provider that Intrinsec (Nov 2024) calls a 'likely related' network of PROSPERO/Proton66; Trustwave SpiderLabs observed IP shifts from Proton66 to Chang Way ASNs and the my.31337.hk panel re-themed 'CHANGWAY/HOSTWAY'. Split out of the PROSPERO row (where it was listed as an alias) on 2026-09-25. Spamhaus ASN-DROP lists five ASNs under changway.hk: Chang Way's own AS57523, AS59425 and AS207566 (none announcing) plus the newly added AS201738 (UFO TECHNOLOGIES LIMITED, GB; 7 /24s, all on Spamhaus DROP) and AS211663 (GALEON LLC, RU; 1 /24). Four other changway.hk ASNs listed in Dec 2025 (AS57678, AS208312, AS209309, AS213355) have since been delisted - a rotating-shell pattern. The name similarity between 'UFO Technologies Limited' and Stark's UFO Hosting is not an established link. T2 on ASN-DROP inclusion plus Intrinsec and SpiderLabs reporting.</t>
+          <t>Lithuanian hoster named by Intrinsec (June 2025) as a transit provider of the BtHoster/BTCloud AS-leasing operation (see the BtHoster row). Spamhaus ASN-DROP lists AS209605 (serveroffer.lt; 6 announced prefixes including 141.98.8.0/22 and 185.36.81.0/24, 5 of them overlapping Spamhaus DROP) and a newly listed Hong Kong sibling, AS135388 'RPL-HK' (RMP Protection Limited; 93.152.223.0/24 and 94.26.0.0/24). A second Host Baltic registration, AS211872 'ALPHA-NETWORKS', has no routes. Added 2026-09-25 as an upstream enabler (ASN-DROP inclusion plus upstream of a T1 entity, two independent sources).</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>Hong Kong-anchored ring of rotating shell ASNs linked to the Proton66/PROSPERO bulletproof cluster; five ASNs on Spamhaus ASN-DROP.</t>
+          <t>Lithuanian hoster and BtHoster transit provider; two serveroffer.lt ASNs on Spamhaus ASN-DROP.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>UAB Host Baltic (serveroffer.lt)</t>
+          <t>VPSVAULT.HOST LTD</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6017,62 +6047,57 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>T2-High Risk (Upstream Enabler)</t>
+          <t>T2-High Risk</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>AS209605 (HOSTBALTIC)</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AS211872 (ALPHA-NETWORKS; no routes); AS135388 (RPL-HK, RMP Protection Limited [HK]; Spamhaus-attributed via serveroffer.lt)</t>
+          <t>AS215925</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>141.98.8.0/22; 185.36.81.0/24 (AS209605); 93.152.223.0/24; 94.26.0.0/24 (AS135388)</t>
+          <t>45.194.92.0/24 (on Spamhaus DROP); 45.198.224.0/24; 45.205.1.0/24</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Lithuania; Hong Kong (sibling ASN)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>UAB Host Baltic</t>
+          <t>VPSVAULT.HOST LTD</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>serveroffer.lt; HOSTBALTIC</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>BtHoster/BTCloud (transit customer); Initial Access Brokers (via BtHoster masscan servers)</t>
+          <t>vpsvault.host</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Mass proxy-scanning sweep (96 hosts; 10.1M connection attempts, Aug 2026)</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>Upstream transit for BPH AS-leasing operators; HK sibling ASN</t>
+          <t>Persistent mass-scanning source</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>Spamhaus ASN-DROP (AS209605; AS135388 under serveroffer.lt); 5 of 6 announced prefixes overlap Spamhaus DROP; Upstream of T1 BtHoster</t>
+          <t>Spamhaus ASN-DROP (AS215925 under vpsvault.host); GreyNoise weekly-brief notable ASN since 2025-12-15</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -6082,24 +6107,24 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>INTRINSEC-BTHOSTER; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>SPAMHAUS-ASNDROP-2026; GREYNOISE-WEEKLY-2026-08; REGISTRY-SNAPSHOT-2026-09</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Lithuanian hoster named by Intrinsec (June 2025) as a transit provider of the BtHoster/BTCloud AS-leasing operation (see the BtHoster row). Spamhaus ASN-DROP lists AS209605 (serveroffer.lt; 6 announced prefixes including 141.98.8.0/22 and 185.36.81.0/24, 5 of them overlapping Spamhaus DROP) and a newly listed Hong Kong sibling, AS135388 'RPL-HK' (RMP Protection Limited; 93.152.223.0/24 and 94.26.0.0/24). A second Host Baltic registration, AS211872 'ALPHA-NETWORKS', has no routes. Added 2026-09-25 as an upstream enabler (ASN-DROP inclusion plus upstream of a T1 entity, two independent sources).</t>
+          <t>UK-registered VPS provider whose AS215925 has been on Spamhaus ASN-DROP since at least Dec 2025. GreyNoise has carried it in its weekly brief since 2025-12-15; in the period to 2026-08-30 it produced 10,135,029 connection attempts in a 96-host proxy-scanning sweep. GreyNoise advises against an ASN-level block (shared tenancy). Announces 45.194.92.0/24 (on Spamhaus DROP), 45.198.224.0/24 and 45.205.1.0/24. Added 2026-09-25 at T2 under the taxonomy's ASN-DROP escalation rule (Spamhaus plus GreyNoise meet the two-source T2 evidence floor); no malware/C2 attribution yet.</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>Lithuanian hoster and BtHoster transit provider; two serveroffer.lt ASNs on Spamhaus ASN-DROP.</t>
+          <t>UK VPS provider on Spamhaus ASN-DROP and a persistent GreyNoise-tracked mass-scanning source.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>VPSVAULT.HOST LTD</t>
+          <t>Feo Prest SRL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6114,52 +6139,52 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>AS215925</t>
+          <t>AS208137</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>45.194.92.0/24 (on Spamhaus DROP); 45.198.224.0/24; 45.205.1.0/24</t>
+          <t>62.60.131.0/24; 213.177.179.0/24; 213.209.159.0/24 (on Spamhaus DROP)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>VPSVAULT.HOST LTD</t>
+          <t>Feo Prest SRL</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>vpsvault.host</t>
+          <t>feoprest.info</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>Mass proxy-scanning sweep (96 hosts; 10.1M connection attempts, Aug 2026)</t>
+          <t>ENV/secret-file crawling; CVE-2025-48927 exploitation attempts</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>Persistent mass-scanning source</t>
+          <t>Persistent high-volume scanning and exploitation source</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>Spamhaus ASN-DROP (AS215925 under vpsvault.host); GreyNoise weekly-brief notable ASN since 2025-12-15</t>
+          <t>Spamhaus ASN-DROP (AS208137 under feoprest.info); GreyNoise weekly-brief notable IPs since 2026-06-22</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -6174,79 +6199,74 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>UK-registered VPS provider whose AS215925 has been on Spamhaus ASN-DROP since at least Dec 2025. GreyNoise has carried it in its weekly brief since 2025-12-15; in the period to 2026-08-30 it produced 10,135,029 connection attempts in a 96-host proxy-scanning sweep. GreyNoise advises against an ASN-level block (shared tenancy). Announces 45.194.92.0/24 (on Spamhaus DROP), 45.198.224.0/24 and 45.205.1.0/24. Added 2026-09-25 at T2 under the taxonomy's ASN-DROP escalation rule (Spamhaus plus GreyNoise meet the two-source T2 evidence floor); no malware/C2 attribution yet.</t>
+          <t>Romanian provider on Spamhaus ASN-DROP (feoprest.info). GreyNoise (weekly brief to 2026-08-30): 40 active hosts; 213.209.159.175, carried since the 2026-06-22 brief, produced 1.8M sessions and 23% of CVE-2025-48927 exploitation attempts; 213.209.159.154 and .175 were top-volume ENV crawlers. Announces 62.60.131.0/24, 213.177.179.0/24 and 213.209.159.0/24 (the last on Spamhaus DROP). Added 2026-09-25 at T2 under the taxonomy's ASN-DROP escalation rule (Spamhaus plus GreyNoise meet the two-source T2 evidence floor); no malware/C2 attribution yet.</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>UK VPS provider on Spamhaus ASN-DROP and a persistent GreyNoise-tracked mass-scanning source.</t>
+          <t>Romanian provider on Spamhaus ASN-DROP hosting persistent high-volume scanning and exploitation sources.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Feo Prest SRL</t>
+          <t>QTFY (QScan / QTRouter)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>flagged</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>T2-High Risk</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>AS208137</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>62.60.131.0/24; 213.177.179.0/24; 213.209.159.0/24 (on Spamhaus DROP)</t>
+          <t>T1-Confirmed BPH (Anonymization/Proxy Enabler)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>China (Nanjing); global proxy/ORB nodes</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Feo Prest SRL</t>
+          <t>Nanjing Xinjiuwei Network Technology Co. (employer of the QTFY operators)</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>feoprest.info</t>
+          <t>QTFY; QScan; QTRouter; qtproxy.xyz; Fast Labyrinth / QTProxy (Lumen tracking names)</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>DOJ/FBI court-authorised seizure of QScan and QTRouter domains, Aug 26 2026</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>PRC state-sponsored actors (MSS and PLA customers)</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>ENV/secret-file crawling; CVE-2025-48927 exploitation attempts</t>
+          <t>QScan (IoT scanner and infector); QTRouter (obfuscation network)</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>Persistent high-volume scanning and exploitation source</t>
+          <t>State-enablement 'infrastructure quartermaster'; ORB network mixing compromised IoT, commercial proxy subscriptions and leased VPS</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>Spamhaus ASN-DROP (AS208137 under feoprest.info); GreyNoise weekly-brief notable IPs since 2026-06-22</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>2026-06</t>
+          <t>LE seizure; Commercial proxy-service nodes and leased VPS chained through Clash</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -6256,79 +6276,69 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>SPAMHAUS-ASNDROP-2026; GREYNOISE-WEEKLY-2026-08; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>DOJ-QTFY-2026; LUMEN-QTFY-2026</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Romanian provider on Spamhaus ASN-DROP (feoprest.info). GreyNoise (weekly brief to 2026-08-30): 40 active hosts; 213.209.159.175, carried since the 2026-06-22 brief, produced 1.8M sessions and 23% of CVE-2025-48927 exploitation attempts; 213.209.159.154 and .175 were top-volume ENV crawlers. Announces 62.60.131.0/24, 213.177.179.0/24 and 213.209.159.0/24 (the last on Spamhaus DROP). Added 2026-09-25 at T2 under the taxonomy's ASN-DROP escalation rule (Spamhaus plus GreyNoise meet the two-source T2 evidence floor); no malware/C2 attribution yet.</t>
+          <t>On 2026-08-26 DOJ and the FBI seized, under court authorisation, the domains hard-coded into QScan (an IoT scanner and infector) and QTRouter (an obfuscation network) run by the 'QTFY' technical-quartermaster group, whose staff work for Nanjing Xinjiuwei Network Technology Co. and whose customers include the MSS and PLA. QTRouter chained compromised IoT devices, bulk-bought Chinese commercial proxy subscriptions and leased VPSs through Clash, with admin servers at qtproxy.xyz; reported victims include NASA, the Federal Reserve, DOE, DOJ, HHS, NIH and the US Senate. Lumen Black Lotus Labs, which tracked the network as 'Fast Labyrinth'/'QTProxy', collaborated. A state-enablement proxy TAE showing commercial proxy supply feeding espionage ORB networks. No ASN of its own has been published.</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>Romanian provider on Spamhaus ASN-DROP hosting persistent high-volume scanning and exploitation sources.</t>
+          <t>PRC 'infrastructure quartermaster' proxy/ORB platform serving state hackers; domains seized by DOJ/FBI in Aug 2026.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>QTFY (QScan / QTRouter)</t>
+          <t>IPIDEA residential-proxy network</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>exposed</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>T1-Confirmed BPH (Anonymization/Proxy Enabler)</t>
+          <t>T2-High Risk (Anonymization/Proxy Enabler)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>China (Nanjing); global proxy/ORB nodes</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Nanjing Xinjiuwei Network Technology Co. (employer of the QTFY operators)</t>
+          <t>Global residential exit nodes</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>QTFY; QScan; QTRouter; qtproxy.xyz; Fast Labyrinth / QTProxy (Lumen tracking names)</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>DOJ/FBI court-authorised seizure of QScan and QTRouter domains, Aug 26 2026</t>
+          <t>360 Proxy; 922 Proxy; ABC Proxy; Cherry Proxy; IP2World; Luna Proxy; PIA S5 Proxy; PY Proxy; SDKs: Castar, Earn, Hex, Packet SDK</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>PRC state-sponsored actors (MSS and PLA customers)</t>
+          <t>550+ threat groups in one week (GTIG), reportedly including APT28, Sandworm and Volt Typhoon</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>QScan (IoT scanner and infector); QTRouter (obfuscation network)</t>
+          <t>BADBOX 2.0 (facilitated)</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>State-enablement 'infrastructure quartermaster'; ORB network mixing compromised IoT, commercial proxy subscriptions and leased VPS</t>
+          <t>Residential-proxy network built from SDK-enrolled and compromised devices; Multi-brand resale</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>LE seizure; Commercial proxy-service nodes and leased VPS chained through Clash</t>
+          <t>Private-sector disruption (Google GTIG, Jan 2026); SDK-based covert device enrollment</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -6338,87 +6348,15 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>DOJ-QTFY-2026; LUMEN-QTFY-2026</t>
+          <t>GTIG-IPIDEA-2026</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>On 2026-08-26 DOJ and the FBI seized, under court authorisation, the domains hard-coded into QScan (an IoT scanner and infector) and QTRouter (an obfuscation network) run by the 'QTFY' technical-quartermaster group, whose staff work for Nanjing Xinjiuwei Network Technology Co. and whose customers include the MSS and PLA. QTRouter chained compromised IoT devices, bulk-bought Chinese commercial proxy subscriptions and leased VPSs through Clash, with admin servers at qtproxy.xyz; reported victims include NASA, the Federal Reserve, DOE, DOJ, HHS, NIH and the US Senate. Lumen Black Lotus Labs, which tracked the network as 'Fast Labyrinth'/'QTProxy', collaborated. A state-enablement proxy TAE showing commercial proxy supply feeding espionage ORB networks. No ASN of its own has been published.</t>
+          <t>On 2026-01-29 Google's Threat Intelligence Group announced legal action against IPIDEA's command domains, with Cloudflare, Spur and Lumen Black Lotus Labs, shrinking its device pool by millions; Play Protect now removes apps carrying IPIDEA SDKs. GTIG saw more than 550 threat groups using the network in a single week (Google's John Hultquist named APT28, Sandworm and Volt Typhoon among them); IPIDEA advertised 6.1M IPs updated daily. It is resold under at least eight brands and enrolled devices through the Castar, Earn, Hex and Packet SDKs; it also facilitated BADBOX 2.0. Part of the residential-proxy enforcement lineage 911 S5 -&gt; Moonlander (5socks/Anyproxy) -&gt; SocksEscort -&gt; IPIDEA -&gt; Asocks -&gt; NetNut -&gt; QTRouter. Operator identity and jurisdiction are unverified; not sanctioned. Status 'exposed' because the disruption was a private-sector legal action rather than a law-enforcement seizure.</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
-        <is>
-          <t>PRC 'infrastructure quartermaster' proxy/ORB platform serving state hackers; domains seized by DOJ/FBI in Aug 2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>IPIDEA residential-proxy network</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>exposed</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>T2-High Risk (Anonymization/Proxy Enabler)</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Global residential exit nodes</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>360 Proxy; 922 Proxy; ABC Proxy; Cherry Proxy; IP2World; Luna Proxy; PIA S5 Proxy; PY Proxy; SDKs: Castar, Earn, Hex, Packet SDK</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>550+ threat groups in one week (GTIG), reportedly including APT28, Sandworm and Volt Typhoon</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>BADBOX 2.0 (facilitated)</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>Residential-proxy network built from SDK-enrolled and compromised devices; Multi-brand resale</t>
-        </is>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>Private-sector disruption (Google GTIG, Jan 2026); SDK-based covert device enrollment</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>GTIG-IPIDEA-2026</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>On 2026-01-29 Google's Threat Intelligence Group announced legal action against IPIDEA's command domains, with Cloudflare, Spur and Lumen Black Lotus Labs, shrinking its device pool by millions; Play Protect now removes apps carrying IPIDEA SDKs. GTIG saw more than 550 threat groups using the network in a single week (Google's John Hultquist named APT28, Sandworm and Volt Typhoon among them); IPIDEA advertised 6.1M IPs updated daily. It is resold under at least eight brands and enrolled devices through the Castar, Earn, Hex and Packet SDKs; it also facilitated BADBOX 2.0. Part of the residential-proxy enforcement lineage 911 S5 -&gt; Moonlander (5socks/Anyproxy) -&gt; SocksEscort -&gt; IPIDEA -&gt; Asocks -&gt; NetNut -&gt; QTRouter. Operator identity and jurisdiction are unverified; not sanctioned. Status 'exposed' because the disruption was a private-sector legal action rather than a law-enforcement seizure.</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
         <is>
           <t>Multi-brand residential-proxy network used by 550+ threat groups; disrupted by Google in Jan 2026.</t>
         </is>

--- a/BPH_Master.xlsx
+++ b/BPH_Master.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="BPH_Master" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BPH_Master" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>flagged</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1627,17 +1627,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AS202412 (OMEGATECH / Omegatech LTD [SC]; live Virtualine network, Spamhaus ASN-DROP under virtualine.org)</t>
+          <t>AS202412 (OMEGATECH / Omegatech LTD [SC]; Virtualine network until the Oct 2026 seizure - seen by 1 of 323 RIS peers since 2026-10-27; Spamhaus ASN-DROP under virtualine.org)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Originated by AS202412 Jan-Oct 2026, all on Spamhaus DROP (2026-10-29): 91.92.240.0/22; 158.94.208.0/22; 178.16.52.0/22 (these three ex-AS209800); 45.132.180.0/24; 94.26.38.0/24; 94.154.35.0/24; 94.154.40.0/24; 94.154.46.0/24; 130.12.180.0/24; 146.19.125.0/24; 193.30.241.0/24. Also short-lived /24s from broker-leased space that moves between unrelated ASNs (re-check the current origin before blocking): 45.74.7.0/24; 45.74.57.0/24; 45.74.59.0/24; 104.250.184.0/24; 172.111.246.0/24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>United States (Kentucky LLC)</t>
+          <t>United States (Kentucky LLC: Railnet); Seychelles (Omegatech LTD, RIPE org created 2026-01-05)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Russia-linked operator; EU-hosted infrastructure</t>
+          <t>Russian-speaking operator; EU-hosted infrastructure (Dutch servers in Limburg seized Oct 2026)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1647,12 +1652,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Virtualine Technologies; RAILNET; OMEGATECH; DripHosting/DiorHost; RetryHost</t>
+          <t>Virtualine Technologies; RAILNET; OMEGATECH; Secury; Massgod; Spamhouse; Lanedo; DripHosting/DiorHost; RetryHost; virtualine.net (seized); virtualine.org</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>aurologic GmbH (AS30823) (~95% of prefixes, Aug 2025); Pfcloud UG (AS51396) (one /24)</t>
+          <t>Pfcloud UG (AS51396) and PEERYX NETWORK SAS (AS213382) (AS202412 neighbours, Oct 2026); aurologic GmbH (AS30823) (~95% of prefixes, Aug 2025; still a DDoS-protection tunnel hop in a community traceroute, Oct 2026)</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1660,29 +1665,39 @@
           <t>aurologic GmbH</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>FBI seizure of virtualine.net under an E.D. Va. warrant (Operation Omegaline), announced Oct 27 2026; Politie Midden-Nederland seized dozens of physical servers in Limburg (hundreds of VPS offline; data on 3,000+ customers); concurrent FBI and German police actions against suspects and crypto - no operators named or charges announced</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>UAC-0050; UAC-0006</t>
+          <t>UAC-0050; UAC-0006; 'Vendor 1' CSAM/NCII and hack-for-hire forum (DOJ); Russian drug marketplace, sextortion scheme and ransomware groups (crypto payers, TRM)</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Latrodectus; AsyncRAT</t>
+          <t>Latrodectus; AsyncRAT; StealC (crypto payer, TRM)</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Underground forum advertising; Prefix shedding; No route diversification</t>
+          <t>Underground forum advertising; Prefix shedding; No route diversification; Shell-company migration sold as a service; No-AML bitcoin payments</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Spamhaus ASN-DROP (AS202412 under virtualine.org; AS214943 and AS214940 listed under virtualine.org in Dec 2025); Underground forum advertising; High malicious traffic ratio</t>
+          <t>Spamhaus ASN-DROP (AS202412 under virtualine.org; AS214943 and AS214940 listed under virtualine.org in Dec 2025); Every AS202412-originated prefix on Spamhaus DROP; Underground forum advertising; High malicious traffic ratio; LE seizure</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1692,12 +1707,17 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>RF-TAE-2026; GBHACKERS-BPH; TEAMCYMRU-VIRTUALINE; SPAMHAUS-BPH; RF-AUROLOGIC; SPAMHAUS-ASNDROP-2026; INTRINSEC-OMEGATECH-2026; INTRINSEC-UAC-2025; REGISTRY-SNAPSHOT-2026-09; INTRINSEC-FDN3-2025</t>
+          <t>RF-TAE-2026; GBHACKERS-BPH; TEAMCYMRU-VIRTUALINE; SPAMHAUS-BPH; RF-AUROLOGIC; SPAMHAUS-ASNDROP-2026; INTRINSEC-OMEGATECH-2026; INTRINSEC-UAC-2025; REGISTRY-SNAPSHOT-2026-09; INTRINSEC-FDN3-2025; DOJ-VIRTUALINE-2026; POLITIE-VIRTUALINE-2026; SILENTPUSH-OMEGATECH-2026; CHAINALYSIS-VIRTUALINE-2026; TRM-VIRTUALINE-2026; THERECORD-VIRTUALINE-2026; THN-VIRTUALINE-2026; LES-VIRTUALINE-2026; REGISTRY-SNAPSHOT-2026-10</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Virtualine Technologies is the operator behind Railnet LLC (AS214943, Kentucky LLC), KPROHOST (AS214940), the 'metaspinner' AS209800 front, likely Karina Rashkovska (AS215789) and now OMEGATECH (AS202412) - at least five number-resource identities. Advertised on Russian-language forums for phishing/spam enablement ('DMCA &amp; Abuse Ignored'). RF ranked Virtualine #1 by Threat Density for 2025; Intrinsec documented UAC-0050/UAC-0006 activity on its infrastructure and, in May 2026, assessed OMEGATECH as 'yet another network created by Virtualine' (642k+ honeypot hits in March 2026). In April 2025 it shifted IPv4 resources to the 'metaspinner' AS209800; those ranges now sit on AS202412. AS214943 has announced nothing since ~2026-02 and was dropped from ASN-DROP; OMEGATECH is the live network (15 /24s, 13 on Spamhaus DROP). Tier raised T2 -&gt; T1 on 2026-09-25 (taxonomy T1: RF top-decile density; forum BPH advertising with infrastructure evidence; 3+ independent vendors). | Merged record (was a duplicate AS214943 row).</t>
+          <t>Virtualine Technologies is the operator behind Railnet LLC (AS214943, Kentucky LLC), KPROHOST (AS214940), the 'metaspinner' AS209800 front, likely Karina Rashkovska (AS215789) and OMEGATECH (AS202412) - at least five number-resource identities. SEIZED 2026-10-27 (Operation Omegaline): the FBI Washington Field Office seized virtualine.net under an E.D. Va. warrant, with Polizei Hessen, Politie Midden-Nederland, the UK NCA and private partners OverRIPE and Lumen; Chainalysis supported. DOJ names the aliases Secury, Massgod, Spamhouse, Lanedo and Omegatech, alleges it knowingly hosted 'Vendor 1' (a forum selling CSAM and non-consensual intimate images, with hack-for-hire) despite notices from German, Canadian and Australian police, NCMEC and a victim's attorney from Jan 2026, and that it laundered customer payments taken via unhosted 'BTC [NO-AML]' addresses. Forum advertising: Exploit.in from 2024-08-28 ('all illegal/black hat activities ... except for child contents and terrorism', Sept 2024); HackForums ('ignored more abuse than your last three therapists', June 2025); in Mar 2026 it sold an 'additional protection plan' moving a customer's server to an unaffiliated shell company after an LE request. Dutch police seized dozens of physical servers in Limburg (hundreds of VPS offline; data on 3,000+ customers) and say the FBI and German police acted against suspects and crypto at the same time; no operators were named or charged. TRM: most illicit-attributed crypto of any TRM-labelled BPH in 2026 (inflows ~44% Russian drug market, ~17% sextortion, ~13% mixer, ~5% ransomware; also StealC and the BPH Volhav). Network: Silent Push saw the move from AS214943 to AS202412 on 2026-02-11; AS202412 originated 24 /24s in the two weeks before the seizure (all on Spamhaus DROP) and has been seen by 1 of 323 RIS peers since 2026-10-27; its last neighbours were Pfcloud (AS51396) and PEERYX (AS213382). The operator posted an open letter on virtualine.org denying the allegations and saying it could rebrand in 'a day, perhaps even less' - watch for a successor ASN. LEAD (not attributed): AS219199 (GENYUS SOFT LTD [SC], created 2026-07-15) announced four broker-leased /24s from 2026-10-22, including 172.111.246.0/24 previously on AS202412, and withdrew them on the morning of the seizure; only a community post calls it Virtualine, and Spamhaus lists it under genyus.sc. Earlier history: RF ranked Virtualine #1 by Threat Density for 2025; Intrinsec documented UAC-0050/UAC-0006 activity and in May 2026 assessed OMEGATECH as 'yet another network created by Virtualine'; in April 2025 it shifted IPv4 resources to AS209800 (Spamhaus reported the expansion in Sept 2025), and those ranges later moved to AS202412. Status flagged -&gt; seized 2026-10-29; tier stays T1 (raised T2 -&gt; T1 on 2026-09-25). | Merged record (was a duplicate AS214943 row).</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Russian-speaking bulletproof host (RF 2025 Threat Density #1); domain seized and Dutch servers taken in the FBI-led Operation Omegaline, Oct 2026.</t>
         </is>
       </c>
     </row>
@@ -2102,17 +2122,17 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>RF-TAE-2026; RF-AUROLOGIC; KREBS-BPH; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>RF-TAE-2026; RF-AUROLOGIC; KREBS-BPH; REGISTRY-SNAPSHOT-2026-09; DOJ-VIRTUALINE-2026; THN-VIRTUALINE-2026</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>AS209800 was created 2025-04-25 and announced solely via aurologic; RF Insikt says it was controlled by Virtualine-affiliated actors who impersonated the long-standing legitimate Hamburg company metaspinner net GmbH (RENAMED 2026-09-25 so the row no longer names that company as the operator). Its prefixes (91.92.240.0/22, 158.94.208.0/22, 178.16.52.0/22) received Virtualine traffic from April 2025 and now originate from OMEGATECH AS202412 (see the Railnet/Virtualine row). The ASN has been re-issued to an unrelated German GbR (ZEMA) - do not block AS209800. Status set to 'dissolved' (network defunct).</t>
+          <t>AS209800 was created 2025-04-25 and announced solely via aurologic; RF Insikt says it was controlled by Virtualine-affiliated actors who impersonated the long-standing legitimate Hamburg company metaspinner net GmbH (RENAMED 2026-09-25 so the row no longer names that company as the operator). Its prefixes (91.92.240.0/22, 158.94.208.0/22, 178.16.52.0/22) received Virtualine traffic from April 2025 and now originate from OMEGATECH AS202412 (see the Railnet/Virtualine row). The ASN has been re-issued to an unrelated German GbR (ZEMA) - do not block AS209800. Status set to 'dissolved' (network defunct). Attribution strengthened 2026-10-29: DOJ lists 'Lanedo' among Virtualine's aliases, matching the LANEDONET re-description, and Spamhaus (Sept 2025) reported Virtualine's expansion onto AS209800. Tier left at T3 as a historical record pending review.</t>
         </is>
       </c>
     </row>
@@ -2179,17 +2199,17 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>RF-AUROLOGIC; RIPE-DB; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09; INTRINSEC-FDN3-2025</t>
+          <t>RF-AUROLOGIC; RIPE-DB; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09; INTRINSEC-FDN3-2025; DOJ-VIRTUALINE-2026</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>RIPE-registered 2024-05-10 by KPROHOST LLC (Frankfort, KY; Kentucky reg. 1360766); abuse contact kprohost.abuse@gmail.com. Intrinsec attributes AS214940 to Virtualine, and Spamhaus listed it under virtualine.org in Dec 2025 (since delisted). Its two historical /24s (195.211.191.0/24, 45.144.212.0/24) now originate from HBING (AS208949) and Pfcloud (AS51396). The ASN has announced nothing since ~2026-08-12. Tier raised T3 -&gt; T2 on 2026-09-25 (shell structure; part of a T1 operator; blocklisting). Correction: its upstreams were Pfcloud and AS215436, not aurologic.</t>
+          <t>RIPE-registered 2024-05-10 by KPROHOST LLC (Frankfort, KY; Kentucky reg. 1360766); abuse contact kprohost.abuse@gmail.com. Intrinsec attributes AS214940 to Virtualine, and Spamhaus listed it under virtualine.org in Dec 2025 (since delisted). Its two historical /24s (195.211.191.0/24, 45.144.212.0/24) now originate from HBING (AS208949) and Pfcloud (AS51396). The ASN has announced nothing since ~2026-08-12. Tier raised T3 -&gt; T2 on 2026-09-25 (shell structure; part of a T1 operator; blocklisting). Correction: its upstreams were Pfcloud and AS215436, not aurologic. Virtualine, the operator, was disrupted in the FBI-led Operation Omegaline on 2026-10-27 (see the Railnet/Virtualine row); AS214940 was already dark.</t>
         </is>
       </c>
     </row>
@@ -5063,17 +5083,17 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>RUDIS-BPH-WATCH; RF-AUROLOGIC; SPAMHAUS-ASNDROP-2026; GREYNOISE-WEEKLY-2026-08; GREYNOISE-REACT2SHELL-2026; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>RUDIS-BPH-WATCH; RF-AUROLOGIC; SPAMHAUS-ASNDROP-2026; GREYNOISE-WEEKLY-2026-08; GREYNOISE-REACT2SHELL-2026; REGISTRY-SNAPSHOT-2026-09; REGISTRY-SNAPSHOT-2026-10; LES-VIRTUALINE-2026</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>German micro-provider (AS51396: 26 IPv4 and 24 IPv6 prefixes). Spamhaus ASN-DROP has listed AS51396 since at least Feb 2024 (with a since-recycled AS202685 'as-pfcloud'); it now also lists AS215310 (USERCLOUD) and AS400328 (Intelligence Hosting LLC) under pfcloud.io. RF lists Pfcloud as an upstream of the Virtualine/Railnet 'hosting island' alongside aurologic. GreyNoise (Aug 2026): 204.76.203.43 on AS51396 generated 393,777 sessions and most of the period's 121,068 Hikvision CVE-2021-36260 exploitation attempts; Pfcloud IPs also appear among React2Shell sources. A community note (Sept 2026, D-grade) describes a Pfcloud open directory staging FortiGate 60F exploit modules on an IP previously listed as AsyncRAT C2. Tier raised T3 -&gt; T2 (status flagged) on 2026-09-25 per the ASN-DROP escalation rule; the earlier single-honeypot caveat is outdated.</t>
+          <t>German micro-provider (AS51396: 26 IPv4 and 24 IPv6 prefixes). Spamhaus ASN-DROP has listed AS51396 since at least Feb 2024 (with a since-recycled AS202685 'as-pfcloud'); it now also lists AS215310 (USERCLOUD) and AS400328 (Intelligence Hosting LLC) under pfcloud.io. RF lists Pfcloud as an upstream of the Virtualine/Railnet 'hosting island' alongside aurologic. GreyNoise (Aug 2026): 204.76.203.43 on AS51396 generated 393,777 sessions and most of the period's 121,068 Hikvision CVE-2021-36260 exploitation attempts; Pfcloud IPs also appear among React2Shell sources. A community note (Sept 2026, D-grade) describes a Pfcloud open directory staging FortiGate 60F exploit modules on an IP previously listed as AsyncRAT C2. Tier raised T3 -&gt; T2 (status flagged) on 2026-09-25 per the ASN-DROP escalation rule; the earlier single-honeypot caveat is outdated. Oct 2026: Pfcloud was one of the last two neighbours of Virtualine's AS202412 when it was seized (Operation Omegaline); a community post says the Dutch servers seized in Limburg were Tube-Hosting (AS49581) hardware resold to Virtualine through Pfcloud (unconfirmed).</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">

--- a/BPH_Master.xlsx
+++ b/BPH_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y71"/>
+  <dimension ref="A1:Y72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6035,17 +6035,17 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>INTRINSEC-BTHOSTER; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>INTRINSEC-BTHOSTER; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09; LES-VIRTUALINE-2026</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Lithuanian hoster named by Intrinsec (June 2025) as a transit provider of the BtHoster/BTCloud AS-leasing operation (see the BtHoster row). Spamhaus ASN-DROP lists AS209605 (serveroffer.lt; 6 announced prefixes including 141.98.8.0/22 and 185.36.81.0/24, 5 of them overlapping Spamhaus DROP) and a newly listed Hong Kong sibling, AS135388 'RPL-HK' (RMP Protection Limited; 93.152.223.0/24 and 94.26.0.0/24). A second Host Baltic registration, AS211872 'ALPHA-NETWORKS', has no routes. Added 2026-09-25 as an upstream enabler (ASN-DROP inclusion plus upstream of a T1 entity, two independent sources).</t>
+          <t>Lithuanian hoster named by Intrinsec (June 2025) as a transit provider of the BtHoster/BTCloud AS-leasing operation (see the BtHoster row). Spamhaus ASN-DROP lists AS209605 (serveroffer.lt; 6 announced prefixes including 141.98.8.0/22 and 185.36.81.0/24, 5 of them overlapping Spamhaus DROP) and a newly listed Hong Kong sibling, AS135388 'RPL-HK' (RMP Protection Limited; 93.152.223.0/24 and 94.26.0.0/24). A second Host Baltic registration, AS211872 'ALPHA-NETWORKS', has no routes. Added 2026-09-25 as an upstream enabler (ASN-DROP inclusion plus upstream of a T1 entity, two independent sources). Oct 2026: a community post says AnonRDP's Lithuanian 'bulletproof' servers (see the AnonRDP / Blatant Technologies row) are hosted here and tunnelled through SMARTNET Germany - unconfirmed.</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
@@ -6379,6 +6379,118 @@
       <c r="Y71" t="inlineStr">
         <is>
           <t>Multi-brand residential-proxy network used by 550+ threat groups; disrupted by Google in Jan 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>AnonRDP / Blatant Technologies</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>seized</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>T1-Confirmed BPH</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AS403005 (BLATANTHOST; Blatant Technologies, LLC [SC/ARIN], registered 2026-09-25; Spamhaus ASN-DROP under blatant.host)</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AS205759 (historical; GHOSTYNETWORKS [US-KY]; deregistered)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Announced by AS403005 from late Sept/Oct 2026, all on Spamhaus DROP (2026-10-29): 31.56.19.0/24; 36.255.97.0/24; 43.228.157.0/24; 46.151.182.0/24; 64.89.160.0/24; 64.89.161.0/24; 196.251.100.0/24; 196.251.102.0/24; 196.251.121.0/24</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Seychelles (Blatant Technologies, LLC; ARIN contacts at a Louisville, Kentucky address); GHOSTYNETWORKS: United States (Kentucky)</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Advertised locations: Lithuania (Vilnius, bulletproof line), Netherlands, New York, Stockholm; AS403005 transits SMARTNET Germany</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Blatant Technologies, LLC (AS403005 registrant)</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>AnonRDP; anonrdp.com (on FBI seizure nameservers since 2026-10-27); anonrdp.st; anonrdp.net; BLATANTHOST; GHOSTYNETWORKS; OPTIBOUNCE (earlier network, per Intrinsec); AnonProtect (FastFlux CDN)</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>SMARTNET Germany GmbH (AS203446) (sole neighbour of AS403005, Oct 2026)</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>SMARTNET Germany GmbH</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>anonrdp.com moved to FBI seizure nameservers (NS1/NS2.FBI.SEIZED.GOV) Oct 27 2026, the day of Operation Omegaline - no seizure page or DOJ statement as of Oct 29 2026</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Malspam operator targeting CIS energy and finance ministries (spam source and backdoor C2 on GHOSTYNETWORKS, Intrinsec, Mar 2026)</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>JavaScript backdoor (unnamed; Intrinsec)</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Self-identified bulletproof; Spamhaus-ignored FastFlux CDN; Scanning servers; Shell company; Rapid ASN replacement; Domain hopping; Telegram operations; Recruits customers of seized hosts</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Spamhaus ASN-DROP (AS403005 under blatant.host); All announced /24s on Spamhaus DROP; Bulletproof self-identification; Newly registered ASN; Single upstream; LE domain seizure</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>SILENTPUSH-OMEGATECH-2026; INTRINSEC-OMEGATECH-2026; REGISTRY-SNAPSHOT-2026-10; CV-ANONRDP-2026-10; ANONRDP-SELF-2026; LES-VIRTUALINE-2026</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Self-styled 'bulletproof anonymous hosting' provider selling crypto-paid VPS/RDP, dedicated and web hosting, 'scanning' servers and a FastFlux CDN advertised as 'Spamhaus Ignored' (anonrdp.com registered 2023-10-04). Network lineage: Intrinsec (May 2026) found March 2026 malspam - a JavaScript backdoor aimed at CIS energy and finance ministries - sent from and controlled via the bulletproof US network GHOSTYNETWORKS (AS205759, Kentucky, registered Jan 2026), which it linked to the OPTIBOUNCE network previously tied to AnonRDP; Silent Push (Oct 2026) calls GHOSTYNETWORKS a shell company of AnonRDP and found the same four SPF addresses on anonrdp.com (Feb-Apr 2026) and ghostynetworks.com. AS205759 has since been deregistered. Current network: CrimsonVector DNS checks (2026-10-29) show solusvm.anonrdp.st and xmpp.anonrdp.st resolving into AS403005 (Blatant Technologies, LLC; ARIN-registered 2026-09-25, Seychelles registrant, Louisville KY contacts), and smtp/smtp01.anonrdp.st resolving to two of the ghostynetworks.com SPF addresses. AS403005 announces nine /24s, all on Spamhaus DROP, through a single upstream, SMARTNET Germany (AS203446); Spamhaus lists the ASN under blatant.host. A community post says the Lithuanian servers sit with UAB Host Baltic (AS209605, tracked here) - unconfirmed. Enforcement: on 2026-10-27, the day of the Virtualine seizure, the registry record for anonrdp.com was pointed at FBI seizure nameservers (13:13 UTC); no seizure page or DOJ statement had appeared by 2026-10-29. That day AnonRDP offered Virtualine customers a 'refugee offer' (it had also run a 'crazyrdp' promo code on 2025-11-15, days after the CrazyRDP seizure); on 2026-10-28 it moved to anonrdp.st, said a 'trusted source' warned it could be next, and said it had triggered an 'emergency kill switch' and was moving datacentres. Backup domains: anonrdp.net and an .onion address. Tier T1 (added 2026-10-29): LE domain seizure plus self-advertised bulletproof hosting with corroborating infrastructure, on Silent Push and Intrinsec (B) and registry/Spamhaus data (C). Status 'seized' covers the domain only - the operation is still running from anonrdp.st, so expect further ASN and prefix moves.</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>Self-styled bulletproof VPS/RDP and fast-flux host; its .com domain moved to FBI seizure nameservers on the day of Operation Omegaline (Oct 2026); now on anonrdp.st and Blatant Technologies AS403005.</t>
         </is>
       </c>
     </row>

--- a/BPH_Master.xlsx
+++ b/BPH_Master.xlsx
@@ -2067,7 +2067,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>T3-Suspected</t>
+          <t>T2-High Risk</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>Impersonated corporate identity; No route diversification; ASN since reassigned</t>
+          <t>Impersonated corporate identity; No route diversification; ASN since reassigned; Former prefixes on Spamhaus DROP</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -2122,17 +2122,17 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>RF-TAE-2026; RF-AUROLOGIC; KREBS-BPH; REGISTRY-SNAPSHOT-2026-09; DOJ-VIRTUALINE-2026; THN-VIRTUALINE-2026</t>
+          <t>RF-TAE-2026; RF-AUROLOGIC; KREBS-BPH; REGISTRY-SNAPSHOT-2026-09; DOJ-VIRTUALINE-2026; THN-VIRTUALINE-2026; REGISTRY-SNAPSHOT-2026-10</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>AS209800 was created 2025-04-25 and announced solely via aurologic; RF Insikt says it was controlled by Virtualine-affiliated actors who impersonated the long-standing legitimate Hamburg company metaspinner net GmbH (RENAMED 2026-09-25 so the row no longer names that company as the operator). Its prefixes (91.92.240.0/22, 158.94.208.0/22, 178.16.52.0/22) received Virtualine traffic from April 2025 and now originate from OMEGATECH AS202412 (see the Railnet/Virtualine row). The ASN has been re-issued to an unrelated German GbR (ZEMA) - do not block AS209800. Status set to 'dissolved' (network defunct). Attribution strengthened 2026-10-29: DOJ lists 'Lanedo' among Virtualine's aliases, matching the LANEDONET re-description, and Spamhaus (Sept 2025) reported Virtualine's expansion onto AS209800. Tier left at T3 as a historical record pending review.</t>
+          <t>AS209800 was created 2025-04-25 and announced solely via aurologic; RF Insikt says it was controlled by Virtualine-affiliated actors who impersonated the long-standing legitimate Hamburg company metaspinner net GmbH (RENAMED 2026-09-25 so the row no longer names that company as the operator). Its prefixes (91.92.240.0/22, 158.94.208.0/22, 178.16.52.0/22) received Virtualine traffic from April 2025 and now originate from OMEGATECH AS202412 (see the Railnet/Virtualine row). The ASN has been re-issued to an unrelated German GbR (ZEMA) - do not block AS209800. Status set to 'dissolved' (network defunct). Attribution strengthened 2026-10-29: DOJ lists 'Lanedo' among Virtualine's aliases, matching the LANEDONET re-description, and Spamhaus (Sept 2025) reported Virtualine's expansion onto AS209800. Tier raised T3 -&gt; T2 on 2026-10-30 to match the other Virtualine sub-networks (KPROHOST, Karina Rashkovska): an operator-controlled front with obscured ownership (impersonated identity), no route diversification and all three former /22s on Spamhaus DROP, on RF (B) and Spamhaus (C) evidence plus the DOJ alias. Kept as a historical record - status stays 'dissolved'.</t>
         </is>
       </c>
     </row>

--- a/BPH_Master.xlsx
+++ b/BPH_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y72"/>
+  <dimension ref="A1:Y74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>GootLoader; SocGholish; SpyNote; FakeBat; XWorm; StrelaStealer; WeaXor/Mallox; SuperBlack; Coper/Octo</t>
+          <t>GootLoader; SocGholish; SpyNote; FakeBat; XWorm; StrelaStealer; WeaXor/Mallox; SuperBlack; Coper/Octo; BoryptGrab-lineage infostealer</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -655,17 +655,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>IOCTA-2026; INTRINSEC-PROSPERO; TRUSTWAVE-PROSPERO; GREYNOISE-PROSPERO; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09; HUNTIO-EE-2026; HUNTIO-GENTLEMEN-2026; LEVELBLUE-BLINDEAGLE-2026</t>
+          <t>IOCTA-2026; INTRINSEC-PROSPERO; TRUSTWAVE-PROSPERO; GREYNOISE-PROSPERO; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09; HUNTIO-EE-2026; HUNTIO-GENTLEMEN-2026; LEVELBLUE-BLINDEAGLE-2026; ARCTICWOLF-BORYPT-2026</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Coupled Russian AS pair assessed by Intrinsec (high confidence) and Trustwave SpiderLabs as one operator marketed on Russian-language forums as BEARHOST/SecureHost/UNDERGROUND. Feb 2026 GreyNoise: 346 of 417 Ivanti EPMM exploitation sessions (83%) came from one AS200593 address, 193.24.123.42. 2026 activity: Hunt.io linked Proton66 to exploitation of Oracle PeopleSoft CVE-2026-35273 attributed to ShinyHunters (July) and found a The Gentlemen RaaS affiliate toolkit in an open directory at 176.120.22.127 (reported June); LevelBlue SpiderLabs reports Blind Eagle delivery infrastructure on Proton66 since June 2025. Chang Way Technologies (HK) is likely related (SpiderLabs saw IP shifts and a re-themed panel) and is tracked as its own row, not as an alias. Corrections 2026-09-25: the former known_prefixes 45.135.232.0/24 and 45.140.17.0/24 were historical Proton66 blocks now held by unrelated networks; FIN7 and the 'St. Petersburg IXP' upstream were removed (no supporting source). Block at CIDR level.</t>
+          <t>Coupled Russian AS pair assessed by Intrinsec (high confidence) and Trustwave SpiderLabs as one operator marketed on Russian-language forums as BEARHOST/SecureHost/UNDERGROUND. Feb 2026 GreyNoise: 346 of 417 Ivanti EPMM exploitation sessions (83%) came from one AS200593 address, 193.24.123.42. 2026 activity: Hunt.io linked Proton66 to exploitation of Oracle PeopleSoft CVE-2026-35273 attributed to ShinyHunters (July) and found a The Gentlemen RaaS affiliate toolkit in an open directory at 176.120.22.127 (reported June); LevelBlue SpiderLabs reports Blind Eagle delivery infrastructure on Proton66 since June 2025. Chang Way Technologies (HK) is likely related (SpiderLabs saw IP shifts and a re-themed panel) and is tracked as its own row, not as an alias. Corrections 2026-09-25: the former known_prefixes 45.135.232.0/24 and 45.140.17.0/24 were historical Proton66 blocks now held by unrelated networks; FIN7 and the 'St. Petersburg IXP' upstream were removed (no supporting source). Block at CIDR level. Arctic Wolf (2026-07-13): a BoryptGrab-lineage infostealer spread through 292 brand-impersonation GitHub pages uses a hardcoded C2 at 193.143.1.131 on AS198953.</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>United Kingdom (Companies House 15109642; UK front of Russia-registered Aeza Group LLC)</t>
+          <t>United Kingdom (Companies House 15109642, dissolved by compulsory strike-off 2026-03-24; UK front of Russia-registered Aeza Group LLC)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -757,17 +757,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>IOCTA-2026; RF-TAE-2026; OFAC-AEZA; CHAINALYSIS-OFAC; UK-COMPANIES-HOUSE; SPAMHAUS-ASNDROP-2026; ARCTICWOLF-DARKCARACAL-2026; HUNTRESS-MACOS-AEZA-2026; FCDO-UK-SANCTIONS-LIST</t>
+          <t>IOCTA-2026; RF-TAE-2026; OFAC-AEZA; CHAINALYSIS-OFAC; UK-COMPANIES-HOUSE; SPAMHAUS-ASNDROP-2026; ARCTICWOLF-DARKCARACAL-2026; HUNTRESS-MACOS-AEZA-2026; FCDO-UK-SANCTIONS-LIST; QURIUM-AEZA-2026; HACKREAD-INFOBLOX-AEZA-2026; CHAINALYSIS-CRYPTOMUS-2026</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>OFAC designated Aeza Group LLC and its UK front Aeza International Ltd on 2025-07-01 (coordinated with the UK NCA) for hosting Meduza and Lumma infostealer operators, BianLian and the BlackSprut market. The TRON address TU4tDFRvcKhAZ1jdihojmBWZqvJhQCnJ4F sits on the Aeza Group LLC SDN entry. Owners Penzev and Bozoyan and two staff were detained by Russian authorities in early April 2025 (a Russian drug-market case, not a Western action). Evasion: 2,100+ IPs moved to the UK front Hypercore (AS211522) from 2025-07-20; Serbian (Smart Digital Ideas DOO) and Uzbek (Datavice MCHJ) vehicles followed - all OFAC-designated 2025-11-19. Sanctions have not ended operational use: AS210644 still announces 176 IPv4 prefixes; Arctic Wolf (Aug 2026) found 23 of 24 Dark Caracal GoCaracal C2s on Aeza networks and Huntress (Aug 2026) traced a ClickFix macOS crypto-drainer's staging and C2 to Aeza. Spamhaus now also lists AS203273 (NetCrafters OU, EE) under aeza.net. Roughly half of Aeza's prefixes transited aurologic AS30823 as of Nov 2025.</t>
+          <t>OFAC designated Aeza Group LLC and its UK front Aeza International Ltd on 2025-07-01 (coordinated with the UK NCA) for hosting Meduza and Lumma infostealer operators, BianLian and the BlackSprut market. The TRON address TU4tDFRvcKhAZ1jdihojmBWZqvJhQCnJ4F sits on the Aeza Group LLC SDN entry. Owners Penzev and Bozoyan and two staff were detained by Russian authorities in early April 2025 (a Russian drug-market case, not a Western action). Evasion: 2,100+ IPs moved to the UK front Hypercore (AS211522) from 2025-07-20; Serbian (Smart Digital Ideas DOO) and Uzbek (Datavice MCHJ) vehicles followed - all OFAC-designated 2025-11-19. Sanctions have not ended operational use: AS210644 still announces 176 IPv4 prefixes; Arctic Wolf (Aug 2026) found 23 of 24 Dark Caracal GoCaracal C2s on Aeza networks and Huntress (Aug 2026) traced a ClickFix macOS crypto-drainer's staging and C2 to Aeza. Spamhaus now also lists AS203273 (NetCrafters OU, EE) under aeza.net. Roughly half of Aeza's prefixes transited aurologic AS30823 as of Nov 2025. Qurium (2026-10-14): on 2026-09-22 Aeza's two ASNs and NetCrafters (AS203273) originated 536 IPv4 /24s (137,216 addresses; 418 on Aeza's ASNs, 118 on NetCrafters) drawn from 42 LIRs, and aurologic (AS30823) was still one of AS210644's upstreams - two rounds of sanctions had 'no real impact' on its access to address space. Infoblox (Feb 2026, via Hackread): rogue DNS resolvers and a traffic distribution system behind a DNS-hijacking campaign against old home routers in 30+ countries were hosted by Aeza International. Chainalysis (Oct 2026) names Cryptomus/Heleket as an Aeza payment rail. The UK company Aeza International Ltd was dissolved on 2026-03-24; the RIPE org behind AS210644 is AEZA GROUP LLC.</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>EU May 20 2025: Council Implementing Regulation (EU) 2025/965 under the hybrid-threats regime Reg. (EU) 2024/2642 (not the 17th Russia package) - Stark Industries Solutions Ltd; Iurie Neculiti; Ivan Neculiti</t>
+          <t>EU May 20 2025: Council Implementing Regulation (EU) 2025/965 under the hybrid-threats regime Reg. (EU) 2024/2642 (not the 17th Russia package) - Stark Industries Solutions Ltd; Iurie Neculiti; Ivan Neculiti; EU renewed the hybrid-threats regime on Oct 8 2026 to Oct 9 2027 (80 individuals, 20 entities; Stark entries not individually re-checked)</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -854,17 +854,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>IOCTA-2026; RF-TAE-2026; RF-STARK; GREYNOISE-STARK; CENSYS-BPH; EU-STARK; UK-COMPANIES-HOUSE; SPAMHAUS-ASNDROP-2026</t>
+          <t>IOCTA-2026; RF-TAE-2026; RF-STARK; GREYNOISE-STARK; CENSYS-BPH; EU-STARK; UK-COMPANIES-HOUSE; SPAMHAUS-ASNDROP-2026; BRUSSELSTIMES-EU-HYBRID-2026; CHAINALYSIS-CRYPTOMUS-2026</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>EU-listed 2025-05-20 (Impl. Reg. 2025/965). UK-incorporated 2022-02-10, two weeks before Russia's full-scale invasion of Ukraine; dissolved 2025-09-16. RF describes Stark as a white-label front for Moldova's PQ.Hosting, with MIRhosting (NL) as a key infrastructure partner. AS44477 moved to PQ Hosting Plus S.R.L. on 2025-05-16 - four days before designation (the often-quoted '12 days' is the lead time from the 2025-05-08 RFE/RL leak); the THE.Hosting rebrand followed on 2025-05-29. GreyNoise saw near-complete abandonment of AS44477 by Nov 2025; it has since left the routing table and the registry. The network continues as WorkTitans/THE.Hosting (AS209847, AS213999) and UFO Hosting (AS33993), all listed by Spamhaus ASN-DROP under stark-industries.solutions. RF attributes the chain's RIPE maintainer to Dmitrii Miasnikov. Doppelganger (an influence operation, not malware) and Sandworm were removed from the malware/actor fields for lack of a Stark-specific source.</t>
+          <t>EU-listed 2025-05-20 (Impl. Reg. 2025/965). UK-incorporated 2022-02-10, two weeks before Russia's full-scale invasion of Ukraine; dissolved 2025-09-16. RF describes Stark as a white-label front for Moldova's PQ.Hosting, with MIRhosting (NL) as a key infrastructure partner. AS44477 moved to PQ Hosting Plus S.R.L. on 2025-05-16 - four days before designation (the often-quoted '12 days' is the lead time from the 2025-05-08 RFE/RL leak); the THE.Hosting rebrand followed on 2025-05-29. GreyNoise saw near-complete abandonment of AS44477 by Nov 2025; it has since left the routing table and the registry. The network continues as WorkTitans/THE.Hosting (AS209847, AS213999) and UFO Hosting (AS33993), all listed by Spamhaus ASN-DROP under stark-industries.solutions. RF attributes the chain's RIPE maintainer to Dmitrii Miasnikov. Doppelganger (an influence operation, not malware) and Sandworm were removed from the malware/actor fields for lack of a Stark-specific source. Chainalysis (Oct 2026) names Cryptomus/Heleket - UK-designated 2026-10-08 - as a Stark payment rail.</t>
         </is>
       </c>
     </row>
@@ -946,17 +946,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>OFAC-ZSERVERS; CHAINALYSIS-BPH; FCDO-UK-SANCTIONS-LIST; AU-DFAT-ZSERVERS; THERECORD-ZSERVERS-SEIZURE; INTRINSEC-UAC-2025; MALTRAIL-WORST-ASNS</t>
+          <t>OFAC-ZSERVERS; CHAINALYSIS-BPH; FCDO-UK-SANCTIONS-LIST; AU-DFAT-ZSERVERS; THERECORD-ZSERVERS-SEIZURE; INTRINSEC-UAC-2025; MALTRAIL-WORST-ASNS; CHAINALYSIS-CRYPTOMUS-2026</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Designated 2025-02-11 by the US, UK and Australia (per-authority lists in sanctions_designations). UK and Australian texts tie Zservers infrastructure to the 2022 Medibank data leak; Chainalysis traced payments from LockBit, BianLian, Hunters International and others. On 2025-02-12 Dutch police took 127 Zservers/XHOST servers offline in Amsterdam. The Zservers/XHOST ASN was AS197414 (historical prefixes 185.170.144.0/24 and 87.251.64.0/24, now held by unrelated networks); Spamhaus listed it under zservers.ru until at least Dec 2025 and it is now deregistered. Intrinsec assessed with high confidence that Zservers prefixes moved to AS213194, AS61336 and AS213010 (small footprints still announced; none on ASN-DROP). CORRECTION 2026-09-25: AS216071, previously listed here as historical, is VDSina / SERVERS TECH FZCO (UAE), an active ~156k-address network with no public link to Zservers - removed from this row; do not block it as Zservers infrastructure.</t>
+          <t>Designated 2025-02-11 by the US, UK and Australia (per-authority lists in sanctions_designations). UK and Australian texts tie Zservers infrastructure to the 2022 Medibank data leak; Chainalysis traced payments from LockBit, BianLian, Hunters International and others. On 2025-02-12 Dutch police took 127 Zservers/XHOST servers offline in Amsterdam. The Zservers/XHOST ASN was AS197414 (historical prefixes 185.170.144.0/24 and 87.251.64.0/24, now held by unrelated networks); Spamhaus listed it under zservers.ru until at least Dec 2025 and it is now deregistered. Intrinsec assessed with high confidence that Zservers prefixes moved to AS213194, AS61336 and AS213010 (small footprints still announced; none on ASN-DROP). CORRECTION 2026-09-25: AS216071, previously listed here as historical, is VDSina / SERVERS TECH FZCO (UAE), an active ~156k-address network with no public link to Zservers - removed from this row; do not block it as Zservers infrastructure. Chainalysis (Oct 2026) names Cryptomus/Heleket - UK-designated 2026-10-08 - as a Zservers payment rail.</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>LockBit; BlackSuit; Play ransomware</t>
+          <t>LockBit; BlackSuit; Play ransomware; Black Basta</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Designated 2025-11-19 by the US, UK and Australia with differing lists (see sanctions_designations); the EU followed on 2026-07-13 and New Zealand designated Volosovik on 2026-08-08. The N.D. Ohio indictment unsealed 2026-07-14 (Operation Riptide) charges Volosovik, Zatolokin, Pankova, Medialand LLC and ML.Cloud LLC over attacks causing more than $62M in victim losses. Treasury described Media Land as a launch pad for LockBit, BlackSuit and Play ransomware. The OFAC SDN entry for Volosovik carries BTC address 18dLDAWi8LmrHbEq3QzDJb9SLxCf4uimXB. Intel 471 (Aug 2026): roughly 80% of ~2,240 yalishanda customer domains stayed online into June 2026, with demand shifting to mainstream clouds and to new services (OtusCloud, reming, fluxy). Corrections 2026-09-25: AS48721 (Flyservers), AS211409 (FoxiBytes) and AS215311 (Regxa) were removed - no source links them to Media Land; AS215376 (ML Cloud Ltd, 176.98.187.0/24) and the dormant AS211805 were added.</t>
+          <t>Designated 2025-11-19 by the US, UK and Australia with differing lists (see sanctions_designations); the EU followed on 2026-07-13 and New Zealand designated Volosovik on 2026-08-08. The N.D. Ohio indictment unsealed 2026-07-14 (Operation Riptide) charges Volosovik, Zatolokin, Pankova, Medialand LLC and ML.Cloud LLC over attacks causing more than $62M in victim losses. Treasury described Media Land as a launch pad for LockBit, BlackSuit and Play ransomware. The OFAC SDN entry for Volosovik carries BTC address 18dLDAWi8LmrHbEq3QzDJb9SLxCf4uimXB. Intel 471 (Aug 2026): yalishanda's fast-flux service went down in late April 2026 and he was banned from the Exploit forum; a Russian court record of 2026-04-30 concerns an appeal against a Moscow house-arrest order in a domestic payment-instruments fraud case. Of 2,240 customer domains tracked before the shutdown, 1,439 were still active in June 2026 and 1,156 of those (about 80% of the active domains, about half of the original set) still resolved to yalishanda infrastructure; the rest shifted to mainstream clouds (Cloudflare first) and to new services (OtusCloud, reming, fluxy). Intel 471 also lists Black Basta among Media Land's ransomware customers. Corrections 2026-09-25: AS48721 (Flyservers), AS211409 (FoxiBytes) and AS215311 (Regxa) were removed - no source links them to Media Land; AS215376 (ML Cloud Ltd, 176.98.187.0/24) and the dormant AS211805 were added.</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>FUNNULL CDN; Fang Neng CDN; funnull.io; Bole CDN / CDN1.ai (pre-sanction front brands)</t>
+          <t>FUNNULL CDN; Fang Neng CDN; funnull.io; Bole CDN / CDN1.ai / Yunray.ai / CDN5.com / CTGCDN (front brands, per Silent Push)</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>OFAC-designated 2025-05-29 (with Liu Lizhi) for infrastructure behind cryptocurrency investment scams causing more than $200M in US victim-reported losses; the FBI FLASH the same day counted 548 FUNNULL CNAMEs linked to 332,000+ domains since Jan 2025. Taguig (Philippines) company run by a Chinese national. CTG Server Limited (AS152194) was one of several ASNs hosting FUNNULL points of presence in Silent Push's 2024 mapping; it is not FUNNULL's parent and was not designated. Silent Push (Apr 2026): Triad Nexus kept operating through 'clean' front brands (Bole CDN, CDN1.ai and others) that were launched before the May 2025 sanctions, plus accounts at major clouds and US-IP geofencing.</t>
+          <t>OFAC-designated 2025-05-29 (with Liu Lizhi) for infrastructure behind cryptocurrency investment scams causing more than $200M in US victim-reported losses; the FBI FLASH the same day counted 548 FUNNULL CNAMEs linked to 332,000+ domains since Jan 2025. Taguig (Philippines) company run by a Chinese national. CTG Server Limited (AS152194) was one of several ASNs hosting FUNNULL points of presence in Silent Push's 2024 mapping; it is not FUNNULL's parent and was not designated. Silent Push (Apr 2026): Triad Nexus kept operating through 'clean' front brands (Bole CDN, CDN1.ai and others) that were launched before the May 2025 sanctions, plus accounts at major clouds and US-IP geofencing (HTTP 451 to US visitors); it moved from nine stable CNAME domains to more than 175 randomly generated ones - a post-sanction figure, separate from the FBI's 548. Whether 'CTGCDN' relates to CTG Server Limited is not established.</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>evading</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>MIRhosting B.V. (AS52000) - Krebs: sole connectivity</t>
+          <t>ADCDATA.COM (AS135330) and FBW Networks (AS49434) (Oct 2026); formerly MIRhosting B.V. (AS52000) - Krebs: sole connectivity</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1324,17 +1324,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>RF-STARK; GREYNOISE-STARK; CENSYS-BPH; EU-STARK; KREBS-FIOD-STARK; DARKREADING-ELLIO-STARK; SPAMHAUS-ASNDROP-2026; CHECKPOINT-WORKTITANS-IRAN-2026</t>
+          <t>RF-STARK; GREYNOISE-STARK; CENSYS-BPH; EU-STARK; KREBS-FIOD-STARK; DARKREADING-ELLIO-STARK; SPAMHAUS-ASNDROP-2026; CHECKPOINT-WORKTITANS-IRAN-2026; REGISTRY-SNAPSHOT-2026-10</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Dutch post-sanctions successor to Stark Industries/PQ.Hosting. WorkTitans B.V. was formed in 2019 as a recruitment firm; its Stark-successor role starts with RIPE org ORG-THE3-RIPE (created 2025-05-28) and prefix transfers from 2025-05-29; AS209847 was created 2025-06-24 and AS213999 (THE-CLIENTS) also belongs to WorkTitans. AS209847 announced 21 prefixes in Aug 2025 and 11 today. GreyNoise confirmed the migration from AS44477 (Aug-Nov 2025); Censys matched RDP hostname reuse (WIN-J9D866ESIJ2). FIOD raided the Dutch nodes on 2026-05-18: 800+ servers seized at data centres in Dronten and Schiphol-Rijk; WorkTitans owner Youssef Zinad and MIRhosting founder Andrey Nesterenko arrested (names press-reported). ELLIO saw scanning back near pre-raid levels more than a week later, but later reports conflict (one telemetry source reports a 94% drop in the indexed fleet; a Russian-language hosting knowledge base says the THE.Hosting site announced it had stopped operating) - status kept 'evading' pending clarity. Check Point (June 2026): three Iranian groups including MuddyWater used WorkTitans infrastructure for core operations.</t>
+          <t>Dutch post-sanctions successor to Stark Industries/PQ.Hosting. WorkTitans B.V. was formed in 2019 as a recruitment firm; its Stark-successor role starts with RIPE org ORG-THE3-RIPE (created 2025-05-28) and prefix transfers from 2025-05-29; AS209847 was created 2025-06-24 and AS213999 (THE-CLIENTS) also belongs to WorkTitans. AS209847 announced 21 prefixes in Aug 2025 and 11 on 2026-09-25; it then withdrew most of its space between 2026-10-01 and 2026-10-14 (and its IPv6 on 2026-10-27), leaving two /24s (45.120.176.0/24, 185.235.240.0/24) - the withdrawn blocks had not reappeared under another origin by 2026-10-30. MIRhosting, its former sole upstream, went dark on 2026-10-19; AS209847 now reaches the internet via ADCDATA.COM (AS135330) and FBW Networks (AS49434). GreyNoise confirmed the migration from AS44477 (Aug-Nov 2025); Censys matched RDP hostname reuse (WIN-J9D866ESIJ2). FIOD raided the Dutch nodes on 2026-05-18: 800+ servers seized at data centres in Dronten and Schiphol-Rijk; WorkTitans owner Youssef Zinad and MIRhosting founder Andrey Nesterenko arrested (names press-reported). ELLIO saw scanning back near pre-raid levels more than a week later, but later reports conflict (one telemetry source reports a 94% drop in the indexed fleet; a Russian-language hosting knowledge base says the THE.Hosting site announced it had stopped operating). Status evading -&gt; seized on 2026-10-30: the May 2026 FIOD action seized infrastructure (partial seizure), and by mid-October 2026 the network had withdrawn nearly all of its space (see below). Check Point (June 2026): three Iranian groups including MuddyWater used WorkTitans infrastructure for core operations.</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United Kingdom (Companies House 16558658; incorporated 2025-07-03; dissolved by compulsory strike-off 2025-12-23)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>UK-registered Aeza Group front (Companies House 16558658; 120 Fleet Street, London); the second iteration of Aeza's UK-shell playbook. AS211522 (RIPE as-name HYPERCORELTD) was allocated ~2025-07-10 and received 2,100+ IPs from Aeza's AS210644 starting 2025-07-20 (Silent Push). OFAC designated Hypercore on 2025-11-19; it is an OFAC-only designation (the earlier 'OFAC/OFSI' wording was wrong). Spamhaus listed AS211522 under aeza.net in Dec 2025; it has since been delisted and the ASN has announced nothing since ~2026-02. Former Hypercore prefixes now originate from First Server Limited ASNs (45.142.122.0/24 via AS205090; 185.174.136.0/24 via AS200740) - a lead, not proof of common control. Incorporation date 2025-07-03 is unverified (possibly conflated with Datavice). CORRECTION 2026-09-25: AS215552, previously the primary ASN, belongs to an unrelated Romanian individual and was removed.</t>
+          <t>UK-registered Aeza Group front (Companies House 16558658; 120 Fleet Street, London); the second iteration of Aeza's UK-shell playbook. AS211522 (RIPE as-name HYPERCORELTD) was allocated ~2025-07-10 and received 2,100+ IPs from Aeza's AS210644 starting 2025-07-20 (Silent Push). OFAC designated Hypercore on 2025-11-19; it is an OFAC-only designation (the earlier 'OFAC/OFSI' wording was wrong). Spamhaus listed AS211522 under aeza.net in Dec 2025; it has since been delisted and the ASN has announced nothing since ~2026-02. Former Hypercore prefixes now originate from First Server Limited ASNs (45.142.122.0/24 via AS205090; 185.174.136.0/24 via AS200740) - a lead, not proof of common control. Companies House confirms incorporation on 2025-07-03; a first Gazette strike-off notice followed on 2025-11-11 (eight days before the OFAC designation) and the company was dissolved on 2025-12-23. Its registered office had already been moved to the Companies House default address on 2025-10-28, so the Fleet Street address is historical. CORRECTION 2026-09-25: AS215552, previously the primary ASN, belongs to an unrelated Romanian individual and was removed.</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>United Kingdom (shell)</t>
+          <t>United Kingdom (shell; Companies House 15885164 - strike-off notice 2026-10-13)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>SVCStealer; CoinMiner; DonutLoader; Rhadamanthys; Stealc; RemcosRAT; QuasarRAT; RedLine; Lumma; OrcusRAT; PrivateLoader; SmokeLoader; Amadey; CastleLoader; Evilginx/EvilGoPhish; DanaBot; Meduza Stealer</t>
+          <t>SVCStealer; CoinMiner; DonutLoader; Rhadamanthys; Stealc; RemcosRAT; QuasarRAT; RedLine; Lumma; OrcusRAT; PrivateLoader; SmokeLoader; Amadey; CastleLoader; Evilginx/EvilGoPhish; DanaBot; Meduza Stealer; MioLab (macOS stealer panels)</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1508,12 +1508,12 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>RF-TAE-2026; RF-AUROLOGIC; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>RF-TAE-2026; RF-AUROLOGIC; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09; LEVELBLUE-MIOLAB-2026; UK-COMPANIES-HOUSE; FCDO-UK-SANCTIONS-LIST</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>UK shell (incorporated 2024-08-08; AS214351 allocated seven days later) that RF Insikt assesses with high confidence to be under the control of the Defhost BPH brand, which advertises 'fast abusive VPS/VDS' resilient against Western law enforcement. Payment via Heleket.com, shared across the cluster. Hosts C2 and loader infrastructure for 15+ malware families. RF ranks Defhost #8 in its 2025 Threat Density top 10 and AS214351 is on Spamhaus ASN-DROP (domain as214351.com). Tier raised T2 -&gt; T1 on 2026-09-25 (taxonomy T1: self-advertised bulletproof with corroborating infrastructure evidence; RF top-decile density). Announced space grew from 2 /24s (62.60.226.0/24, 176.46.152.0/24 at RF publication) to 4 /24s now; 176.46.152.0/24 has moved to an unrelated Iranian network. The unsourced date and place of birth previously given for the director were removed.</t>
+          <t>UK shell (incorporated 2024-08-08; AS214351 allocated seven days later) that RF Insikt assesses with high confidence to be under the control of the Defhost BPH brand, which advertises 'fast abusive VPS/VDS' resilient against Western law enforcement. Payment via Heleket.com, shared across the cluster. Hosts C2 and loader infrastructure for 15+ malware families. RF ranks Defhost #8 in its 2025 Threat Density top 10 and AS214351 is on Spamhaus ASN-DROP (domain as214351.com). Tier raised T2 -&gt; T1 on 2026-09-25 (taxonomy T1: self-advertised bulletproof with corroborating infrastructure evidence; RF top-decile density). Announced space grew from 2 /24s (62.60.226.0/24, 176.46.152.0/24 at RF publication) to 4 /24s now; 176.46.152.0/24 has moved to an unrelated Iranian network. The unsourced date and place of birth previously given for the director were removed. LevelBlue SpiderLabs (2026-03-20) found admin and login panels of the MioLab (aka Nova) macOS stealer on Femo IT addresses (e.g. 196.251.107.97). Companies House: FEMO IT SOLUTIONS LIMITED (15885164) received a first Gazette notice for compulsory strike-off on 2026-10-13 (an earlier notice of 2025-10-28 was discontinued on 2026-01-13) - expect dissolution, which would not by itself end the network. Its payment processor Heleket was UK-designated on 2026-10-08 (see the Xeltox Enterprises row).</t>
         </is>
       </c>
     </row>
@@ -1590,17 +1590,17 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>ABUSECH-FEEDS; HYAS-RISEPRO; QURIUM-DOPPELGANGER; RF-AUROLOGIC; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>ABUSECH-FEEDS; HYAS-RISEPRO; QURIUM-DOPPELGANGER; RF-AUROLOGIC; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09; UK-COMPANIES-HOUSE; QURIUM-AEZA-2026</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>UK-registered (RIPE org TNSECURITY LTD, GB) network that announced 185.172.128.0/24 via AS216309 (as-name EVILEMPIRE-AS) behind aurologic; Qurium tied hundreds of Doppelganger domains to 185.172.128.161 between Oct 2023 and Jul 2024. AS216309 was on Spamhaus ASN-DROP in the Feb 2024 snapshot, but not in Dec 2025 or now. The ASN has since been re-issued to InvisionTech Group S.r.l. (IT) and the Doppelganger IP now sits in an unrelated Russian network, so the entity is no longer identifiable as a live network - status set to 'dissolved' (network defunct) on 2026-09-25. Do not block AS216309. Corrections: registration is UK, not Germany (Germany is where servers sat); ASN-DROP is a Spamhaus list, not abuse.ch.</t>
+          <t>UK-registered (RIPE org TNSECURITY LTD, GB) network that announced 185.172.128.0/24 via AS216309 (as-name EVILEMPIRE-AS) behind aurologic; Qurium tied hundreds of Doppelganger domains to 185.172.128.161 between Oct 2023 and Jul 2024. AS216309 was on Spamhaus ASN-DROP in the Feb 2024 snapshot, but not in Dec 2025 or now. The ASN has since been re-issued to InvisionTech Group S.r.l. (IT) and the Doppelganger IP now sits in an unrelated Russian network, so the entity is no longer identifiable as a live network - status set to 'dissolved' (network defunct) on 2026-09-25. Do not block AS216309. Corrections: registration is UK, not Germany (Germany is where servers sat); ASN-DROP is a Spamhaus list, not abuse.ch. Companies House: a TNSECURITY LTD (15103352, incorporated 2023-08-29) was dissolved on 2025-02-04 (name match to the RIPE org, not confirmed). Qurium (Oct 2026) places Tnsecurity in Aeza's satellite layer.</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Originated by AS202412 Jan-Oct 2026, all on Spamhaus DROP (2026-10-29): 91.92.240.0/22; 158.94.208.0/22; 178.16.52.0/22 (these three ex-AS209800); 45.132.180.0/24; 94.26.38.0/24; 94.154.35.0/24; 94.154.40.0/24; 94.154.46.0/24; 130.12.180.0/24; 146.19.125.0/24; 193.30.241.0/24. Also short-lived /24s from broker-leased space that moves between unrelated ASNs (re-check the current origin before blocking): 45.74.7.0/24; 45.74.57.0/24; 45.74.59.0/24; 104.250.184.0/24; 172.111.246.0/24</t>
+          <t>Originated by AS202412 Jan-Oct 2026 and on Spamhaus DROP at the seizure (94.154.35.0/24 and 45.132.180.0/24 delisted by 2026-10-30): 91.92.240.0/22; 158.94.208.0/22; 178.16.52.0/22 (these three ex-AS209800); 45.132.180.0/24; 94.26.38.0/24 (RetryHost block; re-originated by AS51130 since 2026-10-28); 94.154.35.0/24; 94.154.40.0/24; 94.154.46.0/24; 130.12.180.0/24; 146.19.125.0/24; 193.30.241.0/24. Also short-lived /24s from broker-leased space that moves between unrelated ASNs (re-check the current origin before blocking): 45.74.7.0/24; 45.74.57.0/24; 45.74.59.0/24; 104.250.184.0/24; 172.111.246.0/24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Virtualine Technologies; RAILNET; OMEGATECH; Secury; Massgod; Spamhouse; Lanedo; DripHosting/DiorHost; RetryHost; virtualine.net (seized); virtualine.org</t>
+          <t>Virtualine Technologies; RAILNET; OMEGATECH; Secury; Massgod; Spamhouse; Lanedo; DripHosting/DiorHost; RetryHost (RIPE org maintained by VIRTUALINE-MNT); virtualine.net (seized); virtualine.org</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Virtualine Technologies is the operator behind Railnet LLC (AS214943, Kentucky LLC), KPROHOST (AS214940), the 'metaspinner' AS209800 front, likely Karina Rashkovska (AS215789) and OMEGATECH (AS202412) - at least five number-resource identities. SEIZED 2026-10-27 (Operation Omegaline): the FBI Washington Field Office seized virtualine.net under an E.D. Va. warrant, with Polizei Hessen, Politie Midden-Nederland, the UK NCA and private partners OverRIPE and Lumen; Chainalysis supported. DOJ names the aliases Secury, Massgod, Spamhouse, Lanedo and Omegatech, alleges it knowingly hosted 'Vendor 1' (a forum selling CSAM and non-consensual intimate images, with hack-for-hire) despite notices from German, Canadian and Australian police, NCMEC and a victim's attorney from Jan 2026, and that it laundered customer payments taken via unhosted 'BTC [NO-AML]' addresses. Forum advertising: Exploit.in from 2024-08-28 ('all illegal/black hat activities ... except for child contents and terrorism', Sept 2024); HackForums ('ignored more abuse than your last three therapists', June 2025); in Mar 2026 it sold an 'additional protection plan' moving a customer's server to an unaffiliated shell company after an LE request. Dutch police seized dozens of physical servers in Limburg (hundreds of VPS offline; data on 3,000+ customers) and say the FBI and German police acted against suspects and crypto at the same time; no operators were named or charged. TRM: most illicit-attributed crypto of any TRM-labelled BPH in 2026 (inflows ~44% Russian drug market, ~17% sextortion, ~13% mixer, ~5% ransomware; also StealC and the BPH Volhav). Network: Silent Push saw the move from AS214943 to AS202412 on 2026-02-11; AS202412 originated 24 /24s in the two weeks before the seizure (all on Spamhaus DROP) and has been seen by 1 of 323 RIS peers since 2026-10-27; its last neighbours were Pfcloud (AS51396) and PEERYX (AS213382). The operator posted an open letter on virtualine.org denying the allegations and saying it could rebrand in 'a day, perhaps even less' - watch for a successor ASN. LEAD (not attributed): AS219199 (GENYUS SOFT LTD [SC], created 2026-07-15) announced four broker-leased /24s from 2026-10-22, including 172.111.246.0/24 previously on AS202412, and withdrew them on the morning of the seizure; only a community post calls it Virtualine, and Spamhaus lists it under genyus.sc. Earlier history: RF ranked Virtualine #1 by Threat Density for 2025; Intrinsec documented UAC-0050/UAC-0006 activity and in May 2026 assessed OMEGATECH as 'yet another network created by Virtualine'; in April 2025 it shifted IPv4 resources to AS209800 (Spamhaus reported the expansion in Sept 2025), and those ranges later moved to AS202412. Status flagged -&gt; seized 2026-10-29; tier stays T1 (raised T2 -&gt; T1 on 2026-09-25). | Merged record (was a duplicate AS214943 row).</t>
+          <t>Virtualine Technologies is the operator behind Railnet LLC (AS214943, Kentucky LLC), KPROHOST (AS214940), the 'metaspinner' AS209800 front, likely Karina Rashkovska (AS215789) and OMEGATECH (AS202412) - at least five number-resource identities. SEIZED 2026-10-27 (Operation Omegaline): the FBI Washington Field Office seized virtualine.net under an E.D. Va. warrant, with Polizei Hessen, Politie Midden-Nederland, the UK NCA and private partners OverRIPE and Lumen; Chainalysis supported. DOJ names the aliases Secury, Massgod, Spamhouse, Lanedo and Omegatech, alleges it knowingly hosted 'Vendor 1' (a forum selling CSAM and non-consensual intimate images, with hack-for-hire) despite notices from German, Canadian and Australian police, NCMEC and a victim's attorney from Jan 2026, and that it laundered customer payments taken via unhosted 'BTC [NO-AML]' addresses. Forum advertising: Exploit.in from 2024-08-28 ('all illegal/black hat activities ... except for child contents and terrorism', Sept 2024); HackForums ('ignored more abuse than your last three therapists', June 2025); in Mar 2026 it sold an 'additional protection plan' moving a customer's server to an unaffiliated shell company after an LE request. Dutch police seized dozens of physical servers in Limburg (hundreds of VPS offline; data on 3,000+ customers) and say the FBI and German police acted against suspects and crypto at the same time; no operators were named or charged. TRM: most illicit-attributed crypto of any TRM-labelled BPH in 2026 (inflows ~44% Russian drug market, ~17% sextortion, ~13% mixer, ~5% ransomware; also StealC and the BPH Volhav). Network: Silent Push saw the move from AS214943 to AS202412 on 2026-02-11; AS202412 originated 24 /24s in the two weeks before the seizure (all on Spamhaus DROP) and has been seen by 1 of 323 RIS peers since 2026-10-27; its last neighbours were Pfcloud (AS51396) and PEERYX (AS213382). The operator posted an open letter on virtualine.org denying the allegations and saying it could rebrand in 'a day, perhaps even less' - watch for a successor ASN. LEAD (not attributed): AS219199 (GENYUS SOFT LTD [SC], created 2026-07-15) announced four broker-leased /24s from 2026-10-22, including 172.111.246.0/24 previously on AS202412, and withdrew them on the morning of the seizure; only a community post calls it Virtualine, and Spamhaus lists it under genyus.sc. Earlier history: RF ranked Virtualine #1 by Threat Density for 2025; Intrinsec documented UAC-0050/UAC-0006 activity and in May 2026 assessed OMEGATECH as 'yet another network created by Virtualine'; in April 2025 it shifted IPv4 resources to AS209800 (Spamhaus reported the expansion in Sept 2025), and those ranges later moved to AS202412. Status flagged -&gt; seized 2026-10-29; tier stays T1 (raised T2 -&gt; T1 on 2026-09-25). Post-seizure routing (RIPEstat/RIPE DB, 2026-10-30): (1) 94.26.38.0/24 - registered to the RIPE org RetryHost, which is maintained by VIRTUALINE-MNT - got a new route object on 2026-10-28 (11:06 UTC, created by the parent LIR's maintainer) and has since been announced by AS51130 (Homaye Jahan Nama Co., Iran; dormant apart from this block) via AS214329 (BGP Network LLC) - a possible relocation, not yet attributed; (2) most other former AS202412 /24s have been seen since 2026-10-27 16:00 with origin AS6461 by only ~10 of 323 RIS peers (cause unknown); (3) Spamhaus removed 94.154.35.0/24 and 45.132.180.0/24 from DROP. | Merged record (was a duplicate AS214943 row).</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>flagged</t>
+          <t>dissolved</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>QWINS LTD</t>
+          <t>QWINS LTD (Companies House 16072422; renamed QUALITY IT NETWORK SOLUTIONS LIMITED 2025-04-14; dissolved 2026-07-14)</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1794,17 +1794,17 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>INTEL-INSIGHTS-QWINS; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>INTEL-INSIGHTS-QWINS; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09; UK-COMPANIES-HOUSE</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>UK shell (reported incorporated 2024-11-11) selling cheap VPS via a Telegram bot (~$2/mo), with a six-month nominee director. Vasilis Orlof tied AS213702 to multiple malware families via 141.98.6.0/24. Spamhaus ASN-DROP now lists three ASNs under qwins.co: AS213702, AS218731 (newly listed; registered to an individual in Latvia; announces 35 IPv4 prefixes) and AS214422 (NET67X; no routes). Third parties give UK company no. 16072422 and link QWINS to the Aeza UK-shell network (single source, unverified).</t>
+          <t>UK shell (reported incorporated 2024-11-11) selling cheap VPS via a Telegram bot (~$2/mo), with a six-month nominee director. Vasilis Orlof tied AS213702 to multiple malware families via 141.98.6.0/24. Spamhaus ASN-DROP now lists three ASNs under qwins.co: AS213702, AS218731 (newly listed; registered to an individual in Latvia; announces 35 IPv4 prefixes) and AS214422 (NET67X; no routes). Companies House confirms UK company 16072422: renamed QUALITY IT NETWORK SOLUTIONS LIMITED on 2025-04-14 and dissolved by compulsory strike-off on 2026-07-14 (first Gazette 2026-04-21). Status flagged -&gt; dissolved on 2026-10-30 per taxonomy section 5 (corporate dissolution; the network persists - AS218731 and AS213702 still announce prefixes and remain on ASN-DROP, so keep blocking them). The link to the Aeza UK-shell network remains single-source.</t>
         </is>
       </c>
     </row>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>GCSAS</t>
+          <t>GCSAS; Global Connectivity Solutions (GCS); sister company Global Internet Solutions LLC (GIR, AS207713); FourVPS / 4VPS (brand, per eSentire)</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gamaredon (C2 hosting, 2023); SilkParasite (SpiceRAT C2, 2026 - IP-to-ASN mapping); UAC-linked activity (Intrinsec)</t>
+          <t>Gamaredon (C2 hosting, 2023); SilkParasite (SpiceRAT C2, 2026 - IP-to-ASN mapping); UAC-linked activity (Intrinsec); Storm-1575 (DadSec/Phoenix/Rockstar 2FA PhaaS; eSentire, moderate confidence)</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>Shell company structure; No route diversification; Ransomware C2</t>
+          <t>Spamhaus ASN-DROP (AS215540 under globconnex.com, listed by Oct 2026); Shell company structure; No route diversification; Ransomware C2</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -1871,17 +1871,17 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>GBHACKERS-BPH; ESET-GAMAREDON-IOC; INTRINSEC-UAC-2025; HUNTIO-SILKPARASITE-2026; REGISTRY-SNAPSHOT-2026-09; INTRINSEC-FDN3-2025</t>
+          <t>GBHACKERS-BPH; ESET-GAMAREDON-IOC; INTRINSEC-UAC-2025; HUNTIO-SILKPARASITE-2026; REGISTRY-SNAPSHOT-2026-09; INTRINSEC-FDN3-2025; REGISTRY-SNAPSHOT-2026-10; UK-COMPANIES-HOUSE; ESENTIRE-GCS-2024; SOPHOS-VMMANAGER; QURIUM-AEZA-2026</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>UK LLP operating AS215540: 181 IPv4 prefixes / 62,720 addresses plus 24 IPv6 prefixes (2026-09-25; the earlier '~176 / ~41K' is outdated). ESET lists Gamaredon infrastructure on GCSAS addresses first seen Aug-Sep 2023. Intrinsec named GCSAS in its March 2025 UAC-infrastructure report and in Aug 2025 among shell-fronted networks announcing prefixes moved out of the FDN3 cluster. A SpiceRAT C2 active in March 2026 (Hunt.io, SilkParasite campaign; 171.22.16.187) maps to AS215540 by our own IP-to-ASN lookup. Status raised suspected -&gt; flagged (two independent B-grade sources). Unverified and retained with caution: LLP number OC450701; Black Basta/Cactus C2 routing via Stark AS44477. Not on Spamhaus ASN-DROP.</t>
+          <t>UK LLP operating AS215540: 181 IPv4 prefixes / 62,720 addresses plus 24 IPv6 prefixes (2026-09-25; the earlier '~176 / ~41K' is outdated). ESET lists Gamaredon infrastructure on GCSAS addresses first seen Aug-Sep 2023. Intrinsec named GCSAS in its March 2025 UAC-infrastructure report and in Aug 2025 among shell-fronted networks announcing prefixes moved out of the FDN3 cluster. A SpiceRAT C2 active in March 2026 (Hunt.io, SilkParasite campaign; 171.22.16.187) maps to AS215540 by our own IP-to-ASN lookup. Status raised suspected -&gt; flagged (two independent B-grade sources). Companies House confirms LLP OC450701 (incorporated 2024-01-19), filing dormant-entity accounts while operating AS215540. eSentire (Dec 2024): addresses of GCS and its sister company Global Internet Solutions (GIR, AS207713), which share a person with significant control, produced 64% of its Entra ID account-compromise detections, a subset tied with moderate confidence to Storm-1575; eSentire links both to the 4VPS brand. Sophos (Feb 2026) lists Global Connectivity Solutions among the top hosts of the reused ISPsystem VM hostnames. Qurium (Oct 2026) finds GCS and GIR repeatedly relaying prefixes into and out of Aeza networks. Unverified and retained with caution: Black Basta/Cactus C2 routing via Stark AS44477. Not on Spamhaus ASN-DROP at the 2026-09-25 audit; listed under globconnex.com by 2026-10-29.</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>T3-Suspected</t>
+          <t>T2-High Risk</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Hassan Nozari</t>
+          <t>Hannan Nozari</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>APT10; Sidewinder; APT33; APT34; Kimsuky; Konni; Lazarus; Transparent Tribe; APT29; Turla; OceanLotus; Evil Corp; FIN12; Ghost Clown (Black Basta); Space Kook (Royal); Candiru</t>
+          <t>APT10; Sidewinder; APT33; APT34; Kimsuky; Konni; Lazarus; Transparent Tribe; APT29; Turla; OceanLotus; Evil Corp; FIN12; Ghost Clown (Black Basta); Space Kook (Royal); Candiru; Qilin (exfiltration, Dec 2025; Team Cymru); EvilProxy AiTM smishing operators (SRA, 2026)</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2035,22 +2035,22 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>No KYC; Anonymous crypto RDP VPS; Shell company structure; Halcyon: potentially 40-60% of activity malicious; Historical Spamhaus ASN-DROP listing (Dec 2025; delisted by Sep 2026)</t>
+          <t>No KYC; Anonymous crypto RDP VPS; Shell company structure; Halcyon: potentially 40-60% of activity malicious; Spamhaus ASN-DROP (AS14956 under cloudzy.com; listed Dec 2025, delisted by Sep 2026, re-listed by Oct 2026)</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>HALCYON-CLOUDZY; FLARE-CLOUDZY; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>HALCYON-CLOUDZY; FLARE-CLOUDZY; REGISTRY-SNAPSHOT-2026-09; REGISTRY-SNAPSHOT-2026-10; CYBERSCOOP-CLOUDZY-2023; SRA-CLOUDZY-2026; GUARDZ-CLOUDZY-2026; TEAMCYMRU-RANSOMINFRA-2026</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>US-incorporated command-and-control provider that Halcyon (Aug 2023) exposed as an operational front for the Iranian firm abrNOC (Tehran), estimating that potentially 40-60% of its overall activity could be malicious. Used by a long list of state and criminal actors (see associated_threat_actors; BlueNoroff is not in Halcyon's list). AS14956 (RouterHosting) still announces 66 IPv4 prefixes; it was on Spamhaus ASN-DROP (cloudzy.com) in Dec 2025 and has since been delisted. A UAE registration, AS200038, has no routes. Corrections 2026-09-25: operator name is Hassan (not Hannan) Nozari; the unsourced EvilProxy link was removed.</t>
+          <t>US-incorporated command-and-control provider that Halcyon (Aug 2023) exposed as an operational front for the Iranian firm abrNOC (Tehran), estimating that potentially 40-60% of its overall activity could be malicious. Used by a long list of state and criminal actors (see associated_threat_actors; BlueNoroff is not in Halcyon's list). AS14956 (RouterHosting) still announces 66 IPv4 prefixes; it was on Spamhaus ASN-DROP (cloudzy.com) in Dec 2025, was delisted by the 2026-09-25 audit and is listed again as of 2026-10-29. A UAE registration, AS200038, has no routes. Correction 2026-10-30: the operator is Hannan Nozari, as Cloudzy's own press page and CyberScoop give it - the 2026-09-25 change to 'Hassan' was wrong and is reverted; the EvilProxy link removed then is restored on Security Risk Advisors' March 2026 research tying EvilProxy smishing infrastructure to Cloudzy/RouterHosting. Team Cymru (Sept 2026) recorded Qilin SFTP exfiltration infrastructure on AS14956 (Dec 2025), and Guardz (2026-10-17) traced compromised ConnectWise Cloud Backup (SkyKick) multi-tenant app abuse and AiTM session theft egressing from 144.172.64.0/18. Tier T3 -&gt; T2 on 2026-10-30 under the taxonomy's ASN-DROP escalation rule: re-listed on ASN-DROP plus independent B-grade vendors (Halcyon, SRA).</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AS209946 (ALINDA LLC [UA]; Spamhaus ASN-DROP under altawk.com)</t>
+          <t>AS209946 (ALINDA LLC [UA]; Spamhaus ASN-DROP under altawk.com; no routes since 2026-10-02)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>QURIUM-DOPPELGANGER; RF-AUROLOGIC; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>QURIUM-DOPPELGANGER; RF-AUROLOGIC; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09; REGISTRY-SNAPSHOT-2026-10; UK-COMPANIES-HOUSE; SOPHOS-VMMANAGER</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Named by Qurium as Russia-linked infrastructure behind aurologic serving the Doppelganger disinformation network, historically on AS203727 (now re-issued to byon GmbH - do not block). Spamhaus now lists AS209946 (ALINDA LLC, UA) under altawk.com; it announces 4 prefixes, all on Spamhaus DROP. An earlier Altawk-domain ASN, AS215826, was listed in Dec 2025 and later removed. Tier raised T3 -&gt; T2 on 2026-09-25 (ASN-DROP inclusion plus Qurium).</t>
+          <t>Named by Qurium as Russia-linked infrastructure behind aurologic serving the Doppelganger disinformation network, historically on AS203727 (now re-issued to byon GmbH - do not block). Spamhaus now lists AS209946 (ALINDA LLC, UA) under altawk.com; it announced 4 prefixes, all on Spamhaus DROP, until 2026-10-02 and has announced nothing since (still listed; RIPEstat, 2026-10-30). An earlier Altawk-domain ASN, AS215826, was listed in Dec 2025 and later removed. Tier raised T3 -&gt; T2 on 2026-09-25 (ASN-DROP inclusion plus Qurium). Companies House: PARTNER HOSTING LTD (15332944), the likely GB holder behind the former AS215826, was dissolved on 2026-01-20 (name match); Sophos lists Partner Hosting LTD among the top hosts of the reused ISPsystem VM hostnames.</t>
         </is>
       </c>
     </row>
@@ -2353,17 +2353,17 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>OSINT-FORUMS; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>OSINT-FORUMS; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09; HOSTSLICK-PR-2026</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Offshore host advertising on LowEndTalk, cracked.io, BlackHatWorld and BreachForums, self-described 'DMCA Ignored', with abuse tolerance tied to pricing tier (marketing evidence, grade E). Spamhaus now lists AS197170 (TechTies Inc., SC) under hostslick.de; it announces 13 IPv4 /24s, all on Spamhaus DROP. The earlier AS208046 was ColocationX Ltd's network (a HostSlick VPS sat there in Nov 2023) and has been re-issued - do not block it. Held at T3 (status flagged): ASN-DROP inclusion would normally escalate to T2, but only one independent B/C source supports it.</t>
+          <t>Offshore host advertising on LowEndTalk, cracked.io, BlackHatWorld and BreachForums, self-described 'DMCA Ignored', with abuse tolerance tied to pricing tier (marketing evidence, grade E). Spamhaus now lists AS197170 (TechTies Inc., SC) under hostslick.de; it announces 13 IPv4 /24s, all on Spamhaus DROP. The earlier AS208046 was ColocationX Ltd's network (a HostSlick VPS sat there in Nov 2023) and has been re-issued - do not block it. Held at T3 (status flagged): ASN-DROP inclusion would normally escalate to T2, but only one independent B/C source supports it. HostSlick announced on 2026-02-17 (self-report, grade E) that it had stopped new VPS sales to focus on dedicated and bare-metal servers, claiming GTT and TATA transit.</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AS43043 (AUROLOGIC-CLOUD)</t>
+          <t>AS43043 (AUROLOGIC-BYOIP; formerly AUROLOGIC-CLOUD)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2435,12 +2435,12 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>RF-AUROLOGIC; RF-TAE-2026; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>RF-AUROLOGIC; RF-TAE-2026; REGISTRY-SNAPSHOT-2026-09; REGISTRY-SNAPSHOT-2026-10</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>STISC-ALEXHOST; ARCTICWOLF-DARKCARACAL-2026; HUNTRESS-CLEO-2024; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>STISC-ALEXHOST; ARCTICWOLF-DARKCARACAL-2026; HUNTRESS-CLEO-2024; REGISTRY-SNAPSHOT-2026-09; THERECORD-ALEXHOST-2023; HUNTIO-SMISHING-2026</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Moldovan offshore hoster marketing DMCA-ignored hosting (Silent Push: ~10,000 active IPs and 400+ malicious domains in an 8-day sample). Named in STISC reporting after a 1,330-email phishing wave spoofing the Moldovan government. Arctic Wolf (Aug 2026): Dark Caracal's Bandook C2s were hosted on AlexHost, 'a provider previously associated with Dark Caracal'. Cl0p's Cleo campaign (Dec 2024) used AlexHost addresses (176.123.5.126 per Huntress). Do not conflate with the Russian 'Alex Host LLC' that Intrinsec ties to the FDN3 cluster. Correction 2026-09-25: the former known_prefixes (176.123.0.0/16; 37.221.64.0/19) overstated AlexHost's space - most of those ranges belong to other networks. Unverified: the 'former Soviet bomb shelter' claim.</t>
+          <t>Moldovan offshore hoster marketing DMCA-ignored hosting (Silent Push: ~10,000 active IPs and 400+ malicious domains in an 8-day sample). In January 2023 STISC reported a wave of more than 1,330 phishing emails to Moldovan state accounts sent in AlexHost's name; AlexHost disowned them (corrected 2026-10-30: the emails impersonated AlexHost, and the wave was in 2023, not 2025). Hunt.io (2026-05-27): two AlexHost (AS200019) servers were the only non-cloud VPS backends of a Ghiseul.ro-impersonation smishing operation across 19 countries. Arctic Wolf (Aug 2026): Dark Caracal's Bandook C2s were hosted on AlexHost, 'a provider previously associated with Dark Caracal'. Cl0p's Cleo campaign (Dec 2024) used AlexHost addresses (176.123.5.126 per Huntress). Do not conflate with the Russian 'Alex Host LLC' that Intrinsec ties to the FDN3 cluster. Correction 2026-09-25: the former known_prefixes (176.123.0.0/16; 37.221.64.0/19) overstated AlexHost's space - most of those ranges belong to other networks. Unverified: the 'former Soviet bomb shelter' claim.</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Swiss-marketed offshore brand (privatealps.net) of Private Layer INC (Panama registry holder of AS51852/AS52288), marketing DMCA-ignored, no-logs, anonymous, Monero-friendly hosting. RF ranks PrivateAlps #6 in its 2025 Threat Density top 10, and RF's aurologic report ties Global-Data System IT (SWISSNETWORK02) to PrivateAlps. Independent corroboration: the rud.is weekly Bulletproof Hosting Watch tracks PLI-AS among 26 curated BPH ASNs and names it one of the most aggressive (e.g. week of 2026-06-08: RDP brute-force, DCE/RPC enumeration, WordPress login scanning); a Bolster AI phishing study names Private Alps among high-profile BPH providers popular on underground forums for VPS/RDP/VPN hosting; and PrivateAlps advertised 'Abuse &amp; DMCA ignore' offshore servers on BlackHatWorld. Tier raised T4 -&gt; T1 on 2026-09-25 (taxonomy T1: RF top-decile Threat Density - #6 in RF's 2025 top 10, above Femo IT/Defhost at #8; minimum evidence met by RF, rud.is and Bolster). Not on Spamhaus ASN-DROP, and the rud.is and Bolster texts were read via search excerpts only - re-check both at the next review. Correction: registry entity is Private Layer INC (Panama), not Private Layer AG (Switzerland).</t>
+          <t>Swiss-marketed offshore brand (privatealps.net) of Private Layer INC (Panama registry holder of AS51852/AS52288), marketing DMCA-ignored, no-logs, anonymous, Monero-friendly hosting. RF ranks PrivateAlps #6 in its 2025 Threat Density top 10, and RF's aurologic report ties Global-Data System IT (SWISSNETWORK02) to PrivateAlps. Independent corroboration: the rud.is weekly Bulletproof Hosting Watch tracks PLI-AS among about 25 curated BPH ASNs (25 in the week of 2026-10-26) and names it one of the most aggressive (e.g. week of 2026-06-08: RDP brute-force, DCE/RPC enumeration, WordPress login scanning); a Bolster AI phishing study names Private Alps among high-profile BPH providers popular on underground forums for VPS/RDP/VPN hosting; and PrivateAlps advertised 'Abuse &amp; DMCA ignore' offshore servers on BlackHatWorld. Tier raised T4 -&gt; T1 on 2026-09-25 (taxonomy T1: RF top-decile Threat Density - #6 in RF's 2025 top 10, above Femo IT/Defhost at #8; minimum evidence met by RF, rud.is and Bolster). Not on Spamhaus ASN-DROP, and the rud.is and Bolster texts were read via search excerpts only - re-check both at the next review. Correction: registry entity is Private Layer INC (Panama), not Private Layer AG (Switzerland).</t>
         </is>
       </c>
     </row>
@@ -2810,17 +2810,17 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>TRENDMICRO-INTERPOL; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>TRENDMICRO-INTERPOL; REGISTRY-SNAPSHOT-2026-09; RUDIS-BPH-WATCH</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Commercialized free-speech hosting brand with a multi-jurisdiction presence (Romania, Finland, Iceland); explicit uncensored-hosting marketing. Trend Micro/Interpol 2023 reportedly attributed 13% of Africa-related offshore BPH sourcing to FlokiNET (figure unverified). Correction 2026-09-25: the registry holder is FlokiNET ehf (Iceland); the earlier Seychelles / 'Floki Network Services Ltd' details are unverified.</t>
+          <t>Commercialized free-speech hosting brand with a multi-jurisdiction presence (Romania, Finland, Iceland); explicit uncensored-hosting marketing. Trend Micro/Interpol 2023 reportedly attributed 13% of Africa-related offshore BPH sourcing to FlokiNET (figure unverified). Correction 2026-09-25: the registry holder is FlokiNET ehf (Iceland); the earlier Seychelles / 'Floki Network Services Ltd' details are unverified. The rud.is weekly Bulletproof Hosting Watch includes AS200651 among its curated BPH ASNs (week of 2026-10-26; low-weight, automated).</t>
         </is>
       </c>
     </row>
@@ -3051,17 +3051,17 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>RF-TAE-2026; EU-STARK; RF-STARK</t>
+          <t>RF-TAE-2026; EU-STARK; RF-STARK; PQHOSTING-PR-2026</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Moldova-registered LIR (ORG-PHPS1-RIPE, Chisinau, created 2025-05-13) that received AS44477 from Stark Industries on 2025-05-16, four days before the EU listing. RF: 'although PQ.Hosting was referenced within the sanctions multiple times... the company itself was not sanctioned' - status corrected sanctioned -&gt; evading on 2026-09-25 (T1 retained: sanctioned beneficial owners; sanctions-evasion vehicle). ELLIO reports AS44477 has not been visible in the global routing table since about 2026-04-16; the ASN is now deregistered and was never on Spamhaus ASN-DROP. Successor capacity sits with WorkTitans/THE.Hosting and UFO Hosting.</t>
+          <t>Moldova-registered LIR (ORG-PHPS1-RIPE, Chisinau, created 2025-05-13) that received AS44477 from Stark Industries on 2025-05-16, four days before the EU listing. RF: 'although PQ.Hosting was referenced within the sanctions multiple times... the company itself was not sanctioned' - status corrected sanctioned -&gt; evading on 2026-09-25 (T1 retained: sanctioned beneficial owners; sanctions-evasion vehicle). ELLIO reports AS44477 has not been visible in the global routing table since about 2026-04-16; the ASN is now deregistered and was never on Spamhaus ASN-DROP. Successor capacity sits with WorkTitans/THE.Hosting and UFO Hosting. PQ HOSTING announced on 2026-03-13 (press release, grade E) that it was withdrawing from European markets, blaming DDoS attacks and a 'reputational campaign' and hinting at a challenge in European courts.</t>
         </is>
       </c>
     </row>
@@ -3165,12 +3165,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AS52000</t>
+          <t>AS52000 (no routes since 2026-10-19)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AS206932 (MIRHOSTING-NL)</t>
+          <t>AS206932 (MIRHOSTING-NL; no routes since 2026-09-29)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3215,17 +3215,17 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>KREBS-BPH; RF-INFRA-2025; RF-STARK; GREYNOISE-STARK; KREBS-FIOD-STARK; DCD-FIOD-2026; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>KREBS-BPH; RF-INFRA-2025; RF-STARK; GREYNOISE-STARK; KREBS-FIOD-STARK; DCD-FIOD-2026; REGISTRY-SNAPSHOT-2026-09; REGISTRY-SNAPSHOT-2026-10; AMNEZIA-HOSTING-2026</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Founded in 2004 by Andrey Nesterenko, who was arrested in the FIOD raid of 2026-05-18 (name press-reported). Krebs: WorkTitans reached the internet solely through MIRhosting, and AS52000 is the first peer in AS209847's aut-num. The 2008 StopGeorgia.ru hosting is attributed (Jeffrey Carr) to the related Innovation IT Solutions Corp; Nesterenko said he could not verify it. De Volkskrant data showed WorkTitans and MIRhosting as the most-used networks in pro-Russian attacks on Danish bodies (Nov 2025). AS52000 has shrunk to two IPv4 /24s (185.15.209.0/24, 185.15.210.0/24). Tier raised T2 -&gt; T1 on 2026-09-25 (taxonomy T1: subject of a law-enforcement action targeting hosting infrastructure - its founder was arrested in the FIOD action against the WorkTitans network, which reached the internet solely through MIRhosting; reported by Krebs and DatacenterDynamics). Whether MIRhosting-operated servers were among the 800+ seized is unconfirmed. Unverified: the 'temporarily paused services to WorkTitans' quote.</t>
+          <t>Founded in 2004 by Andrey Nesterenko, who was arrested in the FIOD raid of 2026-05-18 (name press-reported). Krebs: WorkTitans reached the internet solely through MIRhosting, and AS52000 is the first peer in AS209847's aut-num. The 2008 StopGeorgia.ru hosting is attributed (Jeffrey Carr) to the related Innovation IT Solutions Corp; Nesterenko said he could not verify it. De Volkskrant data showed WorkTitans and MIRhosting as the most-used networks in pro-Russian attacks on Danish bodies (Nov 2025). AS52000 had shrunk to two IPv4 /24s (185.15.209.0/24, 185.15.210.0/24) by Sept 2026 and has announced nothing since 2026-10-19 (AS206932 since 2026-09-29) - both ASNs remain registered to MIRhosting. Tier raised T2 -&gt; T1 on 2026-09-25 (taxonomy T1: subject of a law-enforcement action targeting hosting infrastructure - its founder was arrested in the FIOD action against the WorkTitans network, which reached the internet solely through MIRhosting; reported by Krebs and DatacenterDynamics). Whether MIRhosting-operated servers were among the 800+ seized is unconfirmed. Unverified: the 'temporarily paused services to WorkTitans' quote. A Russian-language VPN provider blog (June 2026, grade D) says MIRhosting equipment was among the items seized on 2026-05-18 and that the nLighten data centre cut power to MIRhosting equipment in the Netherlands and Germany in early June, taking downstream hosters offline - unverified.</t>
         </is>
       </c>
     </row>
@@ -3280,6 +3280,11 @@
           <t>aurologic GmbH</t>
         </is>
       </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Doppelganger (front proxies, Aug 2024; Qurium); Akira (Cobalt Strike C2, Jun 2025; Team Cymru)</t>
+        </is>
+      </c>
       <c r="Q33" t="inlineStr">
         <is>
           <t>Cobalt Strike; Sliver; QuasarRAT; Remcos; DCRat; Latrodectus; Amadey; Rhadamanthys; RedLine; Meduza</t>
@@ -3302,17 +3307,17 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>RF-AUROLOGIC; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>RF-AUROLOGIC; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09; QURIUM-AEZA-2026; TEAMCYMRU-RANSOMINFRA-2026; REGISTRY-SNAPSHOT-2026-10</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Seychelles-registered holder of AS34888 and AS42624, transferred from Simple Carrier LLC (July 2024). RF (Sept-Nov 2025): 11 IPv4 prefixes (2,816 addresses) all via aurologic AS30823, top ten for malicious-activity density in Sept 2025, linked to PrivateAlps. Both ASNs were on Spamhaus ASN-DROP (simplecarrier.net) in Dec 2025 and have since been delisted; neither announces anything now (e.g. 185.196.8.0/22 and 185.208.156.0/22 are unrouted). Do not confuse with the unrelated Iranian swissnetwork.io ASNs (AS199467, AS209373). Correction 2026-09-25: registration is Seychelles, not Switzerland. Status flagged -&gt; dormant on 2026-09-25: both ASNs remain registered to Global-Data but announce nothing, and the newest reporting (RF, Sept-Nov 2025) is more than six months old. The T2 tier stands; watch for re-announcement, particularly behind aurologic.</t>
+          <t>Seychelles-registered holder of AS34888 and AS42624, transferred from Simple Carrier LLC (July 2024). RF (Sept-Nov 2025): 11 IPv4 prefixes (2,816 addresses) all via aurologic AS30823, top ten for malicious-activity density in Sept 2025, linked to PrivateAlps. Both ASNs were on Spamhaus ASN-DROP (simplecarrier.net) in Dec 2025 and have since been delisted; neither announces anything now (e.g. 185.196.8.0/22 and 185.208.156.0/22 are unrouted). Do not confuse with the unrelated Iranian swissnetwork.io ASNs (AS199467, AS209373). Correction 2026-09-25: registration is Seychelles, not Switzerland. Status flagged -&gt; dormant on 2026-09-25: both ASNs remain registered to Global-Data but announce nothing, and the newest reporting (RF, Sept-Nov 2025) is more than six months old. The T2 tier stands; watch for re-announcement, particularly behind aurologic. Newer reporting covers past activity only: Qurium (Oct 2026) lists AS42624 among the networks Doppelganger's front proxies moved to in Aug 2024, and Team Cymru (Sept 2026) recorded Akira Cobalt Strike beaconing to AS42624 in June 2025. AS42624 last announced a prefix on 2026-04-07 (RIPEstat), more than six months ago, so 'dormant' stands.</t>
         </is>
       </c>
     </row>
@@ -3558,17 +3563,17 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>RF-AUROLOGIC; QURIUM-DOPPELGANGER; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>RF-AUROLOGIC; QURIUM-DOPPELGANGER; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09; UK-COMPANIES-HOUSE</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>UK-registered operator (AS213887 announces 29 IPv4 and 7 IPv6 prefixes; the earlier '68 IPv4 / 11 IPv6' is outdated). WAIcore activity predates the AS213887 registration: Spamhaus ASN-DROP listed three earlier WAIcore ASNs (AS202973, AS206425, AS210281; domain waicore.com) by Feb 2024; all three have since been re-issued to unrelated networks (do not block them). A new registration, AS219262 'WAICORE-RUSSIA', is held by a Russian individual and has no routes yet. Qurium names WAIcore within Doppelganger infrastructure behind aurologic; the RF naming is unverified. Not on the current ASN-DROP.</t>
+          <t>UK-registered operator (AS213887 announces 29 IPv4 and 7 IPv6 prefixes; the earlier '68 IPv4 / 11 IPv6' is outdated). WAIcore activity predates the AS213887 registration: Spamhaus ASN-DROP listed three earlier WAIcore ASNs (AS202973, AS206425, AS210281; domain waicore.com) by Feb 2024; all three have since been re-issued to unrelated networks (do not block them). A new registration, AS219262 'WAICORE-RUSSIA', is held by a Russian individual and has no routes yet. Qurium names WAIcore within Doppelganger infrastructure behind aurologic; the RF naming is unverified. Not on the current ASN-DROP. Companies House: WAICORE HOSTING LTD (14884560) was dissolved by voluntary strike-off on 2024-06-18; WAICORE LTD (15668439, incorporated 2024-04-22) changed officers on 2026-10-08/09 and received a first Gazette notice for compulsory strike-off on 2026-10-13. Dissolution would not by itself end AS213887.</t>
         </is>
       </c>
     </row>
@@ -3595,7 +3600,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AS50113; AS205090; AS200740; AS204339; AS204154; AS35196; AS214602</t>
+          <t>AS50113; AS205090; AS200740; AS204339; AS204154; AS35196; AS214602 (no routes, Oct 2026)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3615,7 +3620,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Ransomware operators leasing ISPsystem VMmanager templates (LockBit; Qilin; Conti; BlackCat/ALPHV; WantToCry)</t>
+          <t>Ransomware operators leasing ISPsystem VMmanager templates (LockBit; Qilin; Conti; BlackCat/ALPHV; WantToCry); Doppelganger (per research cited by Sophos)</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -3635,17 +3640,17 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>SOPHOS-VMMANAGER; BLEEPINGCOMPUTER-BPH; TROLLEYE-FIRSTSERVER; GREYNOISE-REACT2SHELL-2026; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>SOPHOS-VMMANAGER; BLEEPINGCOMPUTER-BPH; TROLLEYE-FIRSTSERVER; GREYNOISE-REACT2SHELL-2026; REGISTRY-SNAPSHOT-2026-09; REGISTRY-SNAPSHOT-2026-10; QURIUM-AEZA-2026; UK-COMPANIES-HOUSE</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>UK-registered network with at least eight ASNs registered to FIRST SERVER LIMITED (AS204997, AS50113, AS205090, AS200740, AS204339, AS204154, AS35196, AS214602; plus a Spanish affiliate on AS199685). Linked to the Sophos (Feb 2026) research on ISPsystem VMmanager default Windows templates, whose reused hostnames appear across LockBit, Qilin, Conti, BlackCat, Ursnif, NetSupport, PureRAT, Lampion, Lumma and RedLine infrastructure - associations of the template ecosystem, not specifically of First Server; the Sophos naming of First Server could not be re-verified. Former Hypercore prefixes now originate from AS205090 and AS200740 (lead only). Do not confuse AS204997's handle FIRSTBYTE-AS with the unrelated Iranian AS210703 'FIRSTBYTE-AS' on ASN-DROP. TrickBot was removed (not in the Sophos summary).</t>
+          <t>UK-registered network with at least eight ASNs registered to FIRST SERVER LIMITED (AS204997, AS50113, AS205090, AS200740, AS204339, AS204154, AS35196, AS214602; plus a Spanish affiliate on AS199685). Linked to the Sophos (Feb 2026) research on ISPsystem VMmanager default Windows templates, whose reused hostnames appear across LockBit, Qilin, Conti, BlackCat, Ursnif, NetSupport, PureRAT, Lampion, Lumma and RedLine infrastructure - associations of the template ecosystem, not specifically of First Server; Sophos names First Server Limited among the top hosts of the reused hostnames (592 hosts with WIN-J9D866ESIJ2), calls Stark and First Server the two providers with additional links to cybercriminal and Russian state operations, and cites research tying First Server to Doppelganger. Former Hypercore prefixes now originate from AS205090 and AS200740 (lead only). Do not confuse AS204997's handle FIRSTBYTE-AS with the unrelated Iranian AS210703 'FIRSTBYTE-AS' on ASN-DROP. TrickBot was removed (not in the Sophos summary). Qurium (Oct 2026): more than half of 15 Network Management/IP4MARKET prefixes later assigned to Aeza had first been used by NTX Technologies and First Server Limited, and a Spanish 'First Server, SL' (Alicante) appeared in March 2026. Companies House: FIRST SERVER LIMITED (14459750) received a first Gazette notice for compulsory strike-off on 2026-10-13 (name match to the RIPE org).</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3702,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -3707,12 +3712,12 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>EXCEDO-ASN; RF-TAE-2026; ORANGE-CD-BLUESTYLTHON; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>EXCEDO-ASN; RF-TAE-2026; ORANGE-CD-BLUESTYLTHON; REGISTRY-SNAPSHOT-2026-09; UK-COMPANIES-HOUSE</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>UK company reported compulsorily dissolved at Companies House in January 2025 (not re-verified). RF ranked Silent Connection #9 in its 2025 Threat Density top 10; Orange Cyberdefense placed Blue Stylthon WsgiDAV servers delivering XWorm/AsyncRAT (Nov-Dec 2024) in AS215240. As of 2026-09-25 the ASN is registered to Microdex UG (DE) under a new handle and announces nothing, so the earlier 'network remains live' note is outdated. Another German UG holds a second ASN under the same MICRODEX-AS handle - a possible re-homing by the same operator (unproven).</t>
+          <t>UK company SILENT CONNECTION LTD (Companies House 15578799), dissolved by compulsory strike-off on 2025-01-28. RF ranked Silent Connection #9 in its 2025 Threat Density top 10; Orange Cyberdefense placed Blue Stylthon WsgiDAV servers delivering XWorm/AsyncRAT (Nov-Dec 2024) in AS215240. As of 2026-09-25 the ASN is registered to Microdex UG (DE) under a new handle and announces nothing, so the earlier 'network remains live' note is outdated. Another German UG holds a second ASN under the same MICRODEX-AS handle - a possible re-homing by the same operator (unproven).</t>
         </is>
       </c>
     </row>
@@ -3744,12 +3749,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Dolphon 1337 Ltd</t>
+          <t>Dolphin 1337 Limited (Companies House 15589896; dissolved 2025-01-14)</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Dolphin 1337 Limited</t>
+          <t>Dolphin 1337 Limited; Dolphin 1337 Limited (registered name; 'Dolphon' is the spelling used in sources)</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3769,17 +3774,17 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>EXCEDO-ASN; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>EXCEDO-ASN; REGISTRY-SNAPSHOT-2026-09; UK-COMPANIES-HOUSE</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>UK shell reported compulsorily dissolved in Jan 2025 (not re-verified); AS215208 (reported registered 2024-03-28) is now held by PT Citra Celebas Multimedia (Indonesia) and announces three live prefixes - this is ASN recycling, not a dissolved shell still operating, so the ASN must not be blocked. The only source is Excedo. RF's 2025 top-10 #10 is 'DolphinHost Limited' (AS214717/AS207184, dolphinhost.net), a different entity; the repo previously conflated the two. The '1337' naming link to ELITETEAM is speculative. Tier lowered T3 -&gt; T5 on 2026-09-25 (historically associated; currently quiescent; single source).</t>
+          <t>UK shell registered as DOLPHIN 1337 LIMITED (Companies House 15589896; no company named 'Dolphon' exists), dissolved by compulsory strike-off on 2025-01-14; AS215208 (reported registered 2024-03-28) is now held by PT Citra Celebas Multimedia (Indonesia) and announces three live prefixes - this is ASN recycling, not a dissolved shell still operating, so the ASN must not be blocked. The only source is Excedo. RF's 2025 top-10 #10 is 'DolphinHost Limited' (AS214717/AS207184, dolphinhost.net), a different entity; the repo previously conflated the two. The '1337' naming link to ELITETEAM is speculative. Tier lowered T3 -&gt; T5 on 2026-09-25 (historically associated; currently quiescent; single source).</t>
         </is>
       </c>
     </row>
@@ -3980,17 +3985,17 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09; UK-COMPANIES-HOUSE</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Renamed from 'Tiger Net (SOW-A)' on 2026-09-25. Tiger Network Limited (GB) holds AS48589 (5 prefixes, 14,848 addresses of Asian space) and AS211121 (4 prefixes); both are on Spamhaus ASN-DROP (imtigernet) and their prefixes overlap Spamhaus DROP. A relayed Silent Push 2025 table lists 'AS48589 SOW-A-AS (Tiger Net) - Ukraine, Gmail, DGA'. No current 'SOW-A' handle exists; the only registry match, AS43613 'SOWA' (LLC BIGNET UKRAINE), is a separate ASN-DROP entry, so the relay may have merged two records. Raised T5 -&gt; T3 (status flagged); T2 pending a second independent B/C source.</t>
+          <t>Renamed from 'Tiger Net (SOW-A)' on 2026-09-25. Tiger Network Limited (GB) holds AS48589 (5 prefixes, 14,848 addresses of Asian space) and AS211121 (4 prefixes); both are on Spamhaus ASN-DROP (imtigernet) and their prefixes overlap Spamhaus DROP. A relayed Silent Push 2025 table lists 'AS48589 SOW-A-AS (Tiger Net) - Ukraine, Gmail, DGA'. No current 'SOW-A' handle exists; the only registry match, AS43613 'SOWA' (LLC BIGNET UKRAINE), is a separate ASN-DROP entry, so the relay may have merged two records. Raised T5 -&gt; T3 (status flagged); T2 pending a second independent B/C source. Companies House: TIGER NETWORK LIMITED (11161830, incorporated 2018-01-22) files dormant accounts and received a first Gazette notice for compulsory strike-off on 2026-10-13 (name match to the RIPE org).</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4263,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -4268,7 +4273,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Small US-registered operator (AS14315; 51 IPv4 prefixes; ipverse role 'midsize transit') appearing alongside Proton66, Railnet and Femo IT in a Lumma malware hunt (single source; the blog could not be re-read). Not on Spamhaus ASN-DROP.</t>
+          <t>Small US-registered operator (AS14315; 51 IPv4 prefixes; ipverse role 'midsize transit') appearing alongside Proton66, Railnet and Femo IT in a Lumma malware hunt (single source, re-read 2026-10-30: the Intel Insights 'Bulletproof Hosting Hunt' post of 2025-07-27 lists one 1GSERVERS address, 104.251.123.89, among ten Lumma-communicating IPs on ten ASNs that also include M247, Namecheap and G-Core, and makes no BPH claim about 1GSERVERS - very weak evidence). Not on Spamhaus ASN-DROP.</t>
         </is>
       </c>
     </row>
@@ -4422,12 +4427,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>RedHotel (C2, 2022-23); ToolShell/SharePoint exploitation (2025); FortiGate SSO abuse (Dec 2025); Bulbature/GobRAT operators</t>
+          <t>RedHotel (C2, 2022-23); ToolShell/SharePoint exploitation (2025); FortiGate SSO abuse (Dec 2025); Bulbature/GobRAT operators; TA416 / Mustang Panda (PlugX campaigns against European and Middle Eastern governments, 2025-26; Proofpoint)</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>RedHotel tooling; GobRAT; Cobalt Strike</t>
+          <t>RedHotel tooling; GobRAT; Cobalt Strike; PlugX</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4447,7 +4452,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4457,12 +4462,12 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>RF-TAE-2026; SPAMHAUS-ASNDROP-2026; RF-REDHOTEL-2023; ESET-TOOLSHELL-2025; SEKOIA-BULBATURE; GREYNOISE-REACT2SHELL-2026; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>RF-TAE-2026; SPAMHAUS-ASNDROP-2026; RF-REDHOTEL-2023; ESET-TOOLSHELL-2025; SEKOIA-BULBATURE; GREYNOISE-REACT2SHELL-2026; REGISTRY-SNAPSHOT-2026-09; PROOFPOINT-TA416-2026</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Hong Kong ISP (APNIC-registered 2019) announcing 113,664 IPv4 addresses in 168 prefixes on AS138915 (Sept 2026; the earlier '182,272 / 50+ netblocks' is outdated). RF ranks Kaopu #4 in its 2025 Threat Density top 10. Spamhaus ASN-DROP lists three kaopuyun.com ASNs: AS138915, AS58854 and AS154177 (LIGHT NODE LIMITED, 129 IPv4 prefixes); a fourth (AS140666, ANY DIGITAL PTE. LTD.) was listed earlier and removed. Independent vendor evidence: RF Insikt (RedHotel heavily favouring Kaopu for C2, 2022-23); ESET (ToolShell SharePoint exploitation from Kaopu IPs, July 2025); Arctic Wolf (malicious FortiGate SSO logins, Dec 2025); Sekoia (Bulbature/GobRAT staging servers all on AS138915); GreyNoise React2Shell sources. Tier raised T3 -&gt; T1 (status flagged) on 2026-09-25 (taxonomy T1: RF top-decile Threat Density - #4 in RF's 2025 top 10, the basis also used for Femo IT/Defhost at #8; minimum evidence met by RF, Spamhaus, ESET, Sekoia and GreyNoise).</t>
+          <t>Hong Kong ISP (APNIC-registered 2019) announcing 113,664 IPv4 addresses in 168 prefixes on AS138915 (Sept 2026; the earlier '182,272 / 50+ netblocks' is outdated). RF ranks Kaopu #4 in its 2025 Threat Density top 10. Spamhaus ASN-DROP lists three kaopuyun.com ASNs: AS138915, AS58854 and AS154177 (LIGHT NODE LIMITED, 129 IPv4 prefixes); a fourth (AS140666, ANY DIGITAL PTE. LTD.) was listed earlier and removed. Independent vendor evidence: RF Insikt (RedHotel heavily favouring Kaopu for C2, 2022-23); ESET (ToolShell SharePoint exploitation from Kaopu IPs, July 2025); Arctic Wolf (malicious FortiGate SSO logins, Dec 2025); Sekoia (Bulbature/GobRAT staging servers all on AS138915); GreyNoise React2Shell sources. Tier raised T3 -&gt; T1 (status flagged) on 2026-09-25 (taxonomy T1: RF top-decile Threat Density - #4 in RF's 2025 top 10, the basis also used for Femo IT/Defhost at #8; minimum evidence met by RF, Spamhaus, ESET, Sekoia and GreyNoise). Proofpoint (2026): TA416 has heavily favoured Evoxt Enterprise (AS149440), XNNET LLC (AS6134) and Kaopu Cloud HK (AS138915) for C2 throughout 2025 and 2026.</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4504,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Garantex successor; TokenSpot (likely front, per TRM)</t>
+          <t>Garantex successor; TokenSpot (front, per TRM high confidence, Oct 2026; separate row)</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4534,17 +4539,17 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>OFAC-GARANTEX; CHAINALYSIS-A7A5; CHAINALYSIS-OFAC; TRM-A7A5-2026; ELLIPTIC-GRINEX</t>
+          <t>OFAC-GARANTEX; CHAINALYSIS-A7A5; CHAINALYSIS-OFAC; TRM-A7A5-2026; ELLIPTIC-GRINEX; TRM-TOKENSPOT-2026</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Kyrgyzstan-incorporated successor to Garantex: registered December 2024 (TRM) and promoted on Telegram days after the March 2025 Garantex takedown; forensically tied to Garantex by shared on-chain infrastructure and asset migration (user funds plus A7A5 minted via Old Vector). OFAC designated it on 2025-08-14 as Garantex's 'direct successor'. On 2026-04-15 about 12:00 UTC roughly $13-15M was drained (Grinex claimed &gt;1bn rubles and blamed foreign 'special services'; Elliptic measured ~$15M USDT); Grinex then suspended operations, and Chainalysis raised the possibility of a false-flag exit. TokenSpot, a Kyrgyz exchange TRM considers a likely Grinex front, was hit the same day; Rapira had &gt;$72M in direct transactions with Grinex (Elliptic). Exved is a separately designated company, not an alias. Unverified: '&gt;=$4.76B processed in 2025'. Designation stands; operationally offline.</t>
+          <t>Kyrgyzstan-incorporated successor to Garantex: registered December 2024 (TRM) and promoted on Telegram days after the March 2025 Garantex takedown; forensically tied to Garantex by shared on-chain infrastructure and asset migration (user funds plus A7A5 minted via Old Vector). OFAC designated it on 2025-08-14 as Garantex's 'direct successor'. On 2026-04-15 about 12:00 UTC roughly $13-15M was drained (Grinex claimed &gt;1bn rubles and blamed foreign 'special services'; Elliptic measured ~$15M USDT); Grinex then suspended operations, and Chainalysis raised the possibility of a false-flag exit. TokenSpot, a Kyrgyz exchange that TRM (2026-10-06) assesses with high confidence runs on shared wallet infrastructure with Grinex, was hit the same day (see the TokenSpot CJSC row; UK-designated 2026-10-08); Rapira had &gt;$72M in direct transactions with Grinex (Elliptic). Exved is a separately designated company, not an alias. Unverified: '&gt;=$4.76B processed in 2025'. Designation stands; Grinex's own front end remains offline, but the shared TokenSpot deposit aggregator stayed active until 2026-07-29 and TokenSpot is still operating.</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -4596,7 +4601,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>UK May 2025 (A7) and Aug 20 2025 (Old Vector LLC); EU July 2025 (A7) and 19th package Oct 23 2025 (full A7A5 transaction ban from Nov 25 2025); OFAC Aug 14 2025 (Old Vector LLC, A7 LLC, A71 LLC, A7 Agent LLC)</t>
+          <t>UK May 2025 (A7) and Aug 20 2025 (Old Vector LLC); EU July 2025 (A7) and 19th package Oct 23 2025 (full A7A5 transaction ban from Nov 25 2025); OFAC Aug 14 2025 (Old Vector LLC, A7 LLC, A71 LLC, A7 Agent LLC); OFAC Oct 1 2026: whole A7 Network designated a significant transnational criminal organization (E.O. 13581; Operation Economic Outcast); FinCEN Oct 1 2026: section 9714(a) proposed rule against A7 Network Sub-Agents plus an Alert</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4616,17 +4621,17 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>OFAC-GARANTEX; CHAINALYSIS-A7A5; TRM-A7A5-2026</t>
+          <t>OFAC-GARANTEX; CHAINALYSIS-A7A5; TRM-A7A5-2026; OFAC-A7-NETWORK-2026</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Russian ruble-backed stablecoin issued by Kyrgyzstan's Old Vector; A7 LLC is the token's creator. Chainalysis (2026 Crypto Crime Report): $93.3B moved 'in less than a year'; Elliptic: more than $100B in under a year (the $93.1B and $72B figures elsewhere are earlier snapshots). Garantex moved funds into A7A5 from as early as January 2025 (TRM). The no-KYC Instant Swapper reportedly converted &gt;$2.2B of A7A5 into mainstream USD stablecoins (unverified). The EU banned A7A5 transactions from 2025-11-25. Its economy ran through Grinex, so on-chain volume reportedly collapsed after Grinex suspended in April 2026 (the '~96%' figure is unverified). A7 LLC, A71 LLC and A7 Agent LLC are separately designated related entities, not aliases.</t>
+          <t>Russian ruble-backed stablecoin issued by Kyrgyzstan's Old Vector; A7 LLC is the token's creator. Chainalysis (2026 Crypto Crime Report): $93.3B moved 'in less than a year'; Elliptic: more than $100B in under a year (the $93.1B and $72B figures elsewhere are earlier snapshots). Garantex moved funds into A7A5 from as early as January 2025 (TRM). The no-KYC Instant Swapper reportedly converted &gt;$2.2B of A7A5 into mainstream USD stablecoins (unverified). The EU banned A7A5 transactions from 2025-11-25. Its economy ran through Grinex, and on-chain volume reportedly collapsed after Grinex suspended in April 2026 (the '~96%' decline figure is attributed to Elliptic in secondary reporting). On 2026-10-01 Treasury designated the whole A7 Network as a transnational criminal organization: its Sub-Agents processed more than $17B (Jan 2025-Jun 2026) and 'catered to cybercriminals, including ransomware' actors, and the network is linked to Nobitex and to North Korean hacks; FinCEN proposed cutting Sub-Agents off from US transmittals (rule not yet final). A7 LLC, A71 LLC and A7 Agent LLC are separately designated related entities, not aliases.</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -4688,17 +4693,17 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>OFAC-IRAN-FURY; CHAINALYSIS-OFAC</t>
+          <t>OFAC-IRAN-FURY; CHAINALYSIS-OFAC; OFAC-A7-NETWORK-2026</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Iran's largest digital-asset exchange. OFAC-designated 2026-06-02 under 'Economic Fury' - uniquely also under counterterrorism E.O. 13224 - together with four executives. The four designated Iranian exchanges handled about $7.7B, roughly 78% of Iran's attributed 2025 crypto volume. Follow-on actions: OFAC added Central Bank of Iran wallets (2026-07-16) and designated the exchanges Shelbit and Aban Tether (2026-08-07), the latter for transactions with Nobitex, Wallex, Bitpin and Ramzinex.</t>
+          <t>Iran's largest digital-asset exchange. OFAC-designated 2026-06-02 under 'Economic Fury' - uniquely also under counterterrorism E.O. 13224 - together with four executives. The four designated Iranian exchanges handled about $7.7B, roughly 78% of Iran's attributed 2025 crypto volume. Follow-on actions: OFAC added Central Bank of Iran wallets (2026-07-16) and designated the exchanges Shelbit and Aban Tether (2026-08-07), the latter for transactions with Nobitex, Wallex, Bitpin and Ramzinex. Treasury's 2026-10-01 A7 Network action states that the A7 Network has been linked to Nobitex.</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -4936,7 +4941,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>45.142.193.0/24; 77.90.185.0/24; 172.94.9.0/24; 192.253.248.0/24; 206.123.156.0/24; 185.93.89.0/24; 45.129.14.0/24</t>
+          <t>45.142.193.0/24; 77.90.185.0/24; 172.94.9.0/24; 192.253.248.0/24; 206.123.156.0/24 (not announced since 2026-09-09); 185.93.89.0/24; 45.129.14.0/24 (not announced since 2024-08)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4996,12 +5001,12 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>INTRINSEC-BTHOSTER; SECURITYONLINE-BTHOSTER; RIPE-AAWG-BTHOSTER; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>INTRINSEC-BTHOSTER; SECURITYONLINE-BTHOSTER; RIPE-AAWG-BTHOSTER; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09; REGISTRY-SNAPSHOT-2026-10</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
@@ -5038,7 +5043,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AS215310 (USERCLOUD; Pfcloud UG); AS400328 (Intelligence Hosting LLC [NL/ARIN]; Spamhaus-attributed via pfcloud.io)</t>
+          <t>AS215310 (USERCLOUD; Pfcloud UG); AS400328 (Intelligence Hosting LLC [NL/ARIN]; Spamhaus-attributed via pfcloud.io); AS205329 (Muilties Network; individual registrant [DE/RIPE]; Spamhaus-attributed via pfcloud.io)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5083,7 +5088,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -5093,7 +5098,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>German micro-provider (AS51396: 26 IPv4 and 24 IPv6 prefixes). Spamhaus ASN-DROP has listed AS51396 since at least Feb 2024 (with a since-recycled AS202685 'as-pfcloud'); it now also lists AS215310 (USERCLOUD) and AS400328 (Intelligence Hosting LLC) under pfcloud.io. RF lists Pfcloud as an upstream of the Virtualine/Railnet 'hosting island' alongside aurologic. GreyNoise (Aug 2026): 204.76.203.43 on AS51396 generated 393,777 sessions and most of the period's 121,068 Hikvision CVE-2021-36260 exploitation attempts; Pfcloud IPs also appear among React2Shell sources. A community note (Sept 2026, D-grade) describes a Pfcloud open directory staging FortiGate 60F exploit modules on an IP previously listed as AsyncRAT C2. Tier raised T3 -&gt; T2 (status flagged) on 2026-09-25 per the ASN-DROP escalation rule; the earlier single-honeypot caveat is outdated. Oct 2026: Pfcloud was one of the last two neighbours of Virtualine's AS202412 when it was seized (Operation Omegaline); a community post says the Dutch servers seized in Limburg were Tube-Hosting (AS49581) hardware resold to Virtualine through Pfcloud (unconfirmed).</t>
+          <t>German micro-provider (AS51396: 26 IPv4 and 24 IPv6 prefixes). Spamhaus ASN-DROP has listed AS51396 since at least Feb 2024 (with a since-recycled AS202685 'as-pfcloud'); it now also lists AS215310 (USERCLOUD) and AS400328 (Intelligence Hosting LLC) under pfcloud.io. RF lists Pfcloud as an upstream of the Virtualine/Railnet 'hosting island' alongside aurologic. GreyNoise (Aug 2026): 204.76.203.43 on AS51396 generated 393,777 sessions and most of the period's 121,068 Hikvision CVE-2021-36260 exploitation attempts; Pfcloud IPs also appear among React2Shell sources. A community note (Sept 2026, D-grade) describes a Pfcloud open directory staging FortiGate 60F exploit modules on an IP previously listed as AsyncRAT C2. Tier raised T3 -&gt; T2 (status flagged) on 2026-09-25 per the ASN-DROP escalation rule; the earlier single-honeypot caveat is outdated. Oct 2026: Pfcloud was one of the last two neighbours of Virtualine's AS202412 when it was seized (Operation Omegaline); a community post says the Dutch servers seized in Limburg were Tube-Hosting (AS49581) hardware resold to Virtualine through Pfcloud (unconfirmed). Spamhaus has since added a fourth ASN under pfcloud.io, AS205329 (an individual-registered RIPE ASN, created 2022, two IPv4 prefixes). RIS route collectors on 2026-10-30 still showed a residual path 49581 51396 202412 for former Omegatech space - Tube-Hosting carrying Pfcloud carrying AS202412 - which supports the Tube-Hosting/Pfcloud supply chain at the routing level.</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
@@ -5319,17 +5324,17 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>OFAC-HUIONE-PRINCE; FINCEN-HPAY-2026</t>
+          <t>OFAC-HUIONE-PRINCE; FINCEN-HPAY-2026; CAMBOJA-HPAY-2026; THERECORD-LIXIONG-2026</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>FinCEN (announced 2026-06-23 with the DOJ Huione cloud-account seizure and Prince Group designations) proposed amending its Oct 2025 Huione Group Section 311 final rule to cover Cambodia-based H-Pay Service PLC (reg. no. 00074959) and 'any successor entity', to stop Huione circumventing the cut-off. The comment period was extended in July 2026 after a portal outage; the rule is not yet final. FinCEN notes the National Bank of Cambodia revoked H-Pay's payment licence on 2026-04-10.</t>
+          <t>FinCEN (announced 2026-06-23 with the DOJ Huione cloud-account seizure and Prince Group designations) proposed amending its Oct 2025 Huione Group Section 311 final rule to cover Cambodia-based H-Pay Service PLC (reg. no. 00074959) and 'any successor entity', to stop Huione circumventing the cut-off. The comment period was extended in July 2026 after a portal outage; the rule is not yet final. FinCEN notes the National Bank of Cambodia revoked H-Pay's payment licence on 2026-04-10. Liquidator Reach &amp; Partners said on 2026-07-08 that H-Pay had operated beyond its licence and is insolvent, and told creditors to await a court-appointed liquidator. Huione Group's former chairman Li Xiong was extradited from Cambodia to China on 2026-04-01.</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -5570,17 +5575,17 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>OFAC-1VPNS; EUROPOL-SAFFRON-2026</t>
+          <t>OFAC-1VPNS; EUROPOL-SAFFRON-2026; EUROJUST-SAFFRON-2026</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>OFAC-designated 2026-07-13 (sb0559) under E.O. 13694 as amended, in furtherance of E.O. 14390, for enabling ransomware attacks on US targets; the UK did not co-designate it. No-log criminal VPN advertised on cybercrime forums since 2014; ~32 exit nodes in ~27 countries used by at least 25 ransomware groups (FBI FLASH-20260521-001). Administrator Dmytro Rashevskyi (45, Ukrainian) used false identities (Maksim Sorin, Roman Chabanenko) to buy infrastructure. Belarusian cryptor seller Yegeniy Silayev was co-designated. The service was dismantled in Operation Saffron (19-20 May 2026, France- and Netherlands-led with Europol and Eurojust): 33 servers taken down, 1vpns domains seized and a suspected administrator arrested. SDN entries carry 5 addresses for the service and 8 for Rashevskyi.</t>
+          <t>OFAC-designated 2026-07-13 (sb0559) under E.O. 13694 as amended, in furtherance of E.O. 14390, for enabling ransomware attacks on US targets; the UK did not co-designate it. No-log criminal VPN advertised on cybercrime forums since 2014; ~32 exit nodes in ~27 countries used by at least 25 ransomware groups (FBI FLASH-20260521-001). Administrator Dmytro Rashevskyi (45, Ukrainian) used false identities (Maksim Sorin, Roman Chabanenko) to buy infrastructure. Belarusian cryptor seller Yegeniy Silayev was co-designated. The service was dismantled in Operation Saffron (19-20 May 2026, France- and Netherlands-led with Europol and Eurojust): 33 servers taken down, 1vpns domains seized, and a suspect searched and interviewed in Ukraine (Eurojust; no arrest was announced - corrected 2026-10-30). SDN entries carry 5 addresses for the service and 8 for Rashevskyi.</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
@@ -5637,7 +5642,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>Popa (proxy botnet)</t>
+          <t>Popa (proxy botnet); BADBOX 2.0 botnet plugin components; Mirai variants (per GTIG)</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5657,7 +5662,7 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -5667,7 +5672,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>On 2026-07-02 the FBI seized hundreds of NetNut-linked domains (the seizure notice thanks Google, Lumen and Shadowserver) and Google disrupted the associated Popa botnet (at least 2 million hijacked smart TVs, streaming boxes and Android devices): Google disabled accounts used for C2 and set Play Protect to disable apps carrying NetNut SDKs. GTIG observed 316 distinct threat clusters using suspected NetNut exit nodes in a single week of June 2026. Popa was first flagged by QiAnXin XLab in March 2025 as an Android component of the Vo1d botnet and was tied to NetNut in June 2026 by Krebs, Qurium, Nokia Deepfield and Synthient. NetNut is operated by NASDAQ-listed Alarum Technologies (ALAR), which disputes the allegations and paused traffic on the affected network; its shares fell 23.6% after hours. Builds on Google's Jan 2026 IPIDEA disruption. Not sanctioned. Corrections 2026-09-25: IRS-CI involvement and a '~67% stock fall' were not supported by any source and were removed.</t>
+          <t>On 2026-07-02 the FBI seized hundreds of NetNut-linked domains (the seizure notice thanks Google, Lumen and Shadowserver) and Google disrupted the associated Popa botnet (at least 2 million hijacked smart TVs, streaming boxes and Android devices): Google disabled accounts used for C2 and set Play Protect to disable apps carrying NetNut SDKs. GTIG observed 316 distinct threat clusters using suspected NetNut exit nodes in a single week of June 2026. Popa was first flagged by QiAnXin XLab in March 2025 as an Android component of the Vo1d botnet and was tied to NetNut in June 2026 by Krebs, Qurium, Nokia Deepfield and Synthient. NetNut is operated by NASDAQ-listed Alarum Technologies (ALAR), which disputes the allegations and paused traffic on the affected network; its shares fell 23.6% after hours. Builds on Google's Jan 2026 IPIDEA disruption. Not sanctioned. Corrections 2026-09-25: IRS-CI involvement and a '~67% stock fall' were not supported by any source and were removed. GTIG (2026-07-02) found NetNut botnet plugin components in BADBOX 2.0 tooling, cites reporting of NetNut being used to spread Mirai variants, and says many popular proxy brands white-label NetNut.</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -5893,7 +5898,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AS59425 (HORIZONMSK-AS; no routes); AS207566 (LD007-AS; no routes); AS201738 (UFO TECHNOLOGIES LIMITED [GB]; Spamhaus-attributed via changway.hk); AS211663 (GALEON LLC [RU]; Spamhaus-attributed via changway.hk)</t>
+          <t>AS59425 (HORIZONMSK-AS; no routes); AS207566 (LD007-AS; no routes); AS201738 (UFO TECHNOLOGIES LIMITED [GB]; Spamhaus-attributed via changway.hk); AS211663 (GALEON LLC [RU]; Spamhaus-attributed via changway.hk); AS218974 (UFO TECHNOLOGIES LIMITED [HK]; Spamhaus-attributed via changway.hk)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5943,17 +5948,17 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>SPAMHAUS-ASNDROP-2026; INTRINSEC-PROSPERO; TRUSTWAVE-PROSPERO; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>SPAMHAUS-ASNDROP-2026; INTRINSEC-PROSPERO; TRUSTWAVE-PROSPERO; REGISTRY-SNAPSHOT-2026-09; REGISTRY-SNAPSHOT-2026-10</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Hong Kong provider that Intrinsec (Nov 2024) calls a 'likely related' network of PROSPERO/Proton66; Trustwave SpiderLabs observed IP shifts from Proton66 to Chang Way ASNs and the my.31337.hk panel re-themed 'CHANGWAY/HOSTWAY'. Split out of the PROSPERO row (where it was listed as an alias) on 2026-09-25. Spamhaus ASN-DROP lists five ASNs under changway.hk: Chang Way's own AS57523, AS59425 and AS207566 (none announcing) plus the newly added AS201738 (UFO TECHNOLOGIES LIMITED, GB; 7 /24s, all on Spamhaus DROP) and AS211663 (GALEON LLC, RU; 1 /24). Four other changway.hk ASNs listed in Dec 2025 (AS57678, AS208312, AS209309, AS213355) have since been delisted - a rotating-shell pattern. The name similarity between 'UFO Technologies Limited' and Stark's UFO Hosting is not an established link. T2 on ASN-DROP inclusion plus Intrinsec and SpiderLabs reporting.</t>
+          <t>Hong Kong provider that Intrinsec (Nov 2024) calls a 'likely related' network of PROSPERO/Proton66; Trustwave SpiderLabs observed IP shifts from Proton66 to Chang Way ASNs and the my.31337.hk panel re-themed 'CHANGWAY/HOSTWAY'. Split out of the PROSPERO row (where it was listed as an alias) on 2026-09-25. Spamhaus ASN-DROP lists five ASNs under changway.hk: Chang Way's own AS57523, AS59425 and AS207566 (none announcing) plus the newly added AS201738 (UFO TECHNOLOGIES LIMITED, GB; 7 /24s, all on Spamhaus DROP) and AS211663 (GALEON LLC, RU; 1 /24). Four other changway.hk ASNs listed in Dec 2025 (AS57678, AS208312, AS209309, AS213355) have since been delisted - a rotating-shell pattern. The name similarity between 'UFO Technologies Limited' and Stark's UFO Hosting is not an established link. T2 on ASN-DROP inclusion plus Intrinsec and SpiderLabs reporting. By 2026-10-29 Spamhaus had added a sixth ASN under changway.hk: AS218974 (also named UFO TECHNOLOGIES LIMITED, registered 2026-08-12, one /24 announced via OVH since 2026-09-11).</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
@@ -6077,7 +6082,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>45.194.92.0/24 (on Spamhaus DROP); 45.198.224.0/24; 45.205.1.0/24</t>
+          <t>45.194.92.0/24 (on Spamhaus DROP); 45.198.224.0/24; 45.205.1.0/24 (VPSVault origin until 2026-10-21; now LARUS Limited AS17561 - re-check before blocking)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -6122,17 +6127,17 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>SPAMHAUS-ASNDROP-2026; GREYNOISE-WEEKLY-2026-08; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>SPAMHAUS-ASNDROP-2026; GREYNOISE-WEEKLY-2026-08; REGISTRY-SNAPSHOT-2026-09; REGISTRY-SNAPSHOT-2026-10</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>UK-registered VPS provider whose AS215925 has been on Spamhaus ASN-DROP since at least Dec 2025. GreyNoise has carried it in its weekly brief since 2025-12-15; in the period to 2026-08-30 it produced 10,135,029 connection attempts in a 96-host proxy-scanning sweep. GreyNoise advises against an ASN-level block (shared tenancy). Announces 45.194.92.0/24 (on Spamhaus DROP), 45.198.224.0/24 and 45.205.1.0/24. Added 2026-09-25 at T2 under the taxonomy's ASN-DROP escalation rule (Spamhaus plus GreyNoise meet the two-source T2 evidence floor); no malware/C2 attribution yet.</t>
+          <t>UK-registered VPS provider whose AS215925 has been on Spamhaus ASN-DROP since at least Dec 2025. GreyNoise has carried it in its weekly brief since 2025-12-15; in the period to 2026-08-30 it produced 10,135,029 connection attempts in a 96-host proxy-scanning sweep. GreyNoise advises against an ASN-level block (shared tenancy). Announces 45.194.92.0/24 (on Spamhaus DROP) and 45.198.224.0/24; 45.205.1.0/24 left AS215925 on 2026-10-21 and has been originated by LARUS Limited (AS17561) since 2026-10-29. Added 2026-09-25 at T2 under the taxonomy's ASN-DROP escalation rule (Spamhaus plus GreyNoise meet the two-source T2 evidence floor); no malware/C2 attribution yet.</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
@@ -6164,7 +6169,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>62.60.131.0/24; 213.177.179.0/24; 213.209.159.0/24 (on Spamhaus DROP)</t>
+          <t>62.60.131.0/24 (not announced since 2026-10-23); 213.177.179.0/24; 213.209.159.0/24 - all three on Spamhaus DROP (2026-10-29)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6209,17 +6214,17 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>SPAMHAUS-ASNDROP-2026; GREYNOISE-WEEKLY-2026-08; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>SPAMHAUS-ASNDROP-2026; GREYNOISE-WEEKLY-2026-08; REGISTRY-SNAPSHOT-2026-09; REGISTRY-SNAPSHOT-2026-10</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Romanian provider on Spamhaus ASN-DROP (feoprest.info). GreyNoise (weekly brief to 2026-08-30): 40 active hosts; 213.209.159.175, carried since the 2026-06-22 brief, produced 1.8M sessions and 23% of CVE-2025-48927 exploitation attempts; 213.209.159.154 and .175 were top-volume ENV crawlers. Announces 62.60.131.0/24, 213.177.179.0/24 and 213.209.159.0/24 (the last on Spamhaus DROP). Added 2026-09-25 at T2 under the taxonomy's ASN-DROP escalation rule (Spamhaus plus GreyNoise meet the two-source T2 evidence floor); no malware/C2 attribution yet.</t>
+          <t>Romanian provider on Spamhaus ASN-DROP (feoprest.info). GreyNoise (weekly brief to 2026-08-30): 40 active hosts; 213.209.159.175, carried since the 2026-06-22 brief, produced 1.8M sessions and 23% of CVE-2025-48927 exploitation attempts; 213.209.159.154 and .175 were top-volume ENV crawlers. Announced 62.60.131.0/24 (withdrawn 2026-10-23), 213.177.179.0/24 and 213.209.159.0/24; all three are on Spamhaus DROP as of 2026-10-29. Added 2026-09-25 at T2 under the taxonomy's ASN-DROP escalation rule (Spamhaus plus GreyNoise meet the two-source T2 evidence floor); no malware/C2 attribution yet.</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
@@ -6491,6 +6496,165 @@
       <c r="Y72" t="inlineStr">
         <is>
           <t>Self-styled bulletproof VPS/RDP and fast-flux host; its .com domain moved to FBI seizure nameservers on the day of Operation Omegaline (Oct 2026); now on anonrdp.st and Blatant Technologies AS403005.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>TokenSpot CJSC</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>sanctioned</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>T1-Confirmed BPH (Financial Enabler)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Kyrgyzstan (Bishkek)</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kyrgyzstan / Russia</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>TokenSpot CJSC</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>TokenSpot; Grinex front (TRM)</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Grinex (shared operation, per TRM)</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>UK Oct 8 2026 (RUS3758, Russia regime; asset freeze and trust-services sanctions)</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Front company for a sanctioned exchange; Shared wallet infrastructure; Sanctions evasion</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Shared TRON deposit-aggregation and fee addresses with Grinex; Sanctioned entity</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>TRM-TOKENSPOT-2026; FCDO-UK-SANCTIONS-LIST; CHAINALYSIS-CRYPTOMUS-2026</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Kyrgyz exchange that TRM (2026-10-06) assesses with high confidence runs on shared wallet infrastructure with Grinex - two legal entities, one operation. A Grinex-listed deposit aggregator (TA8vyBg93KXaiQXV22WWXTB9hz3caN81DE, active 2026-02-05 to 2026-07-29) collected USD 146.3M from 126 TokenSpot deposit addresses; six TRON addresses and a TRX fee-collection address are shared. TokenSpot's TRON addresses received USD 3.54B and sent USD 3.14B (Dec 2023 - Sept 2026); A7, Grinex and Garantex are its largest counterparties. Two TokenSpot addresses were drained in the 2026-04-15 Grinex incident. The UK designated TokenSpot CJSC on 2026-10-08 alongside Cryptomus/Heleket (Xeltox Enterprises). T1 as a front of the T1 Grinex operation (same basis as the Aeza fronts); the UK designation itself is under the Russia regime, not the cyber regime.</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>Kyrgyz exchange assessed as a Grinex front; UK-designated Oct 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Xeltox Enterprises Ltd (Cryptomus / Heleket)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>sanctioned</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>T2-High Risk (Financial Enabler)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Canada (Vancouver address on the UK listing)</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Global; Russia-facing payment processing</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Xeltox Enterprises Ltd</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Cryptomus; Heleket; Certa Payments; cryptomus.com; heleket.com</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>UK Oct 8 2026 (RUS3755, Russia regime; asset freeze, trust-services and director-disqualification sanctions); FINTRAC (Canada) penalty Oct 2025</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Payments from Zservers, Stark Industries, First VPN, Aeza Group and Black Basta-linked funds (Chainalysis)</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Crypto payment processor for cybercrime infrastructure; Cybercrime-forum advertising; Rebranding (Cryptomus -&gt; Heleket)</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Sanctioned entity; Used as payment rail by tracked BPH providers</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>FCDO-UK-SANCTIONS-LIST; CHAINALYSIS-CRYPTOMUS-2026; TRM-TOKENSPOT-2026; KREBS-CRYPTOMUS-2026</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Crypto payment processor operating as Cryptomus and Heleket, designated by the UK on 2026-10-08 (entry for Xeltox Enterprises Ltd with name variations Certa Payments, Cryptomus and Heleket). Chainalysis: both brands received funds from more than 15,000 illicit actors and were 'payment rails of choice' for malicious-infrastructure vendors including Zservers, Stark Industries, First VPN and Aeza Group; use surged after Garantex fell. The Femo IT/Defhost row already records Heleket as its payment processor. Krebs (2026-10-14) reports that Heleket's support denies any Cryptomus affiliation. T2 (Financial Enabler): the UK designation is under the Russia regime rather than for cyber operations, and two B-grade vendors (Chainalysis, TRM) plus Krebs meet the T2 evidence floor; T1 would need a cyber-specific designation or a third independent vendor.</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>Cryptomus/Heleket crypto payment rail used by BPH providers; UK-designated Oct 2026.</t>
         </is>
       </c>
     </row>

--- a/BPH_Master.xlsx
+++ b/BPH_Master.xlsx
@@ -4601,7 +4601,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>UK May 2025 (A7) and Aug 20 2025 (Old Vector LLC); EU July 2025 (A7) and 19th package Oct 23 2025 (full A7A5 transaction ban from Nov 25 2025); OFAC Aug 14 2025 (Old Vector LLC, A7 LLC, A71 LLC, A7 Agent LLC); OFAC Oct 1 2026: whole A7 Network designated a significant transnational criminal organization (E.O. 13581; Operation Economic Outcast); FinCEN Oct 1 2026: section 9714(a) proposed rule against A7 Network Sub-Agents plus an Alert</t>
+          <t>UK May 2025 (A7) and Aug 20 2025 (Old Vector LLC); EU July 2025 (A7) and 19th package Oct 23 2025 (full A7A5 transaction ban from Nov 25 2025); EU 21st package Jul 23 2026 (four A7-network designations incl. A7 Nigeria and A7 Africa; transaction ban on 14 crypto platforms); OFAC Aug 14 2025 (Old Vector LLC, A7 LLC, A71 LLC, A7 Agent LLC); OFAC Oct 1 2026: whole A7 Network designated a significant transnational criminal organization (E.O. 13581; Operation Economic Outcast); FinCEN Oct 1 2026: section 9714(a) proposed rule against A7 Network Sub-Agents plus an Alert</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>OFAC-GARANTEX; CHAINALYSIS-A7A5; TRM-A7A5-2026; OFAC-A7-NETWORK-2026</t>
+          <t>OFAC-GARANTEX; CHAINALYSIS-A7A5; TRM-A7A5-2026; OFAC-A7-NETWORK-2026; EU-21ST-PACKAGE; TRM-EU21-2026; CRYPTOPOLITAN-A7A5-2026; ALJAZEERA-YANDEX-2026</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Russian ruble-backed stablecoin issued by Kyrgyzstan's Old Vector; A7 LLC is the token's creator. Chainalysis (2026 Crypto Crime Report): $93.3B moved 'in less than a year'; Elliptic: more than $100B in under a year (the $93.1B and $72B figures elsewhere are earlier snapshots). Garantex moved funds into A7A5 from as early as January 2025 (TRM). The no-KYC Instant Swapper reportedly converted &gt;$2.2B of A7A5 into mainstream USD stablecoins (unverified). The EU banned A7A5 transactions from 2025-11-25. Its economy ran through Grinex, and on-chain volume reportedly collapsed after Grinex suspended in April 2026 (the '~96%' decline figure is attributed to Elliptic in secondary reporting). On 2026-10-01 Treasury designated the whole A7 Network as a transnational criminal organization: its Sub-Agents processed more than $17B (Jan 2025-Jun 2026) and 'catered to cybercriminals, including ransomware' actors, and the network is linked to Nobitex and to North Korean hacks; FinCEN proposed cutting Sub-Agents off from US transmittals (rule not yet final). A7 LLC, A71 LLC and A7 Agent LLC are separately designated related entities, not aliases.</t>
+          <t>Russian ruble-backed stablecoin issued by Kyrgyzstan's Old Vector; A7 LLC is the token's creator. Chainalysis (2026 Crypto Crime Report): $93.3B moved 'in less than a year'; Elliptic: more than $100B in under a year (the $93.1B and $72B figures elsewhere are earlier snapshots). Garantex moved funds into A7A5 from as early as January 2025 (TRM). The no-KYC Instant Swapper reportedly converted &gt;$2.2B of A7A5 into mainstream USD stablecoins (unverified). The EU banned A7A5 transactions from 2025-11-25. Its economy ran through Grinex, and on-chain volume reportedly collapsed after Grinex suspended in April 2026 (the '~96%' decline figure is attributed to Elliptic in secondary reporting). On 2026-10-01 Treasury designated the whole A7 Network as a transnational criminal organization: its Sub-Agents processed more than $17B (Jan 2025-Jun 2026) and 'catered to cybercriminals, including ransomware' actors, and the network is linked to Nobitex and to North Korean hacks; FinCEN proposed cutting Sub-Agents off from US transmittals (rule not yet final). Ukrainian drone strikes on Yandex data centres (Sasovo, 2026-10-08, and Kaluga the same week) disrupted A7A5's exchange service, which Elliptic's Tom Robinson says is hosted there: crypto press citing Robinson and Etherscan/Tronscan data report daily transfers falling from about 600 to about 61, mostly DEX swaps, and holders unpaid interest since 2026-10-09 (Elliptic's own write-up not read; figures C-grade). A7 LLC, A71 LLC and A7 Agent LLC are separately designated related entities, not aliases.</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Recorded Future/Insikt: major Chinese-language guarantee (danbao) Telegram marketplace resembling the defunct Huione Guarantee, with thousands of thematic channels (overseas phishing, laundering, 'sweeping' goods in Japan and South Korea) and a search bot. The RF report appears to date from about April 2026 (the relaying digest is dated 2026-04-23), not February. Reported emergence ~Dec 2024 and ~19,225 members in its largest group are unverified. Flare counts more than 30 marketplaces that emerged after Huione Guarantee ceased operations in May 2025; Xinbi (disrupted by the US on 2026-09-09) is the largest of the successors.</t>
+          <t>Recorded Future/Insikt: major Chinese-language guarantee (danbao) Telegram marketplace resembling the defunct Huione Guarantee, with thousands of thematic channels (overseas phishing, laundering, 'sweeping' goods in Japan and South Korea) and a search bot. The RF report appears to date from about April 2026 (the relaying digest is dated 2026-04-23), not February. RF says Dabai was likely founded in December 2024 (based on its Telegram channel's creation date) and counted 19,225 members in its 'Dabai Guarantee Big Group' (@dabai_c) at the time of writing (verified 2026-10-30). Flare counts more than 30 marketplaces that emerged after Huione Guarantee ceased operations in May 2025; Xinbi (disrupted by the US on 2026-09-09) is the largest of the successors.</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Huione / Haowang Guarantee (announced a stake in Dec 2024; 30% figure unverified)</t>
+          <t>Huione / Haowang Guarantee (announced a stake in Dec 2024; 30% stake per Elliptic)</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Huione's designated successor: in December 2024 Haowang (ex-Huione) Guarantee announced it was buying a stake in Tudou (FinCEN; the 30% figure is unverified). Processed &gt;$12B - the third-largest illicit marketplace ever (Elliptic). In January 2026, after Prince Group chairman Chen Zhi was arrested in Cambodia and extradited to China (reported 2026-01-07), Tudou effectively ceased transactions through its public Telegram groups and admin-wallet activity collapsed; gambling operations continue and Elliptic says it remains to be seen whether this is a full shutdown or a pivot. Status corrected dissolved -&gt; flagged on 2026-09-25 (no legal dissolution documented).</t>
+          <t>Huione's designated successor: in December 2024 Haowang (ex-Huione) Guarantee announced it was buying a stake in Tudou (FinCEN; Elliptic gives the size as a 30% stake, acquired by Huione Guarantee in December 2024 - verified 2026-10-30). Processed &gt;$12B - the third-largest illicit marketplace ever (Elliptic). In January 2026, after Prince Group chairman Chen Zhi was arrested in Cambodia and extradited to China (reported 2026-01-07), Tudou effectively ceased transactions through its public Telegram groups and admin-wallet activity collapsed; gambling operations continue and Elliptic says it remains to be seen whether this is a full shutdown or a pivot. Status corrected dissolved -&gt; flagged on 2026-09-25 (no legal dissolution documented).</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">

--- a/BPH_Master.xlsx
+++ b/BPH_Master.xlsx
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>United States (incorporated; Wyoming unverified)</t>
+          <t>United States (Wyoming; registered under a registered-agent lawyer per CyberScoop/Halcyon)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2964,17 +2964,17 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>OSINT-REVIEWS; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>OSINT-REVIEWS; REGISTRY-SNAPSHOT-2026-09; REGISTRY-SNAPSHOT-2026-10</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Dutch hoster (reported address Keteldiep 15, Urk) rebranded from Flaunt7. AS49042 was historically 'Phanes Networks B.V.' and is now absent from the registry and routing data. Silent Push reports 'bulletproof' in Phanes' marketing and a 4-day abuse response; Trustpilot reviews document unresponsive handling of phishing complaints. SpectraIP is its peering partner, not an alias. SKB Enterprise B.V. held a separate ASN (AS64425) and its relationship to Phanes is unverified.</t>
+          <t>Dutch hoster (reported address Keteldiep 15, Urk) rebranded from Flaunt7. AS49042 was historically 'Phanes Networks B.V.' and is now absent from the registry and routing data. Silent Push reports 'bulletproof' in Phanes' marketing and a 4-day abuse response; Trustpilot reviews document unresponsive handling of phishing complaints. SpectraIP is its peering partner, not an alias. SKB Enterprise B.V. held a separate ASN (AS64425, now unregistered): routing history shows AS64425 announcing 45.148.120.0/24 and 45.148.123.0/24 until 2023-04-28 and Phanes' AS49042 announcing the same prefixes from 2023-04-17, with both ASNs going silent in Sept 2025 - the two carried the same address space (RIPEstat, checked 2026-10-30).</t>
         </is>
       </c>
     </row>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Switzerland (claimed; unverified); aurologic-transited</t>
+          <t>Switzerland claimed only by the SWISSNETWORK name - no registry or geolocation evidence (its former /22s geolocated to DE, GB, FR, KZ, US, RU, UZ and UA, and have since been returned); aurologic-transited</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -5441,6 +5441,11 @@
           <t>T1-Confirmed BPH</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AS206336 (Datavice; registered to DATAVICE MCHJ [UZ] since 2025-07-18; no routes)</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
           <t>Uzbekistan</t>
@@ -5493,17 +5498,17 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>OFAC-MEDIALAND</t>
+          <t>OFAC-MEDIALAND; REGISTRY-SNAPSHOT-2026-10</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Uzbekistan-registered (Tashkent) Aeza expansion entity. OFAC SDN record: established 2025-07-03; Tax ID 312252645; Business Registration 2868352; address 3 Irrigator Massive, Hamid Olimjon MFY, Tashkent; programs CYBER4 and CAATSA-RUSSIA; 'Linked To: AEZA GROUP LLC'. Designated 2025-11-19 alongside Hypercore Ltd, Smart Digital Ideas DOO, Maksim Makarov and Ilya Zakirov; absent from the UK's 19 Nov 2025 notices (OFAC-only). No ASN is stated in the designation; the registry lists a dark AS206336 as 'DATAVICE MCHJ', but per-ASN metadata still shows a previous holder, so treat it as an unverified lead.</t>
+          <t>Uzbekistan-registered (Tashkent) Aeza expansion entity. OFAC SDN record: established 2025-07-03; Tax ID 312252645; Business Registration 2868352; address 3 Irrigator Massive, Hamid Olimjon MFY, Tashkent; programs CYBER4 and CAATSA-RUSSIA; 'Linked To: AEZA GROUP LLC'. Designated 2025-11-19 alongside Hypercore Ltd, Smart Digital Ideas DOO, Maksim Makarov and Ilya Zakirov; absent from the UK's 19 Nov 2025 notices (OFAC-only). No ASN is stated in the designation, but the RIPE database assigns AS206336 to DATAVICE MCHJ (ORG-DM279-RIPE, Tashkent; aut-num re-created 2025-07-18, fifteen days after the company was established). Datavice is its own LIR (lir-uz-datavice-1-MNT), and its org object lists aeza-mnt among its referenced maintainers - a direct registry tie to Aeza. AS206336 has announced nothing since the re-registration (its 2017-2023 routing history belongs to a previous holder) and is not on Spamhaus ASN-DROP (checked 2026-10-30).</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -5759,17 +5764,17 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>CV-GSHELL-2026-07; CV-OPENDIR-2026-09; GREYNOISE-REACT2SHELL-2026; C2INTELFEEDS; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>CV-GSHELL-2026-07; CV-OPENDIR-2026-09; GREYNOISE-REACT2SHELL-2026; C2INTELFEEDS; REGISTRY-SNAPSHOT-2026-09; REGISTRY-SNAPSHOT-2026-10</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>AS400619 is registered to AROSSCLOUD INC. (US) and originates 70 IPv4 prefixes (191,744 addresses), including 103.112.96.0/22 which covers the tracked 103.112.97.0/24; SHANGXING TECH LIMITED itself holds AS136452 and AS151468 (HK; neither announced), so the row name most likely reflects the inetnum holder while AROSSCLOUD owns the origin ASN (APNIC inetnum not yet confirmed). AS400619 and Fastmos (AS138644) tile 191.124.0.0/16 exactly between them - strong registry evidence of a shared reseller relationship. Hosts the July 2026 unreported Gshell C2 cluster (103.112.97.163/.199) and a Sept 2026 mass web-exploitation workspace (Fastmos :8889 - gen_targets/CVE-PoC/Java-memshell RCE-verify/k8s scan, 283KB target list) plus a second exploit box (AROSSCLOUD :9999) - first-party CrimsonVector open-directory hunts. Public corroboration: GreyNoise lists AS400619 among React2Shell exploitation sources (Jan 2026); C2IntelFeeds recorded Cobalt Strike C2s on AROSSCLOUD addresses (Aug-Sep 2026); community RAT feeds list several 103.112.97.x hosts. PEG TECH INC and 'AS Data HK' links are unverified.</t>
+          <t>AS400619 is registered to AROSSCLOUD INC. (US) and originates 70 IPv4 prefixes (191,744 addresses), including 103.112.96.0/22 which covers the tracked 103.112.97.0/24; SHANGXING TECH LIMITED itself holds AS136452 and AS151468 (HK; neither announced), so the row name most likely reflects the inetnum holder while AROSSCLOUD owns the origin ASN (confirmed: APNIC's record for 103.112.97.0/24, registered 2025-12-16, carries the name AROSS-AS with SHANGXING TECH LIMITED, Kwai Chung, Hong Kong, as administrative and technical contact). AS400619 and Fastmos (AS138644) tile 191.124.0.0/16 exactly between them - strong registry evidence of a shared reseller relationship. Hosts the July 2026 unreported Gshell C2 cluster (103.112.97.163/.199) and a Sept 2026 mass web-exploitation workspace (Fastmos :8889 - gen_targets/CVE-PoC/Java-memshell RCE-verify/k8s scan, 283KB target list) plus a second exploit box (AROSSCLOUD :9999) - first-party CrimsonVector open-directory hunts. Public corroboration: GreyNoise lists AS400619 among React2Shell exploitation sources (Jan 2026); C2IntelFeeds recorded Cobalt Strike C2s on AROSSCLOUD addresses (Aug-Sep 2026); community RAT feeds list several 103.112.97.x hosts. The earlier PEG TECH INC and 'AS Data HK' links were removed on 2026-10-30: neither appears among AS400619's neighbours or in the routing history of 103.112.96.0/22.</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
@@ -6040,17 +6045,17 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>INTRINSEC-BTHOSTER; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09; LES-VIRTUALINE-2026</t>
+          <t>INTRINSEC-BTHOSTER; SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09; LES-VIRTUALINE-2026; REGISTRY-SNAPSHOT-2026-10</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Lithuanian hoster named by Intrinsec (June 2025) as a transit provider of the BtHoster/BTCloud AS-leasing operation (see the BtHoster row). Spamhaus ASN-DROP lists AS209605 (serveroffer.lt; 6 announced prefixes including 141.98.8.0/22 and 185.36.81.0/24, 5 of them overlapping Spamhaus DROP) and a newly listed Hong Kong sibling, AS135388 'RPL-HK' (RMP Protection Limited; 93.152.223.0/24 and 94.26.0.0/24). A second Host Baltic registration, AS211872 'ALPHA-NETWORKS', has no routes. Added 2026-09-25 as an upstream enabler (ASN-DROP inclusion plus upstream of a T1 entity, two independent sources). Oct 2026: a community post says AnonRDP's Lithuanian 'bulletproof' servers (see the AnonRDP / Blatant Technologies row) are hosted here and tunnelled through SMARTNET Germany - unconfirmed.</t>
+          <t>Lithuanian hoster named by Intrinsec (June 2025) as a transit provider of the BtHoster/BTCloud AS-leasing operation (see the BtHoster row). Spamhaus ASN-DROP lists AS209605 (serveroffer.lt; 6 announced prefixes including 141.98.8.0/22 and 185.36.81.0/24, 5 of them overlapping Spamhaus DROP) and a newly listed Hong Kong sibling, AS135388 'RPL-HK' (RMP Protection Limited; 93.152.223.0/24 and 94.26.0.0/24). A second Host Baltic registration, AS211872 'ALPHA-NETWORKS', has no routes. Added 2026-09-25 as an upstream enabler (ASN-DROP inclusion plus upstream of a T1 entity, two independent sources). Oct 2026: a community post says AnonRDP's Lithuanian 'bulletproof' servers (see the AnonRDP / Blatant Technologies row) are hosted here and tunnelled through SMARTNET Germany - unconfirmed (none of AS403005's prefixes geolocate to Lithuania; checked 2026-10-30).</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
@@ -6480,7 +6485,7 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
@@ -6490,7 +6495,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Self-styled 'bulletproof anonymous hosting' provider selling crypto-paid VPS/RDP, dedicated and web hosting, 'scanning' servers and a FastFlux CDN advertised as 'Spamhaus Ignored' (anonrdp.com registered 2023-10-04). Network lineage: Intrinsec (May 2026) found March 2026 malspam - a JavaScript backdoor aimed at CIS energy and finance ministries - sent from and controlled via the bulletproof US network GHOSTYNETWORKS (AS205759, Kentucky, registered Jan 2026), which it linked to the OPTIBOUNCE network previously tied to AnonRDP; Silent Push (Oct 2026) calls GHOSTYNETWORKS a shell company of AnonRDP and found the same four SPF addresses on anonrdp.com (Feb-Apr 2026) and ghostynetworks.com. AS205759 has since been deregistered. Current network: CrimsonVector DNS checks (2026-10-29) show solusvm.anonrdp.st and xmpp.anonrdp.st resolving into AS403005 (Blatant Technologies, LLC; ARIN-registered 2026-09-25, Seychelles registrant, Louisville KY contacts), and smtp/smtp01.anonrdp.st resolving to two of the ghostynetworks.com SPF addresses. AS403005 announces nine /24s, all on Spamhaus DROP, through a single upstream, SMARTNET Germany (AS203446); Spamhaus lists the ASN under blatant.host. A community post says the Lithuanian servers sit with UAB Host Baltic (AS209605, tracked here) - unconfirmed. Enforcement: on 2026-10-27, the day of the Virtualine seizure, the registry record for anonrdp.com was pointed at FBI seizure nameservers (13:13 UTC); no seizure page or DOJ statement had appeared by 2026-10-29. That day AnonRDP offered Virtualine customers a 'refugee offer' (it had also run a 'crazyrdp' promo code on 2025-11-15, days after the CrazyRDP seizure); on 2026-10-28 it moved to anonrdp.st, said a 'trusted source' warned it could be next, and said it had triggered an 'emergency kill switch' and was moving datacentres. Backup domains: anonrdp.net and an .onion address. Tier T1 (added 2026-10-29): LE domain seizure plus self-advertised bulletproof hosting with corroborating infrastructure, on Silent Push and Intrinsec (B) and registry/Spamhaus data (C). Status 'seized' covers the domain only - the operation is still running from anonrdp.st, so expect further ASN and prefix moves.</t>
+          <t>Self-styled 'bulletproof anonymous hosting' provider selling crypto-paid VPS/RDP, dedicated and web hosting, 'scanning' servers and a FastFlux CDN advertised as 'Spamhaus Ignored' (anonrdp.com registered 2023-10-04). Network lineage: Intrinsec (May 2026) found March 2026 malspam - a JavaScript backdoor aimed at CIS energy and finance ministries - sent from and controlled via the bulletproof US network GHOSTYNETWORKS (AS205759, Kentucky, registered Jan 2026), which it linked to the OPTIBOUNCE network previously tied to AnonRDP; Silent Push (Oct 2026) calls GHOSTYNETWORKS a shell company of AnonRDP and found the same four SPF addresses on anonrdp.com (Feb-Apr 2026) and ghostynetworks.com. AS205759 has since been deregistered. Current network: CrimsonVector DNS checks (2026-10-29) show solusvm.anonrdp.st and xmpp.anonrdp.st resolving into AS403005 (Blatant Technologies, LLC; ARIN-registered 2026-09-25, Seychelles registrant, Louisville KY contacts), and smtp/smtp01.anonrdp.st resolving to two of the ghostynetworks.com SPF addresses. AS403005 announces nine /24s, all on Spamhaus DROP, through a single upstream, SMARTNET Germany (AS203446); Spamhaus lists the ASN under blatant.host. The RIPE record for one of AS403005's /24s, 46.151.182.0/24 (netname Ghosty-24, created 2026-09-13), is maintained by GHOSTYNETWORKS-MNT for Ghosty Networks LLC (Scottsville, Kentucky) - a direct registry link between Blatant's network and GHOSTYNETWORKS; 31.56.19.0/24 is registered as BLATANT-NET to a Seychelles org. A community post says the Lithuanian servers sit with UAB Host Baltic (AS209605, tracked here); none of AS403005's prefixes geolocate to Lithuania, so this stays unconfirmed. Enforcement: on 2026-10-27, the day of the Virtualine seizure, the registry record for anonrdp.com was pointed at FBI seizure nameservers (13:13 UTC); no seizure page or DOJ statement had appeared by 2026-10-29. That day AnonRDP offered Virtualine customers a 'refugee offer' (it had also run a 'crazyrdp' promo code on 2025-11-15, days after the CrazyRDP seizure); on 2026-10-28 it moved to anonrdp.st, said a 'trusted source' warned it could be next, and said it had triggered an 'emergency kill switch' and was moving datacentres. Backup domains: anonrdp.net and an .onion address. Tier T1 (added 2026-10-29): LE domain seizure plus self-advertised bulletproof hosting with corroborating infrastructure, on Silent Push and Intrinsec (B) and registry/Spamhaus data (C). Status 'seized' covers the domain only - the operation is still running from anonrdp.st, so expect further ASN and prefix moves.</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">

--- a/BPH_Master.xlsx
+++ b/BPH_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y74"/>
+  <dimension ref="A1:Y80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -767,7 +767,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>OFAC designated Aeza Group LLC and its UK front Aeza International Ltd on 2025-07-01 (coordinated with the UK NCA) for hosting Meduza and Lumma infostealer operators, BianLian and the BlackSprut market. The TRON address TU4tDFRvcKhAZ1jdihojmBWZqvJhQCnJ4F sits on the Aeza Group LLC SDN entry. Owners Penzev and Bozoyan and two staff were detained by Russian authorities in early April 2025 (a Russian drug-market case, not a Western action). Evasion: 2,100+ IPs moved to the UK front Hypercore (AS211522) from 2025-07-20; Serbian (Smart Digital Ideas DOO) and Uzbek (Datavice MCHJ) vehicles followed - all OFAC-designated 2025-11-19. Sanctions have not ended operational use: AS210644 still announces 176 IPv4 prefixes; Arctic Wolf (Aug 2026) found 23 of 24 Dark Caracal GoCaracal C2s on Aeza networks and Huntress (Aug 2026) traced a ClickFix macOS crypto-drainer's staging and C2 to Aeza. Spamhaus now also lists AS203273 (NetCrafters OU, EE) under aeza.net. Roughly half of Aeza's prefixes transited aurologic AS30823 as of Nov 2025. Qurium (2026-10-14): on 2026-09-22 Aeza's two ASNs and NetCrafters (AS203273) originated 536 IPv4 /24s (137,216 addresses; 418 on Aeza's ASNs, 118 on NetCrafters) drawn from 42 LIRs, and aurologic (AS30823) was still one of AS210644's upstreams - two rounds of sanctions had 'no real impact' on its access to address space. Infoblox (Feb 2026, via Hackread): rogue DNS resolvers and a traffic distribution system behind a DNS-hijacking campaign against old home routers in 30+ countries were hosted by Aeza International. Chainalysis (Oct 2026) names Cryptomus/Heleket as an Aeza payment rail. The UK company Aeza International Ltd was dissolved on 2026-03-24; the RIPE org behind AS210644 is AEZA GROUP LLC.</t>
+          <t>OFAC designated Aeza Group LLC and its UK front Aeza International Ltd on 2025-07-01 (coordinated with the UK NCA) for hosting Meduza and Lumma infostealer operators, BianLian and the BlackSprut market. The TRON address TU4tDFRvcKhAZ1jdihojmBWZqvJhQCnJ4F sits on the Aeza Group LLC SDN entry. Owners Penzev and Bozoyan and two staff were detained by Russian authorities in early April 2025 (a Russian drug-market case, not a Western action). Evasion: 2,100+ IPs moved to the UK front Hypercore (AS211522) from 2025-07-20; Serbian (Smart Digital Ideas DOO) and Uzbek (Datavice MCHJ) vehicles followed - all OFAC-designated 2025-11-19. Sanctions have not ended operational use: AS210644 still announces 176 IPv4 prefixes; Arctic Wolf (Aug 2026) found 23 of 24 Dark Caracal GoCaracal C2s on Aeza networks and Huntress (Aug 2026) traced a ClickFix macOS crypto-drainer's staging and C2 to Aeza. Spamhaus now also lists AS203273 (NetCrafters OU, EE) under aeza.net. Roughly half of Aeza's prefixes transited aurologic AS30823 as of Nov 2025. Qurium (2026-10-14): on 2026-09-22 Aeza's two ASNs and NetCrafters (AS203273) originated 536 IPv4 /24s (137,216 addresses; 418 on Aeza's ASNs, 118 on NetCrafters) drawn from 42 LIRs, and aurologic (AS30823) was still one of AS210644's upstreams - two rounds of sanctions had 'no real impact' on its access to address space. Infoblox (Feb 2026, via Hackread): rogue DNS resolvers and a traffic distribution system behind a DNS-hijacking campaign against old home routers in 30+ countries were hosted by Aeza International. Chainalysis (Oct 2026) names Cryptomus/Heleket as an Aeza payment rail. The UK company Aeza International Ltd was dissolved on 2026-03-24; the RIPE org behind AS210644 is AEZA GROUP LLC. Qurium's supplier breakdown (Oct 2026, single source): about two-thirds of the Aeza/NetCrafters estate comes from eleven LIRs, including Andwase Limited (BVI; tracked as a T5 row), Prostie Reshenia (Armenia; T5 row), Technology Enriched Company FZCO (UAE; 27 of 32 /24s in the upper half of 77.110.64.0/18 tied to Aeza), Axiom Asia Services (Singapore), Plant Holding (Switzerland; Aeza assignment objects re-modified in March and June 2026), RapidSeedbox (a commercial IP lessor; 17+ /24s originated by Aeza ASNs) and IROST (Iran; about 9%). None of these is on Spamhaus DROP or ASN-DROP; only Andwase and Prostie Reshenia are tracked as rows.</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>T2-High Risk</t>
+          <t>T1-Confirmed BPH</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1841,17 +1841,17 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>GCSAS; Global Connectivity Solutions (GCS); sister company Global Internet Solutions LLC (GIR, AS207713); FourVPS / 4VPS (brand, per eSentire)</t>
+          <t>GCSAS; Global Connectivity Solutions (GCS); sister company Global Internet Solutions LLC (GIR, AS207713); 4VPS / 4vps.su / FourVPS (brand fronted by GCS and GIR, per Intrinsec, eSentire and RF)</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gamaredon (C2 hosting, 2023); SilkParasite (SpiceRAT C2, 2026 - IP-to-ASN mapping); UAC-linked activity (Intrinsec); Storm-1575 (DadSec/Phoenix/Rockstar 2FA PhaaS; eSentire, moderate confidence)</t>
+          <t>Gamaredon / UAC-0010 (C2 hosting, 2023); UAC-0050 (Remcos C2); UAC-0006 (SmokeLoader C2); Black Basta and Cactus (BackConnect C2, 2025); RansomHub (C2, per GuidePoint via Intrinsec); NoName057(16) (DDoSia C2; RF); SilkParasite (SpiceRAT C2, 2026); Storm-1575 (DadSec/Phoenix/Rockstar 2FA PhaaS; eSentire, moderate confidence); Russian state-sponsored groups (RF, 4VPS cluster)</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Gamaredon tooling; SpiceRAT</t>
+          <t>Gamaredon tooling; SpiceRAT; Remcos; SmokeLoader; BackConnect (QBACKCONNECT); DDoSia</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1874,14 +1874,19 @@
           <t>2026-10-30</t>
         </is>
       </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>RF 2025 top-10 (#7, as 4VPS - AS215540 with GIR AS207713)</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>GBHACKERS-BPH; ESET-GAMAREDON-IOC; INTRINSEC-UAC-2025; HUNTIO-SILKPARASITE-2026; REGISTRY-SNAPSHOT-2026-09; INTRINSEC-FDN3-2025; REGISTRY-SNAPSHOT-2026-10; UK-COMPANIES-HOUSE; ESENTIRE-GCS-2024; SOPHOS-VMMANAGER; QURIUM-AEZA-2026</t>
+          <t>GBHACKERS-BPH; ESET-GAMAREDON-IOC; INTRINSEC-UAC-2025; HUNTIO-SILKPARASITE-2026; REGISTRY-SNAPSHOT-2026-09; INTRINSEC-FDN3-2025; REGISTRY-SNAPSHOT-2026-10; UK-COMPANIES-HOUSE; ESENTIRE-GCS-2024; SOPHOS-VMMANAGER; QURIUM-AEZA-2026; TRENDMICRO-BACKCONNECT-2025; RF-INFRA-2025; RF-DDOSIA-2025; ESENTIRE-TEAMS-2026</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>UK LLP operating AS215540: 181 IPv4 prefixes / 62,720 addresses plus 24 IPv6 prefixes (2026-09-25; the earlier '~176 / ~41K' is outdated). ESET lists Gamaredon infrastructure on GCSAS addresses first seen Aug-Sep 2023. Intrinsec named GCSAS in its March 2025 UAC-infrastructure report and in Aug 2025 among shell-fronted networks announcing prefixes moved out of the FDN3 cluster. A SpiceRAT C2 active in March 2026 (Hunt.io, SilkParasite campaign; 171.22.16.187) maps to AS215540 by our own IP-to-ASN lookup. Status raised suspected -&gt; flagged (two independent B-grade sources). Companies House confirms LLP OC450701 (incorporated 2024-01-19), filing dormant-entity accounts while operating AS215540. eSentire (Dec 2024): addresses of GCS and its sister company Global Internet Solutions (GIR, AS207713), which share a person with significant control, produced 64% of its Entra ID account-compromise detections, a subset tied with moderate confidence to Storm-1575; eSentire links both to the 4VPS brand. Sophos (Feb 2026) lists Global Connectivity Solutions among the top hosts of the reused ISPsystem VM hostnames. Qurium (Oct 2026) finds GCS and GIR repeatedly relaying prefixes into and out of Aeza networks. Unverified and retained with caution: Black Basta/Cactus C2 routing via Stark AS44477. Not on Spamhaus ASN-DROP at the 2026-09-25 audit; listed under globconnex.com by 2026-10-29.</t>
+          <t>UK LLP operating AS215540: 181 IPv4 prefixes / 62,720 addresses plus 24 IPv6 prefixes (2026-09-25; the earlier '~176 / ~41K' is outdated). ESET lists Gamaredon infrastructure on GCSAS addresses first seen Aug-Sep 2023. Intrinsec named GCSAS in its March 2025 UAC-infrastructure report and in Aug 2025 among shell-fronted networks announcing prefixes moved out of the FDN3 cluster. A SpiceRAT C2 active in March 2026 (171.22.16.187) is listed by Hunt.io itself under 'Global Connectivity Solutions' (SilkParasite campaign). Status raised suspected -&gt; flagged (two independent B-grade sources). Companies House confirms LLP OC450701 (incorporated 2024-01-19), filing dormant-entity accounts while operating AS215540. eSentire (Dec 2024): addresses of GCS and its sister company Global Internet Solutions (GIR, AS207713), which share a person with significant control, produced 64% of its Entra ID account-compromise detections, a subset tied with moderate confidence to Storm-1575; eSentire links both to the 4VPS brand. Sophos (Feb 2026) lists Global Connectivity Solutions among the top hosts of the reused ISPsystem VM hostnames. Qurium (Oct 2026) finds GCS and GIR repeatedly relaying prefixes into and out of Aeza networks. Trend Micro (Mar 2025) listed Black Basta/Cactus BackConnect C2s 5.181.3.164, 89.185.80.86 and 89.185.80.251; Intrinsec (Mar 2025) mapped them to AS215540, called GCS and GIR 'legal fronts for the bulletproof hosting provider 4vps.su', noted that GCS shares its two Seychelles LLP officers with sanctioned Zservers and that 61% of its peerings were shared with Stark (AS44477), and added RansomHub C2s; all three IPs still originate from AS215540 (RIPEstat 2026-10-30). Intrinsec's Aug 2025 FDN3 report calls GCS-AS 'a known Russian bulletproof hosting provider ... managed by the same Russian individual as gir.network (AS207713)'. Recorded Future ranks 4VPS (AS215540 plus GIR AS207713) #7 in its 2025 Threat Density top 10 and names 'TAE 4VPS (Global Connectivity Solutions LLP, AS215540)' among infrastructure used by Russian state-sponsored groups; its DDoSia analysis (July 2025) puts GCS third among hosts of NoName057(16) Tier-1 C2s (6%). eSentire (Apr 2026) names GCS among the 'bulletproof hosting providers' behind Teams IT-impersonation phishing. Tier T2 -&gt; T1 on 2026-10-30 (taxonomy T1: RF top-decile Threat Density, and three independent B-grade vendors - Intrinsec, eSentire, RF - classify it as BPH/TAE with named malware or actors). Not on Spamhaus ASN-DROP at the 2026-09-25 audit; listed under globconnex.com by 2026-10-29.</t>
         </is>
       </c>
     </row>
@@ -1958,17 +1963,17 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>HYAS-RISEPRO; RF-AUROLOGIC; REGISTRY-SNAPSHOT-2026-09; INTRINSEC-UAC-2025</t>
+          <t>HYAS-RISEPRO; RF-AUROLOGIC; REGISTRY-SNAPSHOT-2026-09; INTRINSEC-UAC-2025; REGISTRY-SNAPSHOT-2026-10</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Individual-registered RIPE network (2024) behind aurologic that HYAS (Apr 2024) flagged for RisePro stealer C2 (147.45.47.93); Intrinsec (via a third party) ties AS215789 to Virtualine's UAC-0050 spam. AS215789 has since been returned and re-issued to BLIK / Polski Standard Platnosci SA (PL), which announces nothing from it - do not block AS215789. Its former prefixes now originate from SYSECT D.O.O. (AS202799, ME) and PSB Hosting Ltd (AS214927, on Spamhaus ASN-DROP under psb.hosting) - successor-watch leads, not attribution. Status set to 'dissolved' (registration defunct) on 2026-09-25. Unverified: the exact 2024-01-03 date and the '2223 domains across 72 IPs' figure.</t>
+          <t>Individual-registered RIPE network (2024) behind aurologic that HYAS (Apr 2024) flagged for RisePro stealer C2 (147.45.47.93); Intrinsec (via a third party) ties AS215789 to Virtualine's UAC-0050 spam. AS215789 has since been returned and re-issued to BLIK / Polski Standard Platnosci SA (PL), which announces nothing from it - do not block AS215789. Its former prefixes now originate from SYSECT D.O.O. (AS202799, ME) and PSB Hosting Ltd (AS214927, on Spamhaus ASN-DROP under psb.hosting) - successor-watch leads, not attribution. Status set to 'dissolved' (registration defunct) on 2026-09-25. RIPE NCC delegated statistics show AS215789 allocated to the Ukrainian holder on 2024-01-03 and re-allocated to Poland on 2025-12-01. The earlier '2223 domains across 72 IPs' figure could not be traced to any source and was removed (2026-10-30).</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2445,12 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>RF-AUROLOGIC; RF-TAE-2026; REGISTRY-SNAPSHOT-2026-09; REGISTRY-SNAPSHOT-2026-10</t>
+          <t>RF-AUROLOGIC; RF-TAE-2026; REGISTRY-SNAPSHOT-2026-09; REGISTRY-SNAPSHOT-2026-10; INTERISLE-DROP-2026</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Central upstream for Europe's high-risk hosting ecosystem. RF: formed in 2023 following the transition of combahton GmbH's fastpipe (combahton announced the transition in Nov 2023); multi-terabit backbone at Tornado Datacenter, Langen. RF's 2025 review says it transits about 70% of the most prominent high-risk TAE networks, and ~50% of Aeza's announced prefixes ran via aurologic (Nov 2025). Downstreams named by RF: Femo IT/Defhost, Global-Data (SWISSNETWORK02), the metaspinner-named front, Railnet/Virtualine and Aeza; Qurium adds Tnsecurity, WAIcore and Altawk. Corrections 2026-09-25: the 'top-10 globally' ranking belongs to SWISSNETWORK02, not aurologic; the '1-5 Tbps' figure is unsourced; KPROHOST is not an aurologic downstream. Several named downstreams have since gone dark or had their ASNs re-issued.</t>
+          <t>Central upstream for Europe's high-risk hosting ecosystem. RF: formed in 2023 following the transition of combahton GmbH's fastpipe (combahton announced the transition in Nov 2023); multi-terabit backbone at Tornado Datacenter, Langen. RF's 2025 review says it transits about 70% of the most prominent high-risk TAE networks, and ~50% of Aeza's announced prefixes ran via aurologic (Nov 2025). Downstreams named by RF: Femo IT/Defhost, Global-Data (SWISSNETWORK02), the metaspinner-named front, Railnet/Virtualine and Aeza; Qurium adds Tnsecurity, WAIcore and Altawk. Corrections 2026-09-25: the 'top-10 globally' ranking belongs to SWISSNETWORK02, not aurologic; the '1-5 Tbps' figure is unsourced; KPROHOST is not an aurologic downstream. Several named downstreams have since gone dark or had their ASNs re-issued. Interisle (Aug 2026, AI-assisted, grade C) also flagged NEON CORE NETWORK LLC (AS205775) as an aurologic peer with high phishing and spam counts; AS205775 has since been deregistered (no RIPE aut-num, nothing announced since 2026-09-05), so it is not tracked as a row.</t>
         </is>
       </c>
     </row>
@@ -2512,17 +2517,17 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>OFAC-GARANTEX; CHAINALYSIS-OFAC; CHAINALYSIS-BPH; DOJ-GARANTEX-2025</t>
+          <t>OFAC-GARANTEX; CHAINALYSIS-OFAC; CHAINALYSIS-BPH; DOJ-GARANTEX-2025; KHARON-MKAN-2023</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Cryptocurrency exchange founded 2019 (not a mixer; the 'EUR 1.3B since 2016' figure belongs to Cryptomixer). DOJ: processed at least $96B since 2019. Foundational payment rail for the BPH/ransomware ecosystem - Zservers, Aeza and Media Land proceeds moved through Garantex wallets. The US Secret Service seized garantex.org/.io/.academy around 2025-03-06 and DOJ unsealed charges; Grinex (Kyrgyzstan, registered Dec 2024) became the successor. The Aug 2025 OFAC action also designated Exved and InDeFi Bank (Mendeleev-linked payment firms) and the A7 network (A7 LLC, A71 LLC, A7 Agent LLC, Old Vector LLC) - related entities, not aliases. In May 2026 the UK designated Exmo, Rapira, Bitpapa and ABCeX (Nueva Cryptologia), so earlier 'active successor' labels for those venues are outdated; MKAN Coin is unverified.</t>
+          <t>Cryptocurrency exchange founded 2019 (not a mixer; the 'EUR 1.3B since 2016' figure belongs to Cryptomixer). DOJ: processed at least $96B since 2019. Foundational payment rail for the BPH/ransomware ecosystem - Zservers, Aeza and Media Land proceeds moved through Garantex wallets. The US Secret Service seized garantex.org/.io/.academy around 2025-03-06 and DOJ unsealed charges; Grinex (Kyrgyzstan, registered Dec 2024) became the successor. The Aug 2025 OFAC action also designated Exved and InDeFi Bank (Mendeleev-linked payment firms) and the A7 network (A7 LLC, A71 LLC, A7 Agent LLC, Old Vector LLC) - related entities, not aliases. In May 2026 the UK designated Exmo, Rapira, Bitpapa and ABCeX (Nueva Cryptologia), so earlier 'active successor' labels for those venues are outdated; MKAN Coin, a crypto-to-cash exchange, was founded after Garantex's CEO stepped down in April 2022 and maintains an official partnership with Garantex (Kharon, Apr 2023); no sanctions designation found.</t>
         </is>
       </c>
     </row>
@@ -2579,22 +2584,22 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>OSINT-REVIEWS; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>OSINT-REVIEWS; REGISTRY-SNAPSHOT-2026-09; BUYVM-SELF; REGISTRY-SNAPSHOT-2026-10</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Low-cost VPS provider (AS53667, PONYNET) with data centres in Las Vegas and Luxembourg. Permits Tor exit relays. AUP formally prohibits malicious content but abuse response is slow. Scamalytics 40/100 fraud score. AS53667 appears in maltrail's worst-ASN list; it is not on Spamhaus ASN-DROP. Founding year and fraud score are unverified.</t>
+          <t>Low-cost VPS provider (AS53667, PONYNET) with data centres in Las Vegas and Luxembourg. Permits Tor exit relays. AUP formally prohibits malicious content but abuse response is slow. Scamalytics fraud score 26/100 (snapshot 2026-10-30; rolling). AS53667 appears in maltrail's worst-ASN list; it is not on Spamhaus ASN-DROP. Founded 2010: BuyVM says 'since 2010', and ARIN registered the FranTech org on 2010-07-21 and AS53667 on 2010-11-19.</t>
         </is>
       </c>
     </row>
@@ -2671,12 +2676,12 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>STISC-ALEXHOST; ARCTICWOLF-DARKCARACAL-2026; HUNTRESS-CLEO-2024; REGISTRY-SNAPSHOT-2026-09; THERECORD-ALEXHOST-2023; HUNTIO-SMISHING-2026</t>
+          <t>STISC-ALEXHOST; ARCTICWOLF-DARKCARACAL-2026; HUNTRESS-CLEO-2024; REGISTRY-SNAPSHOT-2026-09; THERECORD-ALEXHOST-2023; HUNTIO-SMISHING-2026; ALEXHOST-SELF; SILENTPUSH-BPH-WP-2025</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Moldovan offshore hoster marketing DMCA-ignored hosting (Silent Push: ~10,000 active IPs and 400+ malicious domains in an 8-day sample). In January 2023 STISC reported a wave of more than 1,330 phishing emails to Moldovan state accounts sent in AlexHost's name; AlexHost disowned them (corrected 2026-10-30: the emails impersonated AlexHost, and the wave was in 2023, not 2025). Hunt.io (2026-05-27): two AlexHost (AS200019) servers were the only non-cloud VPS backends of a Ghiseul.ro-impersonation smishing operation across 19 countries. Arctic Wolf (Aug 2026): Dark Caracal's Bandook C2s were hosted on AlexHost, 'a provider previously associated with Dark Caracal'. Cl0p's Cleo campaign (Dec 2024) used AlexHost addresses (176.123.5.126 per Huntress). Do not conflate with the Russian 'Alex Host LLC' that Intrinsec ties to the FDN3 cluster. Correction 2026-09-25: the former known_prefixes (176.123.0.0/16; 37.221.64.0/19) overstated AlexHost's space - most of those ranges belong to other networks. Unverified: the 'former Soviet bomb shelter' claim.</t>
+          <t>Moldovan offshore hoster marketing DMCA-ignored hosting (Silent Push: ~10,000 active IPs and 400+ malicious domains in an 8-day sample). In January 2023 STISC reported a wave of more than 1,330 phishing emails to Moldovan state accounts sent in AlexHost's name; AlexHost disowned them (corrected 2026-10-30: the emails impersonated AlexHost, and the wave was in 2023, not 2025). Hunt.io (2026-05-27): two AlexHost (AS200019) servers were the only non-cloud VPS backends of a Ghiseul.ro-impersonation smishing operation across 19 countries. Arctic Wolf (Aug 2026): Dark Caracal's Bandook C2s were hosted on AlexHost, 'a provider previously associated with Dark Caracal'. Cl0p's Cleo campaign (Dec 2024) used AlexHost addresses (176.123.5.126 per Huntress). Do not conflate with the Russian 'Alex Host LLC' that Intrinsec ties to the FDN3 cluster. Correction 2026-09-25: the former known_prefixes (176.123.0.0/16; 37.221.64.0/19) overstated AlexHost's space - most of those ranges belong to other networks. AlexHost itself describes its Chisinau data centre (opened 2013) as a bomb shelter about 5 m underground in a former Soviet military factory (self-reported). Silent Push's Dec 2025 whitepaper is the source of the ~10,000 IPs / 400+ domains figures.</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2795,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Romania / Finland / Iceland</t>
+          <t>Romania / Finland / Iceland / Netherlands</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>FlokiNET ehf</t>
+          <t>FlokiNET ehf (Iceland, current); Flokinet Ltd (Seychelles, reg. 185278; AS200651 holder 2017-05 to 2024-03)</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Flokinet Ltd</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2815,12 +2825,12 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>TRENDMICRO-INTERPOL; REGISTRY-SNAPSHOT-2026-09; RUDIS-BPH-WATCH</t>
+          <t>TRENDMICRO-INTERPOL; REGISTRY-SNAPSHOT-2026-09; RUDIS-BPH-WATCH; REGISTRY-SNAPSHOT-2026-10</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Commercialized free-speech hosting brand with a multi-jurisdiction presence (Romania, Finland, Iceland); explicit uncensored-hosting marketing. Trend Micro/Interpol 2023 reportedly attributed 13% of Africa-related offshore BPH sourcing to FlokiNET (figure unverified). Correction 2026-09-25: the registry holder is FlokiNET ehf (Iceland); the earlier Seychelles / 'Floki Network Services Ltd' details are unverified. The rud.is weekly Bulletproof Hosting Watch includes AS200651 among its curated BPH ASNs (week of 2026-10-26; low-weight, automated).</t>
+          <t>Commercialized free-speech hosting brand with a multi-jurisdiction presence (Romania, Finland, Iceland); explicit uncensored-hosting marketing. Trend Micro (Aug 2023, intelligence shared with INTERPOL's Africa Cyber Surge II) listed 'Flokinet Ltd (13%)' among 'prolific offshore bulletproof hosters', with 1337team Limited (ELITETEAM) at 48% and Petersburg Internet Network at 19%; it does not say what the percentages measure. Correction 2026-09-25: the registry holder is FlokiNET ehf (Iceland); the Seychelles entity was Flokinet Ltd (RIPE ORG-FL176-RIPE, reg. 185278), which held AS200651 from 2017-05 to 2024-03 before the transfer to FlokiNET ehf; no source uses 'Floki Network Services Ltd'. The rud.is weekly Bulletproof Hosting Watch includes AS200651 among its curated BPH ASNs (week of 2026-10-26; low-weight, automated).</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2867,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>NL; RU; BG; LT; SG; LU; HK</t>
+          <t>MY; NL; RU; BG; LT; SG; LU; HK</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2882,22 +2892,22 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>~2003</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>SPAMHAUS-BPH; OSINT-FORUMS; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>SPAMHAUS-BPH; OSINT-FORUMS; REGISTRY-SNAPSHOT-2026-09; SILENTPUSH-BPH-WP-2025; SHINJIRU-SELF</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Veteran Malaysian offshore host (APNIC holder Shinjiru Technology Sdn Bhd; AS45839 announces 16 IPv4 prefixes, 5 overlapping Spamhaus DROP). Markets DMCA-ignored hosting across several jurisdictions; Silent Push reports a 12-day abuse response and a 10-day grace period. Spamhaus flagged an unnamed Malaysia-based ISP matching Shinjiru's profile. Unverified: founding year (~2003) and the eight-jurisdiction count.</t>
+          <t>Veteran Malaysian offshore host (APNIC holder Shinjiru Technology Sdn Bhd; AS45839 announces 16 IPv4 prefixes, 5 overlapping Spamhaus DROP). Markets DMCA-ignored hosting across several jurisdictions; Silent Push reports a 12-day abuse response and a 10-day grace period. Spamhaus flagged an unnamed Malaysia-based ISP matching Shinjiru's profile. Founded 2000 (Shinjiru; Silent Push; shinjiru.com registered 2000-01-21) and markets eight offshore locations (MY, BG, NL, HK, LT, LU, RU, SG). Silent Push's Dec 2025 whitepaper names Shinjiru (AS45839) as a BPH and is the source of the 12-day abuse-response and 10-day grace-period figures.</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3230,12 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>KREBS-BPH; RF-INFRA-2025; RF-STARK; GREYNOISE-STARK; KREBS-FIOD-STARK; DCD-FIOD-2026; REGISTRY-SNAPSHOT-2026-09; REGISTRY-SNAPSHOT-2026-10; AMNEZIA-HOSTING-2026</t>
+          <t>KREBS-BPH; RF-INFRA-2025; RF-STARK; GREYNOISE-STARK; KREBS-FIOD-STARK; DCD-FIOD-2026; REGISTRY-SNAPSHOT-2026-09; REGISTRY-SNAPSHOT-2026-10; AMNEZIA-HOSTING-2026; FIOD-WORKTITANS-2026; MIRHOSTING-STMT-2026; DCD-NLIGHTEN-2026; KOMMERSANT-NLIGHTEN-2026</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Founded in 2004 by Andrey Nesterenko, who was arrested in the FIOD raid of 2026-05-18 (name press-reported). Krebs: WorkTitans reached the internet solely through MIRhosting, and AS52000 is the first peer in AS209847's aut-num. The 2008 StopGeorgia.ru hosting is attributed (Jeffrey Carr) to the related Innovation IT Solutions Corp; Nesterenko said he could not verify it. De Volkskrant data showed WorkTitans and MIRhosting as the most-used networks in pro-Russian attacks on Danish bodies (Nov 2025). AS52000 had shrunk to two IPv4 /24s (185.15.209.0/24, 185.15.210.0/24) by Sept 2026 and has announced nothing since 2026-10-19 (AS206932 since 2026-09-29) - both ASNs remain registered to MIRhosting. Tier raised T2 -&gt; T1 on 2026-09-25 (taxonomy T1: subject of a law-enforcement action targeting hosting infrastructure - its founder was arrested in the FIOD action against the WorkTitans network, which reached the internet solely through MIRhosting; reported by Krebs and DatacenterDynamics). Whether MIRhosting-operated servers were among the 800+ seized is unconfirmed. Unverified: the 'temporarily paused services to WorkTitans' quote. A Russian-language VPN provider blog (June 2026, grade D) says MIRhosting equipment was among the items seized on 2026-05-18 and that the nLighten data centre cut power to MIRhosting equipment in the Netherlands and Germany in early June, taking downstream hosters offline - unverified.</t>
+          <t>Founded in 2004 by Andrey Nesterenko, who was arrested in the FIOD raid of 2026-05-18 (name press-reported). Krebs: WorkTitans reached the internet solely through MIRhosting, and AS52000 is the first peer in AS209847's aut-num. The 2008 StopGeorgia.ru hosting is attributed (Jeffrey Carr) to the related Innovation IT Solutions Corp; Nesterenko said he could not verify it. De Volkskrant data showed WorkTitans and MIRhosting as the most-used networks in pro-Russian attacks on Danish bodies (Nov 2025). AS52000 had shrunk to two IPv4 /24s (185.15.209.0/24, 185.15.210.0/24) by Sept 2026 and has announced nothing since 2026-10-19 (AS206932 since 2026-09-29) - both ASNs remain registered to MIRhosting. Tier raised T2 -&gt; T1 on 2026-09-25 (taxonomy T1: subject of a law-enforcement action targeting hosting infrastructure - its founder was arrested in the FIOD action against the WorkTitans network, which reached the internet solely through MIRhosting; reported by Krebs and DatacenterDynamics). The FIOD release names no companies, so whether MIRhosting-owned equipment was among the 800+ servers seized is unconfirmed (only a grade-D blog says so). MIRhosting's own statement of 2026-05-22 says it 'temporarily suspended' services to Work Titans, to which it supplied colocation only, and that service to other customers continued (Krebs paraphrased this as 'paused'). On 2026-06-02 the nLighten data centre cut power to MIRhosting equipment without notice, taking its colocation customers offline; nLighten says it co-operated with the Dutch investigations and terminated the relationship (DCD; Kommersant). Only a Russian-language blog (grade D) also mentions German sites.</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3394,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -3394,7 +3404,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Long-running St. Petersburg hoster (AS44050 announces 13 IPv4 prefixes; sister AS34665 PINDC-AS announces 69). Unit 42 (Sept 2023): a Cl0p torrent-seeding server, 95.215.0.76, was hosted by PIN DC on AS34665 (that block is now originated by AS44050). Securonix: TACTICALOCTOPUS C2 addresses 5.8.8.100 and 109.206.240.67 were registered to Petersburg Internet Network Ltd. Its T2 tier rests heavily on the Trend Micro/Interpol 2023 figure (PIN 19% of malicious offshore BPH sourcing, behind ELITETEAM 48% and ahead of FlokiNET 13%), which could not be re-verified; without it the vendor evidence supports T3. Not on Spamhaus ASN-DROP.</t>
+          <t>Long-running St. Petersburg hoster (AS44050 announces 13 IPv4 prefixes; sister AS34665 PINDC-AS announces 69). Unit 42 (Sept 2023): a Cl0p torrent-seeding server, 95.215.0.76, was hosted by PIN DC on AS34665 (that block is now originated by AS44050). Securonix: TACTICALOCTOPUS C2 addresses 5.8.8.100 and 109.206.240.67 were registered to Petersburg Internet Network Ltd. Its T2 tier rests heavily on the Trend Micro/Interpol 2023 figure (Trend Micro, Aug 2023: 'Petersburg Internet Network Ltd (19%)' among 'prolific offshore bulletproof hosters', behind 1337team Limited 48% and ahead of Flokinet Ltd 13% - the base of the percentages is not stated); without it the vendor evidence supports T3. Not on Spamhaus ASN-DROP.</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3476,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -3476,7 +3486,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Hong Kong-registered ASN (119 IPv4 prefixes, 192,768 addresses) that hosted FUNNULL CDN points of presence in Silent Push's Oct 2024 mapping (Silent Push labels it 'China Telecom Global'); a hosting relationship, not ownership - CTG is not FUNNULL's parent and was not designated. Infoblox (June 2026): about 6% of visible DCloud Uni-App investment-scam domains use BPH providers such as CTG Server Limited; the campaign spans 236,493 distinct scam SLDs since mid-2022. Spamhaus ASN-DROP lists AS152194 (ctgserver.com; not in the Feb 2024 snapshot). Current activity: Cobalt Strike C2s on CTG addresses (Aug-Sep 2026, C2IntelFeeds) and AS152194 among GreyNoise's React2Shell exploitation sources. Kept T1 (multiple independent vendors plus Spamhaus). Corrections 2026-09-25: the OFAC 'via FUNNULL designation' entry was removed; '175+ rotating CNAMEs' conflicts with the FBI's 548 FUNNULL CNAMEs; the '19 of the top 20' figure is unverified.</t>
+          <t>Hong Kong-registered ASN (119 IPv4 prefixes, 192,768 addresses) that hosted FUNNULL CDN points of presence in Silent Push's Oct 2024 mapping (Silent Push labels it 'China Telecom Global'); a hosting relationship, not ownership - CTG is not FUNNULL's parent and was not designated. Infoblox (June 2026): about 6% of visible DCloud Uni-App investment-scam domains use BPH providers such as CTG Server Limited; the campaign spans 236,493 distinct scam SLDs since mid-2022. Spamhaus ASN-DROP lists AS152194 (ctgserver.com; not in the Feb 2024 snapshot). Current activity: Cobalt Strike C2s on CTG addresses (Aug-Sep 2026, C2IntelFeeds) and AS152194 among GreyNoise's React2Shell exploitation sources. Kept T1 (multiple independent vendors plus Spamhaus). Corrections 2026-09-25: the OFAC 'via FUNNULL designation' entry was removed; the '19 of the top 20' figure is Infoblox's (June 2026): of the top twenty bulletproof-hosted DCloud scam SLDs seen in its cloud customers, nineteen are on CTG Server (myctgs.com). The '175+ CNAMEs' figure belongs to Silent Push's FUNNULL reporting, not to CTG.</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -3573,7 +3583,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>UK-registered operator (AS213887 announces 29 IPv4 and 7 IPv6 prefixes; the earlier '68 IPv4 / 11 IPv6' is outdated). WAIcore activity predates the AS213887 registration: Spamhaus ASN-DROP listed three earlier WAIcore ASNs (AS202973, AS206425, AS210281; domain waicore.com) by Feb 2024; all three have since been re-issued to unrelated networks (do not block them). A new registration, AS219262 'WAICORE-RUSSIA', is held by a Russian individual and has no routes yet. Qurium names WAIcore within Doppelganger infrastructure behind aurologic; the RF naming is unverified. Not on the current ASN-DROP. Companies House: WAICORE HOSTING LTD (14884560) was dissolved by voluntary strike-off on 2024-06-18; WAICORE LTD (15668439, incorporated 2024-04-22) changed officers on 2026-10-08/09 and received a first Gazette notice for compulsory strike-off on 2026-10-13. Dissolution would not by itself end AS213887.</t>
+          <t>UK-registered operator (AS213887 announces 29 IPv4 and 7 IPv6 prefixes; the earlier '68 IPv4 / 11 IPv6' is outdated). WAIcore activity predates the AS213887 registration: Spamhaus ASN-DROP listed three earlier WAIcore ASNs (AS202973, AS206425, AS210281; domain waicore.com) by Feb 2024; all three have since been re-issued to unrelated networks (do not block them). A new registration, AS219262 'WAICORE-RUSSIA', is held by a Russian individual and has no routes yet. Qurium (July 2024) says aurologic provides peering for Altawk, WAIcore Hosting and Tnsecurity, and Recorded Future's aurologic report (Nov 2025) names WAIcore Hosting (AS210281) among aurologic's long-standing relationships and lists AS213887 among active aurologic-linked networks (verified 2026-10-30). Not on the current ASN-DROP. Companies House: WAICORE HOSTING LTD (14884560) was dissolved by voluntary strike-off on 2024-06-18; WAICORE LTD (15668439, incorporated 2024-04-22) changed officers on 2026-10-08/09 and received a first Gazette notice for compulsory strike-off on 2026-10-13. Dissolution would not by itself end AS213887.</t>
         </is>
       </c>
     </row>
@@ -4196,17 +4206,17 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>REGISTRY-SNAPSHOT-2026-09</t>
+          <t>REGISTRY-SNAPSHOT-2026-09; KREBS-DDOSGUARD-2021</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Dual-use Russian DDoS mitigation and hosting provider. Main network is AS57724 (21 IPv4 prefixes); AS49612 now announces a single /24 under the handle COGNITIVE-CLOUD-NET; a further 'DDoS-Guard Corp' ASN (AS262254) is dark. Historically an upstream of ELITETEAM (as of Sept 2022, per Team Cymru). Not on Spamhaus ASN-DROP. Unverified in this audit: the Parler/8chan hosting history. Not classified BPH, but persistently present in the Russian cybercrime ecosystem.</t>
+          <t>Dual-use Russian DDoS mitigation and hosting provider. Main network is AS57724 (21 IPv4 prefixes); AS49612 now announces a single /24 under the handle COGNITIVE-CLOUD-NET; a further 'DDoS-Guard Corp' ASN (AS262254) is dark. Historically an upstream of ELITETEAM (as of Sept 2022, per Team Cymru). Not on Spamhaus ASN-DROP. It protected or fronted rather than directly hosted: the 8kun/QAnon sites moved behind DDoS-Guard in Oct 2020 and Parler in Jan 2021 (Krebs; Reuters). Not classified BPH, but persistently present in the Russian cybercrime ecosystem.</t>
         </is>
       </c>
     </row>
@@ -4544,12 +4554,12 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>OFAC-GARANTEX; CHAINALYSIS-A7A5; CHAINALYSIS-OFAC; TRM-A7A5-2026; ELLIPTIC-GRINEX; TRM-TOKENSPOT-2026</t>
+          <t>OFAC-GARANTEX; CHAINALYSIS-A7A5; CHAINALYSIS-OFAC; TRM-A7A5-2026; ELLIPTIC-GRINEX; TRM-TOKENSPOT-2026; CHAINALYSIS-SANCTIONS-2026</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Kyrgyzstan-incorporated successor to Garantex: registered December 2024 (TRM) and promoted on Telegram days after the March 2025 Garantex takedown; forensically tied to Garantex by shared on-chain infrastructure and asset migration (user funds plus A7A5 minted via Old Vector). OFAC designated it on 2025-08-14 as Garantex's 'direct successor'. On 2026-04-15 about 12:00 UTC roughly $13-15M was drained (Grinex claimed &gt;1bn rubles and blamed foreign 'special services'; Elliptic measured ~$15M USDT); Grinex then suspended operations, and Chainalysis raised the possibility of a false-flag exit. TokenSpot, a Kyrgyz exchange that TRM (2026-10-06) assesses with high confidence runs on shared wallet infrastructure with Grinex, was hit the same day (see the TokenSpot CJSC row; UK-designated 2026-10-08); Rapira had &gt;$72M in direct transactions with Grinex (Elliptic). Exved is a separately designated company, not an alias. Unverified: '&gt;=$4.76B processed in 2025'. Designation stands; Grinex's own front end remains offline, but the shared TokenSpot deposit aggregator stayed active until 2026-07-29 and TokenSpot is still operating.</t>
+          <t>Kyrgyzstan-incorporated successor to Garantex: registered December 2024 (TRM) and promoted on Telegram days after the March 2025 Garantex takedown; forensically tied to Garantex by shared on-chain infrastructure and asset migration (user funds plus A7A5 minted via Old Vector). OFAC designated it on 2025-08-14 as Garantex's 'direct successor'. On 2026-04-15 about 12:00 UTC roughly $13-15M was drained (Grinex claimed &gt;1bn rubles and blamed foreign 'special services'; Elliptic measured ~$15M USDT); Grinex then suspended operations, and Chainalysis raised the possibility of a false-flag exit. TokenSpot, a Kyrgyz exchange that TRM (2026-10-06) assesses with high confidence runs on shared wallet infrastructure with Grinex, was hit the same day (see the TokenSpot CJSC row; UK-designated 2026-10-08); Rapira had &gt;$72M in direct transactions with Grinex (Elliptic). Exved is a separately designated company, not an alias. Chainalysis: processed at least $4.76B in 2025. Designation stands; Grinex's own front end remains offline, but the shared TokenSpot deposit aggregator stayed active until 2026-07-29 and TokenSpot is still operating.</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -4626,12 +4636,12 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>OFAC-GARANTEX; CHAINALYSIS-A7A5; TRM-A7A5-2026; OFAC-A7-NETWORK-2026; EU-21ST-PACKAGE; TRM-EU21-2026; CRYPTOPOLITAN-A7A5-2026; ALJAZEERA-YANDEX-2026</t>
+          <t>OFAC-GARANTEX; CHAINALYSIS-A7A5; TRM-A7A5-2026; OFAC-A7-NETWORK-2026; EU-21ST-PACKAGE; TRM-EU21-2026; CRYPTOPOLITAN-A7A5-2026; ALJAZEERA-YANDEX-2026; CHAINALYSIS-SANCTIONS-2026</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Russian ruble-backed stablecoin issued by Kyrgyzstan's Old Vector; A7 LLC is the token's creator. Chainalysis (2026 Crypto Crime Report): $93.3B moved 'in less than a year'; Elliptic: more than $100B in under a year (the $93.1B and $72B figures elsewhere are earlier snapshots). Garantex moved funds into A7A5 from as early as January 2025 (TRM). The no-KYC Instant Swapper reportedly converted &gt;$2.2B of A7A5 into mainstream USD stablecoins (unverified). The EU banned A7A5 transactions from 2025-11-25. Its economy ran through Grinex, and on-chain volume reportedly collapsed after Grinex suspended in April 2026 (the '~96%' decline figure is attributed to Elliptic in secondary reporting). On 2026-10-01 Treasury designated the whole A7 Network as a transnational criminal organization: its Sub-Agents processed more than $17B (Jan 2025-Jun 2026) and 'catered to cybercriminals, including ransomware' actors, and the network is linked to Nobitex and to North Korean hacks; FinCEN proposed cutting Sub-Agents off from US transmittals (rule not yet final). Ukrainian drone strikes on Yandex data centres (Sasovo, 2026-10-08, and Kaluga the same week) disrupted A7A5's exchange service, which Elliptic's Tom Robinson says is hosted there: crypto press citing Robinson and Etherscan/Tronscan data report daily transfers falling from about 600 to about 61, mostly DEX swaps, and holders unpaid interest since 2026-10-09 (Elliptic's own write-up not read; figures C-grade). A7 LLC, A71 LLC and A7 Agent LLC are separately designated related entities, not aliases.</t>
+          <t>Russian ruble-backed stablecoin issued by Kyrgyzstan's Old Vector; A7 LLC is the token's creator. Chainalysis (2026 Crypto Crime Report): $93.3B moved 'in less than a year'; Elliptic: more than $100B in under a year (the $93.1B and $72B figures elsewhere are earlier snapshots). Garantex moved funds into A7A5 from as early as January 2025 (TRM). Chainalysis (Mar 2026): over $2.2B in value has moved through the no-KYC A7A5 Instant Swapper, which converts A7A5 into USD-pegged stablecoins. The EU banned A7A5 transactions from 2025-11-25. Its economy ran through Grinex, and on-chain volume reportedly collapsed after Grinex suspended in April 2026 (the '~96%' decline figure is attributed to Elliptic in secondary reporting). On 2026-10-01 Treasury designated the whole A7 Network as a transnational criminal organization: its Sub-Agents processed more than $17B (Jan 2025-Jun 2026) and 'catered to cybercriminals, including ransomware' actors, and the network is linked to Nobitex and to North Korean hacks; FinCEN proposed cutting Sub-Agents off from US transmittals (rule not yet final). Ukrainian drone strikes on Yandex data centres (Sasovo, 2026-10-08, and Kaluga the same week) disrupted A7A5's exchange service, which Elliptic's Tom Robinson says is hosted there: crypto press citing Robinson and Etherscan/Tronscan data report daily transfers falling from about 600 to about 61, mostly DEX swaps, and holders unpaid interest since 2026-10-09 (Elliptic's own write-up not read; figures C-grade). A7 LLC, A71 LLC and A7 Agent LLC are separately designated related entities, not aliases.</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -5446,6 +5456,11 @@
           <t>AS206336 (Datavice; registered to DATAVICE MCHJ [UZ] since 2025-07-18; no routes)</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2a0a:8700::/29 (UZ-DATAVICE-20250718; allocated to Datavice as LIR; not announced)</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
           <t>Uzbekistan</t>
@@ -6338,7 +6353,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>China (Xuzhou, Jiangsu)</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6346,9 +6361,14 @@
           <t>Global residential exit nodes</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Jiangsu Aidi Information Technology Co., Ltd. (IPIDEA trademark applicant; iTnews)</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>360 Proxy; 922 Proxy; ABC Proxy; Cherry Proxy; IP2World; Luna Proxy; PIA S5 Proxy; PY Proxy; SDKs: Castar, Earn, Hex, Packet SDK</t>
+          <t>360 Proxy; 922 Proxy; ABC Proxy; Cherry Proxy; IP2World; Luna Proxy; PIA S5 Proxy; PY Proxy; SDKs: Castar, Earn, Hex, Packet SDK; Door VPN; Galleon VPN; Radish VPN; Tab Proxy; ipidea.io</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -6373,17 +6393,17 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>GTIG-IPIDEA-2026</t>
+          <t>GTIG-IPIDEA-2026; USPTO-IPIDEA; ITNEWS-IPIDEA-2026</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>On 2026-01-29 Google's Threat Intelligence Group announced legal action against IPIDEA's command domains, with Cloudflare, Spur and Lumen Black Lotus Labs, shrinking its device pool by millions; Play Protect now removes apps carrying IPIDEA SDKs. GTIG saw more than 550 threat groups using the network in a single week (Google's John Hultquist named APT28, Sandworm and Volt Typhoon among them); IPIDEA advertised 6.1M IPs updated daily. It is resold under at least eight brands and enrolled devices through the Castar, Earn, Hex and Packet SDKs; it also facilitated BADBOX 2.0. Part of the residential-proxy enforcement lineage 911 S5 -&gt; Moonlander (5socks/Anyproxy) -&gt; SocksEscort -&gt; IPIDEA -&gt; Asocks -&gt; NetNut -&gt; QTRouter. Operator identity and jurisdiction are unverified; not sanctioned. Status 'exposed' because the disruption was a private-sector legal action rather than a law-enforcement seizure.</t>
+          <t>On 2026-01-28 Google's Threat Intelligence Group announced legal action against IPIDEA's command domains, with Cloudflare, Spur and Lumen Black Lotus Labs, shrinking its device pool by millions; Play Protect now removes apps carrying IPIDEA SDKs. GTIG saw more than 550 threat groups using the network in a single week (Google's John Hultquist named APT28, Sandworm and Volt Typhoon among them); IPIDEA advertised 6.1M IPs updated daily. GTIG lists 13 brands controlled by the same actors (adding Door VPN, Galleon VPN, Radish VPN, Tab Proxy and ipidea.io to those below) and enrolled devices through the Castar, Earn, Hex and Packet SDKs; it also facilitated BADBOX 2.0. Part of the residential-proxy enforcement lineage 911 S5 -&gt; Moonlander (5socks/Anyproxy) -&gt; SocksEscort -&gt; IPIDEA -&gt; Asocks -&gt; NetNut -&gt; QTRouter. Operator: GTIG names none, citing 'intentionally murky ownership structures', but the USPTO record for the IPIDEA trademark names Jiangsu Aidi Information Technology Co., Ltd. (Xuzhou, China) and iTnews reports IPIDEA is part of that company; code-signing certificates belong to Hong Kong-registered companies. Not sanctioned. Status 'exposed' because the disruption was a private-sector legal action rather than a law-enforcement seizure.</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
@@ -6660,6 +6680,508 @@
       <c r="Y74" t="inlineStr">
         <is>
           <t>Cryptomus/Heleket crypto payment rail used by BPH providers; UK-designated Oct 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Global Internet Solutions LLC (GIR / 4VPS)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>flagged</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>T1-Confirmed BPH</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AS207713 (GIR-AS; Spamhaus ASN-DROP under gir.network)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Russia (Sevastopol, occupied Crimea)</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Russia / occupied Crimea; EU-hosted infrastructure</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>OOO Global Internet Resheniya (Global Internet Solutions LLC; OGRN 1229200002316)</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>GIR; GIS; GIR-AS; gir.network; 4VPS / 4vps.su / FourVPS; sister GCSAS (Global Connectivity Solutions LLP, AS215540)</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Gamaredon / UAC-0010 (Ukraine NCCC 2023; Intrinsec); NoName057(16) (DDoSia C2, Feb 2024; Sekoia); Doppelganger (Qurium 2024); Storm-1575 (eSentire, moderate confidence, with GCS); UAC-0050 / UAC-0006 (Intrinsec); Russian state-sponsored groups (RF, 4VPS cluster)</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>DDoSia; Rockstar 2FA / DadSec phishing kit (moderate confidence)</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Legal front for the 4VPS.SU VPS brand; Underground forum advertising; Prefix migration to sister GCSAS; Shared beneficial owner with GCSAS</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Spamhaus ASN-DROP (AS207713 under gir.network); RF Threat Density top 10 (as 4VPS); Underground forum advertising</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>RF 2025 top-10 (#7, as 4VPS - with GCSAS AS215540)</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>INTRINSEC-UAC-2025; INTRINSEC-FDN3-2025; ESENTIRE-GCS-2024; RF-INFRA-2025; NCCC-GAMAREDON-2023; SEKOIA-DDOSIA-2024; QURIUM-DOPPELGANGER; QURIUM-AEZA-2026; 4VPS-SELF; REGISTRY-SNAPSHOT-2026-10</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Russian LLC in Sevastopol (occupied Crimea) that, with its UK sister GCSAS (AS215540), fronts the 4VPS.SU VPS brand - Intrinsec calls both 'legal fronts for the bulletproof hosting provider 4vps.su'; the 4vps.su site footer names the Sevastopol company. RIPE org created 2022-05-12, AS207713 on 2022-05-24. Ukraine's NCCC (Aug 2023) said Gamaredon 'overwhelmingly prefers' GIR-AS and that its Sevastopol location may point to links with the FSB in Crimea; Sekoia saw DDoSia C2s on GIR-AS in Feb 2024; Qurium tied Doppelganger domains to it in 2024. Recorded Future ranks 4VPS (GIR plus GCS) #7 in its 2025 Threat Density top 10, active throughout 2025. Intrinsec and eSentire say the two networks share a Russian beneficial owner (Companies House confirms the Russian owner on the GCS side); prefixes have moved from AS207713 to AS215540. On Spamhaus ASN-DROP (gir.network); AS207713 announces 37 IPv4 prefixes, none on Spamhaus DROP (2026-10-30). T1 on RF top-decile density plus three independent B-grade vendors (Intrinsec, eSentire, RF) and a Grade A government report (NCCC).</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>Sevastopol-registered sister of GCSAS behind the 4VPS bulletproof VPS brand; RF 2025 top-10 TAE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>BL Networks (BitLaunch)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>flagged</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>T3-Suspected</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AS399629 (BLNWX)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>United States (Wyoming registered-agent LLC); United Kingdom (Liber Systems Ltd, per Qurium)</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Global (own prefixes plus resold DigitalOcean, Linode and Vultr capacity)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>BL Networks</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>BitLaunch; bitlaunch.io; BLNWX; BL Networks GB</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>NoName057(16) (DDoSia C2; RF); Doppelganger (Qurium 2024); k0t initial-access broker (AdaptixC2; Group-IB 2026); Lorenz ransomware (exfiltration servers; Arctic Wolf 2022)</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>DDoSia C2; AdaptixC2; Cobalt Strike</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Crypto-paid anonymous VPS; Reseller over mainstream clouds plus own prefixes; Registered-agent shell structure</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Top host of DDoSia Tier-1 C2s (RF); Not on Spamhaus ASN-DROP; Responsive to takedowns (self-reported)</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>RF-DDOSIA-2025; GROUPIB-K0T-2026; ARCTICWOLF-LORENZ-2022; QURIUM-DOPPELGANGER; QURIUM-AEZA-2026; BUSHIDOTOKEN-BITLAUNCH-2025; REGISTRY-SNAPSHOT-2026-10</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Crypto-paid anonymous VPS provider (BitLaunch, active since at least 2017). Recorded Future (July 2025) names AS399629 (BL Networks, 'belonging to BitLaunch[.]io, a popular internet service provider among threat actors') as the most prominent host of NoName057(16) DDoSia Tier-1 C2s (8%, ahead of Aeza 7.5% and GCS 6%). Group-IB (2026-10-21): AdaptixC2 beacons of the k0t edge-device access broker sat on BitLaunch. Arctic Wolf (2022): Lorenz ransomware exfiltrated over SSH to two AS399629 servers. Qurium (2024) found most Doppelganger domains of one cluster on BL Networks and says it is a Wyoming registered-agent company with routing tied to UK Liber Systems Ltd; its Oct 2026 report lists BL Networks among networks Doppelganger proxies moved to in Aug 2024. BushidoToken (2025) notes it also resells mainstream clouds and appears responsive to takedowns; BitLaunch says abuse affects about 1% of servers. AS399629 announces 68 IPv4 prefixes, none on Spamhaus DROP, and is not on ASN-DROP (2026-10-30). T3: several B-grade vendors name it with specific indicators, but it lacks ASN-DROP listing and shows abuse response; block specific IPs rather than the ASN.</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>Crypto-paid anonymous VPS (BitLaunch); top host of DDoSia C2s per Recorded Future.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Andwase Limited (ex-Network Management / IP4MARKET)</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>T5-Watch List (Upstream Enabler)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>British Virgin Islands</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>IPv4 address leasing (RIPE LIR vg.andwase)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Andwase Limited</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>vg.andwase; Network Management Ltd (sc.netman); IP4MARKET</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>LIR / IPv4 broker; LIR migration sc.netman -&gt; vg.andwase from 2025-07-04</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>Single source; ~88,000 IPv4 addresses across 82 allocations; Not on Spamhaus DROP or ASN-DROP</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>QURIUM-AEZA-2026; REGISTRY-SNAPSHOT-2026-10</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>BVI RIPE LIR that appeared in June 2025; Qurium (Oct 2026) says the estate of Network Management Ltd / IP4MARKET began moving to it on 2025-07-04, three days after Aeza's OFAC designation, and that it controlled close to 90,000 IPv4 addresses across 82 allocations by 2026. At least 4,864 Andwase-sourced addresses appeared across Aeza and related networks over time (256 still announced via NetCrafters), and Qurium found that more than half of 15 Network Management prefixes later assigned to Aeza had first been used by NTX Technologies and First Server Limited (tracked here). A registry mirror confirms the ~88K figure. No abuse reporting beyond Qurium - T5 watch-list, named in a single report.</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>BVI IPv4 LIR that supplied address space to Aeza and First Server (Qurium).</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Prostie Reshenia LLC (WebRocket)</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>T5-Watch List (Upstream Enabler)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>AS49037 (A1-TELECOM; no routes since 2025-02-12)</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AS214729 (FreedomCommunications; Prostie Reshenia LLC)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Armenia (RIPE LIR am.webrocket, org created 2023-04-28)</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Russia (Taganrog; legacy Megalink / PG-19 estate)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Prostie Reshenia LLC</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>WebRocket; am.webrocket; WEBROCKET-MNT; Megalink / PG-19 (legacy)</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>LIR / IPv4 supplier to a sanctioned hoster</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>Single source; Aeza sub-assignments from its allocations (2024); Not on Spamhaus DROP or ASN-DROP</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>QURIUM-AEZA-2026; REGISTRY-SNAPSHOT-2026-10</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Armenian RIPE LIR (am.webrocket) holding the legacy Megalink (Taganrog) estate. Qurium (Oct 2026): subnets of 46.226.160.0/21, 92.246.132.0-92.246.143.255 and 89.169.52.0/22 were registered to AEZA GROUP LLC from Jan-Nov 2024, and Prostie Reshenia accounts for more than 8,000 addresses (about 6%) of the current Aeza/NetCrafters estate. Registry: AS49037 is dark since 2025-02-12; AS214729 (created 2024-06-11) announces one /24; WEBROCKET-MNT is among the maintainers referenced by the OFAC-designated Datavice MCHJ org object (no assignment to Datavice found). T5 watch-list; reassess if further assignments to sanctioned holders appear.</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>Armenian IPv4 LIR that assigned address space to Aeza (Qurium).</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Zomro B.V.</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>T5-Watch List</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Netherlands (KvK 75862662)</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Netherlands / US (on NovoServe infrastructure)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Zomro B.V.</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>zomro.com</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>CyberXero (initial-access broker; SOCRadar 2026)</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Reused ISPsystem VM templates (Sophos hostname data)</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>Large ISPsystem VMmanager footprint; Mainstream budget VPS</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>Top-3 host of reused ISPsystem VM hostnames (Sophos); Not on Spamhaus DROP or ASN-DROP</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>SOPHOS-VMMANAGER; SOCRADAR-CYBERXERO-2026; REGISTRY-SNAPSHOT-2026-10</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Dutch VPS provider (Enschede). Sophos (Feb 2026) lists Zomro among the most prevalent hosts of the reused ISPsystem VM hostnames (308 WIN-J9D866ESIJ2 and 455 WIN-LIVFRVQFMKO hosts) but ties only Stark and First Server to criminal and state operations. SOCRadar (2026-10-06): the CyberXero access broker's workstation, provisioning and scanning servers sat on 'AS204601, Zomro NL'. Zomro has no ASN of its own: its space is announced by NovoServe B.V. (AS204601), a separate company at the same address that presents Zomro as a customer - do not block AS204601 as Zomro. Its AUP forbids malware and C2. T5: dual-use host with periodic abuse.</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>Dutch budget VPS host prominent in Sophos VM-template data; watch-list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Evoxt Enterprise</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>T5-Watch List</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>AS149440 (EVOXTSDNBHD-AS-AP)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Global VPS (about 16 regions incl. Europe)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Evoxt Sdn. Bhd.</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Evoxt</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>TA416 / Mustang Panda (Proofpoint 2026); SHADOW-EARTH-066 / UAC-0226 (Trend Micro 2026)</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>PlugX; SHADOW-EARTH-066 tooling (CVE-2025-8088 WinRAR exploitation)</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Actor-preferred mainstream VPS (repeat tenancy)</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>Repeat state-actor C2 tenancy; Not on Spamhaus DROP or ASN-DROP</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>PROOFPOINT-TA416-2026; TRENDMICRO-UAC0226-2026; REGISTRY-SNAPSHOT-2026-10</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Malaysian budget VPS provider with no bulletproof marketing. Proofpoint (2026): TA416 heavily favoured Evoxt, XNNET LLC (AS6134) and Kaopu Cloud HK for C2 in 2025-26. Trend Micro (2026-06-08): all seven SHADOW-EARTH-066 / UAC-0226 servers in a WinRAR-exploit campaign against Ukraine were on Evoxt. AS149440 announces 181 IPv4 prefixes, none on Spamhaus DROP (2026-10-30). Tracked under the repeat-tenancy pattern (taxonomy 3.10): watch the actor-specific servers; no blanket block. XNNET is noted here rather than tracked (single source, no identifiable entity).</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>Malaysian VPS repeatedly used by Chinese and Russia-aligned state actors; watch-list.</t>
         </is>
       </c>
     </row>

--- a/BPH_Master.xlsx
+++ b/BPH_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y80"/>
+  <dimension ref="A1:AC80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -453,6 +453,10 @@
     <col width="18" customWidth="1" min="23" max="23"/>
     <col width="60" customWidth="1" min="24" max="24"/>
     <col width="50" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
+    <col width="18" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="28" max="28"/>
+    <col width="18" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -581,6 +585,26 @@
           <t>description</t>
         </is>
       </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>geo_cluster</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>primary_role</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>tier_basis</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>last_verified</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -668,6 +692,26 @@
           <t>Coupled Russian AS pair assessed by Intrinsec (high confidence) and Trustwave SpiderLabs as one operator marketed on Russian-language forums as BEARHOST/SecureHost/UNDERGROUND. Feb 2026 GreyNoise: 346 of 417 Ivanti EPMM exploitation sessions (83%) came from one AS200593 address, 193.24.123.42. 2026 activity: Hunt.io linked Proton66 to exploitation of Oracle PeopleSoft CVE-2026-35273 attributed to ShinyHunters (July) and found a The Gentlemen RaaS affiliate toolkit in an open directory at 176.120.22.127 (reported June); LevelBlue SpiderLabs reports Blind Eagle delivery infrastructure on Proton66 since June 2025. Chang Way Technologies (HK) is likely related (SpiderLabs saw IP shifts and a re-themed panel) and is tracked as its own row, not as an alias. Corrections 2026-09-25: the former known_prefixes 45.135.232.0/24 and 45.140.17.0/24 were historical Proton66 blocks now held by unrelated networks; FIN7 and the 'St. Petersburg IXP' upstream were removed (no supporting source). Block at CIDR level. Arctic Wolf (2026-07-13): a BoryptGrab-lineage infostealer spread through 292 brand-impersonation GitHub pages uses a hardcoded C2 at 193.143.1.131 on AS198953.</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Russia / St. Petersburg</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Pure BPH</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>T1 crit. 3+5: forum-advertised self-described bulletproof host with infrastructure evidence (Intrinsec); Trustwave, GreyNoise, Hunt.io, Arctic Wolf name hosted malware; both ASNs on ASN-DROP</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -770,6 +814,26 @@
           <t>OFAC designated Aeza Group LLC and its UK front Aeza International Ltd on 2025-07-01 (coordinated with the UK NCA) for hosting Meduza and Lumma infostealer operators, BianLian and the BlackSprut market. The TRON address TU4tDFRvcKhAZ1jdihojmBWZqvJhQCnJ4F sits on the Aeza Group LLC SDN entry. Owners Penzev and Bozoyan and two staff were detained by Russian authorities in early April 2025 (a Russian drug-market case, not a Western action). Evasion: 2,100+ IPs moved to the UK front Hypercore (AS211522) from 2025-07-20; Serbian (Smart Digital Ideas DOO) and Uzbek (Datavice MCHJ) vehicles followed - all OFAC-designated 2025-11-19. Sanctions have not ended operational use: AS210644 still announces 176 IPv4 prefixes; Arctic Wolf (Aug 2026) found 23 of 24 Dark Caracal GoCaracal C2s on Aeza networks and Huntress (Aug 2026) traced a ClickFix macOS crypto-drainer's staging and C2 to Aeza. Spamhaus now also lists AS203273 (NetCrafters OU, EE) under aeza.net. Roughly half of Aeza's prefixes transited aurologic AS30823 as of Nov 2025. Qurium (2026-10-14): on 2026-09-22 Aeza's two ASNs and NetCrafters (AS203273) originated 536 IPv4 /24s (137,216 addresses; 418 on Aeza's ASNs, 118 on NetCrafters) drawn from 42 LIRs, and aurologic (AS30823) was still one of AS210644's upstreams - two rounds of sanctions had 'no real impact' on its access to address space. Infoblox (Feb 2026, via Hackread): rogue DNS resolvers and a traffic distribution system behind a DNS-hijacking campaign against old home routers in 30+ countries were hosted by Aeza International. Chainalysis (Oct 2026) names Cryptomus/Heleket as an Aeza payment rail. The UK company Aeza International Ltd was dissolved on 2026-03-24; the RIPE org behind AS210644 is AEZA GROUP LLC. Qurium's supplier breakdown (Oct 2026, single source): about two-thirds of the Aeza/NetCrafters estate comes from eleven LIRs, including Andwase Limited (BVI; tracked as a T5 row), Prostie Reshenia (Armenia; T5 row), Technology Enriched Company FZCO (UAE; 27 of 32 /24s in the upper half of 77.110.64.0/18 tied to Aeza), Axiom Asia Services (Singapore), Plant Holding (Switzerland; Aeza assignment objects re-modified in March and June 2026), RapidSeedbox (a commercial IP lessor; 17+ /24s originated by Aeza ASNs) and IROST (Iran; about 9%). None of these is on Spamhaus DROP or ASN-DROP; only Andwase and Prostie Reshenia are tracked as rows.</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Russia / St. Petersburg (UK front)</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Pure BPH</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>T1 crit. 1: OFAC (Jul 2025) and UK designations for hosting cybercrime</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -867,6 +931,26 @@
           <t>EU-listed 2025-05-20 (Impl. Reg. 2025/965). UK-incorporated 2022-02-10, two weeks before Russia's full-scale invasion of Ukraine; dissolved 2025-09-16. RF describes Stark as a white-label front for Moldova's PQ.Hosting, with MIRhosting (NL) as a key infrastructure partner. AS44477 moved to PQ Hosting Plus S.R.L. on 2025-05-16 - four days before designation (the often-quoted '12 days' is the lead time from the 2025-05-08 RFE/RL leak); the THE.Hosting rebrand followed on 2025-05-29. GreyNoise saw near-complete abandonment of AS44477 by Nov 2025; it has since left the routing table and the registry. The network continues as WorkTitans/THE.Hosting (AS209847, AS213999) and UFO Hosting (AS33993), all listed by Spamhaus ASN-DROP under stark-industries.solutions. RF attributes the chain's RIPE maintainer to Dmitrii Miasnikov. Doppelganger (an influence operation, not malware) and Sandworm were removed from the malware/actor fields for lack of a Stark-specific source. Chainalysis (Oct 2026) names Cryptomus/Heleket - UK-designated 2026-10-08 - as a Stark payment rail.</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>UK Shell / Moldova</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Pure BPH (historical)</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>T1 crit. 1: EU hybrid-threats designation (May 2025) for enabling Russian cyber operations; company dissolved, tier kept as historical record</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -959,6 +1043,26 @@
           <t>Designated 2025-02-11 by the US, UK and Australia (per-authority lists in sanctions_designations). UK and Australian texts tie Zservers infrastructure to the 2022 Medibank data leak; Chainalysis traced payments from LockBit, BianLian, Hunters International and others. On 2025-02-12 Dutch police took 127 Zservers/XHOST servers offline in Amsterdam. The Zservers/XHOST ASN was AS197414 (historical prefixes 185.170.144.0/24 and 87.251.64.0/24, now held by unrelated networks); Spamhaus listed it under zservers.ru until at least Dec 2025 and it is now deregistered. Intrinsec assessed with high confidence that Zservers prefixes moved to AS213194, AS61336 and AS213010 (small footprints still announced; none on ASN-DROP). CORRECTION 2026-09-25: AS216071, previously listed here as historical, is VDSina / SERVERS TECH FZCO (UAE), an active ~156k-address network with no public link to Zservers - removed from this row; do not block it as Zservers infrastructure. Chainalysis (Oct 2026) names Cryptomus/Heleket - UK-designated 2026-10-08 - as a Zservers payment rail.</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Russia (Barnaul)</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Pure BPH</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>T1 crit. 1: OFAC/UK/AU designations (Feb 2025) for LockBit hosting; Dutch server seizure</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1056,6 +1160,26 @@
           <t>Designated 2025-11-19 by the US, UK and Australia with differing lists (see sanctions_designations); the EU followed on 2026-07-13 and New Zealand designated Volosovik on 2026-08-08. The N.D. Ohio indictment unsealed 2026-07-14 (Operation Riptide) charges Volosovik, Zatolokin, Pankova, Medialand LLC and ML.Cloud LLC over attacks causing more than $62M in victim losses. Treasury described Media Land as a launch pad for LockBit, BlackSuit and Play ransomware. The OFAC SDN entry for Volosovik carries BTC address 18dLDAWi8LmrHbEq3QzDJb9SLxCf4uimXB. Intel 471 (Aug 2026): yalishanda's fast-flux service went down in late April 2026 and he was banned from the Exploit forum; a Russian court record of 2026-04-30 concerns an appeal against a Moscow house-arrest order in a domestic payment-instruments fraud case. Of 2,240 customer domains tracked before the shutdown, 1,439 were still active in June 2026 and 1,156 of those (about 80% of the active domains, about half of the original set) still resolved to yalishanda infrastructure; the rest shifted to mainstream clouds (Cloudflare first) and to new services (OtusCloud, reming, fluxy). Intel 471 also lists Black Basta among Media Land's ransomware customers. Corrections 2026-09-25: AS48721 (Flyservers), AS211409 (FoxiBytes) and AS215311 (Regxa) were removed - no source links them to Media Land; AS215376 (ML Cloud Ltd, 176.98.187.0/24) and the dormant AS211805 were added.</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Russia / St. Petersburg</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Pure BPH</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>T1 crit. 1+2: US/UK/AU (Nov 2025) and EU (Jul 2026) designations; DOJ indictment (Operation Riptide)</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1148,6 +1272,26 @@
           <t>Russia-operated BPH registered in the Seychelles at an address that appears in the Panama Papers/Offshore Leaks (Team Cymru). Team Cymru (2022) listed four 1337TEAM ASNs operating mainly from AS51381 and recommended blocking 185.215.113.0/24, a long-running Amadey/RedLine C2 block. Current state (2026-09-25): AS51381 and AS56873 are still registered to 1337TEAM LIMITED and remain on Spamhaus ASN-DROP but announce nothing; AS39770 and AS60424 are gone from the registry; 185.215.113.0/24 is unrouted. Status set to 'dormant' on 2026-09-25: both live ASNs remain registered to 1337TEAM LIMITED but announce nothing, and no dissolution, sanction or seizure is documented, so the T1 tier stands; watch AS51381/AS56873 for re-announcement or transfer. Corrections 2026-09-25: upstreams are historical and Filanco (AS3175, Datahouse.ru) was a downstream, not an upstream; the Turla link was removed (Microsoft's Secret Blizzard/Amadey reporting does not name ELITETEAM); the unsourced 'VirusTotal 100%' claim and BabbleLoader were removed.</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Russia (Seychelles reg.)</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Pure BPH (dormant)</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>T1 crit. 5 (historical): Team Cymru and Trend Micro/INTERPOL (48% of prolific offshore BPH) plus ASN-DROP; kept as dormant</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1235,6 +1379,26 @@
           <t>OFAC-designated 2025-05-29 (with Liu Lizhi) for infrastructure behind cryptocurrency investment scams causing more than $200M in US victim-reported losses; the FBI FLASH the same day counted 548 FUNNULL CNAMEs linked to 332,000+ domains since Jan 2025. Taguig (Philippines) company run by a Chinese national. CTG Server Limited (AS152194) was one of several ASNs hosting FUNNULL points of presence in Silent Push's 2024 mapping; it is not FUNNULL's parent and was not designated. Silent Push (Apr 2026): Triad Nexus kept operating through 'clean' front brands (Bole CDN, CDN1.ai and others) that were launched before the May 2025 sanctions, plus accounts at major clouds and US-IP geofencing (HTTP 451 to US visitors); it moved from nine stable CNAME domains to more than 175 randomly generated ones - a post-sanction figure, separate from the FBI's 548. Whether 'CTGCDN' relates to CTG Server Limited is not established.</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>APAC / Triad Nexus (Philippines)</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Infrastructure Laundering</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>T1 crit. 1: OFAC designation (May 2025) for scam infrastructure</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1337,6 +1501,26 @@
           <t>Dutch post-sanctions successor to Stark Industries/PQ.Hosting. WorkTitans B.V. was formed in 2019 as a recruitment firm; its Stark-successor role starts with RIPE org ORG-THE3-RIPE (created 2025-05-28) and prefix transfers from 2025-05-29; AS209847 was created 2025-06-24 and AS213999 (THE-CLIENTS) also belongs to WorkTitans. AS209847 announced 21 prefixes in Aug 2025 and 11 on 2026-09-25; it then withdrew most of its space between 2026-10-01 and 2026-10-14 (and its IPv6 on 2026-10-27), leaving two /24s (45.120.176.0/24, 185.235.240.0/24) - the withdrawn blocks had not reappeared under another origin by 2026-10-30. MIRhosting, its former sole upstream, went dark on 2026-10-19; AS209847 now reaches the internet via ADCDATA.COM (AS135330) and FBW Networks (AS49434). GreyNoise confirmed the migration from AS44477 (Aug-Nov 2025); Censys matched RDP hostname reuse (WIN-J9D866ESIJ2). FIOD raided the Dutch nodes on 2026-05-18: 800+ servers seized at data centres in Dronten and Schiphol-Rijk; WorkTitans owner Youssef Zinad and MIRhosting founder Andrey Nesterenko arrested (names press-reported). ELLIO saw scanning back near pre-raid levels more than a week later, but later reports conflict (one telemetry source reports a 94% drop in the indexed fleet; a Russian-language hosting knowledge base says the THE.Hosting site announced it had stopped operating). Status evading -&gt; seized on 2026-10-30: the May 2026 FIOD action seized infrastructure (partial seizure), and by mid-October 2026 the network had withdrawn nearly all of its space (see below). Check Point (June 2026): three Iranian groups including MuddyWater used WorkTitans infrastructure for core operations.</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Sanctions Evasion (Stark)</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>T1 crit. 2: FIOD raid and seizure of 800+ servers (May 2026); Stark successor with sanctioned beneficial owners</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1414,6 +1598,26 @@
           <t>UK-registered Aeza Group front (Companies House 16558658; 120 Fleet Street, London); the second iteration of Aeza's UK-shell playbook. AS211522 (RIPE as-name HYPERCORELTD) was allocated ~2025-07-10 and received 2,100+ IPs from Aeza's AS210644 starting 2025-07-20 (Silent Push). OFAC designated Hypercore on 2025-11-19; it is an OFAC-only designation (the earlier 'OFAC/OFSI' wording was wrong). Spamhaus listed AS211522 under aeza.net in Dec 2025; it has since been delisted and the ASN has announced nothing since ~2026-02. Former Hypercore prefixes now originate from First Server Limited ASNs (45.142.122.0/24 via AS205090; 185.174.136.0/24 via AS200740) - a lead, not proof of common control. Companies House confirms incorporation on 2025-07-03; a first Gazette strike-off notice followed on 2025-11-11 (eight days before the OFAC designation) and the company was dissolved on 2025-12-23. Its registered office had already been moved to the Companies House default address on 2025-10-28, so the Fleet Street address is historical. CORRECTION 2026-09-25: AS215552, previously the primary ASN, belongs to an unrelated Romanian individual and was removed.</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>UK Shell</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Sanctions Evasion (Aeza)</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>T1 crit. 1: OFAC designation (Nov 2025) as Aeza front</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1516,6 +1720,26 @@
           <t>UK shell (incorporated 2024-08-08; AS214351 allocated seven days later) that RF Insikt assesses with high confidence to be under the control of the Defhost BPH brand, which advertises 'fast abusive VPS/VDS' resilient against Western law enforcement. Payment via Heleket.com, shared across the cluster. Hosts C2 and loader infrastructure for 15+ malware families. RF ranks Defhost #8 in its 2025 Threat Density top 10 and AS214351 is on Spamhaus ASN-DROP (domain as214351.com). Tier raised T2 -&gt; T1 on 2026-09-25 (taxonomy T1: self-advertised bulletproof with corroborating infrastructure evidence; RF top-decile density). Announced space grew from 2 /24s (62.60.226.0/24, 176.46.152.0/24 at RF publication) to 4 /24s now; 176.46.152.0/24 has moved to an unrelated Iranian network. The unsourced date and place of birth previously given for the director were removed. LevelBlue SpiderLabs (2026-03-20) found admin and login panels of the MioLab (aka Nova) macOS stealer on Femo IT addresses (e.g. 196.251.107.97). Companies House: FEMO IT SOLUTIONS LIMITED (15885164) received a first Gazette notice for compulsory strike-off on 2026-10-13 (an earlier notice of 2025-10-28 was discontinued on 2026-01-13) - expect dissolution, which would not by itself end the network. Its payment processor Heleket was UK-designated on 2026-10-08 (see the Xeltox Enterprises row).</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>aurologic downstream</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Pure BPH (UK shell)</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>T1 crit. 3+4: self-advertised bulletproof with infrastructure evidence; RF 2025 Threat Density #8</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1603,6 +1827,26 @@
           <t>UK-registered (RIPE org TNSECURITY LTD, GB) network that announced 185.172.128.0/24 via AS216309 (as-name EVILEMPIRE-AS) behind aurologic; Qurium tied hundreds of Doppelganger domains to 185.172.128.161 between Oct 2023 and Jul 2024. AS216309 was on Spamhaus ASN-DROP in the Feb 2024 snapshot, but not in Dec 2025 or now. The ASN has since been re-issued to InvisionTech Group S.r.l. (IT) and the Doppelganger IP now sits in an unrelated Russian network, so the entity is no longer identifiable as a live network - status set to 'dissolved' (network defunct) on 2026-09-25. Do not block AS216309. Corrections: registration is UK, not Germany (Germany is where servers sat); ASN-DROP is a Spamhaus list, not abuse.ch. Companies House: a TNSECURITY LTD (15103352, incorporated 2023-08-29) was dissolved on 2025-02-04 (name match to the RIPE org, not confirmed). Qurium (Oct 2026) places Tnsecurity in Aeza's satellite layer.</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>aurologic downstream (UK reg.)</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>BPH downstream (defunct)</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>T2 (historical): ASN-DROP (Feb 2024) plus Qurium Doppelganger hosting and aurologic downstream; network defunct</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1720,6 +1964,26 @@
           <t>Russian-speaking bulletproof host (RF 2025 Threat Density #1); domain seized and Dutch servers taken in the FBI-led Operation Omegaline, Oct 2026.</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>aurologic downstream (US LLC)</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Pure BPH</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>T1 crit. 2+4: FBI seizure (Operation Omegaline, Oct 2026); RF 2025 Threat Density #1</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1807,6 +2071,26 @@
           <t>UK shell (reported incorporated 2024-11-11) selling cheap VPS via a Telegram bot (~$2/mo), with a six-month nominee director. Vasilis Orlof tied AS213702 to multiple malware families via 141.98.6.0/24. Spamhaus ASN-DROP now lists three ASNs under qwins.co: AS213702, AS218731 (newly listed; registered to an individual in Latvia; announces 35 IPv4 prefixes) and AS214422 (NET67X; no routes). Companies House confirms UK company 16072422: renamed QUALITY IT NETWORK SOLUTIONS LIMITED on 2025-04-14 and dissolved by compulsory strike-off on 2026-07-14 (first Gazette 2026-04-21). Status flagged -&gt; dissolved on 2026-10-30 per taxonomy section 5 (corporate dissolution; the network persists - AS218731 and AS213702 still announce prefixes and remain on ASN-DROP, so keep blocking them). The link to the Aeza UK-shell network remains single-source.</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>UK Shell</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>BPH</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>T2: ASN-DROP (three ASNs) plus Intel Insights malware attribution and no-KYC shell structure</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1889,6 +2173,26 @@
           <t>UK LLP operating AS215540: 181 IPv4 prefixes / 62,720 addresses plus 24 IPv6 prefixes (2026-09-25; the earlier '~176 / ~41K' is outdated). ESET lists Gamaredon infrastructure on GCSAS addresses first seen Aug-Sep 2023. Intrinsec named GCSAS in its March 2025 UAC-infrastructure report and in Aug 2025 among shell-fronted networks announcing prefixes moved out of the FDN3 cluster. A SpiceRAT C2 active in March 2026 (171.22.16.187) is listed by Hunt.io itself under 'Global Connectivity Solutions' (SilkParasite campaign). Status raised suspected -&gt; flagged (two independent B-grade sources). Companies House confirms LLP OC450701 (incorporated 2024-01-19), filing dormant-entity accounts while operating AS215540. eSentire (Dec 2024): addresses of GCS and its sister company Global Internet Solutions (GIR, AS207713), which share a person with significant control, produced 64% of its Entra ID account-compromise detections, a subset tied with moderate confidence to Storm-1575; eSentire links both to the 4VPS brand. Sophos (Feb 2026) lists Global Connectivity Solutions among the top hosts of the reused ISPsystem VM hostnames. Qurium (Oct 2026) finds GCS and GIR repeatedly relaying prefixes into and out of Aeza networks. Trend Micro (Mar 2025) listed Black Basta/Cactus BackConnect C2s 5.181.3.164, 89.185.80.86 and 89.185.80.251; Intrinsec (Mar 2025) mapped them to AS215540, called GCS and GIR 'legal fronts for the bulletproof hosting provider 4vps.su', noted that GCS shares its two Seychelles LLP officers with sanctioned Zservers and that 61% of its peerings were shared with Stark (AS44477), and added RansomHub C2s; all three IPs still originate from AS215540 (RIPEstat 2026-10-30). Intrinsec's Aug 2025 FDN3 report calls GCS-AS 'a known Russian bulletproof hosting provider ... managed by the same Russian individual as gir.network (AS207713)'. Recorded Future ranks 4VPS (AS215540 plus GIR AS207713) #7 in its 2025 Threat Density top 10 and names 'TAE 4VPS (Global Connectivity Solutions LLP, AS215540)' among infrastructure used by Russian state-sponsored groups; its DDoSia analysis (July 2025) puts GCS third among hosts of NoName057(16) Tier-1 C2s (6%). eSentire (Apr 2026) names GCS among the 'bulletproof hosting providers' behind Teams IT-impersonation phishing. Tier T2 -&gt; T1 on 2026-10-30 (taxonomy T1: RF top-decile Threat Density, and three independent B-grade vendors - Intrinsec, eSentire, RF - classify it as BPH/TAE with named malware or actors). Not on Spamhaus ASN-DROP at the 2026-09-25 audit; listed under globconnex.com by 2026-10-29.</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>UK Shell</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Corporate Shell / BPH (4VPS front)</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>T1 crit. 4+5: RF 2025 Threat Density #7 (as 4VPS); Intrinsec, eSentire and RF classify it as BPH/TAE with named malware and actors</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1976,6 +2280,26 @@
           <t>Individual-registered RIPE network (2024) behind aurologic that HYAS (Apr 2024) flagged for RisePro stealer C2 (147.45.47.93); Intrinsec (via a third party) ties AS215789 to Virtualine's UAC-0050 spam. AS215789 has since been returned and re-issued to BLIK / Polski Standard Platnosci SA (PL), which announces nothing from it - do not block AS215789. Its former prefixes now originate from SYSECT D.O.O. (AS202799, ME) and PSB Hosting Ltd (AS214927, on Spamhaus ASN-DROP under psb.hosting) - successor-watch leads, not attribution. Status set to 'dissolved' (registration defunct) on 2026-09-25. RIPE NCC delegated statistics show AS215789 allocated to the Ukrainian holder on 2024-01-03 and re-allocated to Poland on 2025-12-01. The earlier '2223 domains across 72 IPs' figure could not be traced to any source and was removed (2026-10-30).</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>aurologic downstream</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>BPH downstream (defunct; Virtualine)</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>T2 (historical): RisePro C2 hosting (HYAS), Virtualine sub-network, aurologic downstream; registration defunct</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2058,6 +2382,26 @@
           <t>US-incorporated command-and-control provider that Halcyon (Aug 2023) exposed as an operational front for the Iranian firm abrNOC (Tehran), estimating that potentially 40-60% of its overall activity could be malicious. Used by a long list of state and criminal actors (see associated_threat_actors; BlueNoroff is not in Halcyon's list). AS14956 (RouterHosting) still announces 66 IPv4 prefixes; it was on Spamhaus ASN-DROP (cloudzy.com) in Dec 2025, was delisted by the 2026-09-25 audit and is listed again as of 2026-10-29. A UAE registration, AS200038, has no routes. Correction 2026-10-30: the operator is Hannan Nozari, as Cloudzy's own press page and CyberScoop give it - the 2026-09-25 change to 'Hassan' was wrong and is reverted; the EvilProxy link removed then is restored on Security Risk Advisors' March 2026 research tying EvilProxy smishing infrastructure to Cloudzy/RouterHosting. Team Cymru (Sept 2026) recorded Qilin SFTP exfiltration infrastructure on AS14956 (Dec 2025), and Guardz (2026-10-17) traced compromised ConnectWise Cloud Backup (SkyKick) multi-tenant app abuse and AiTM session theft egressing from 144.172.64.0/18. Tier T3 -&gt; T2 on 2026-10-30 under the taxonomy's ASN-DROP escalation rule: re-listed on ASN-DROP plus independent B-grade vendors (Halcyon, SRA).</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>BPH-Adjacent (front)</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>T2 via ASN-DROP escalation rule: ASN-DROP (re-listed Oct 2026) plus Halcyon and SRA (B)</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2140,6 +2484,26 @@
           <t>AS209800 was created 2025-04-25 and announced solely via aurologic; RF Insikt says it was controlled by Virtualine-affiliated actors who impersonated the long-standing legitimate Hamburg company metaspinner net GmbH (RENAMED 2026-09-25 so the row no longer names that company as the operator). Its prefixes (91.92.240.0/22, 158.94.208.0/22, 178.16.52.0/22) received Virtualine traffic from April 2025 and now originate from OMEGATECH AS202412 (see the Railnet/Virtualine row). The ASN has been re-issued to an unrelated German GbR (ZEMA) - do not block AS209800. Status set to 'dissolved' (network defunct). Attribution strengthened 2026-10-29: DOJ lists 'Lanedo' among Virtualine's aliases, matching the LANEDONET re-description, and Spamhaus (Sept 2025) reported Virtualine's expansion onto AS209800. Tier raised T3 -&gt; T2 on 2026-10-30 to match the other Virtualine sub-networks (KPROHOST, Karina Rashkovska): an operator-controlled front with obscured ownership (impersonated identity), no route diversification and all three former /22s on Spamhaus DROP, on RF (B) and Spamhaus (C) evidence plus the DOJ alias. Kept as a historical record - status stays 'dissolved'.</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>aurologic downstream</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>BPH downstream (defunct; Virtualine)</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>T2 (historical): operator-controlled Virtualine front with impersonated identity; RF and Spamhaus evidence plus DOJ alias</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2217,6 +2581,26 @@
           <t>RIPE-registered 2024-05-10 by KPROHOST LLC (Frankfort, KY; Kentucky reg. 1360766); abuse contact kprohost.abuse@gmail.com. Intrinsec attributes AS214940 to Virtualine, and Spamhaus listed it under virtualine.org in Dec 2025 (since delisted). Its two historical /24s (195.211.191.0/24, 45.144.212.0/24) now originate from HBING (AS208949) and Pfcloud (AS51396). The ASN has announced nothing since ~2026-08-12. Tier raised T3 -&gt; T2 on 2026-09-25 (shell structure; part of a T1 operator; blocklisting). Correction: its upstreams were Pfcloud and AS215436, not aurologic. Virtualine, the operator, was disrupted in the FBI-led Operation Omegaline on 2026-10-27 (see the Railnet/Virtualine row); AS214940 was already dark.</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>US Shell (Virtualine)</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>BPH downstream</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>T2: shell structure, part of T1 Virtualine, historical ASN-DROP listing (Intrinsec, Spamhaus)</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2299,6 +2683,26 @@
           <t>Named by Qurium as Russia-linked infrastructure behind aurologic serving the Doppelganger disinformation network, historically on AS203727 (now re-issued to byon GmbH - do not block). Spamhaus now lists AS209946 (ALINDA LLC, UA) under altawk.com; it announced 4 prefixes, all on Spamhaus DROP, until 2026-10-02 and has announced nothing since (still listed; RIPEstat, 2026-10-30). An earlier Altawk-domain ASN, AS215826, was listed in Dec 2025 and later removed. Tier raised T3 -&gt; T2 on 2026-09-25 (ASN-DROP inclusion plus Qurium). Companies House: PARTNER HOSTING LTD (15332944), the likely GB holder behind the former AS215826, was dissolved on 2026-01-20 (name match); Sophos lists Partner Hosting LTD among the top hosts of the reused ISPsystem VM hostnames.</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>aurologic downstream</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>BPH downstream</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>T2 via ASN-DROP escalation rule: ASN-DROP plus Qurium (Doppelganger infrastructure)</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2371,6 +2775,26 @@
           <t>Offshore host advertising on LowEndTalk, cracked.io, BlackHatWorld and BreachForums, self-described 'DMCA Ignored', with abuse tolerance tied to pricing tier (marketing evidence, grade E). Spamhaus now lists AS197170 (TechTies Inc., SC) under hostslick.de; it announces 13 IPv4 /24s, all on Spamhaus DROP. The earlier AS208046 was ColocationX Ltd's network (a HostSlick VPS sat there in Nov 2023) and has been re-issued - do not block it. Held at T3 (status flagged): ASN-DROP inclusion would normally escalate to T2, but only one independent B/C source supports it. HostSlick announced on 2026-02-17 (self-report, grade E) that it had stopped new VPS sales to focus on dedicated and bare-metal servers, claiming GTT and TATA transit.</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Seychelles / Netherlands</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>BPH-Adjacent</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>T3 (held below T2): ASN-DROP plus forum marketing, but only one independent B/C source</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2453,6 +2877,26 @@
           <t>Central upstream for Europe's high-risk hosting ecosystem. RF: formed in 2023 following the transition of combahton GmbH's fastpipe (combahton announced the transition in Nov 2023); multi-terabit backbone at Tornado Datacenter, Langen. RF's 2025 review says it transits about 70% of the most prominent high-risk TAE networks, and ~50% of Aeza's announced prefixes ran via aurologic (Nov 2025). Downstreams named by RF: Femo IT/Defhost, Global-Data (SWISSNETWORK02), the metaspinner-named front, Railnet/Virtualine and Aeza; Qurium adds Tnsecurity, WAIcore and Altawk. Corrections 2026-09-25: the 'top-10 globally' ranking belongs to SWISSNETWORK02, not aurologic; the '1-5 Tbps' figure is unsourced; KPROHOST is not an aurologic downstream. Several named downstreams have since gone dark or had their ASNs re-issued. Interisle (Aug 2026, AI-assisted, grade C) also flagged NEON CORE NETWORK LLC (AS205775) as an aurologic peer with high phishing and spam counts; AS205775 has since been deregistered (no RIPE aut-num, nothing announced since 2026-09-05), so it is not tracked as a row.</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Germany/Netherlands</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Upstream Enabler</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>T2 (Upstream Enabler): RF says it transits ~70% of prominent high-risk TAE networks; upstream of T1 entities (Aeza, Defhost)</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2530,6 +2974,26 @@
           <t>Cryptocurrency exchange founded 2019 (not a mixer; the 'EUR 1.3B since 2016' figure belongs to Cryptomixer). DOJ: processed at least $96B since 2019. Foundational payment rail for the BPH/ransomware ecosystem - Zservers, Aeza and Media Land proceeds moved through Garantex wallets. The US Secret Service seized garantex.org/.io/.academy around 2025-03-06 and DOJ unsealed charges; Grinex (Kyrgyzstan, registered Dec 2024) became the successor. The Aug 2025 OFAC action also designated Exved and InDeFi Bank (Mendeleev-linked payment firms) and the A7 network (A7 LLC, A71 LLC, A7 Agent LLC, Old Vector LLC) - related entities, not aliases. In May 2026 the UK designated Exmo, Rapira, Bitpapa and ABCeX (Nueva Cryptologia), so earlier 'active successor' labels for those venues are outdated; MKAN Coin, a crypto-to-cash exchange, was founded after Garantex's CEO stepped down in April 2022 and maintains an official partnership with Garantex (Kharon, Apr 2023); no sanctions designation found.</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Russia (Estonia-registered)</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Financial Enabler</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>T1 crit. 1: OFAC designation (2022; 2025 re-designation) and EU listing; domains seized 2025</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2602,6 +3066,26 @@
           <t>Low-cost VPS provider (AS53667, PONYNET) with data centres in Las Vegas and Luxembourg. Permits Tor exit relays. AUP formally prohibits malicious content but abuse response is slow. Scamalytics fraud score 26/100 (snapshot 2026-10-30; rolling). AS53667 appears in maltrail's worst-ASN list; it is not on Spamhaus ASN-DROP. Founded 2010: BuyVM says 'since 2010', and ARIN registered the FranTech org on 2010-07-21 and AS53667 on 2010-11-19.</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Canada / US / Luxembourg</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>BPH-Adjacent</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>T4: permissive offshore-style marketing and slow abuse handling; no LE action</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2684,6 +3168,26 @@
           <t>Moldovan offshore hoster marketing DMCA-ignored hosting (Silent Push: ~10,000 active IPs and 400+ malicious domains in an 8-day sample). In January 2023 STISC reported a wave of more than 1,330 phishing emails to Moldovan state accounts sent in AlexHost's name; AlexHost disowned them (corrected 2026-10-30: the emails impersonated AlexHost, and the wave was in 2023, not 2025). Hunt.io (2026-05-27): two AlexHost (AS200019) servers were the only non-cloud VPS backends of a Ghiseul.ro-impersonation smishing operation across 19 countries. Arctic Wolf (Aug 2026): Dark Caracal's Bandook C2s were hosted on AlexHost, 'a provider previously associated with Dark Caracal'. Cl0p's Cleo campaign (Dec 2024) used AlexHost addresses (176.123.5.126 per Huntress). Do not conflate with the Russian 'Alex Host LLC' that Intrinsec ties to the FDN3 cluster. Correction 2026-09-25: the former known_prefixes (176.123.0.0/16; 37.221.64.0/19) overstated AlexHost's space - most of those ranges belong to other networks. AlexHost itself describes its Chisinau data centre (opened 2013) as a bomb shelter about 5 m underground in a former Soviet military factory (self-reported). Silent Push's Dec 2025 whitepaper is the source of the ~10,000 IPs / 400+ domains figures.</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Moldova</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>BPH-Adjacent</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>T4: DMCA-ignored marketing and repeated tenant abuse (Silent Push, Arctic Wolf, Huntress); no LE action</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2766,6 +3270,26 @@
           <t>Swiss-marketed offshore brand (privatealps.net) of Private Layer INC (Panama registry holder of AS51852/AS52288), marketing DMCA-ignored, no-logs, anonymous, Monero-friendly hosting. RF ranks PrivateAlps #6 in its 2025 Threat Density top 10, and RF's aurologic report ties Global-Data System IT (SWISSNETWORK02) to PrivateAlps. Independent corroboration: the rud.is weekly Bulletproof Hosting Watch tracks PLI-AS among about 25 curated BPH ASNs (25 in the week of 2026-10-26) and names it one of the most aggressive (e.g. week of 2026-06-08: RDP brute-force, DCE/RPC enumeration, WordPress login scanning); a Bolster AI phishing study names Private Alps among high-profile BPH providers popular on underground forums for VPS/RDP/VPN hosting; and PrivateAlps advertised 'Abuse &amp; DMCA ignore' offshore servers on BlackHatWorld. Tier raised T4 -&gt; T1 on 2026-09-25 (taxonomy T1: RF top-decile Threat Density - #6 in RF's 2025 top 10, above Femo IT/Defhost at #8; minimum evidence met by RF, rud.is and Bolster). Not on Spamhaus ASN-DROP, and the rud.is and Bolster texts were read via search excerpts only - re-check both at the next review. Correction: registry entity is Private Layer INC (Panama), not Private Layer AG (Switzerland).</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Panama reg. / Switzerland (marketed)</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Offshore BPH brand (RF top 10)</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>T1 crit. 4: RF 2025 Threat Density #6; corroborated by rud.is watch, Bolster and its own abuse-ignored advertising</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2833,6 +3357,26 @@
           <t>Commercialized free-speech hosting brand with a multi-jurisdiction presence (Romania, Finland, Iceland); explicit uncensored-hosting marketing. Trend Micro (Aug 2023, intelligence shared with INTERPOL's Africa Cyber Surge II) listed 'Flokinet Ltd (13%)' among 'prolific offshore bulletproof hosters', with 1337team Limited (ELITETEAM) at 48% and Petersburg Internet Network at 19%; it does not say what the percentages measure. Correction 2026-09-25: the registry holder is FlokiNET ehf (Iceland); the Seychelles entity was Flokinet Ltd (RIPE ORG-FL176-RIPE, reg. 185278), which held AS200651 from 2017-05 to 2024-03 before the transfer to FlokiNET ehf; no source uses 'Floki Network Services Ltd'. The rud.is weekly Bulletproof Hosting Watch includes AS200651 among its curated BPH ASNs (week of 2026-10-26; low-weight, automated).</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>Iceland / Romania / Finland</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>BPH-Adjacent</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>T4: free-speech/offshore marketing; listed by Trend Micro (2023) among prolific offshore bulletproof hosters; no LE action</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2910,6 +3454,26 @@
           <t>Veteran Malaysian offshore host (APNIC holder Shinjiru Technology Sdn Bhd; AS45839 announces 16 IPv4 prefixes, 5 overlapping Spamhaus DROP). Markets DMCA-ignored hosting across several jurisdictions; Silent Push reports a 12-day abuse response and a 10-day grace period. Spamhaus flagged an unnamed Malaysia-based ISP matching Shinjiru's profile. Founded 2000 (Shinjiru; Silent Push; shinjiru.com registered 2000-01-21) and markets eight offshore locations (MY, BG, NL, HK, LT, LU, RU, SG). Silent Push's Dec 2025 whitepaper names Shinjiru (AS45839) as a BPH and is the source of the 12-day abuse-response and 10-day grace-period figures.</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>BPH-Adjacent</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>T4: DMCA-ignored offshore marketing, 12-day abuse response (Silent Push); no LE action</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2987,6 +3551,26 @@
           <t>Dutch hoster (reported address Keteldiep 15, Urk) rebranded from Flaunt7. AS49042 was historically 'Phanes Networks B.V.' and is now absent from the registry and routing data. Silent Push reports 'bulletproof' in Phanes' marketing and a 4-day abuse response; Trustpilot reviews document unresponsive handling of phishing complaints. SpectraIP is its peering partner, not an alias. SKB Enterprise B.V. held a separate ASN (AS64425, now unregistered): routing history shows AS64425 announcing 45.148.120.0/24 and 45.148.123.0/24 until 2023-04-28 and Phanes' AS49042 announcing the same prefixes from 2023-04-17, with both ASNs going silent in Sept 2025 - the two carried the same address space (RIPEstat, checked 2026-10-30).</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Netherlands (Urk)</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>BPH-Adjacent</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>T4: bulletproof wording in marketing, slow abuse response (Silent Push, reviews); ASN now deregistered</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3074,6 +3658,26 @@
           <t>Moldova-registered LIR (ORG-PHPS1-RIPE, Chisinau, created 2025-05-13) that received AS44477 from Stark Industries on 2025-05-16, four days before the EU listing. RF: 'although PQ.Hosting was referenced within the sanctions multiple times... the company itself was not sanctioned' - status corrected sanctioned -&gt; evading on 2026-09-25 (T1 retained: sanctioned beneficial owners; sanctions-evasion vehicle). ELLIO reports AS44477 has not been visible in the global routing table since about 2026-04-16; the ASN is now deregistered and was never on Spamhaus ASN-DROP. Successor capacity sits with WorkTitans/THE.Hosting and UFO Hosting. PQ HOSTING announced on 2026-03-13 (press release, grade E) that it was withdrawing from European markets, blaming DDoS attacks and a 'reputational campaign' and hinting at a challenge in European courts.</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>Moldova</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Sanctions Evasion (Stark)</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>T1: sanctions-evasion vehicle for EU-listed Stark with sanctioned beneficial owners (not itself listed)</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3156,6 +3760,26 @@
           <t>Russian ISP (company registered 2025-02-18; INN 5043089443; Chekhov district, Moscow region) whose RIPE org was created 2025-03-13. RF identified it as the sanctions-resilient vehicle for Stark Industries' Russian prefixes, with most transfers on 2025-04-13. AS33993 announced 21 prefixes as of 2025-05-16 and 27 today; Spamhaus lists it under stark-industries.solutions. Russian-language sources report THE.Hosting, UFO.Hosting and GEO.Hosting customers losing VPSs around the May 2026 raid (D-grade). Correction 2026-09-25: StormWall s.r.o. provided DDoS-protection fronting for Stark/PQ domains; it is not a BGP upstream.</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Sanctions Evasion (Stark)</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>T2: Stark successor vehicle (RF) on ASN-DROP under stark-industries.solutions</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3238,6 +3862,26 @@
           <t>Founded in 2004 by Andrey Nesterenko, who was arrested in the FIOD raid of 2026-05-18 (name press-reported). Krebs: WorkTitans reached the internet solely through MIRhosting, and AS52000 is the first peer in AS209847's aut-num. The 2008 StopGeorgia.ru hosting is attributed (Jeffrey Carr) to the related Innovation IT Solutions Corp; Nesterenko said he could not verify it. De Volkskrant data showed WorkTitans and MIRhosting as the most-used networks in pro-Russian attacks on Danish bodies (Nov 2025). AS52000 had shrunk to two IPv4 /24s (185.15.209.0/24, 185.15.210.0/24) by Sept 2026 and has announced nothing since 2026-10-19 (AS206932 since 2026-09-29) - both ASNs remain registered to MIRhosting. Tier raised T2 -&gt; T1 on 2026-09-25 (taxonomy T1: subject of a law-enforcement action targeting hosting infrastructure - its founder was arrested in the FIOD action against the WorkTitans network, which reached the internet solely through MIRhosting; reported by Krebs and DatacenterDynamics). The FIOD release names no companies, so whether MIRhosting-owned equipment was among the 800+ servers seized is unconfirmed (only a grade-D blog says so). MIRhosting's own statement of 2026-05-22 says it 'temporarily suspended' services to Work Titans, to which it supplied colocation only, and that service to other customers continued (Krebs paraphrased this as 'paused'). On 2026-06-02 the nLighten data centre cut power to MIRhosting equipment without notice, taking its colocation customers offline; nLighten says it co-operated with the Dutch investigations and terminated the relationship (DCD; Kommersant). Only a Russian-language blog (grade D) also mentions German sites.</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Infrastructure Pillar</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>T1 crit. 2: founder arrested in the FIOD action against WorkTitans, whose sole upstream it was</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3330,6 +3974,26 @@
           <t>Seychelles-registered holder of AS34888 and AS42624, transferred from Simple Carrier LLC (July 2024). RF (Sept-Nov 2025): 11 IPv4 prefixes (2,816 addresses) all via aurologic AS30823, top ten for malicious-activity density in Sept 2025, linked to PrivateAlps. Both ASNs were on Spamhaus ASN-DROP (simplecarrier.net) in Dec 2025 and have since been delisted; neither announces anything now (e.g. 185.196.8.0/22 and 185.208.156.0/22 are unrouted). Do not confuse with the unrelated Iranian swissnetwork.io ASNs (AS199467, AS209373). Correction 2026-09-25: registration is Seychelles, not Switzerland. Status flagged -&gt; dormant on 2026-09-25: both ASNs remain registered to Global-Data but announce nothing, and the newest reporting (RF, Sept-Nov 2025) is more than six months old. The T2 tier stands; watch for re-announcement, particularly behind aurologic. Newer reporting covers past activity only: Qurium (Oct 2026) lists AS42624 among the networks Doppelganger's front proxies moved to in Aug 2024, and Team Cymru (Sept 2026) recorded Akira Cobalt Strike beaconing to AS42624 in June 2025. AS42624 last announced a prefix on 2026-04-07 (RIPEstat), more than six months ago, so 'dormant' stands.</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>aurologic downstream (Seychelles reg.)</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>BPH downstream (dormant)</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>T2: RF top-ten density (Sept 2025), historical ASN-DROP, aurologic downstream; dormant</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3407,6 +4071,26 @@
           <t>Long-running St. Petersburg hoster (AS44050 announces 13 IPv4 prefixes; sister AS34665 PINDC-AS announces 69). Unit 42 (Sept 2023): a Cl0p torrent-seeding server, 95.215.0.76, was hosted by PIN DC on AS34665 (that block is now originated by AS44050). Securonix: TACTICALOCTOPUS C2 addresses 5.8.8.100 and 109.206.240.67 were registered to Petersburg Internet Network Ltd. Its T2 tier rests heavily on the Trend Micro/Interpol 2023 figure (Trend Micro, Aug 2023: 'Petersburg Internet Network Ltd (19%)' among 'prolific offshore bulletproof hosters', behind 1337team Limited 48% and ahead of Flokinet Ltd 13% - the base of the percentages is not stated); without it the vendor evidence supports T3. Not on Spamhaus ASN-DROP.</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>Russia / St. Petersburg</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Pure BPH</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>T2 (tentative): Trend Micro 2023 list (19%), Unit 42 and Securonix tenant reporting; T3 without the Trend Micro figure</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3494,6 +4178,26 @@
           <t>FUNNULL/Triad Nexus backbone ASN; Hong Kong-registered; hosts the bulk of BPH-hosted DCloud scam SLDs.</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>FUNNULL hosting ASN</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>T1 crit. 5: Silent Push, Infoblox, GreyNoise and C2IntelFeeds tie it to FUNNULL and scam/C2 hosting; ASN-DROP</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3586,6 +4290,26 @@
           <t>UK-registered operator (AS213887 announces 29 IPv4 and 7 IPv6 prefixes; the earlier '68 IPv4 / 11 IPv6' is outdated). WAIcore activity predates the AS213887 registration: Spamhaus ASN-DROP listed three earlier WAIcore ASNs (AS202973, AS206425, AS210281; domain waicore.com) by Feb 2024; all three have since been re-issued to unrelated networks (do not block them). A new registration, AS219262 'WAICORE-RUSSIA', is held by a Russian individual and has no routes yet. Qurium (July 2024) says aurologic provides peering for Altawk, WAIcore Hosting and Tnsecurity, and Recorded Future's aurologic report (Nov 2025) names WAIcore Hosting (AS210281) among aurologic's long-standing relationships and lists AS213887 among active aurologic-linked networks (verified 2026-10-30). Not on the current ASN-DROP. Companies House: WAICORE HOSTING LTD (14884560) was dissolved by voluntary strike-off on 2024-06-18; WAICORE LTD (15668439, incorporated 2024-04-22) changed officers on 2026-10-08/09 and received a first Gazette notice for compulsory strike-off on 2026-10-13. Dissolution would not by itself end AS213887.</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>aurologic downstream</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>BPH downstream</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>T2: historical ASN-DROP (three ASNs), serial ASN rotation, Qurium and RF aurologic-downstream naming</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3663,6 +4387,26 @@
           <t>UK-registered network with at least eight ASNs registered to FIRST SERVER LIMITED (AS204997, AS50113, AS205090, AS200740, AS204339, AS204154, AS35196, AS214602; plus a Spanish affiliate on AS199685). Linked to the Sophos (Feb 2026) research on ISPsystem VMmanager default Windows templates, whose reused hostnames appear across LockBit, Qilin, Conti, BlackCat, Ursnif, NetSupport, PureRAT, Lampion, Lumma and RedLine infrastructure - associations of the template ecosystem, not specifically of First Server; Sophos names First Server Limited among the top hosts of the reused hostnames (592 hosts with WIN-J9D866ESIJ2), calls Stark and First Server the two providers with additional links to cybercriminal and Russian state operations, and cites research tying First Server to Doppelganger. Former Hypercore prefixes now originate from AS205090 and AS200740 (lead only). Do not confuse AS204997's handle FIRSTBYTE-AS with the unrelated Iranian AS210703 'FIRSTBYTE-AS' on ASN-DROP. TrickBot was removed (not in the Sophos summary). Qurium (Oct 2026): more than half of 15 Network Management/IP4MARKET prefixes later assigned to Aeza had first been used by NTX Technologies and First Server Limited, and a Spanish 'First Server, SL' (Alicante) appeared in March 2026. Companies House: FIRST SERVER LIMITED (14459750) received a first Gazette notice for compulsory strike-off on 2026-10-13 (name match to the RIPE org).</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>Russia-linked (UK reg.)</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>BPH (VMmanager fleet)</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>T2: Sophos names it a top host of reused VMmanager templates tied to criminal and state activity; GreyNoise exploitation sources; Qurium IP-supply link</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3730,6 +4474,26 @@
           <t>UK company SILENT CONNECTION LTD (Companies House 15578799), dissolved by compulsory strike-off on 2025-01-28. RF ranked Silent Connection #9 in its 2025 Threat Density top 10; Orange Cyberdefense placed Blue Stylthon WsgiDAV servers delivering XWorm/AsyncRAT (Nov-Dec 2024) in AS215240. As of 2026-09-25 the ASN is registered to Microdex UG (DE) under a new handle and announces nothing, so the earlier 'network remains live' note is outdated. Another German UG holds a second ASN under the same MICRODEX-AS handle - a possible re-homing by the same operator (unproven).</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>UK Shell</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>Corporate Shell</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>T3 (historical): RF 2025 Threat Density #9 and Orange Cyberdefense XWorm/AsyncRAT hosting; company dissolved, ASN re-registered</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3797,6 +4561,26 @@
           <t>UK shell registered as DOLPHIN 1337 LIMITED (Companies House 15589896; no company named 'Dolphon' exists), dissolved by compulsory strike-off on 2025-01-14; AS215208 (reported registered 2024-03-28) is now held by PT Citra Celebas Multimedia (Indonesia) and announces three live prefixes - this is ASN recycling, not a dissolved shell still operating, so the ASN must not be blocked. The only source is Excedo. RF's 2025 top-10 #10 is 'DolphinHost Limited' (AS214717/AS207184, dolphinhost.net), a different entity; the repo previously conflated the two. The '1337' naming link to ELITETEAM is speculative. Tier lowered T3 -&gt; T5 on 2026-09-25 (historically associated; currently quiescent; single source).</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>UK Shell</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>Corporate Shell (ASN recycled)</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>T5: historically associated, single source (Excedo); ASN recycled</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3859,6 +4643,26 @@
           <t>AS213194, registered to a Russian individual (the AS-name derives from the registrant's surname), announces only 193.37.69.0/24. It is the same ASN the Zservers row lists as a post-sanction hop: Intrinsec (March 2025) assessed with high confidence that Zservers prefixes moved to AS213194, AS61336 and AS213010. A relayed Silent Push 2025 table flags it for 100% DGA domains and a TutaMail abuse contact. Tier raised T5 -&gt; T3 on 2026-09-25; merging into the Zservers row is an alternative. Not on Spamhaus ASN-DROP.</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>Zservers successor hop</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>T3: Zservers successor hop (Intrinsec) on an individual-registered ASN</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3931,6 +4735,26 @@
           <t>Four ASNs registered to 'net innovation llc' - AS62864 (ARIN; 14 prefixes including DROP-listed 164.155.0.0/16 and 168.80.0.0/15 space), AS34985 (7), AS23865 (5) and AS149286 (none) - all on Spamhaus ASN-DROP under netinnovation.net (cc JP). A relayed Silent Push 2025 table flags AS34985 for a Gmail abuse contact, DGA usage and an 18-day abuse response. The earlier 'no public CTI designation' note was wrong. Raised T5 -&gt; T3 (status flagged) on 2026-09-25; the ASN-DROP escalation rule implies T2 once a second independent B/C source is read directly.</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>US reg. / mixed APAC-ARIN space</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>BPH (ASN-DROP listed)</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>T3 (T2 pending a second source): all four ASNs on ASN-DROP; Silent Push relay</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4008,6 +4832,26 @@
           <t>Renamed from 'Tiger Net (SOW-A)' on 2026-09-25. Tiger Network Limited (GB) holds AS48589 (5 prefixes, 14,848 addresses of Asian space) and AS211121 (4 prefixes); both are on Spamhaus ASN-DROP (imtigernet) and their prefixes overlap Spamhaus DROP. A relayed Silent Push 2025 table lists 'AS48589 SOW-A-AS (Tiger Net) - Ukraine, Gmail, DGA'. No current 'SOW-A' handle exists; the only registry match, AS43613 'SOWA' (LLC BIGNET UKRAINE), is a separate ASN-DROP entry, so the relay may have merged two records. Raised T5 -&gt; T3 (status flagged); T2 pending a second independent B/C source. Companies House: TIGER NETWORK LIMITED (11161830, incorporated 2018-01-22) files dormant accounts and received a first Gazette notice for compulsory strike-off on 2026-10-13 (name match to the RIPE org).</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>UK reg. / Asian address space</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>BPH (ASN-DROP listed)</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>T3 (T2 pending a second source): both ASNs on ASN-DROP; Silent Push relay</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4075,6 +4919,26 @@
           <t>AS49217 is registered to HOSTYPE LLC (registry cc US; Spamhaus cc TR; a relayed Silent Push 2025 table calls it a Wyoming shell with a Gmail abuse contact, DGA usage and a 30-day abuse response). It was on Spamhaus ASN-DROP in the Feb 2024 and Dec 2025 snapshots, has since been delisted, and announces nothing. Fits T5's 'historically associated with abuse, currently quiescent'; status set to 'dormant' on 2026-09-25 - watch for re-announcement or transfer.</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>US (Wyoming LLC) / Turkey</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>Watch list (dormant)</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>T5: historically on ASN-DROP, currently quiescent (dormant)</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4152,6 +5016,26 @@
           <t>Singapore-registered hosting brand. A relayed Silent Push 2025 table lists AS140224 'STARCLOUD GLOBAL SG' as Triad Nexus infrastructure with a residential Colorado address and a 4-day abuse response; a phishing-ASN ranking put AS140224 at #13 (237,056 routed IPv4; 3,032 phishing attacks). ESET lists Silver Fox domains on 149.104.24.24 with hosting provider 'STARCLOUD GLOBAL PTE. LTD.' (first seen 2026-03-10), and a Cobalt Strike C2 on 154.38.114.115 was recorded under the same provider (Sept 2026); both IPs are now routed by other HK ASNs. AS140224 now shows as 'Nebula Global LLC' (US) and AS149040 announces nothing. CORRECTION 2026-09-25: StarCloud is NOT an OFAC designee - the earlier 'OFAC May 29 2025 (via FUNNULL lineage)' entry was removed (OFAC named only Funnull Technology Inc. and Liu Lizhi).</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>Singapore / APAC</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>Triad Nexus front brand</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>T3: Triad Nexus front brand (Silent Push), ESET Silver Fox hosting, phishing-ASN ranking</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4219,6 +5103,26 @@
           <t>Dual-use Russian DDoS mitigation and hosting provider. Main network is AS57724 (21 IPv4 prefixes); AS49612 now announces a single /24 under the handle COGNITIVE-CLOUD-NET; a further 'DDoS-Guard Corp' ASN (AS262254) is dark. Historically an upstream of ELITETEAM (as of Sept 2022, per Team Cymru). Not on Spamhaus ASN-DROP. It protected or fronted rather than directly hosted: the 8kun/QAnon sites moved behind DDoS-Guard in Oct 2020 and Parler in Jan 2021 (Krebs; Reuters). Not classified BPH, but persistently present in the Russian cybercrime ecosystem.</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>Dual-use / Peering</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>T5: dual-use DDoS protection that has fronted abusive sites (Parler, 8kun); historical upstream of ELITETEAM</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4286,6 +5190,26 @@
           <t>Small US-registered operator (AS14315; 51 IPv4 prefixes; ipverse role 'midsize transit') appearing alongside Proton66, Railnet and Femo IT in a Lumma malware hunt (single source, re-read 2026-10-30: the Intel Insights 'Bulletproof Hosting Hunt' post of 2025-07-27 lists one 1GSERVERS address, 104.251.123.89, among ten Lumma-communicating IPs on ten ASNs that also include M247, Namecheap and G-Core, and makes no BPH claim about 1GSERVERS - very weak evidence). Not on Spamhaus ASN-DROP.</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Watch list</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>T5: single weak source (one Lumma IP in a blog list)</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4383,6 +5307,26 @@
           <t>Major no-KYC RDP/VPS host (RF 2025 Threat Density #2). On 2025-11-12 Dutch police seized about 250 physical servers in data centres in The Hague and Zoetermeer (thousands of virtual servers taken offline) of a bulletproof hoster active since 2022 and seen in 80+ investigations (ransomware, botnets, phishing, CSAM). Police did not name it; sources told BleepingComputer it was CrazyRDP, which went offline. Dutch police told BleepingComputer the case is NOT connected to Operation Endgame (the earlier Endgame label was wrong). The Limenet (AS394711) and Delis (AS211252) ASNs rest on community sources and Spamhaus ASN-DROP listings of Feb 2024 (limenet.io; delis.one); both ASNs have since been re-issued to unrelated companies - do not block them.</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>Netherlands (servers)</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>RDP-as-a-service (seized)</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>T1 crit. 2+4: Dutch police seizure (Nov 2025, press-attributed); RF 2025 Threat Density #2</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4480,6 +5424,26 @@
           <t>Hong Kong ISP (APNIC-registered 2019) announcing 113,664 IPv4 addresses in 168 prefixes on AS138915 (Sept 2026; the earlier '182,272 / 50+ netblocks' is outdated). RF ranks Kaopu #4 in its 2025 Threat Density top 10. Spamhaus ASN-DROP lists three kaopuyun.com ASNs: AS138915, AS58854 and AS154177 (LIGHT NODE LIMITED, 129 IPv4 prefixes); a fourth (AS140666, ANY DIGITAL PTE. LTD.) was listed earlier and removed. Independent vendor evidence: RF Insikt (RedHotel heavily favouring Kaopu for C2, 2022-23); ESET (ToolShell SharePoint exploitation from Kaopu IPs, July 2025); Arctic Wolf (malicious FortiGate SSO logins, Dec 2025); Sekoia (Bulbature/GobRAT staging servers all on AS138915); GreyNoise React2Shell sources. Tier raised T3 -&gt; T1 (status flagged) on 2026-09-25 (taxonomy T1: RF top-decile Threat Density - #4 in RF's 2025 top 10, the basis also used for Femo IT/Defhost at #8; minimum evidence met by RF, Spamhaus, ESET, Sekoia and GreyNoise). Proofpoint (2026): TA416 has heavily favoured Evoxt Enterprise (AS149440), XNNET LLC (AS6134) and Kaopu Cloud HK (AS138915) for C2 throughout 2025 and 2026.</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>Hong Kong/Global</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>APAC BPH cluster</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>T1 crit. 4: RF 2025 Threat Density #4; Spamhaus, ESET, Sekoia, GreyNoise, Proofpoint corroborate</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4567,6 +5531,26 @@
           <t>Russian no-KYC cryptocurrency exchange; primary Garantex successor laundering rail for the BPH/ransomware ecosystem.</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>Russia / Kyrgyzstan</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>Financial Enabler (Garantex successor)</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>T1 crit. 1: OFAC (Aug 2025) and UK designations as Garantex successor</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4649,6 +5633,26 @@
           <t>Sanctions-evasion stablecoin and swap rail bridging sanctioned Russian crypto into mainstream stablecoins.</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>Russia / Kyrgyzstan</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>Financial Enabler (sanctions-evasion stablecoin)</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>T1 crit. 1: OFAC, UK and EU designations; A7 Network designated a TCO (Oct 2026)</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4721,6 +5725,26 @@
           <t>Iranian cryptocurrency exchange sanctioned for terror finance and sanctions evasion.</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>Financial Enabler</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>T2: designated on non-cyber grounds (terror finance, Iran); tiered on cyber-enablement evidence only</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4788,6 +5812,26 @@
           <t>Iranian cryptocurrency exchange sanctioned June 2026.</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>Financial Enabler</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>T3: designated under E.O. 13902 (non-cyber); limited cyber-enablement evidence</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4855,6 +5899,26 @@
           <t>Iranian cryptocurrency exchange sanctioned June 2026.</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>Financial Enabler</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>T3: designated under E.O. 13902 (non-cyber); limited cyber-enablement evidence</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4922,6 +5986,26 @@
           <t>Iranian cryptocurrency exchange sanctioned June 2026.</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>Financial Enabler</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>T3: designated under E.O. 13902 (non-cyber); limited cyber-enablement evidence</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5029,6 +6113,26 @@
           <t>Confirmed bulletproof / AS-leasing operator ('BTCloud') running rotating UK nominee shells; live as Limited Network LTD (AS213790)/AS213388; masscan-as-a-service to IABs.</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>Lithuania / Bulgaria (UK shells)</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>Pure BPH (AS-leasing)</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>T1 crit. 3: self-advertised bulletproof host with infrastructure evidence (Intrinsec); ASNs and all transit ASNs on ASN-DROP</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5116,6 +6220,26 @@
           <t>German micro-provider, bulletproof-adjacent; corroborated abuse signal with single-honeypot caveat.</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>BPH downstream / upstream of Virtualine</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>T2 via ASN-DROP escalation rule: ASN-DROP (four ASNs) plus GreyNoise and RF</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5198,6 +6322,26 @@
           <t>Chinese-language Telegram guarantee/escrow marketplace and laundering facilitator; Huione successor.</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>SEA / China</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>Financial Enabler (guarantee marketplace)</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>T2 (Financial Enabler): RF and Flare document a Huione-successor guarantee marketplace serving fraud and laundering groups</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5270,6 +6414,26 @@
           <t>Telegram guarantee marketplace for the SEA scam economy; Huione successor, wound down Jan 2026.</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>Financial Enabler (public market ceased)</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>T2 (Financial Enabler): Elliptic ($12B processed) and FinCEN document it as Huione successor</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5352,6 +6516,26 @@
           <t>Cambodian successor facilitator to the shut-down Huione Pay laundering operation.</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>Cambodia</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>Financial Enabler (Huione successor)</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>T2 (Financial Enabler): FinCEN proposed Section 311 coverage as Huione successor (Jun 2026)</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5434,6 +6618,26 @@
           <t>Malicious residential-proxy / anonymity-infrastructure TAE built on covertly infected devices; LE-disrupted May 2026 (Asocks attribution is press-sourced).</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>Netherlands (servers) / global</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>Residential-proxy TAE</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>T2: Dutch residential-proxy botnet takedown press-attributed to Asocks (police did not name it), plus vendor reporting</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5531,6 +6735,26 @@
           <t>OFAC-sanctioned Aeza expansion/front entity registered in Uzbekistan; designated alongside Hypercore in the Nov 2025 Aeza action.</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>Uzbekistan (Tashkent)</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>Sanctions Evasion (Aeza)</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>T1 crit. 1: OFAC designation (Nov 2025) as Aeza evasion vehicle</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5613,6 +6837,26 @@
           <t>OFAC-sanctioned criminal no-log VPN / anonymization enabler.</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>Ukrainian admin / ~27 countries</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>Anonymization/Proxy Enabler (criminal VPN)</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>T1 crit. 1+2: OFAC cyber designation (Jul 2026) and Operation Saffron takedown (May 2026)</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5700,6 +6944,26 @@
           <t>LE-seized commercial residential-proxy platform (Alarum/NASDAQ: ALAR) with botnet-sourced exit nodes.</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>Israel / global exit nodes</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>Anonymization/Proxy Enabler (commercial, botnet-sourced)</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>T2: FBI domain seizure and GTIG disruption of a botnet-sourced proxy network run by a listed company that disputes the allegations</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5797,6 +7061,26 @@
           <t>HK reseller ASN, recurring China-nexus C2 and mass-exploitation host (SHANGXING/Fastmos/Arosscloud).</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>Hong Kong/US</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>HK reseller ASN (China-nexus C2 / exploitation staging)</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>T2: GreyNoise exploitation source, C2IntelFeeds Cobalt Strike C2s plus first-party Gshell and exploit-staging findings</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5894,6 +7178,26 @@
           <t>Bulgarian commercial hosting brand (HZ Hosting Ltd; four country-coded ASNs) repeatedly chosen by Cl0p and other advanced actors; gray-zone rather than bulletproof on current evidence.</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>Bulgaria (servers NL/US/CA/EE and others)</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>BPH-Adjacent (Cl0p-preferred)</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>T4: repeated actor-preferred tenancy (Cl0p and others) without evidence of deliberate enablement; KYC and AUP present</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5986,6 +7290,26 @@
           <t>Hong Kong-anchored ring of rotating shell ASNs linked to the Proton66/PROSPERO bulletproof cluster; five ASNs on Spamhaus ASN-DROP.</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>Hong Kong (UK/RU shells)</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>Pure BPH shell ring (Proton66-linked)</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>T2 via ASN-DROP escalation rule: ASN-DROP (six ASNs) plus Intrinsec and SpiderLabs</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6078,6 +7402,26 @@
           <t>Lithuanian hoster and BtHoster transit provider; two serveroffer.lt ASNs on Spamhaus ASN-DROP.</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>Upstream Enabler (BtHoster transit)</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>T2 (Upstream Enabler): ASN-DROP plus upstream of T1 BtHoster</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6165,6 +7509,26 @@
           <t>UK VPS provider on Spamhaus ASN-DROP and a persistent GreyNoise-tracked mass-scanning source.</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>Mass-scanning source</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>T2 via ASN-DROP escalation rule: ASN-DROP plus GreyNoise</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6252,6 +7616,26 @@
           <t>Romanian provider on Spamhaus ASN-DROP hosting persistent high-volume scanning and exploitation sources.</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>Mass-scanning / exploitation source</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>T2 via ASN-DROP escalation rule: ASN-DROP plus GreyNoise</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6334,6 +7718,26 @@
           <t>PRC 'infrastructure quartermaster' proxy/ORB platform serving state hackers; domains seized by DOJ/FBI in Aug 2026.</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>Anonymization/Proxy Enabler (state ORB; seized)</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>T1 crit. 2: DOJ/FBI court-authorised domain seizure (Aug 2026)</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6411,6 +7815,26 @@
           <t>Multi-brand residential-proxy network used by 550+ threat groups; disrupted by Google in Jan 2026.</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>Global exit nodes</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>Anonymization/Proxy Enabler (residential proxy)</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>T2: GTIG legal disruption (Jan 2026) of a proxy network used by 550+ threat groups; private-sector, not LE</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6523,6 +7947,26 @@
           <t>Self-styled bulletproof VPS/RDP and fast-flux host; its .com domain moved to FBI seizure nameservers on the day of Operation Omegaline (Oct 2026); now on anonrdp.st and Blatant Technologies AS403005.</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>Seychelles shell / Lithuania, Netherlands (servers)</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>Pure BPH</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>T1 crit. 2+3: domain on FBI seizure nameservers (Oct 2026); self-advertised bulletproof with infrastructure evidence (Silent Push, Intrinsec, registry)</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6605,6 +8049,26 @@
           <t>Kyrgyz exchange assessed as a Grinex front; UK-designated Oct 2026.</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>Kyrgyzstan</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>Financial Enabler (Grinex front)</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>T1: front of T1 Grinex (TRM, high confidence); UK-designated (Russia regime)</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6682,6 +8146,26 @@
           <t>Cryptomus/Heleket crypto payment rail used by BPH providers; UK-designated Oct 2026.</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>Canada / global</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>Financial Enabler (crypto payment rail)</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>T2 (Financial Enabler): UK designation on non-cyber grounds; Chainalysis and TRM name it the payment rail of tracked BPH providers</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6774,6 +8258,26 @@
           <t>Sevastopol-registered sister of GCSAS behind the 4VPS bulletproof VPS brand; RF 2025 top-10 TAE.</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>Russia (Sevastopol, occupied Crimea)</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>Pure BPH (4VPS front)</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>T1 crit. 4+5: RF 2025 Threat Density #7 (as 4VPS); Intrinsec, eSentire, RF and Ukraine NCCC; ASN-DROP</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6861,6 +8365,26 @@
           <t>Crypto-paid anonymous VPS (BitLaunch); top host of DDoSia C2s per Recorded Future.</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>US (Wyoming) / UK</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>BPH-Adjacent (crypto-paid anonymous VPS)</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>T3: several B-grade vendors with specific indicators (RF, Group-IB, Arctic Wolf) but no ASN-DROP listing and abuse response present</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6933,6 +8457,26 @@
           <t>BVI IPv4 LIR that supplied address space to Aeza and First Server (Qurium).</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>British Virgin Islands</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>Upstream Enabler (IPv4 LIR / broker)</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>T5: named in a single report (Qurium) as IPv4 supplier to Aeza and First Server</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7015,6 +8559,26 @@
           <t>Armenian IPv4 LIR that assigned address space to Aeza (Qurium).</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>Armenia / Russia</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>Upstream Enabler (IPv4 LIR)</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>T5: named in a single report (Qurium) as IPv4 supplier to Aeza</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7097,6 +8661,26 @@
           <t>Dutch budget VPS host prominent in Sophos VM-template data; watch-list.</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>BPH-Adjacent (dual-use VPS)</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>T5: dual-use VPS host with periodic abuse (Sophos, SOCRadar)</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7182,6 +8766,26 @@
       <c r="Y80" t="inlineStr">
         <is>
           <t>Malaysian VPS repeatedly used by Chinese and Russia-aligned state actors; watch-list.</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>Actor-preferred VPS (repeat tenancy)</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>T5: mainstream VPS repeatedly used by state actors (Proofpoint, Trend Micro); repeat-tenancy pattern</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>

--- a/BPH_Master.xlsx
+++ b/BPH_Master.xlsx
@@ -1426,6 +1426,11 @@
           <t>AS213999 (THE-CLIENTS; registered, no routes)</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Former AS209847 prefixes originated by AS51722 (PIXOOF TEKNOLOJI, TR) since 2026-09-10 under route objects THE-HOSTING-MNT created on 2026-09-07/10: 193.46.56.0/24; 45.89.52.0/24; 5.180.45.0/24; 62.3.12.0/24; 94.131.108.0/24 (route objects also cover 103.231.75.0/24; 185.153.182.0/24; 185.234.66.0/24; 45.12.143.0/24; 94.131.123.0/24). 2.56.127.0/24 (from AS209847) and 109.120.130.0/24 (from AS213999) are now originated by AS203273 (Aeza's NetCrafters)</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Netherlands</t>
@@ -1498,7 +1503,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Dutch post-sanctions successor to Stark Industries/PQ.Hosting. WorkTitans B.V. was formed in 2019 as a recruitment firm; its Stark-successor role starts with RIPE org ORG-THE3-RIPE (created 2025-05-28) and prefix transfers from 2025-05-29; AS209847 was created 2025-06-24 and AS213999 (THE-CLIENTS) also belongs to WorkTitans. AS209847 announced 21 prefixes in Aug 2025 and 11 on 2026-09-25; it then withdrew most of its space between 2026-10-01 and 2026-10-14 (and its IPv6 on 2026-10-27), leaving two /24s (45.120.176.0/24, 185.235.240.0/24) - the withdrawn blocks had not reappeared under another origin by 2026-10-30. MIRhosting, its former sole upstream, went dark on 2026-10-19; AS209847 now reaches the internet via ADCDATA.COM (AS135330) and FBW Networks (AS49434). GreyNoise confirmed the migration from AS44477 (Aug-Nov 2025); Censys matched RDP hostname reuse (WIN-J9D866ESIJ2). FIOD raided the Dutch nodes on 2026-05-18: 800+ servers seized at data centres in Dronten and Schiphol-Rijk; WorkTitans owner Youssef Zinad and MIRhosting founder Andrey Nesterenko arrested (names press-reported). ELLIO saw scanning back near pre-raid levels more than a week later, but later reports conflict (one telemetry source reports a 94% drop in the indexed fleet; a Russian-language hosting knowledge base says the THE.Hosting site announced it had stopped operating). Status evading -&gt; seized on 2026-10-30: the May 2026 FIOD action seized infrastructure (partial seizure), and by mid-October 2026 the network had withdrawn nearly all of its space (see below). Check Point (June 2026): three Iranian groups including MuddyWater used WorkTitans infrastructure for core operations.</t>
+          <t>Dutch post-sanctions successor to Stark Industries/PQ.Hosting. WorkTitans B.V. was formed in 2019 as a recruitment firm; its Stark-successor role starts with RIPE org ORG-THE3-RIPE (created 2025-05-28) and prefix transfers from 2025-05-29; AS209847 was created 2025-06-24 and AS213999 (THE-CLIENTS) also belongs to WorkTitans. AS209847 announced 21 prefixes in Aug 2025 and 11 on 2026-09-25; it then withdrew most of its space between 2026-10-01 and 2026-10-14 (and its IPv6 on 2026-10-27), leaving two /24s (45.120.176.0/24, 185.235.240.0/24) - the withdrawn blocks had not reappeared under another origin by 2026-10-30. MIRhosting, its former sole upstream, went dark on 2026-10-19; AS209847 now reaches the internet via ADCDATA.COM (AS135330) and FBW Networks (AS49434). GreyNoise confirmed the migration from AS44477 (Aug-Nov 2025); Censys matched RDP hostname reuse (WIN-J9D866ESIJ2). FIOD raided the Dutch nodes on 2026-05-18: 800+ servers seized at data centres in Dronten and Schiphol-Rijk; WorkTitans owner Youssef Zinad and MIRhosting founder Andrey Nesterenko arrested (names press-reported). ELLIO saw scanning back near pre-raid levels more than a week later, but later reports conflict (one telemetry source reports a 94% drop in the indexed fleet; a Russian-language hosting knowledge base says the THE.Hosting site announced it had stopped operating). Status evading -&gt; seized on 2026-10-30: the May 2026 FIOD action seized infrastructure (partial seizure), and by mid-October 2026 the network had withdrawn nearly all of its space (see below). Check Point (June 2026): three Iranian groups including MuddyWater used WorkTitans infrastructure for core operations. WorkTitans' own maintainer (THE-HOSTING-MNT) created route objects on 2026-09-07/10 authorising AS51722 (PIXOOF TEKNOLOJI, Turkey) to originate its space; five former AS209847 prefixes have been announced from AS51722 since 2026-09-10 (REGISTRY-SNAPSHOT-2026-10).</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1876,7 +1881,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Originated by AS202412 Jan-Oct 2026 and on Spamhaus DROP at the seizure (94.154.35.0/24 and 45.132.180.0/24 delisted by 2026-10-30): 91.92.240.0/22; 158.94.208.0/22; 178.16.52.0/22 (these three ex-AS209800); 45.132.180.0/24; 94.26.38.0/24 (RetryHost block; re-originated by AS51130 since 2026-10-28); 94.154.35.0/24; 94.154.40.0/24; 94.154.46.0/24; 130.12.180.0/24; 146.19.125.0/24; 193.30.241.0/24. Also short-lived /24s from broker-leased space that moves between unrelated ASNs (re-check the current origin before blocking): 45.74.7.0/24; 45.74.57.0/24; 45.74.59.0/24; 104.250.184.0/24; 172.111.246.0/24</t>
+          <t>Originated by AS202412 Jan-Oct 2026 and on Spamhaus DROP at the seizure (94.154.35.0/24 and 45.132.180.0/24 delisted by 2026-10-30): 91.92.240.0/22; 158.94.208.0/22; 178.16.52.0/22 (these three ex-AS209800); 45.132.180.0/24; 94.26.38.0/24 (RetryHost block; re-originated by AS51130 since 2026-10-28); 94.154.35.0/24; 94.154.40.0/24; 94.154.46.0/24; 130.12.180.0/24; 146.19.125.0/24; 193.30.241.0/24. From 2026-10-27 16:00 UTC, when AS202412 went dark, AS6461 (Zayo Bandwidth, US) originates all of these except 94.26.38.0/24, most of them seen by only about 10 RIS full-feed peers. Also short-lived /24s from broker-leased space that moves between unrelated ASNs (re-check the current origin before blocking): 45.74.7.0/24; 45.74.57.0/24; 45.74.59.0/24; 104.250.184.0/24 (these four also originated by AS6461 since 2026-10-27, 45.74.57.0/24 alongside AS9009 and 104.250.184.0/24 alongside AS205960); 172.111.246.0/24 (last originated by AS219199 until 2026-10-27; not announced since)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1956,7 +1961,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Virtualine Technologies is the operator behind Railnet LLC (AS214943, Kentucky LLC), KPROHOST (AS214940), the 'metaspinner' AS209800 front, likely Karina Rashkovska (AS215789) and OMEGATECH (AS202412) - at least five number-resource identities. SEIZED 2026-10-27 (Operation Omegaline): the FBI Washington Field Office seized virtualine.net under an E.D. Va. warrant, with Polizei Hessen, Politie Midden-Nederland, the UK NCA and private partners OverRIPE and Lumen; Chainalysis supported. DOJ names the aliases Secury, Massgod, Spamhouse, Lanedo and Omegatech, alleges it knowingly hosted 'Vendor 1' (a forum selling CSAM and non-consensual intimate images, with hack-for-hire) despite notices from German, Canadian and Australian police, NCMEC and a victim's attorney from Jan 2026, and that it laundered customer payments taken via unhosted 'BTC [NO-AML]' addresses. Forum advertising: Exploit.in from 2024-08-28 ('all illegal/black hat activities ... except for child contents and terrorism', Sept 2024); HackForums ('ignored more abuse than your last three therapists', June 2025); in Mar 2026 it sold an 'additional protection plan' moving a customer's server to an unaffiliated shell company after an LE request. Dutch police seized dozens of physical servers in Limburg (hundreds of VPS offline; data on 3,000+ customers) and say the FBI and German police acted against suspects and crypto at the same time; no operators were named or charged. TRM: most illicit-attributed crypto of any TRM-labelled BPH in 2026 (inflows ~44% Russian drug market, ~17% sextortion, ~13% mixer, ~5% ransomware; also StealC and the BPH Volhav). Network: Silent Push saw the move from AS214943 to AS202412 on 2026-02-11; AS202412 originated 24 /24s in the two weeks before the seizure (all on Spamhaus DROP) and has been seen by 1 of 323 RIS peers since 2026-10-27; its last neighbours were Pfcloud (AS51396) and PEERYX (AS213382). The operator posted an open letter on virtualine.org denying the allegations and saying it could rebrand in 'a day, perhaps even less' - watch for a successor ASN. LEAD (not attributed): AS219199 (GENYUS SOFT LTD [SC], created 2026-07-15) announced four broker-leased /24s from 2026-10-22, including 172.111.246.0/24 previously on AS202412, and withdrew them on the morning of the seizure; only a community post calls it Virtualine, and Spamhaus lists it under genyus.sc. Earlier history: RF ranked Virtualine #1 by Threat Density for 2025; Intrinsec documented UAC-0050/UAC-0006 activity and in May 2026 assessed OMEGATECH as 'yet another network created by Virtualine'; in April 2025 it shifted IPv4 resources to AS209800 (Spamhaus reported the expansion in Sept 2025), and those ranges later moved to AS202412. Status flagged -&gt; seized 2026-10-29; tier stays T1 (raised T2 -&gt; T1 on 2026-09-25). Post-seizure routing (RIPEstat/RIPE DB, 2026-10-30): (1) 94.26.38.0/24 - registered to the RIPE org RetryHost, which is maintained by VIRTUALINE-MNT - got a new route object on 2026-10-28 (11:06 UTC, created by the parent LIR's maintainer) and has since been announced by AS51130 (Homaye Jahan Nama Co., Iran; dormant apart from this block) via AS214329 (BGP Network LLC) - a possible relocation, not yet attributed; (2) most other former AS202412 /24s have been seen since 2026-10-27 16:00 with origin AS6461 by only ~10 of 323 RIS peers (cause unknown); (3) Spamhaus removed 94.154.35.0/24 and 45.132.180.0/24 from DROP. | Merged record (was a duplicate AS214943 row).</t>
+          <t>Virtualine Technologies is the operator behind Railnet LLC (AS214943, Kentucky LLC), KPROHOST (AS214940), the 'metaspinner' AS209800 front, likely Karina Rashkovska (AS215789) and OMEGATECH (AS202412) - at least five number-resource identities. SEIZED 2026-10-27 (Operation Omegaline): the FBI Washington Field Office seized virtualine.net under an E.D. Va. warrant, with Polizei Hessen, Politie Midden-Nederland, the UK NCA and private partners OverRIPE and Lumen; Chainalysis supported. DOJ names the aliases Secury, Massgod, Spamhouse, Lanedo and Omegatech, alleges it knowingly hosted 'Vendor 1' (a forum selling CSAM and non-consensual intimate images, with hack-for-hire) despite notices from German, Canadian and Australian police, NCMEC and a victim's attorney from Jan 2026, and that it laundered customer payments taken via unhosted 'BTC [NO-AML]' addresses. Forum advertising: Exploit.in from 2024-08-28 ('all illegal/black hat activities ... except for child contents and terrorism', Sept 2024); HackForums ('ignored more abuse than your last three therapists', June 2025); in Mar 2026 it sold an 'additional protection plan' moving a customer's server to an unaffiliated shell company after an LE request. Dutch police seized dozens of physical servers in Limburg (hundreds of VPS offline; data on 3,000+ customers) and say the FBI and German police acted against suspects and crypto at the same time; no operators were named or charged. TRM: most illicit-attributed crypto of any TRM-labelled BPH in 2026 (inflows ~44% Russian drug market, ~17% sextortion, ~13% mixer, ~5% ransomware; also StealC and the BPH Volhav). Network: Silent Push saw the move from AS214943 to AS202412 on 2026-02-11; AS202412 originated 24 /24s in the two weeks before the seizure (all on Spamhaus DROP) and has been seen by 1 of 323 RIS peers since 2026-10-27; its last neighbours were Pfcloud (AS51396) and PEERYX (AS213382). The operator posted an open letter on virtualine.org denying the allegations and saying it could rebrand in 'a day, perhaps even less' - watch for a successor ASN. LEAD (not attributed): AS219199 (GENYUS SOFT LTD [SC], created 2026-07-15) announced four broker-leased /24s from 2026-10-22, including 172.111.246.0/24 previously on AS202412, and withdrew them on the morning of the seizure; only a community post calls it Virtualine, and Spamhaus lists it under genyus.sc. Earlier history: RF ranked Virtualine #1 by Threat Density for 2025; Intrinsec documented UAC-0050/UAC-0006 activity and in May 2026 assessed OMEGATECH as 'yet another network created by Virtualine'; in April 2025 it shifted IPv4 resources to AS209800 (Spamhaus reported the expansion in Sept 2025), and those ranges later moved to AS202412. Status flagged -&gt; seized 2026-10-29; tier stays T1 (raised T2 -&gt; T1 on 2026-09-25). Post-seizure routing (RIPEstat/RIPE DB, 2026-10-30): (1) 94.26.38.0/24 - registered to the RIPE org RetryHost, which is maintained by VIRTUALINE-MNT - got a new route object on 2026-10-28 (11:06 UTC, created by the parent LIR's maintainer) and has since been announced by AS51130 (Homaye Jahan Nama Co., Iran; dormant apart from this block) via AS214329 (BGP Network LLC) - a possible relocation, not yet attributed; (2) most other former AS202412 /24s have been seen since 2026-10-27 16:00 with origin AS6461 by only ~10 of 323 RIS peers (cause unknown); (3) Spamhaus removed 94.154.35.0/24 and 45.132.180.0/24 from DROP. | Merged record (was a duplicate AS214943 row). After the seizure, AS6461 (Zayo Bandwidth) began originating the former AS202412 prefixes at 2026-10-27 16:00 UTC, the hour AS202412 dropped to one RIS peer; the reason is not public (REGISTRY-SNAPSHOT-2026-10).</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2628,6 +2633,11 @@
           <t>AS203727 (historical; reassigned to byon GmbH [DE] - do not block); AS215826 (Partner Hosting LTD [GB]; listed under altawk.com in Dec 2025, delisted)</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Former AS209946 prefixes originated by AS218688 (WULDI LLC; ASN registered 2026-09-11) since 2026-09-22: 185.102.115.0/24; 193.148.56.0/24; 193.148.57.0/24; 45.13.186.0/24; 95.85.238.0/24</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>Russia</t>
@@ -2680,7 +2690,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Named by Qurium as Russia-linked infrastructure behind aurologic serving the Doppelganger disinformation network, historically on AS203727 (now re-issued to byon GmbH - do not block). Spamhaus now lists AS209946 (ALINDA LLC, UA) under altawk.com; it announced 4 prefixes, all on Spamhaus DROP, until 2026-10-02 and has announced nothing since (still listed; RIPEstat, 2026-10-30). An earlier Altawk-domain ASN, AS215826, was listed in Dec 2025 and later removed. Tier raised T3 -&gt; T2 on 2026-09-25 (ASN-DROP inclusion plus Qurium). Companies House: PARTNER HOSTING LTD (15332944), the likely GB holder behind the former AS215826, was dissolved on 2026-01-20 (name match); Sophos lists Partner Hosting LTD among the top hosts of the reused ISPsystem VM hostnames.</t>
+          <t>Named by Qurium as Russia-linked infrastructure behind aurologic serving the Doppelganger disinformation network, historically on AS203727 (now re-issued to byon GmbH - do not block). Spamhaus now lists AS209946 (ALINDA LLC, UA) under altawk.com; it announced 4 prefixes, all on Spamhaus DROP, until 2026-10-02 and has announced nothing since (still listed; RIPEstat, 2026-10-30). An earlier Altawk-domain ASN, AS215826, was listed in Dec 2025 and later removed. Tier raised T3 -&gt; T2 on 2026-09-25 (ASN-DROP inclusion plus Qurium). Companies House: PARTNER HOSTING LTD (15332944), the likely GB holder behind the former AS215826, was dissolved on 2026-01-20 (name match); Sophos lists Partner Hosting LTD among the top hosts of the reused ISPsystem VM hostnames. All five prefixes AS209946 announced before going dark are originated since 2026-09-22 by AS218688 (WULDI LLC), an ASN registered on 2026-09-11 - a successor candidate, not yet attributed (REGISTRY-SNAPSHOT-2026-10).</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -3446,12 +3456,12 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>SPAMHAUS-BPH; OSINT-FORUMS; REGISTRY-SNAPSHOT-2026-09; SILENTPUSH-BPH-WP-2025; SHINJIRU-SELF</t>
+          <t>SPAMHAUS-BPH; OSINT-FORUMS; REGISTRY-SNAPSHOT-2026-09; SILENTPUSH-BPH-WP-2025; SHINJIRU-SELF; REGISTRY-SNAPSHOT-2026-10</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Veteran Malaysian offshore host (APNIC holder Shinjiru Technology Sdn Bhd; AS45839 announces 16 IPv4 prefixes, 5 overlapping Spamhaus DROP). Markets DMCA-ignored hosting across several jurisdictions; Silent Push reports a 12-day abuse response and a 10-day grace period. Spamhaus flagged an unnamed Malaysia-based ISP matching Shinjiru's profile. Founded 2000 (Shinjiru; Silent Push; shinjiru.com registered 2000-01-21) and markets eight offshore locations (MY, BG, NL, HK, LT, LU, RU, SG). Silent Push's Dec 2025 whitepaper names Shinjiru (AS45839) as a BPH and is the source of the 12-day abuse-response and 10-day grace-period figures.</t>
+          <t>Veteran Malaysian offshore host (APNIC holder Shinjiru Technology Sdn Bhd; AS45839 announced 16 IPv4 prefixes, 5 overlapping Spamhaus DROP, at the 2026-09 audit; on 2026-10-30 it announced 37, with 20 Spamhaus DROP entries inside them - most added since September). Markets DMCA-ignored hosting across several jurisdictions; Silent Push reports a 12-day abuse response and a 10-day grace period. Spamhaus flagged an unnamed Malaysia-based ISP matching Shinjiru's profile. Founded 2000 (Shinjiru; Silent Push; shinjiru.com registered 2000-01-21) and markets eight offshore locations (MY, BG, NL, HK, LT, LU, RU, SG). Silent Push's Dec 2025 whitepaper names Shinjiru (AS45839) as a BPH and is the source of the 12-day abuse-response and 10-day grace-period figures.</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -3807,6 +3817,11 @@
           <t>AS206932 (MIRHOSTING-NL; no routes since 2026-09-29)</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Former AS52000 prefixes originated by AS48729 (ServerKing B.V., NL) since September-October 2026: 194.147.115.0/24; 194.147.148.0/24; 194.147.149.0/24; 194.242.127.0/24; 31.15.19.0/24; 31.184.242.0/24; 45.135.181.0/24; 45.157.141.0/24; 2a0f:4240::/29</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>Netherlands</t>
@@ -3859,7 +3874,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Founded in 2004 by Andrey Nesterenko, who was arrested in the FIOD raid of 2026-05-18 (name press-reported). Krebs: WorkTitans reached the internet solely through MIRhosting, and AS52000 is the first peer in AS209847's aut-num. The 2008 StopGeorgia.ru hosting is attributed (Jeffrey Carr) to the related Innovation IT Solutions Corp; Nesterenko said he could not verify it. De Volkskrant data showed WorkTitans and MIRhosting as the most-used networks in pro-Russian attacks on Danish bodies (Nov 2025). AS52000 had shrunk to two IPv4 /24s (185.15.209.0/24, 185.15.210.0/24) by Sept 2026 and has announced nothing since 2026-10-19 (AS206932 since 2026-09-29) - both ASNs remain registered to MIRhosting. Tier raised T2 -&gt; T1 on 2026-09-25 (taxonomy T1: subject of a law-enforcement action targeting hosting infrastructure - its founder was arrested in the FIOD action against the WorkTitans network, which reached the internet solely through MIRhosting; reported by Krebs and DatacenterDynamics). The FIOD release names no companies, so whether MIRhosting-owned equipment was among the 800+ servers seized is unconfirmed (only a grade-D blog says so). MIRhosting's own statement of 2026-05-22 says it 'temporarily suspended' services to Work Titans, to which it supplied colocation only, and that service to other customers continued (Krebs paraphrased this as 'paused'). On 2026-06-02 the nLighten data centre cut power to MIRhosting equipment without notice, taking its colocation customers offline; nLighten says it co-operated with the Dutch investigations and terminated the relationship (DCD; Kommersant). Only a Russian-language blog (grade D) also mentions German sites.</t>
+          <t>Founded in 2004 by Andrey Nesterenko, who was arrested in the FIOD raid of 2026-05-18 (name press-reported). Krebs: WorkTitans reached the internet solely through MIRhosting, and AS52000 is the first peer in AS209847's aut-num. The 2008 StopGeorgia.ru hosting is attributed (Jeffrey Carr) to the related Innovation IT Solutions Corp; Nesterenko said he could not verify it. De Volkskrant data showed WorkTitans and MIRhosting as the most-used networks in pro-Russian attacks on Danish bodies (Nov 2025). AS52000 had shrunk to two IPv4 /24s (185.15.209.0/24, 185.15.210.0/24) by Sept 2026 and has announced nothing since 2026-10-19 (AS206932 since 2026-09-29) - both ASNs remain registered to MIRhosting. Tier raised T2 -&gt; T1 on 2026-09-25 (taxonomy T1: subject of a law-enforcement action targeting hosting infrastructure - its founder was arrested in the FIOD action against the WorkTitans network, which reached the internet solely through MIRhosting; reported by Krebs and DatacenterDynamics). The FIOD release names no companies, so whether MIRhosting-owned equipment was among the 800+ servers seized is unconfirmed (only a grade-D blog says so). MIRhosting's own statement of 2026-05-22 says it 'temporarily suspended' services to Work Titans, to which it supplied colocation only, and that service to other customers continued (Krebs paraphrased this as 'paused'). On 2026-06-02 the nLighten data centre cut power to MIRhosting equipment without notice, taking its colocation customers offline; nLighten says it co-operated with the Dutch investigations and terminated the relationship (DCD; Kommersant). Only a Russian-language blog (grade D) also mentions German sites. Nine former AS52000 prefixes, including its IPv6 /29, have been originated by ServerKing B.V. (AS48729) since September-October 2026, while AS52000 and AS206932 went dark (REGISTRY-SNAPSHOT-2026-10).</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -4018,7 +4033,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AS34665 (PINDC-AS; Petersburg Internet Network Ltd)</t>
+          <t>AS34665 (PINDC-AS; Petersburg Internet Network Ltd); AS45054 (Metrobit-AS; Petersburg Internet Network ltd.; registered, no routes)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Former AS34665 prefixes originated by AS209641 (IHOR HOSTING LTD) since July 2026: 194.242.124.0/23; 194.242.126.0/24; 91.231.8.0/24; 91.241.46.0/24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4063,12 +4083,12 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>TRENDMICRO-INTERPOL; UNIT42-CL0P-TORRENTS; SECURONIX-TACTICALOCTOPUS; REGISTRY-SNAPSHOT-2026-09</t>
+          <t>TRENDMICRO-INTERPOL; UNIT42-CL0P-TORRENTS; SECURONIX-TACTICALOCTOPUS; REGISTRY-SNAPSHOT-2026-09; REGISTRY-SNAPSHOT-2026-10</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Long-running St. Petersburg hoster (AS44050 announces 13 IPv4 prefixes; sister AS34665 PINDC-AS announces 69). Unit 42 (Sept 2023): a Cl0p torrent-seeding server, 95.215.0.76, was hosted by PIN DC on AS34665 (that block is now originated by AS44050). Securonix: TACTICALOCTOPUS C2 addresses 5.8.8.100 and 109.206.240.67 were registered to Petersburg Internet Network Ltd. Its T2 tier rests heavily on the Trend Micro/Interpol 2023 figure (Trend Micro, Aug 2023: 'Petersburg Internet Network Ltd (19%)' among 'prolific offshore bulletproof hosters', behind 1337team Limited 48% and ahead of Flokinet Ltd 13% - the base of the percentages is not stated); without it the vendor evidence supports T3. Not on Spamhaus ASN-DROP.</t>
+          <t>Long-running St. Petersburg hoster (AS44050 announces 13 IPv4 prefixes; sister AS34665 PINDC-AS announces 69). Unit 42 (Sept 2023): a Cl0p torrent-seeding server, 95.215.0.76, was hosted by PIN DC on AS34665 (that block is now originated by AS44050). Securonix: TACTICALOCTOPUS C2 addresses 5.8.8.100 and 109.206.240.67 were registered to Petersburg Internet Network Ltd. Its T2 tier rests heavily on the Trend Micro/Interpol 2023 figure (Trend Micro, Aug 2023: 'Petersburg Internet Network Ltd (19%)' among 'prolific offshore bulletproof hosters', behind 1337team Limited 48% and ahead of Flokinet Ltd 13% - the base of the percentages is not stated); without it the vendor evidence supports T3. Not on Spamhaus ASN-DROP. RIPE DB (2026-10-30): the PINSPB organisation also holds AS45054 'Metrobit-AS', which announces nothing; four AS34665 prefixes have been originated by IHOR HOSTING LTD (AS209641) since July 2026.</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
@@ -4334,7 +4354,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AS50113; AS205090; AS200740; AS204339; AS204154; AS35196; AS214602 (no routes, Oct 2026)</t>
+          <t>AS50113; AS205090; AS200740; AS204339; AS204154; AS35196; AS214602 (no routes, Oct 2026); AS197703 (FIRST-SERVER-AE; IP MARKET - FZCO [AE]; route objects maintained by FIRST-SERVER-MNT since 2026-09)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>157.228.156.0/23; 157.228.176.0/23 (route objects for AS197703 created by FIRST-SERVER-MNT, 2026-09-01 and 2026-09-18). Former AS50113 space originated by IHOR HOSTING LTD since mid-October 2026: 194.63.140.0/24; 194.63.142.0/24 (AS207569); 2a04:5203::/32; 2a04:5204::/32; 2a04:5205::/32; 2a04:5206::/32 (AS209641)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4384,7 +4409,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>UK-registered network with at least eight ASNs registered to FIRST SERVER LIMITED (AS204997, AS50113, AS205090, AS200740, AS204339, AS204154, AS35196, AS214602; plus a Spanish affiliate on AS199685). Linked to the Sophos (Feb 2026) research on ISPsystem VMmanager default Windows templates, whose reused hostnames appear across LockBit, Qilin, Conti, BlackCat, Ursnif, NetSupport, PureRAT, Lampion, Lumma and RedLine infrastructure - associations of the template ecosystem, not specifically of First Server; Sophos names First Server Limited among the top hosts of the reused hostnames (592 hosts with WIN-J9D866ESIJ2), calls Stark and First Server the two providers with additional links to cybercriminal and Russian state operations, and cites research tying First Server to Doppelganger. Former Hypercore prefixes now originate from AS205090 and AS200740 (lead only). Do not confuse AS204997's handle FIRSTBYTE-AS with the unrelated Iranian AS210703 'FIRSTBYTE-AS' on ASN-DROP. TrickBot was removed (not in the Sophos summary). Qurium (Oct 2026): more than half of 15 Network Management/IP4MARKET prefixes later assigned to Aeza had first been used by NTX Technologies and First Server Limited, and a Spanish 'First Server, SL' (Alicante) appeared in March 2026. Companies House: FIRST SERVER LIMITED (14459750) received a first Gazette notice for compulsory strike-off on 2026-10-13 (name match to the RIPE org).</t>
+          <t>UK-registered network with at least eight ASNs registered to FIRST SERVER LIMITED (AS204997, AS50113, AS205090, AS200740, AS204339, AS204154, AS35196, AS214602; plus a Spanish affiliate on AS199685). Linked to the Sophos (Feb 2026) research on ISPsystem VMmanager default Windows templates, whose reused hostnames appear across LockBit, Qilin, Conti, BlackCat, Ursnif, NetSupport, PureRAT, Lampion, Lumma and RedLine infrastructure - associations of the template ecosystem, not specifically of First Server; Sophos names First Server Limited among the top hosts of the reused hostnames (592 hosts with WIN-J9D866ESIJ2), calls Stark and First Server the two providers with additional links to cybercriminal and Russian state operations, and cites research tying First Server to Doppelganger. Former Hypercore prefixes now originate from AS205090 and AS200740 (lead only). Do not confuse AS204997's handle FIRSTBYTE-AS with the unrelated Iranian AS210703 'FIRSTBYTE-AS' on ASN-DROP. TrickBot was removed (not in the Sophos summary). Qurium (Oct 2026): more than half of 15 Network Management/IP4MARKET prefixes later assigned to Aeza had first been used by NTX Technologies and First Server Limited, and a Spanish 'First Server, SL' (Alicante) appeared in March 2026. Companies House: FIRST SERVER LIMITED (14459750) received a first Gazette notice for compulsory strike-off on 2026-10-13 (name match to the RIPE org). RIPE DB (2026-10-30): FIRST-SERVER-MNT, which maintains AS204339, created route objects in September 2026 for AS197703 'FIRST-SERVER-AE', registered to IP MARKET - FZCO (UAE), which announces 7 IPv4 prefixes. AS50113 prefixes moved to IHOR HOSTING LTD ASNs in October 2026, as PINSPB prefixes did in July. Companies House: a confirmation statement was filed on 2026-10-14, the day after the Gazette notice, which can lead Companies House to discontinue the strike-off.</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -4824,12 +4849,12 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09; UK-COMPANIES-HOUSE</t>
+          <t>SPAMHAUS-ASNDROP-2026; REGISTRY-SNAPSHOT-2026-09; UK-COMPANIES-HOUSE; REGISTRY-SNAPSHOT-2026-10</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Renamed from 'Tiger Net (SOW-A)' on 2026-09-25. Tiger Network Limited (GB) holds AS48589 (5 prefixes, 14,848 addresses of Asian space) and AS211121 (4 prefixes); both are on Spamhaus ASN-DROP (imtigernet) and their prefixes overlap Spamhaus DROP. A relayed Silent Push 2025 table lists 'AS48589 SOW-A-AS (Tiger Net) - Ukraine, Gmail, DGA'. No current 'SOW-A' handle exists; the only registry match, AS43613 'SOWA' (LLC BIGNET UKRAINE), is a separate ASN-DROP entry, so the relay may have merged two records. Raised T5 -&gt; T3 (status flagged); T2 pending a second independent B/C source. Companies House: TIGER NETWORK LIMITED (11161830, incorporated 2018-01-22) files dormant accounts and received a first Gazette notice for compulsory strike-off on 2026-10-13 (name match to the RIPE org).</t>
+          <t>Renamed from 'Tiger Net (SOW-A)' on 2026-09-25. Tiger Network Limited (GB) holds AS48589 (5 prefixes, 14,848 addresses of Asian space) and AS211121 (4 prefixes); both are on Spamhaus ASN-DROP (imtigernet) and their prefixes overlap Spamhaus DROP. A relayed Silent Push 2025 table lists 'AS48589 SOW-A-AS (Tiger Net) - Ukraine, Gmail, DGA'. No current 'SOW-A' handle exists; the only registry match, AS43613 'SOWA' (LLC BIGNET UKRAINE), is a separate ASN-DROP entry, so the relay may have merged two records. Raised T5 -&gt; T3 (status flagged); T2 pending a second independent B/C source. Companies House: TIGER NETWORK LIMITED (11161830, incorporated 2018-01-22) files dormant accounts and received a first Gazette notice for compulsory strike-off on 2026-10-13 (name match to the RIPE org). RIPE DB (2026-10-30): TOKOWA-MNT, the maintainer of AS211121, created route objects in August-September 2026 for AS213220 (DATA-DELTA-AS, Delta Ltd; 103.24.207.0/24, 116.206.95.0/24, 144.48.11.0/24, 195.78.48.0/24) and AS197860 (Haruka Network Limited; 103.76.86.0/24).</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
@@ -5354,6 +5379,11 @@
           <t>AS58854 (Kaopu Cloud [CN]); AS154177 (LIGHT NODE LIMITED [HK]; Spamhaus-attributed via kaopuyun.com)</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Former AS138915 prefixes originated by AS63139 (BEDGE CO LIMITED) since late August-early September 2026: 149.104.108.0/24; 156.225.117.0/24; 156.229.51.0/24; 38.60.172.0/24; 45.197.74.0/24; 45.197.75.0/24</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>Hong Kong</t>
@@ -5416,12 +5446,12 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>RF-TAE-2026; SPAMHAUS-ASNDROP-2026; RF-REDHOTEL-2023; ESET-TOOLSHELL-2025; SEKOIA-BULBATURE; GREYNOISE-REACT2SHELL-2026; REGISTRY-SNAPSHOT-2026-09; PROOFPOINT-TA416-2026</t>
+          <t>RF-TAE-2026; SPAMHAUS-ASNDROP-2026; RF-REDHOTEL-2023; ESET-TOOLSHELL-2025; SEKOIA-BULBATURE; GREYNOISE-REACT2SHELL-2026; REGISTRY-SNAPSHOT-2026-09; PROOFPOINT-TA416-2026; REGISTRY-SNAPSHOT-2026-10</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Hong Kong ISP (APNIC-registered 2019) announcing 113,664 IPv4 addresses in 168 prefixes on AS138915 (Sept 2026; the earlier '182,272 / 50+ netblocks' is outdated). RF ranks Kaopu #4 in its 2025 Threat Density top 10. Spamhaus ASN-DROP lists three kaopuyun.com ASNs: AS138915, AS58854 and AS154177 (LIGHT NODE LIMITED, 129 IPv4 prefixes); a fourth (AS140666, ANY DIGITAL PTE. LTD.) was listed earlier and removed. Independent vendor evidence: RF Insikt (RedHotel heavily favouring Kaopu for C2, 2022-23); ESET (ToolShell SharePoint exploitation from Kaopu IPs, July 2025); Arctic Wolf (malicious FortiGate SSO logins, Dec 2025); Sekoia (Bulbature/GobRAT staging servers all on AS138915); GreyNoise React2Shell sources. Tier raised T3 -&gt; T1 (status flagged) on 2026-09-25 (taxonomy T1: RF top-decile Threat Density - #4 in RF's 2025 top 10, the basis also used for Femo IT/Defhost at #8; minimum evidence met by RF, Spamhaus, ESET, Sekoia and GreyNoise). Proofpoint (2026): TA416 has heavily favoured Evoxt Enterprise (AS149440), XNNET LLC (AS6134) and Kaopu Cloud HK (AS138915) for C2 throughout 2025 and 2026.</t>
+          <t>Hong Kong ISP (APNIC-registered 2019) announcing 113,664 IPv4 addresses in 168 prefixes on AS138915 (Sept 2026; the earlier '182,272 / 50+ netblocks' is outdated). RF ranks Kaopu #4 in its 2025 Threat Density top 10. Spamhaus ASN-DROP lists three kaopuyun.com ASNs: AS138915, AS58854 and AS154177 (LIGHT NODE LIMITED, 129 IPv4 prefixes); a fourth (AS140666, ANY DIGITAL PTE. LTD.) was listed earlier and removed. Independent vendor evidence: RF Insikt (RedHotel heavily favouring Kaopu for C2, 2022-23); ESET (ToolShell SharePoint exploitation from Kaopu IPs, July 2025); Arctic Wolf (malicious FortiGate SSO logins, Dec 2025); Sekoia (Bulbature/GobRAT staging servers all on AS138915); GreyNoise React2Shell sources. Tier raised T3 -&gt; T1 (status flagged) on 2026-09-25 (taxonomy T1: RF top-decile Threat Density - #4 in RF's 2025 top 10, the basis also used for Femo IT/Defhost at #8; minimum evidence met by RF, Spamhaus, ESET, Sekoia and GreyNoise). Proofpoint (2026): TA416 has heavily favoured Evoxt Enterprise (AS149440), XNNET LLC (AS6134) and Kaopu Cloud HK (AS138915) for C2 throughout 2025 and 2026. Six former AS138915 prefixes have been originated by BEDGE CO LIMITED (AS63139) since late August-early September 2026 (REGISTRY-SNAPSHOT-2026-10).</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
@@ -7282,7 +7312,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Hong Kong provider that Intrinsec (Nov 2024) calls a 'likely related' network of PROSPERO/Proton66; Trustwave SpiderLabs observed IP shifts from Proton66 to Chang Way ASNs and the my.31337.hk panel re-themed 'CHANGWAY/HOSTWAY'. Split out of the PROSPERO row (where it was listed as an alias) on 2026-09-25. Spamhaus ASN-DROP lists five ASNs under changway.hk: Chang Way's own AS57523, AS59425 and AS207566 (none announcing) plus the newly added AS201738 (UFO TECHNOLOGIES LIMITED, GB; 7 /24s, all on Spamhaus DROP) and AS211663 (GALEON LLC, RU; 1 /24). Four other changway.hk ASNs listed in Dec 2025 (AS57678, AS208312, AS209309, AS213355) have since been delisted - a rotating-shell pattern. The name similarity between 'UFO Technologies Limited' and Stark's UFO Hosting is not an established link. T2 on ASN-DROP inclusion plus Intrinsec and SpiderLabs reporting. By 2026-10-29 Spamhaus had added a sixth ASN under changway.hk: AS218974 (also named UFO TECHNOLOGIES LIMITED, registered 2026-08-12, one /24 announced via OVH since 2026-09-11).</t>
+          <t>Hong Kong provider that Intrinsec (Nov 2024) calls a 'likely related' network of PROSPERO/Proton66; Trustwave SpiderLabs observed IP shifts from Proton66 to Chang Way ASNs and the my.31337.hk panel re-themed 'CHANGWAY/HOSTWAY'. Split out of the PROSPERO row (where it was listed as an alias) on 2026-09-25. Spamhaus ASN-DROP lists five ASNs under changway.hk: Chang Way's own AS57523, AS59425 and AS207566 (none announcing) plus the newly added AS201738 (UFO TECHNOLOGIES LIMITED, GB; 7 /24s, all on Spamhaus DROP) and AS211663 (GALEON LLC, RU; 1 /24). Four other changway.hk ASNs listed in Dec 2025 (AS57678, AS208312, AS209309, AS213355) have since been delisted - a rotating-shell pattern. The name similarity between 'UFO Technologies Limited' and Stark's UFO Hosting is not an established link. T2 on ASN-DROP inclusion plus Intrinsec and SpiderLabs reporting. By 2026-10-29 Spamhaus had added a sixth ASN under changway.hk: AS218974 (also named UFO TECHNOLOGIES LIMITED, registered 2026-08-12, one /24 announced via OVH since 2026-09-11). RIPE DB (2026-10-30): UFOCORP-MNT and lir-hk-changway-1-MNT created route objects between 2026-09-30 and 2026-10-24 authorising AS55286 (B2 Net Solutions / ServerMania, ARIN) to originate 185.7.214.0/24, 85.193.68.0/24, 85.193.69.0/24 and 92.255.57.0/24.</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
@@ -7451,7 +7481,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United Kingdom (Scotland; Companies House SC832751, name match)</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7496,12 +7526,12 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>SPAMHAUS-ASNDROP-2026; GREYNOISE-WEEKLY-2026-08; REGISTRY-SNAPSHOT-2026-09; REGISTRY-SNAPSHOT-2026-10</t>
+          <t>SPAMHAUS-ASNDROP-2026; GREYNOISE-WEEKLY-2026-08; REGISTRY-SNAPSHOT-2026-09; REGISTRY-SNAPSHOT-2026-10; UK-COMPANIES-HOUSE</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>UK-registered VPS provider whose AS215925 has been on Spamhaus ASN-DROP since at least Dec 2025. GreyNoise has carried it in its weekly brief since 2025-12-15; in the period to 2026-08-30 it produced 10,135,029 connection attempts in a 96-host proxy-scanning sweep. GreyNoise advises against an ASN-level block (shared tenancy). Announces 45.194.92.0/24 (on Spamhaus DROP) and 45.198.224.0/24; 45.205.1.0/24 left AS215925 on 2026-10-21 and has been originated by LARUS Limited (AS17561) since 2026-10-29. Added 2026-09-25 at T2 under the taxonomy's ASN-DROP escalation rule (Spamhaus plus GreyNoise meet the two-source T2 evidence floor); no malware/C2 attribution yet.</t>
+          <t>UK-registered VPS provider whose AS215925 has been on Spamhaus ASN-DROP since at least Dec 2025. GreyNoise has carried it in its weekly brief since 2025-12-15; in the period to 2026-08-30 it produced 10,135,029 connection attempts in a 96-host proxy-scanning sweep. GreyNoise advises against an ASN-level block (shared tenancy). Announces 45.194.92.0/24 (on Spamhaus DROP) and 45.198.224.0/24; 45.205.1.0/24 left AS215925 on 2026-10-21 and has been originated by LARUS Limited (AS17561) since 2026-10-29. Added 2026-09-25 at T2 under the taxonomy's ASN-DROP escalation rule (Spamhaus plus GreyNoise meet the two-source T2 evidence floor); no malware/C2 attribution yet. Companies House: VPSVAULT.HOST LTD (SC832751, incorporated 2024-12-30; exact name match) received a first Gazette notice for compulsory strike-off on 2025-12-23 (discontinued 2026-05-02) and another on 2026-08-25; its registered office moved to the Companies House default address on 2026-10-15.</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
@@ -7939,7 +7969,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Self-styled 'bulletproof anonymous hosting' provider selling crypto-paid VPS/RDP, dedicated and web hosting, 'scanning' servers and a FastFlux CDN advertised as 'Spamhaus Ignored' (anonrdp.com registered 2023-10-04). Network lineage: Intrinsec (May 2026) found March 2026 malspam - a JavaScript backdoor aimed at CIS energy and finance ministries - sent from and controlled via the bulletproof US network GHOSTYNETWORKS (AS205759, Kentucky, registered Jan 2026), which it linked to the OPTIBOUNCE network previously tied to AnonRDP; Silent Push (Oct 2026) calls GHOSTYNETWORKS a shell company of AnonRDP and found the same four SPF addresses on anonrdp.com (Feb-Apr 2026) and ghostynetworks.com. AS205759 has since been deregistered. Current network: CrimsonVector DNS checks (2026-10-29) show solusvm.anonrdp.st and xmpp.anonrdp.st resolving into AS403005 (Blatant Technologies, LLC; ARIN-registered 2026-09-25, Seychelles registrant, Louisville KY contacts), and smtp/smtp01.anonrdp.st resolving to two of the ghostynetworks.com SPF addresses. AS403005 announces nine /24s, all on Spamhaus DROP, through a single upstream, SMARTNET Germany (AS203446); Spamhaus lists the ASN under blatant.host. The RIPE record for one of AS403005's /24s, 46.151.182.0/24 (netname Ghosty-24, created 2026-09-13), is maintained by GHOSTYNETWORKS-MNT for Ghosty Networks LLC (Scottsville, Kentucky) - a direct registry link between Blatant's network and GHOSTYNETWORKS; 31.56.19.0/24 is registered as BLATANT-NET to a Seychelles org. A community post says the Lithuanian servers sit with UAB Host Baltic (AS209605, tracked here); none of AS403005's prefixes geolocate to Lithuania, so this stays unconfirmed. Enforcement: on 2026-10-27, the day of the Virtualine seizure, the registry record for anonrdp.com was pointed at FBI seizure nameservers (13:13 UTC); no seizure page or DOJ statement had appeared by 2026-10-29. That day AnonRDP offered Virtualine customers a 'refugee offer' (it had also run a 'crazyrdp' promo code on 2025-11-15, days after the CrazyRDP seizure); on 2026-10-28 it moved to anonrdp.st, said a 'trusted source' warned it could be next, and said it had triggered an 'emergency kill switch' and was moving datacentres. Backup domains: anonrdp.net and an .onion address. Tier T1 (added 2026-10-29): LE domain seizure plus self-advertised bulletproof hosting with corroborating infrastructure, on Silent Push and Intrinsec (B) and registry/Spamhaus data (C). Status 'seized' covers the domain only - the operation is still running from anonrdp.st, so expect further ASN and prefix moves.</t>
+          <t>Self-styled 'bulletproof anonymous hosting' provider selling crypto-paid VPS/RDP, dedicated and web hosting, 'scanning' servers and a FastFlux CDN advertised as 'Spamhaus Ignored' (anonrdp.com registered 2023-10-04). Network lineage: Intrinsec (May 2026) found March 2026 malspam - a JavaScript backdoor aimed at CIS energy and finance ministries - sent from and controlled via the bulletproof US network GHOSTYNETWORKS (AS205759, Kentucky, registered Jan 2026), which it linked to the OPTIBOUNCE network previously tied to AnonRDP; Silent Push (Oct 2026) calls GHOSTYNETWORKS a shell company of AnonRDP and found the same four SPF addresses on anonrdp.com (Feb-Apr 2026) and ghostynetworks.com. AS205759 has since been deregistered. Current network: CrimsonVector DNS checks (2026-10-29) show solusvm.anonrdp.st and xmpp.anonrdp.st resolving into AS403005 (Blatant Technologies, LLC; ARIN-registered 2026-09-25, Seychelles registrant, Louisville KY contacts), and smtp/smtp01.anonrdp.st resolving to two of the ghostynetworks.com SPF addresses. AS403005 announces nine /24s, all on Spamhaus DROP, through a single upstream, SMARTNET Germany (AS203446); Spamhaus lists the ASN under blatant.host. The RIPE record for one of AS403005's /24s, 46.151.182.0/24 (netname Ghosty-24, created 2026-09-13), is maintained by GHOSTYNETWORKS-MNT for Ghosty Networks LLC (Scottsville, Kentucky); its route object names AS36680 (Netiface LLC, ARIN; announces nothing) as origin, although AS403005 announces the prefix - a direct registry link between Blatant's network and GHOSTYNETWORKS; 31.56.19.0/24 is registered as BLATANT-NET to a Seychelles org. A community post says the Lithuanian servers sit with UAB Host Baltic (AS209605, tracked here); none of AS403005's prefixes geolocate to Lithuania, so this stays unconfirmed. Enforcement: on 2026-10-27, the day of the Virtualine seizure, the registry record for anonrdp.com was pointed at FBI seizure nameservers (13:13 UTC); no seizure page or DOJ statement had appeared by 2026-10-29. That day AnonRDP offered Virtualine customers a 'refugee offer' (it had also run a 'crazyrdp' promo code on 2025-11-15, days after the CrazyRDP seizure); on 2026-10-28 it moved to anonrdp.st, said a 'trusted source' warned it could be next, and said it had triggered an 'emergency kill switch' and was moving datacentres. Backup domains: anonrdp.net and an .onion address. Tier T1 (added 2026-10-29): LE domain seizure plus self-advertised bulletproof hosting with corroborating infrastructure, on Silent Push and Intrinsec (B) and registry/Spamhaus data (C). Status 'seized' covers the domain only - the operation is still running from anonrdp.st, so expect further ASN and prefix moves.</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
@@ -8188,6 +8218,11 @@
           <t>AS207713 (GIR-AS; Spamhaus ASN-DROP under gir.network)</t>
         </is>
       </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AS203319 (GIR-AS-1; registered to Global Internet Solutions LLC; Spamhaus ASN-DROP under gir.network; no routes)</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
           <t>Russia (Sevastopol, occupied Crimea)</t>
@@ -8250,7 +8285,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Russian LLC in Sevastopol (occupied Crimea) that, with its UK sister GCSAS (AS215540), fronts the 4VPS.SU VPS brand - Intrinsec calls both 'legal fronts for the bulletproof hosting provider 4vps.su'; the 4vps.su site footer names the Sevastopol company. RIPE org created 2022-05-12, AS207713 on 2022-05-24. Ukraine's NCCC (Aug 2023) said Gamaredon 'overwhelmingly prefers' GIR-AS and that its Sevastopol location may point to links with the FSB in Crimea; Sekoia saw DDoSia C2s on GIR-AS in Feb 2024; Qurium tied Doppelganger domains to it in 2024. Recorded Future ranks 4VPS (GIR plus GCS) #7 in its 2025 Threat Density top 10, active throughout 2025. Intrinsec and eSentire say the two networks share a Russian beneficial owner (Companies House confirms the Russian owner on the GCS side); prefixes have moved from AS207713 to AS215540. On Spamhaus ASN-DROP (gir.network); AS207713 announces 37 IPv4 prefixes, none on Spamhaus DROP (2026-10-30). T1 on RF top-decile density plus three independent B-grade vendors (Intrinsec, eSentire, RF) and a Grade A government report (NCCC).</t>
+          <t>Russian LLC in Sevastopol (occupied Crimea) that, with its UK sister GCSAS (AS215540), fronts the 4VPS.SU VPS brand - Intrinsec calls both 'legal fronts for the bulletproof hosting provider 4vps.su'; the 4vps.su site footer names the Sevastopol company. RIPE org created 2022-05-12, AS207713 on 2022-05-24. Ukraine's NCCC (Aug 2023) said Gamaredon 'overwhelmingly prefers' GIR-AS and that its Sevastopol location may point to links with the FSB in Crimea; Sekoia saw DDoSia C2s on GIR-AS in Feb 2024; Qurium tied Doppelganger domains to it in 2024. Recorded Future ranks 4VPS (GIR plus GCS) #7 in its 2025 Threat Density top 10, active throughout 2025. Intrinsec and eSentire say the two networks share a Russian beneficial owner (Companies House confirms the Russian owner on the GCS side); prefixes have moved from AS207713 to AS215540. On Spamhaus ASN-DROP (gir.network); AS207713 announces 37 IPv4 prefixes, none on Spamhaus DROP (2026-10-30). T1 on RF top-decile density plus three independent B-grade vendors (Intrinsec, eSentire, RF) and a Grade A government report (NCCC). A second ASN, AS203319 (GIR-AS-1, registered to Global Internet Solutions LLC), is also on Spamhaus ASN-DROP under gir.network; it announces nothing (found by the Phase 2 monitor, 2026-10-30).</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">

--- a/BPH_Master.xlsx
+++ b/BPH_Master.xlsx
@@ -2486,7 +2486,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>AS209800 was created 2025-04-25 and announced solely via aurologic; RF Insikt says it was controlled by Virtualine-affiliated actors who impersonated the long-standing legitimate Hamburg company metaspinner net GmbH (RENAMED 2026-09-25 so the row no longer names that company as the operator). Its prefixes (91.92.240.0/22, 158.94.208.0/22, 178.16.52.0/22) received Virtualine traffic from April 2025 and now originate from OMEGATECH AS202412 (see the Railnet/Virtualine row). The ASN has been re-issued to an unrelated German GbR (ZEMA) - do not block AS209800. Status set to 'dissolved' (network defunct). Attribution strengthened 2026-10-29: DOJ lists 'Lanedo' among Virtualine's aliases, matching the LANEDONET re-description, and Spamhaus (Sept 2025) reported Virtualine's expansion onto AS209800. Tier raised T3 -&gt; T2 on 2026-10-30 to match the other Virtualine sub-networks (KPROHOST, Karina Rashkovska): an operator-controlled front with obscured ownership (impersonated identity), no route diversification and all three former /22s on Spamhaus DROP, on RF (B) and Spamhaus (C) evidence plus the DOJ alias. Kept as a historical record - status stays 'dissolved'.</t>
+          <t>AS209800 was created 2025-04-25 and announced solely via aurologic; RF Insikt says it was controlled by Virtualine-affiliated actors who impersonated the long-standing legitimate Hamburg company metaspinner net GmbH (RENAMED 2026-09-25 so the row no longer names that company as the operator). Its prefixes (91.92.240.0/22, 158.94.208.0/22, 178.16.52.0/22) received Virtualine traffic from April 2025 and were originated by OMEGATECH AS202412 until the October 2026 seizure and by AS6461 (Zayo) since 2026-10-27 (see the Railnet/Virtualine row). The ASN has been re-issued to an unrelated German GbR (ZEMA) - do not block AS209800. Status set to 'dissolved' (network defunct). Attribution strengthened 2026-10-29: DOJ lists 'Lanedo' among Virtualine's aliases, matching the LANEDONET re-description, and Spamhaus (Sept 2025) reported Virtualine's expansion onto AS209800. Tier raised T3 -&gt; T2 on 2026-10-30 to match the other Virtualine sub-networks (KPROHOST, Karina Rashkovska): an operator-controlled front with obscured ownership (impersonated identity), no route diversification and all three former /22s on Spamhaus DROP, on RF (B) and Spamhaus (C) evidence plus the DOJ alias. Kept as a historical record - status stays 'dissolved'.</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
